--- a/mitoderm-catalog/site/MITODERM-3D-story.xlsx
+++ b/mitoderm-catalog/site/MITODERM-3D-story.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>готово (критики учтены)</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>готово (критики учтены)</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>готово (критики учтены)</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>готово (критики учтены)</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>готово (критики учтены)</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>готово (критики учтены)</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>готово (критики учтены)</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>готово (критики учтены)</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>черновик, правка критиков идёт</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Окружение линейки BIOSPICULE зелёное. Фон #12382A, дым #1E4634, к краям он уходит в базу бренда #0a0a0b. Свечение за продуктом тоже зелёное и светлеет к центру. Частицы, нити пептидов и волосяные линии — золото бренда #c9a24b / #d8bd7e: оно повторяет золотую монограмму M и золотой текст на тёмно-зелёной полосе коробки. Своей капли у средства нет (по design-rules капля есть только у EXOCELL, CELL RENEW и MITOSCAN), поэтому акцент держит цвет линейки. Зелёный CELL RENEW #4fb285 как свечение не используем. Коробки CELL RENEW 1.5% и DERMA RECOVERY CREAM (шалфей #9AA889, та же линейка) несут свой цвет только печатью, второго цвета линейки на странице нет. Шаг «Защита» — временное потепление света, а не новый цвет. Оттенок серии показан на экране 1: глубокий зелёный, крупная золотая M и бейдж BIOSPICULE. На экране 7 монограмма повторяется. Назначение (домашний уход) обозначено бейджем — золотой контур «טיפוח ביתי», а не цветом фона.</t>
+          <t>Окружение линейки BIOSPICULE зелёное. Фон #12382A, дым #1E4634, к краям он уходит в базу бренда #0a0a0b. Свечение за продуктом тоже зелёное и светлеет к центру. Частицы, нити пептидов и волосяные линии — золото бренда #c9a24b / #d8bd7e: оно повторяет золотую монограмму M и золотой текст на тёмно-зелёной полосе коробки. Своей капли у средства нет (по design-rules капля есть только у EXOCELL, CELL RENEW и MITOSCAN), поэтому акцент держит цвет линейки. Зелёный CELL RENEW #4fb285 как свечение не используем. Коробки CELL RENEW 1.5% (экран 2) и DERMA RECOVERY CREAM (экран 5; шалфейная полоса #9AA889 на её коробке) несут свой цвет только печатью, второго цвета линейки на странице нет. Шаг «Защита» — это временное потепление света, а не новый цвет. Оттенок серии показан на экране 1: глубокий зелёный, золотая монограмма M в дыму (размытая: файл — растр 600 px) и бейдж линейки. На экране 7 монограмма повторяется. Линейка и назначение передаются парой бейджей из cat.eyebrow: «סרום BIOSPICULE™» — бейдж линейки, «טיפוח ביתי» — золотой контур. Назначение цветом фона не передаём.</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Высокая узкая ивори-коробка CELLULAR AGE DEFENSE 2.5%: тёмно-зелёная полоса с золотым текстом, круглый медальон со спикулами, сверху золотая M. Это куб с фасадом из пакшота. Второй герой — белый airless-флакон 30 мл с помпой, он появляется с экрана 4, когда будет фото.</t>
+          <t>Высокая узкая ивори-коробка CELLULAR AGE DEFENSE 2.5%: тёмно-зелёная полоса с золотым текстом, круглый медальон со спикулами, сверху золотая M. Это куб с фасадом из пакшота protocols/print/img/cellular-age-25.webp, поворот не больше ±20°. По умолчанию страница собирается только с коробкой. Белый airless-флакон 30 мл (фото №9 в Figma) раньше экрана 4 не появляется. Он добавляется только после ответа заказчика про печать 'CELL CELLULAR' и только на экранах 4 (крупно одна головка помпы) и 7.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Коробка 2.5% встаёт на ступень выше CELL RENEW 1.5%. Камера проходит сквозь медальон, где напечатанные спикулы оживают вместе с пятью золотыми нитями пептидов. Всё это собирается в одну каплю на помпе airless-флакона: капля покалывает и требует мягких движений. Лестница ухода (2.5% → DERMA RECOVERY → дневная защита) приводит к экрану покупки с одним флаконом 30 мл.</t>
+          <t>Коробка 2.5% встаёт на ступень выше CELL RENEW 1.5%, камера проходит сквозь её медальон, где через поле спикул идут пять золотых нитей пептидов, Bakuchiol и Adenosine (у 1.5% их нет), всё собирается в одну каплю, которая покалывает и требует мягких движений, а лестница ухода (2.5% → DERMA RECOVERY → дневная защита) ведёт к экрану покупки с одной коробкой 30 мл.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>8</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>черновик, правка критиков идёт</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Окружение линейки BIOSPICULE (зелёное, слово заказчика 11/10). База дальнего слоя — тёмный зелёный #12382A, дым — #1E4634, подсветка за объектами — шалфей DERMA #9AA889 (это цвет DERMA в таблице линеек и цвет полосы на коробке). Шалфей — «капля» средства, не больше ~10% площади: свечение за банкой, точки меток, чипы. Искры в дыму кремовые #f6f3ec. Золото бренда #c9a24b — волосяные линии, кикеры, кнопка. В шапке вместо белого логотипа стоит золотая монограмма M (site/img/mitoderm-m-gold.png). На экране 5 дым густеет до насыщенного #1E4634, и за объектами проступает крупная полупрозрачная золотая M — это оттенок серии. Исключений нет: бирюза MASK здесь не используется. Мятный #4fb285 (капля CELL RENEW) тоже не используется. Золотые упаковки V-TECH и EXO-NAD в кадр не выводятся, эти средства упоминаются только текстом в b4.line, чтобы не смешивать два цвета линеек. Назначение (домашний уход) показывает бейдж с золотым контуром (home.sl-3), а не цвет фона.</t>
+          <t>Зелёное окружение линейки BIOSPICULE (слово заказчика 11/10). База дальнего слоя — #12382A, дым — #1E4634. Подсветка за объектами — шалфей DERMA #9AA889: это цвет DERMA в таблице линеек и цвет полосы на коробке. Шалфей — «капля» средства, не больше ~10% площади. Он есть только у крема и барьера: свечение за банкой, лента крема, атласный слой, точки меток. Искры в дыму кремовые #f6f3ec. Иглы-спикулы на экране 2 естественного серо-оливкового цвета, как на site/img/spicules-macro.png. Шалфея в них нет, чтобы иглы не читались как часть крема. Золото бренда #c9a24b — волосяные линии, кикеры, главная кнопка, выноски. В шапке вместо белого логотипа стоит золотая монограмма M (site/img/mitoderm-m-gold.png). Оттенок серии — экран 5: дым густеет до насыщенного #1E4634, за объектами проступает крупная полупрозрачная золотая M. Исключений нет: бирюза MASK не используется. Мятный #4fb285 (капля CELL RENEW) тоже не используется, кроме печати на билборде её коробки. Золотые упаковки V-TECH и EXO-NAD в кадр не выводятся, эти средства есть только в тексте b4.line, чтобы на странице не было двух цветов линеек. Назначение показывает бейдж, а не цвет фона. Бейдж ui.use_home с золотым контуром стоит на экранах 1 и 7. У MICRO BOOST 10% на экране 5 маленький бейдж home.tg с золотой заливкой (по design-rules).</t>
         </is>
       </c>
       <c r="G11" s="2" t="n">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Банка 50 мл из матового белого пластика с прозрачной матовой крышкой над чёрным пояском. Она лежит в коробке цвета слоновой кости с шалфейной полосой и золотой надписью DERMA RECOVERY / CREAM. Экран 1 открывает коробка (её фасад готов). Дальше героями становятся банка и сам белый крем.</t>
+          <t>Матовая белая банка 50 мл. Материал в источниках не указан. Крышка матовая, над чёрным пояском: в packaging-text.json она clear frosted, на фото 1 выглядит белой. Банка лежит в коробке цвета слоновой кости с шалфейной полосой и золотой надписью DERMA RECOVERY / CREAM. Экран 1 открывает коробка, её фасад готов. Дальше герои — банка и сам белый крем. Фасад банки берётся с фото заказчика в Figma: фото 1, узел 93:8080, фасад с этикеткой. Открытая банка — фото 73, узел 113:8211. Поэтому банку показываем фасадом и поворачиваем не больше чем на ±20°. Задняя сторона банки не снята.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>После острых игл обновления (спикулы, процедура) — мягкость: банка поднимается из коробки, открывается без единой иглы, лента крема разглаживает сухие хлопья в ровный слой барьера, а банка встаёт последней точкой в ряду BIOSPICULE после сывороток и MICRO BOOST 10%.</t>
+          <t>После игл обновления приходит мягкость: банка поднимается из коробки и открывается без единой иглы, лента крема ложится на кожу у зеркала, а на зелёном экране серии обе ветки BIOSPICULE — домашние сыворотки и MICRO BOOST 10% в клинике — сходятся к DERMA.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>черновик, правка критиков идёт</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Тёмная база бренда #0a0a0b. Дальний слой — медленный дым цвета шампань-металл #d8c48a и мелкие серебряные частицы #d9d4cc, как металлическая пыль (цвета линейки DEVICES). Слой поворачивается за курсором, по кромке пера идёт холодный серебряный контровой свет. Золото бренда #c9a24b — только волосяные линии и кикеры. Кнопка цены по раскадровке b6: угольная заливка, текст цвета шампань. Своей «капли» у MITOPEN нет (по правилам палитры работает цвет линейки), тёплое пятно на странице одно — розово-золотое кольцо и кнопка самого прибора. V-TECH SYSTEM и EXOSIGNAL HAIR на экране 5 стоят только как предметы, их цвет на фон не переносится: два цвета линеек на одной странице запрещены. MICRO BOOST 10% (зелёная BIOSPICULE) показан только меткой, без упаковки. Оттенок серии: весь фон в цвете DEVICES, а явная метка серии — на экране 7 (как у MASK). Там самый яркий шампань-серебряный свет страницы и бейдж линейки «מכשור» (home.sl-2) рядом с золотым значком «לשימוש מקצועי בלבד».</t>
+          <t>Фон — тёмная база бренда #0a0a0b. Дальний слой поворачивается за курсором: медленный холодный серебряный дым #d9d4cc с тонкими прожилками шампань-металла #d8c48a и мелкая серебряная пыль. Это цвет линейки DEVICES, как на странице MITOSCAN. Серебро ведущее, потому что шампань #d8c48a у DEVICES совпадает с цветом линейки PEELING (EXO-NAD), и различить их можно только по серебру. К тому же перо цвета шампань лучше читается на серебре. По кромке пера идёт холодный серебряный контровой свет. Золото бренда #c9a24b используется только для волосяных линий, кикеров, бейджа назначения «מקצועי» (золотая заливка) и кнопок цены. Главная кнопка и кнопка в липкой панели — с заливкой #c9a24b и текстом #0a0a0b, как .btn.primary в proto/exocell-3d-template.html. Призрачные кнопки на экранах 1 и 5 — с золотым контуром. «Угольную заливку» из примечания к b6.cta не используем: #1a1a1f на #0a0a0b даёт контраст около 1.1:1. Своей капли у MITOPEN нет, поэтому работает цвет линейки. Единственное тёплое пятно на странице — розово-золотое кольцо и кнопка самого прибора. V-TECH SYSTEM и EXOSIGNAL HAIR на экране 5 стоят только как предметы, их цвета на фон не переносим: два цвета линеек на одной странице запрещены. MICRO BOOST 10% (зелёная BIOSPICULE) упоминается только меткой b4.label4. Оттенок серии — на экране 7: там самый яркий серебряный дым и контровой свет страницы, шампань идёт вторым цветом, а рядом с бейджем «מקצועי» стоит бейдж линейки «מכשור» (home.sl-2) с серебряным контуром.</t>
         </is>
       </c>
       <c r="G12" s="2" t="n">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN — беспроводная ручка для микронидлинга. Корпус из металла цвета шампань-золото, розово-золотое кольцо с насечками и такая же кнопка, прозрачный картридж с иглами. На корпусе вертикально белая надпись «MITOPEN», у верхнего конуса маленькая гравированная V (packaging-text.json → mitopen). Коробки в источниках нет — героем идёт сам прибор.</t>
+          <t>MITOPEN — беспроводная ручка для микронидлинга. Корпус из металла цвета шампань-золото. Розово-золотое ребристое кольцо рукоятки (в packaging-text.json это «rose-gold knurled grip ring»; задаёт ли оно глубину, в источниках не сказано — вопрос 2). Такого же цвета кнопка с маленькой точкой над ней, прозрачный картридж с иглами. Надписи берём только с фото: вертикальная белая «MITOPEN» на корпусе и маленькая гравированная V у верхнего конуса. На пакшоте ось пера отклонена от вертикали примерно на 12° (замер по альфа-каналу mitopen.webp): конус вверху справа, картридж внизу слева. Коробки в источниках нет, поэтому героем идёт сам прибор.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Поворот розово-золотого кольца MITOPEN выставляет глубину, иглы прозрачного картриджа открывают ровную сетку временных микроканалов, и по ним уходят V-TECH SYSTEM в кожу лица и EXOSIGNAL HAIR в кожу головы: одна ручка — точная и повторяемая процедура.</t>
+          <t>MITOPEN задаёт глубину 0.25–2.5 мм и одну из пяти скоростей, прозрачный картридж оставляет ровную сетку временных микроканалов, а по ней уходят V-TECH SYSTEM в кожу лица и EXOSIGNAL HAIR в кожу головы: одна ручка — точная и повторяемая процедура.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>черновик, правка критиков идёт</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>База бренда: фон #0a0a0b. Дальний слой, дым и частицы, сделан в цвете линейки DEVICES (правило «цветовое окружение по линейке»): холодный серебряный дым #d9d4cc с тёплыми прожилками шампань-металла #d8c48a и мелкая серебряная пыль. На белых корпусах и хроме базы контровой свет шампань. Капля средства, синий MITOSCAN #5aa9e6, занимает не больше ~10% площади. Это только свечение экрана планшета, активный сегмент ×50 / ×200 и узкий рефлекс на белом щупе. Страницу целиком в синий не красим. Золото бренда #c9a24b идёт на волосяные выноски, кикеры, кнопку цены и бейдж «מקצועי» (home.tg, золотая заливка). MITOSCAN не исключение, в отличие от MASK, поэтому окружение строится по правилу линейки. Бирюзово-фиолетовая мишень на экране — это печать экрана с пакшота: её не перекрашиваем и в фон не выносим. Белая клиническая студия из site/prompts/mitoscan.md написана до правила линеек и сюда не идёт. Белые объекты стоят на тёмном фоне.</t>
+          <t>База бренда: фон #0a0a0b. Дальний слой, дым и частицы, сделан в цвете линейки DEVICES по правилу «цветовое окружение по линейке»: холодный серебряный дым #d9d4cc с тёплыми прожилками шампань-металла #d8c48a и мелкая серебряная пыль. На белых корпусах и хроме лежит контровой свет шампань. MITOSCAN не исключение, в отличие от MASK. Капля средства — синий MITOSCAN #5aa9e6, не больше ~10% площади: свечение экрана, активный сегмент ×50 / ×200 и узкий рефлекс на щупе. Страницу целиком в синий не красим. Золото бренда #c9a24b идёт на волосяные выноски, кикеры, кнопку цены и бейдж «מקצועי» (home.tg, золотая заливка). Кнопка цены золотая по правилу палитры. Синяя заливка из EN-описания b6.cta противоречит правилу «капля ≤10%», её не берём. Бирюзово-фиолетовая мишень на экране — это печать экрана с пакшота: её не перекрашиваем и в фон не выносим. Белая клиническая студия и «blue on dark» из site/prompts/mitoscan.md написаны до правила линеек и сюда не идут. Белые объекты стоят на тёмном фоне.</t>
         </is>
       </c>
       <c r="G13" s="2" t="n">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Щуп-сканер: белый корпус, чёрная овальная панель с надписями 'Mitoscan' / 'By Mitoderm Ltd', спиральный кабель. В иврите сайта он называется «המצלמה», и сюжет ведёт он. Рядом второй герой — планшет на подставке: на его экране появляется результат. Серебряный цилиндр-база держит композицию снизу.</t>
+          <t>Система MITOSCAN целиком, как на пакшоте. Белый планшет на белой подставке с экраном-логотипом (мишень, 'Mitoscan', 'By Mitoderm Ltd'). Справа в держателе щуп-сканер: белый корпус, чёрная овальная панель 'Mitoscan' / 'By Mitoderm Ltd', спиральный кабель. Спереди серебряный цилиндр с хромовым шильдиком 'Mitoscan'. Сюжет ведёт щуп, «המצלמה» из b0.cta, а результат появляется на экране. Пока нет фото частей по отдельности, всё строится одним биллбордом целого пакшота: части не двигаются, работают камера и маски.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Щуп MITOSCAN поднимается из держателя и прорезает дымку «на глаз». На экране планшета открываются ×50 и ×200, экран поворачивается к пациенту и проводит через «сканирование · объяснение · отслеживание», а в конце система разбирается на части и собирается обратно на экране покупки.</t>
+          <t>Камера поднимается к щупу MITOSCAN, сквозь дымку «на глаз» переходит к экрану, где открываются ×50 и ×200, показывает то, что видит пациент, проводит через «сканирование · объяснение · отслеживание» и отъезжает к целой системе на экране покупки.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>6</v>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>черновик, правка критиков идёт</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Экраны 1 и 7 — база бренда: фон #0a0a0b, поверхности #111114 / #1a1a1f, тёплый дым #c9a24b (8–12%), пыль #d8bd7e, текст крем #f6f3ec. Цветов линеек на них нет: на одном экране две линейки не смешиваются, поэтому группы в герое различаются расстановкой и подписями, а не цветом. Экраны 2–6 — каждый в окружении своей линейки, цвет меняется только в зоне перехода: 2 V-TECH FACE — чёрный + золото #c9a24b, блики зеркальной фольги; 3 PEELING — шампань-золото #d8c48a; 4 BIOSPICULE — зелёный #1E4634, тёмный #12382A, шалфей #9AA889 под DERMA, золотая монограмма M; 5 DEVICES — шампань-металл #d8c48a + серебро #d9d4cc; 6 HAIR — чёрный + золото. Капля средства — только узкое свечение под упаковкой, не больше ~10% площади: EXOCELL MASK, бирюза #6fb7ba, на экране 2; CELL RENEW #4fb285 на экране 4; MITOSCAN #5aa9e6 на экране 5. На главной MASK стоит в чёрно-золотом окружении своей серии V-TECH FACE: её бирюзовое окружение — исключение только на её собственной странице. Назначение показывают бейджи, а не фон: «מקצועי» — золотая заливка, домашний уход — золотой контур. Оттенок серии виден на всех экранах 2–6; в поле ниже указан первый из них.</t>
+          <t>Экраны 1 и 7 — нейтральная база бренда (design-rules, слой 1). Фон #0a0a0b, поверхности #111114 / #1a1a1f, графитовый дым, кремовая пыль #f6f3ec не больше 8%, текст крем #f6f3ec. Золото #c9a24b здесь только в волосяных линиях, кикерах и кнопке. Цветов линеек на этих экранах нет: группы в герое и на полке различаются расстановкой и подписями. Экраны 2–6 — каждый в окружении своей линейки, цвет меняется только в зоне перехода. 2 V-TECH FACE — чёрный, тёплый золотой дым #c9a24b, золотая пыль #d8bd7e, блики зеркальной фольги. 3 PEELING — шампань-золото #d8c48a. 4 BIOSPICULE — зелёный #1E4634 и тёмный #12382A, подложка шалфея #9AA889 под DERMA, золотая монограмма M. 5 DEVICES — холодный шампань-металл #d8c48a и серебро #d9d4cc. 6 HAIR — чёрный, золотой дым и пыль. Золотой дым есть только на экранах 2 и 6, поэтому на переходах 1→2 и 6→7 меняется цвет, а не только плотность дыма. V-TECH FACE и HAIR по правилам одного цвета, их различает бейдж линейки. Это подпись группы под волосяной линией: точка и название в цвете линейки, как бейдж серии на экране покупки MASK. Капля средства — только узкое свечение под упаковкой, не больше ~10% площади: EXOCELL MASK бирюза #6fb7ba на экране 2, CELL RENEW #4fb285 на экране 4, MITOSCAN #5aa9e6 на экране 5. На главной MASK стоит в чёрно-золотом окружении своей серии V-TECH FACE: её бирюзовое окружение — исключение только на её собственной странице. Назначение показывают бейджи, а не фон: «מקצועי» — золотая заливка, домашний уход — золотой контур. Оттенок серии виден на всех экранах 2–6; в поле ниже указан первый из них.</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Вся линейка: 12 настоящих упаковок пятью группами на пологой дуге (V-TECH FACE · PEELING · BIOSPICULE · DEVICES · HAIR). Ближе всех и в центре — золотой зеркальный картон V-TECH SYSTEM. MITOTECH CELL BOOSTER до появления фото в 3D не показывается.</t>
+          <t>Вся линейка: 12 настоящих упаковок пятью группами на пологой дуге (V-TECH FACE · PEELING · BIOSPICULE · DEVICES · HAIR). Ближе всех и в центре — золотой зеркальный картон V-TECH SYSTEM. MITOTECH CELL BOOSTER без фото в 3D не показывается. EXOSIGNAL SPRAY до студийного пакшота — только маленький билборд коробки в глубине, без флакона.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Главная — прогулка по полке MITODERM: вся линейка стоит дугой из пяти групп, с каждым экраном вперёд выходит одна серия в своём цветовом окружении (лицо, пилинг, биоспикулы, приборы, волосы) и ведёт на страницы своих средств, а в конце все упаковки возвращаются на общую полку рядом с одной кнопкой «צרו קשר».</t>
+          <t>Главная — прогулка по полке MITODERM: вся линейка стоит дугой из пяти групп, с каждым экраном вперёд выходит одна серия в своём цветовом окружении (лицо, пилинг, биоспикулы, приборы, волосы) и ведёт на страницы своих средств, а в конце все упаковки возвращаются на общую полку с составом каждой линейки и одной кнопкой «לקבלת פרטים על מחירים».</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>8</v>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>черновик, правка критиков идёт</t>
+          <t>готово</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1344,14 +1344,13 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Экраны 1, 2 и 7 стоят на базе бренда: фон #0a0a0b, медленный золотой дым #c9a24b, частицы крем и золото, белый логотип. На каталоге есть все линейки, поэтому правило «не смешивать два цвета линеек» соблюдается поэкранно: на экране всегда только один цвет линейки, а при переходе между экранами дым плавно перетекает за 600 мс.
-Экран 3 (V-TECH FACE + HAIR): чёрный фон и тёплое золото V-TECH FACE. Свечение сильнее, чем у базы, у подзаголовка стоит бейдж линейки. Бирюза EXOCELL #6fb7ba даётся только узким свечением-каплей под её карточкой (≤10%). Бирюзово-синее окружение MASK остаётся на её собственной странице.
+          <t>Экраны 1, 2 и 7 стоят на базе бренда: фон #0a0a0b, медленный золотой дым #c9a24b, частицы цвета крема и золота, белый логотип. На каталоге есть все линейки, поэтому правило «не смешивать два цвета линеек» соблюдается поэкранно: на каждом экране только один цвет линейки, при переходе дым перетекает за 600 мс.
+Экран 3 (V-TECH FACE + HAIR): чёрный и тёплое золото V-TECH FACE, свечение сильнее, чем на базе. Бирюза EXOCELL #6fb7ba даётся только узкой каплей под её карточкой (не больше 10%), а бирюзово-синее окружение MASK остаётся на её странице.
 Экран 4 (PEELING): шампань-золото #d8c48a на чёрном.
-Экран 5 (BIOSPICULE): зелёный #1E4634, глубокий #12382A, золотая монограмма M в дальнем слое. Под CELL RENEW 1.5% капля #4fb285, под DERMA RECOVERY CREAM свечение шалфея #9AA889.
-Экран 6 (DEVICES): шампань-металл #d8c48a и серебро #d9d4cc, под MITOSCAN синяя капля #5aa9e6.
-Фильтр: на экране 2 наведение или выбор чипа перекрашивает дым в цвет линейки этой категории. Exosomes, Masks и Hair — чёрный с золотом, Peels — шампань, Bio-Spicules — зелёный, Devices — шампань с серебром. All и Home care остаются на базе, потому что Home care проходит через три линейки. На экранах 3–6 каждый экран держит свой цвет, а не подходящие под фильтр карточки просто схлопываются.
-Назначение показывается бейджем, а не цветом: מקצועי — золотая заливка, טיפול ביתי — золотой контур.
-Оттенок серии виден на каждом из экранов 3–6. В поле указан экран 3, потому что там он появляется впервые: тёплое золото V-TECH FACE, как на экране покупки MASK.</t>
+Экран 5 (BIOSPICULE): зелёный #1E4634, глубокий #12382A, золотая монограмма M в дальнем слое. Капля #4fb285 под CELL RENEW 1.5%, свечение шалфея #9AA889 под DERMA RECOVERY CREAM.
+Экран 6 (DEVICES): шампань-металл #d8c48a и серебро #d9d4cc, синяя капля #5aa9e6 под MITOSCAN.
+Фильтр: на экране 2 наведение на чип или его выбор перекрашивает дым в цвет линейки категории. Exosomes, Masks и Hair — чёрный с золотом, Peels — шампань, Bio-Spicules — зелёный, Devices — шампань с серебром. All и Home care остаются на базе: домашний уход проходит через три линейки (V-TECH FACE, HAIR, BIOSPICULE). На экранах 3–6 каждый экран держит свой цвет, неподходящие карточки схлопываются.
+Назначение показывается бейджем, а не цветом: home.tg — золотая заливка, catalog.chips[6] — золотой контур. Бейдж и чип домашнего ухода берутся из одного ключа. Оттенок серии виден на каждом из экранов 3–6; в поле стоит экран 3, где он появляется впервые: тёплое золото V-TECH FACE, как на экране покупки MASK.</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
@@ -1359,12 +1358,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Одного героя нет. На экране 1 стоит «витрина линеек» из пяти представителей: коробки V-TECH SYSTEM, EXO-NAD, EXOSIGNAL HAIR и MICRO BOOST 10% (кубоиды) и MITOPEN (билборд). Дальше 3D работает только в карточках: товар поворачивается при наведении.</t>
+          <t>Одного героя нет. На экране 1 стоит «витрина линеек» из пяти представителей: коробки V-TECH SYSTEM, EXO-NAD, EXOSIGNAL HAIR и MICRO BOOST 10% (кубоиды почти фасадом, рыскание не больше 12°, потому что печать их боковин неизвестна) и MITOPEN (строго фронтальный билборд). Дальше 3D работает в карточках: при наведении товар поворачивается к фасаду.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Каталог — спокойная витрина: пять представителей линеек встречают на чёрно-золотом фоне и спускаются на полку категорий, дальше каждая линейка проходит своим экраном в своём цвете, а товар поворачивается к посетителю только тогда, когда к нему тянется курсор.</t>
+          <t>Каталог — спокойная витрина: пять представителей линеек встречают посетителя на чёрно-золотом фоне и спускаются на полку категорий; дальше каждая линейка идёт своим экраном в своём цвете, в каждой карточке видно, что лежит в коробке, а вся страница ведёт к одной кнопке цены.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1378,10 +1377,10 @@
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -6757,12 +6756,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Дальний слой: медленный тёмно-зелёный дым линейки с редкими золотыми искрами, слой поворачивается за указателем. Справа — высокая узкая ивори-коробка (куб, фасад из пакшота) в развороте 3/4 на тёмном постаменте-ступени. За ней в дыму проступает крупная золотая монограмма M — повтор знака с верха коробки. При загрузке коробка один раз «шагает вверх»: поднимается на ступень и замирает, а по золотому тексту тёмно-зелёной полосы проходит блик. Слева копия на иврите (RTL), внизу док из 7 блоков (nav[0]…nav[6]). Бейджи: «BIOSPICULE» и «טיפוח ביתי» (золотой контур).</t>
+          <t>Дальний слой: медленный тёмно-зелёный дым линейки с редкими золотыми искрами, слой поворачивается за указателем. Справа высокая узкая ивори-коробка (куб, фасад из пакшота) стоит почти анфас на тёмном постаменте-ступени. Поворот не больше 20°: фото боковин нет. За ней в дыму размыто проступает крупная золотая монограмма M — повтор знака с верха коробки. При загрузке коробка один раз «шагает вверх»: поднимается на ступень и замирает, по золотому тексту тёмно-зелёной полосы проходит блик. Слева копия на иврите (RTL). Кикер cat.eyebrow набран парой бейджей, отдельной строки кикера нет: «סרום BIOSPICULE™» — бейдж линейки, «טיפוח ביתי» — бейдж назначения с золотым контуром. Внизу док из 7 блоков, nav[0]…nav[6]. Пункт 5 на этой странице подписан cat.s04[0] «נפח», а не nav[5] «ערכה ועובדות»: набора нет, внутри один флакон. Кнопка «איפה לקנות» из b0.cta открывает экран «Ask your clinic» (решение 17 в project-council.md).</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Камера отъезжает и чуть опускается. Слева и ниже из дыма выдвигается вторая, более низкая ступень с коробкой CELL RENEW 1.5%. Монограмма M растворяется.</t>
+          <t>Камера отъезжает и чуть опускается. Монограмма M растворяется. Слева из дыма выдвигается вторая, более низкая ступень с коробкой CELL RENEW 1.5%.</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -6812,7 +6811,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Коробка по центру сверху, около 50% высоты. На указатель сцена не реагирует, дым медленно дрейфует сам. Ниже кикер, заголовок, фраза, метки строкой с горизонтальным скроллом и кнопка «איפה לקנות» во всю ширину. Док — точки с названием текущего блока.</t>
+          <t>Коробка по центру сверху, около 50% высоты. На указатель сцена не реагирует, дым медленно дрейфует сам. Ниже пара бейджей, заголовок, фраза, метки строкой с горизонтальным скроллом и кнопка «איפה לקנות» во всю ширину. Док — точки с названием текущего блока. Липкая панель (cat.name · b0.label4 и иконка WhatsApp) появляется, когда первый экран ушёл. Показывается она только при условии, что у «איפה לקנות» есть адресат.</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -6837,22 +6836,22 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Две ступени: 1.5% → 2.5%</t>
+          <t>Сначала проблема, потом две ступени: 1.5% → 2.5%</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Две коробки на двух ступенях. CELL RENEW 1.5% стоит ниже и левее, приглушённая. CELLULAR AGE DEFENSE 2.5% — выше и правее, в ключевом свете. Ступени — простые тёмные кубы без печати. Четыре метки b1 тянутся тонкими золотыми линиями к верхней ступени, к 2.5%: так видна «программа интенсивнее, чем 1.5%» из фразы блока. Лиц и «морщин» не рисуем.</t>
+          <t>Сначала проблема. По скроллу на дыме по одной загораются четыре метки b1.label1–4. Лиц и «морщин» не рисуем. Затем из дыма в свет выходят две ступени: ниже и левее — CELL RENEW 1.5%, выше и правее — CELLULAR AGE DEFENSE 2.5%. Обе коробки стоят в одинаковом ровном свете, 1.5% не приглушаем: часть этих показаний есть и в её каталоге. О следующем шаге говорят только высота ступени и фраза b1.line. На подступенках крупные золотые цифры «1.5%» (cat[cell-renew-1-5].stats[0][0]) и «2.5%» (cat.stats[0][0]). Без них почти одинаковые коробки не различить. После этого от меток к коробке 2.5% тянутся тонкие золотые линии: это её показания. Обе коробки почти анфас, поворот не больше ±20°.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Коробка 1.5% уходит в дым. Камера наезжает на круглый медальон на фасаде коробки 2.5% и проходит сквозь его кольцо.</t>
+          <t>Метки гаснут, коробка 1.5% со своей ступенью уходит в дым. Камера наезжает на круглый медальон на фасаде коробки 2.5% и проходит сквозь его кольцо.</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>אינדיקציות</t>
+          <t>למי מתאים הסרום?</t>
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr">
@@ -6867,7 +6866,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>קמטים וקמטוטים · אלסטיות · עור עייף ועמום · צלקות פוסט אקנה</t>
+          <t>קמטים וקמטוטים · אלסטיות · עור עייף ועמום · צלקות פוסט אקנה · 1.5% · 2.5%</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
@@ -6887,7 +6886,7 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Wrinkles &amp; fine lines · Elasticity · Tired, dull skin · Post-acne scars</t>
+          <t>Wrinkles &amp; fine lines · Elasticity · Tired, dull skin · Post-acne scars · 1.5% · 2.5%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -6897,12 +6896,12 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>Ступени сжаты по ширине: две коробки рядом в верхней половине, 1.5% ниже. Метки сеткой 2×2 под текстом. Линии к меткам не рисуются — метки подсвечиваются, когда в свет выходит коробка 2.5%.</t>
+          <t>Сначала метки сеткой 2×2 поверх дыма. Потом над ними в верхней половине появляются две коробки рядом, 1.5% ниже, крупные цифры на подступенках видны. Линии к меткам не рисуются: метки подсвечиваются, когда в свет выходит ступень 2.5%.</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>cat.s05[0] | b1.title | b1.line | b1.label1,b1.label2,b1.label3,b1.label4 | b1.cta</t>
+          <t>cat.s05[1] | b1.title | b1.line | b1.label1,b1.label2,b1.label3,b1.label4,cat[cell-renew-1-5].stats[0][0],cat.stats[0][0] | b1.cta</t>
         </is>
       </c>
     </row>
@@ -6922,17 +6921,17 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Внутри медальона: спикулы, пять пептидов, Bakuchiol</t>
+          <t>Внутри медальона: пять пептидов, Bakuchiol, Adenosine</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Камера внутри медальона. Напечатанные тёмно-зелёные спикулы отрываются от картона и становятся объёмным полем тонких веретён (инстансы лейт-формы, вид по site/img/spicules-macro.png) — плотнее, чем на странице 1.5%. По скроллу сквозь поле проходят пять золотых нитей (5 пептидов) и две отдельные светлые частицы — Bakuchiol и Adenosine. Каждая зажигает свою метку b2.label1–4. Наведение или тап на «5 פפטידים» раскрывает пять имён (cat.ingredients[2] и cat.ingredients[3]), каждое на своей нити. Ссылка на полный состав раскрывает cat.ingredients на месте. Поле медленно поворачивается за указателем.</t>
+          <t>Камера внутри медальона. Напечатанные тёмно-зелёные спикулы отрываются от картона и становятся объёмным полем тонких веретён (вид по site/img/spicules-macro.png). Поле служит фоном и подсвечивает b2.label1. Первым сквозь поле по скроллу проходит то, чего у 1.5% по каталогу нет: пять золотых нитей (b2.label3), затем две светлые частицы — Bakuchiol (b2.label2) и Adenosine (b2.label4). Наведение или тап на «5 פפטידים» раскрывает пять имён (cat.ingredients[2] + cat.ingredients[3]), каждое на своей нити. Ссылка cat.s03[1] «הרכיבים הפעילים המרכזיים» раскрывает на месте cat.ingredients. Полным составом этот список не называем: это 8 ключевых активов, а не INCI. Поле медленно поворачивается за указателем.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Поле спикул и нити стягиваются в одну прозрачную каплю. Камера отъезжает: капля висит на носике нажатой помпы белого airless-флакона, который вышел вперёд, а коробка отступила влево в расфокус.</t>
+          <t>Поле спикул и нити стягиваются в одну прозрачную каплю, и она повисает перед медальоном. Камера отъезжает, коробка 2.5% уходит влево и вверх в расфокус. Капля остаётся в центре кадра сама по себе, без флакона и помпы.</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -6952,7 +6951,7 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>2.5% ספיקולות · Bakuchiol · 5 פפטידים · Adenosine</t>
+          <t>2.5% ספיקולות · Bakuchiol · 5 פפטידים · Adenosine · Acetyl Hexapeptide-8 · Acetyl Tetrapeptide-5 · Palmitoyl Tetrapeptide-7 · Palmitoyl Tripeptide-5 · Carnosine · הרכיבים הפעילים המרכזיים · Hydrolyzed Sponge – ספיקולות בריכוז 2.5% · Bakuchiol – בקוצ׳יול · Acetyl Hexapeptide-8 · Acetyl Tetrapeptide-5 · Palmitoyl Tetrapeptide-7 · Palmitoyl Tripeptide-5 · Carnosine · Hydrolyzed Collagen Extract · Adenosine · Yeast Beta-Glucan – בטא־גלוקן המופק משמרים · תמציות Akebia Quinata ו-Camellia Japonica</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
@@ -6972,7 +6971,7 @@
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>2.5% spicules · Bakuchiol · 5 peptides · Adenosine</t>
+          <t>2.5% spicules · Bakuchiol · 5 peptides · Adenosine · Acetyl Hexapeptide-8 · Acetyl Tetrapeptide-5 · Palmitoyl Tetrapeptide-7 · Palmitoyl Tripeptide-5 · Carnosine · Key active ingredients · Hydrolyzed Sponge — spicules at 2.5% · Bakuchiol · Acetyl Hexapeptide-8 · Acetyl Tetrapeptide-5 · Palmitoyl Tetrapeptide-7 · Palmitoyl Tripeptide-5 · Carnosine · Hydrolyzed collagen extract · Adenosine · Yeast beta-glucan · Akebia quinata &amp; Camellia japonica extracts</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
@@ -6982,12 +6981,12 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>Поле спикул на весь экран за текстом, под копией затемнено. Метки 2×2 внизу. Имена пептидов открываются нижней шторкой по тапу на «5 פפטידים».</t>
+          <t>Поле спикул на весь экран за текстом, под копией затемнено. Метки 2×2 внизу. Имена пептидов открываются нижней шторкой по тапу на «5 פפטידים». Ссылка cat.s03[1] открывает в той же шторке список cat.ingredients.</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>cat.s03[0] | b2.title | b2.line | b2.label1,b2.label2,b2.label3,b2.label4 | b2.cta</t>
+          <t>cat.s03[0] | b2.title | b2.line | b2.label1,b2.label2,b2.label3,b2.label4,cat.ingredients[2] + cat.ingredients[3],cat.s03[1],cat.ingredients | b2.cta</t>
         </is>
       </c>
     </row>
@@ -7007,17 +7006,17 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Помпа и капля: покалывание, не тереть</t>
+          <t>Капля на коже: покалывание, не тереть</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Справа крупно airless-флакон (лейт-модель с печатью из фото), головка помпы нажата, на носике капля. По скроллу капля отрывается и в замедлении падает на тёплую изогнутую поверхность кожи — абстрактную, без лица; фото-кадр только после ответа заказчика. В момент касания по поверхности пробегает короткое мелкое золотое мерцание (b3.label1). Затем идёт одно медленное круговое движение-волна (b3.label2); скорость волны ограничена, «растирания» нет. На последних четвертях появляются b3.label3 и b3.label4. Поверхность при этом не меняется, «до/после» не показываем — в каталоге его нет.</t>
+          <t>Это ключевой кадр Feel it (по design-rules ключевых кадров три: Meet · Feel it · Offer). Основной вариант — кадр с человеком по образцу утверждённого кадра MASK с лицом: пальцы у линии челюсти, одно мягкое круговое движение. Запасной вариант — тёплая изогнутая поверхность кожи без лица. Выбор за заказчиком (вопрос 5). Кадр с человеком — платная генерация: только после цены, баланса и «утверждаю», в публичный репозиторий он не идёт. По скроллу капля сверху в замедлении падает на кожу. В момент касания — короткое мелкое золотое мерцание (b3.label1). Затем одно медленное круговое движение пальцев или волна по поверхности (b3.label2), скорость ограничена, «растирания» нет. На последних четвертях появляются b3.label3 и b3.label4. «До/после» не показываем: в каталоге его нет. Если заказчик подтвердит флакон, капля выходит из носика нажатой помпы. Тогда в кадре только белая головка помпы, а печатный корпус вне кадра или в расфокусе.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Поверхность темнеет и уходит вниз. Флакон отъезжает влево и встаёт на ступень. Лестница из экрана 2 возвращается из дыма и достраивается вправо и вверх до трёх ступеней.</t>
+          <t>Кадр темнеет и уходит вниз. Коробка 2.5% выходит из расфокуса и встаёт на ступень. Лестница с экрана 2 возвращается из дыма и достраивается вправо и вверх до трёх ступеней.</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -7067,7 +7066,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>Флакон и падение капли идут вертикально по центру, поверхность внизу экрана. Текст под сценой. Метки появляются по одной в той же последовательности.</t>
+          <t>Капля падает вертикально по центру, кожа (кадр) внизу экрана. Текст под сценой. Метки появляются по одной в той же последовательности.</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -7097,12 +7096,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Протокол поверх отступивших объектов — лестница из трёх ступеней слева-снизу вправо-вверх. Ступень 1 «1 · מריחה» — флакон 2.5%. Ступень 2 «2 · שיקום» — коробка DERMA RECOVERY CREAM (куб из пакшота). Ступень 3 «3 · הגנה» без предмета: свет на ней теплеет до дневного, по ступени проходит мягкий солнечный блик. Солнцезащитное средство не рисуем — его нет в каталоге MITODERM. Ниже первой ступени, на отдельной низкой ступени, стоит коробка CELL RENEW 1.5% с меткой b4.label4. Тап или наведение на ступень раскрывает её фразу из каталога: cat.steps[0][1], cat.steps[1][1], cat.steps[2][1].</t>
+          <t>Протокол идёт поверх отступивших объектов: лестница из трёх ступеней, слева снизу вправо вверх. Ступень 1 «1 · מריחה» — коробка 2.5%. Ступень 2 «2 · שיקום» — коробка DERMA RECOVERY CREAM: куб с фасадом из protocols/assets/img/derma-recovery.webp, его шалфейная полоса отличает её от тёмно-зелёной полосы 2.5%. Ступень 3 «3 · הגנה» без предмета: свет на ней теплеет до дневного, по ступени проходит мягкий солнечный блик. Солнцезащитное средство не рисуем — в каталоге MITODERM его нет. Обе коробки поворачиваются не больше ±20°. CELL RENEW 1.5% здесь не вторая 3D-коробка, а отдельная карточка у первой ступени: b4.label4 и cat[cell-renew-1-5].name со ссылкой на её страницу. Тап или наведение на ступень раскрывает фразу шага: cat.steps[0][1], cat.steps[1][1], cat.steps[2][1].</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Лестница и коробки DERMA и CELL RENEW уходят в дым. Коробка 2.5% выходит из глубины вперёд фасадом, флакон встаёт рядом справа. Камера опускается на уровень глаз.</t>
+          <t>Лестница с коробкой DERMA уходит в дым, карточка 1.5% гаснет. Коробка 2.5% выходит из глубины вперёд фасадом. Камера опускается на уровень глаз.</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -7122,7 +7121,7 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>1 · מריחה · 2 · שיקום · 3 · הגנה · חדשים? התחילו ב-1.5%</t>
+          <t>1 · מריחה · 2 · שיקום · 3 · הגנה · חדשים? התחילו ב-1.5% · CELL RENEW 1.5% · על עור נקי ויבש יש למרוח ולעסות בעדינות. עשויה להופיע תחושת עקצוץ מורגשת – אין לשפשף בחוזקה. · לאחר הסרום מומלץ למרוח DERMA RECOVERY CREAM לתמיכה בלחות ובחיוניות העור. · בשעות היום חובה להשתמש במסנן קרינה. בעור שאינו מורגל – מעבר הדרגתי מ־CELL RENEW 1.5%.</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
@@ -7142,7 +7141,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>1 · Apply · 2 · Recover · 3 · Protect · Start with 1.5% if new</t>
+          <t>1 · Apply · 2 · Recover · 3 · Protect · Start with 1.5% if new · CELL RENEW 1.5% · On clean, dry skin; massage gently. A noticeable tingling may occur — do not rub vigorously. · Follow with DERMA RECOVERY CREAM to support the moisture barrier. · Sunscreen during the day. Start with CELL RENEW 1.5% if the skin is not yet accustomed.</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -7152,12 +7151,12 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>Лестница вертикально, ступени одна под другой, ступень 1 сверху. CELL RENEW 1.5% внизу отдельной карточкой со ссылкой на её страницу. Фразы шагов открыты сразу, без наведения.</t>
+          <t>Лестница идёт вертикально, ступени одна под другой, ступень 1 сверху. Карточка CELL RENEW 1.5% внизу, со ссылкой на её страницу. Фразы шагов открыты сразу, без наведения.</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>cat.s02[0] | b4.title | b4.line | b4.label1,b4.label2,b4.label3,b4.label4 | b4.cta</t>
+          <t>cat.s02[0] | b4.title | b4.line | b4.label1,b4.label2,b4.label3,b4.label4,cat[cell-renew-1-5].name,cat.steps[0][1],cat.steps[1][1],cat.steps[2][1] | b4.cta</t>
         </is>
       </c>
     </row>
@@ -7177,17 +7176,17 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>30 мл: коробка и флакон</t>
+          <t>30 мл: коробка и факты</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Коробка фасадом к зрителю и флакон рядом в правой половине. Пара поворачивается за указателем не больше чем на ±20°, потому что фото боковин нет. Метки-факты выходят из напечатанных мест: «2.5% ספיקולות» — от полосы 'DEFENSE 2.5%', «30 מ״ל» — от нижней строки '30ml ℮ 1.0 fl.oz.'. «5 פפטידים» и «Bakuchiol» висят свободно, а пять золотых нитей один раз обвивают флакон — повтор мотива экрана 3.</t>
+          <t>Коробка стоит фасадом к зрителю в правой половине. За указателем она поворачивается не больше ±20°: фото боковин нет. Метки-факты выходят из напечатанных мест: b5.label1 «2.5% ספיקולות» — от полосы 'DEFENSE 2.5%', b5.label2 «30 מ״ל» — от нижней строки '30 ml ℮ 1.0 fl.oz.' (так на пакшоте, с пробелом). b5.label3 «5 פפטידים» и b5.label4 «Bakuchiol» висят свободно, а пять золотых нитей один раз обвивают коробку — повтор мотива экрана 3. В доке этот пункт подписан cat.s04[0].</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Камера поднимается, свет теплеет до золота линейки. Пара сдвигается вправо и вниз, за ней из дыма проступает крупная золотая монограмма M. Слева выезжает карточка покупки, сзади в мягком фокусе появляется коробка DERMA RECOVERY CREAM.</t>
+          <t>Камера поднимается, свет теплеет. Коробка сдвигается вправо и вниз, за ней в зелёном дыму размыто проступает золотая монограмма M. Слева выезжает карточка покупки.</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -7237,7 +7236,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>Пара в верхней половине, за указателем не поворачивается: при входе короткий автоповорот ±10°. Факты сеткой 2×2 под текстом.</t>
+          <t>Коробка в верхней половине и за указателем не поворачивается: при входе короткий автоповорот ±10°. Факты сеткой 2×2 под текстом.</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -7267,13 +7266,13 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Справа коробка 2.5% и флакон в ключевом свете, за ними крупная золотая монограмма M в зелёном дыму линейки. Чуть позади в мягком фокусе стоит коробка DERMA RECOVERY CREAM как пара (b6.label4). Слева карточка покупки. В ней заголовок cat.s04[1] и строка cat.kit[0] (1× флакон, 30 ml ℮ 1.0 fl.oz.) с мини-рендером коробки, ниже cat.s03[1] и свёрнутый список cat.ingredients. Одна главная кнопка b6.label1 «איפה לקנות» с золотой заливкой. Под ней строка контактов WhatsApp · телефон · e-mail и текстовая ссылка для клиник b6.label3. Бейджи «BIOSPICULE» и «טיפוח ביתי» (золотой контур). Пометки «только для специалистов» нет: это средство для домашнего ухода.</t>
+          <t>Справа коробка 2.5% в ключевом свете (±20°), за ней размытая золотая монограмма M в зелёном дыму линейки. Других коробок в 3D нет. Слева карточка покупки. Сверху в ней пара бейджей cat.eyebrow (линейка и «טיפוח ביתי» с золотым контуром), под ними заголовок nav[2] «מה בפנים». Дальше строка cat.kit[0] с мини-рендером коробки (alt — cat.name + cat.hero_sub), ниже свёрнутый список: подпись cat.s03[1], внутри cat.ingredients. Одна главная кнопка b6.label1 «איפה לקנות» с золотой заливкой открывает экран «Ask your clinic» (решение 17), под ней подпись b6.label2. Ниже строка контактов, как в образце MASK: иконка WhatsApp, затем ui.phone_label + ui.phone и ui.email_label + ui.email. Текстовая ссылка b6.label3 «לקליניקות: לקבלת הצעת מחיר» ведёт в WhatsApp. Её текст — ui.wa_text_product с {name} = CELLULAR AGE DEFENSE 2.5% и кодом страницы #CAD-HE-6 (исправление 7); тот же текст у иконки WhatsApp. Под карточкой, отдельно от неё, мини-карточка пары: b6.label4 «בשילוב עם DERMA RECOVERY» со ссылкой на страницу крема. В набор она не входит. Пометки «только для специалистов» нет: это средство для домашнего ухода. Флакон ставится рядом с коробкой только после ответа заказчика.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>השלב הבא בשגרת BIOSPICULE™</t>
+          <t>הצעה</t>
         </is>
       </c>
       <c r="H72" s="3" t="inlineStr">
@@ -7288,7 +7287,7 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>קליניקות שותפות · בשילוב עם DERMA RECOVERY · לקליניקות: לקבלת הצעת מחיר · ⏳ перевод на иврит и две проверки идут</t>
+          <t>סרום BIOSPICULE™ · טיפוח ביתי · מה בפנים · 1× · CELLULAR AGE DEFENSE 2.5% · 30 ml ℮ 1.0 fl.oz. – Advanced Biospicule Technology · הרכיבים הפעילים המרכזיים · Hydrolyzed Sponge – ספיקולות בריכוז 2.5% · Bakuchiol – בקוצ׳יול · Acetyl Hexapeptide-8 · Acetyl Tetrapeptide-5 · Palmitoyl Tetrapeptide-7 · Palmitoyl Tripeptide-5 · Carnosine · Hydrolyzed Collagen Extract · Adenosine · Yeast Beta-Glucan – בטא־גלוקן המופק משמרים · תמציות Akebia Quinata ו-Camellia Japonica · קליניקות שותפות · לכל הפרטים: · 054-326-2182 · דוא״ל: · info@mitoderm.com · לקליניקות: לקבלת הצעת מחיר · בשילוב עם DERMA RECOVERY</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
@@ -7308,7 +7307,7 @@
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Partner clinics · Pair: DERMA RECOVERY · For clinics: request price · WhatsApp · Call · Email</t>
+          <t>BIOSPICULE™ SERUM · HOME CARE · Inside · 1× · CELLULAR AGE DEFENSE 2.5% · 30 ml ℮ 1.0 fl.oz. — Advanced Biospicule Technology. · Key active ingredients · Hydrolyzed Sponge — spicules at 2.5% · Bakuchiol · Acetyl Hexapeptide-8 · Acetyl Tetrapeptide-5 · Palmitoyl Tetrapeptide-7 · Palmitoyl Tripeptide-5 · Carnosine · Hydrolyzed collagen extract · Adenosine · Yeast beta-glucan · Akebia quinata &amp; Camellia japonica extracts · Partner clinics ·  · 054-326-2182 ·  · info@mitoderm.com · For clinics: request price · Pair: DERMA RECOVERY</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -7318,12 +7317,12 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>Рендер коробки и флакона сверху, около 40% высоты. Ниже карточка «что внутри», состав свёрнут. Внизу липкая панель с кнопкой «איפה לקנות» и иконкой WhatsApp. Контакты и ссылка для клиник — под карточкой.</t>
+          <t>Рендер коробки сверху, около 40% высоты. Ниже карточка «מה בפנים», состав свёрнут, кнопка «איפה לקנות» во всю ширину внутри карточки. Липкая панель прячется, когда кнопка карточки на экране. Контакты, ссылка для клиник и мини-карточка DERMA — под карточкой.</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>cat.cta[0] | b6.title | b6.line | b6.label2,b6.label4,b6.label3,s7.contacts | b6.label1</t>
+          <t>nav[6] | b6.title | b6.line | cat.eyebrow,nav[2],cat.kit[0],cat.s03[1],cat.ingredients,b6.label2,ui.phone_label + ui.phone,ui.email_label + ui.email,b6.label3,b6.label4 | b6.label1</t>
         </is>
       </c>
     </row>
@@ -7428,22 +7427,22 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Знакомство: коробка в шалфейном дыму</t>
+          <t>Знакомство: коробка в зелёном дыму</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Коробка (кубоид, фасад с пакшота) стоит справа анфас. Она медленно покачивается по оси Y в пределах ±12° (боковые грани пока без печати) и чуть «дышит» вверх-вниз. Вокруг неё по пологой орбите скользит одна белая кремовая лента — объёмное эхо напечатанного на фасаде завитка крема. Дальний слой: тёмно-зелёный дым с шалфейным свечением точно за коробкой и редкие кремовые искры, весь слой поворачивается за курсором. Текст — в левой половине, RTL.</t>
+          <t>Справа анфас стоит коробка DERMA (кубоид, фасад с пакшота). Она покачивается по оси Y не больше чем на ±12°, потому что боковины пока без печати, и чуть «дышит» вверх-вниз. Вокруг неё по пологой орбите скользит одна белая кремовая лента — объёмное эхо завитка, напечатанного на фасаде. Дальний слой: тёмно-зелёный дым, узкое шалфейное свечение прямо за коробкой, редкие кремовые искры. Весь слой поворачивается за указателем. Слева текст RTL. Как в герое MASK, сверху ряд бейджей: кикер cat.eyebrow с маленькой золотой M (это метка линейки) и рядом бейдж назначения ui.use_home с золотым контуром. Ниже заголовок, фраза и три чипа b0.label1–3. b0.label4 (SNAIL COLLAGEN) не нужен: он уже есть в кикере. Кнопки b0.cta: главная ведёт к экрану 8 (специалисты и клиники), вторичная — скролл к экрану 3.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Коробка отъезжает назад-вправо до ~70% размера и поворачивается на ~20°. Лента крема истончается и уходит в дым. В дальний слой вплывают тонкие шалфейные иглы-спикулы и сухие хлопья цвета слоновой кости. Дым становится зернистее, свечение за коробкой гаснет наполовину.</t>
+          <t>Коробка уходит в глубину и растворяется в дыму, на экране 2 упаковки нет. Лента крема истончается и гаснет. Свечение гаснет наполовину, дым становится зернистее. В отдельном дальнем плане появляются тонкие серо-оливковые иглы-спикулы и сухие хлопья цвета слоновой кости.</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>קרם משקם · 50 מ״ל</t>
+          <t>סדרת BIOSPICULE™ · SNAIL COLLAGEN</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
@@ -7458,7 +7457,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>0% ספיקולות · 50 מ״ל · יומיומי · SNAIL COLLAGEN</t>
+          <t>טיפוח ביתי · 0% ספיקולות · 50 מ״ל · יומיומי</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
@@ -7478,7 +7477,7 @@
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>0% spicules · 50 ml · Daily · Snail collagen</t>
+          <t xml:space="preserve"> · 0% spicules · 50 ml · Daily</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
@@ -7488,12 +7487,12 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>Коробка — по центру в верхних ~50% экрана, покачивание ±8°. Текст ниже, выравнивание вправо (RTL), метки сеткой 2×2. Кнопка «איפה לקנות» во всю ширину. Док скрыт, вместо него липкая нижняя панель с той же кнопкой. Частиц вдвое меньше. При prefers-reduced-motion или без WebGL — статичный кадр коробки на зелёном градиенте.</t>
+          <t>Коробка по центру в верхних ~50% экрана, покачивание ±8°. Ниже текст, выравнивание вправо (RTL). Кикер с маленькой M и бейдж ui.use_home — одной строкой, под ними три чипа. Главная кнопка b6.label1 во всю ширину. Док скрыт, вместо него липкая нижняя панель с той же кнопкой. Частиц вдвое меньше. При prefers-reduced-motion или без WebGL — статичный кадр коробки на зелёном градиенте.</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>cat.hero_sub | b0.title | b0.line | b0.label1,b0.label2,b0.label3,b0.label4 | b0.cta</t>
+          <t>cat.eyebrow | b0.title | b0.line | ui.use_home,b0.label1,b0.label2,b0.label3 | b0.cta</t>
         </is>
       </c>
     </row>
@@ -7518,12 +7517,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Коробка стоит в глубине справа, развёрнута на ~20°, её свечение приглушено. Перед ней по диагонали медленно пролетают тонкие шалфейные иглы-спикулы (образ «после спикул и процедуры») и матовые сухие хлопья цвета слоновой кости. Хлопья кружатся и крошатся — так выглядит сухая, стянутая, шелушащаяся кожа из b1.line. Иглы относятся только к прошлой процедуре: внутри крема их нет, и на экране 3 они исчезают.</t>
+          <t>Упаковки в кадре нет. В отдельном дальнем плане, ни с чем не пересекаясь, по диагонали медленно пролетают иглы-спикулы естественного серо-оливкового цвета (вид как на site/img/spicules-macro.png). Это образ прошлой процедуры из b1.line, а не состав крема. Перед ними кружатся и крошатся матовые сухие хлопья цвета слоновой кости — сухая, стянутая, шелушащаяся кожа. Шалфея на этом экране нет. Иглы больше нигде на странице не появляются.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Верхний клапан коробки откидывается, из коробки вертикально поднимается банка и выходит вперёд. Коробка опускается и растворяется в дыму. Иглы-спикулы гаснут и больше на странице не появляются. Хлопья остаются висеть по краям кадра.</t>
+          <t>Иглы гаснут. Из дыма выходит коробка, верхний клапан откидывается (изнутри чистый картон). Банка вертикально поднимается из коробки фасадом к зрителю (этикетка по фото 1) и выходит вперёд. Коробка опускается и растворяется. Хлопья остаются висеть по краям кадра.</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -7573,7 +7572,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>Коробка уменьшена и сдвинута вверх-вправо. Иглы и хлопья — лёгкий слой частиц на всю ширину верхней половины. Текст ниже, RTL, метки 2×2. Липкая нижняя панель «איפה לקנות».</t>
+          <t>Иглы и хлопья — лёгкий слой частиц в верхней половине экрана, упаковки нет. Ниже текст RTL, метки сеткой 2×2. Липкая нижняя панель с b6.label1.</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -7603,12 +7602,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Банка (токарная модель) стоит справа, камера смотрит чуть сверху. Крышка снимается и зависает над банкой, открывая гладкий белый крем с мягким завитком на поверхности. Из крема медленно поднимаются семь мягких круглых полупрозрачных жемчужин — по одной на ключевой актив из b2.line — и встают кольцом над банкой. В кадре нет ни одной острой формы: это «0% спикул». Пока нет фото банки, камера смотрит в открытую банку сверху, и этикетка не видна.</t>
+          <t>Справа стоит банка (токарная модель). Фасад берётся с фото 1, поворот не больше ±20°, чтобы не показать неснятую заднюю сторону. Камера смотрит чуть сверху. Крышка поднимается и отходит в сторону, её видно сбоку. Под ней гладкий белый крем с мягким завитком; обод открытой банки — по фото 73. Из крема медленно поднимаются семь мягких круглых полупрозрачных жемчужин, по одной на актив из b2.line, и встают кольцом над банкой. В кадре нет ни одной острой формы — это «0% спикул».</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Жемчужины опускаются обратно в крем. Банка наклоняется к зрителю на ~25°, и из неё начинает выходить мягкая кремовая лента. Хлопья с краёв кадра медленно стягиваются к центру.</t>
+          <t>Жемчужины опускаются обратно в крем. Банка наклоняется к зрителю на ~20°, и из неё выходит мягкая лента крема. Лента проходит сквозь хлопья, и каждый хлопок, которого она коснулась, тает в мягкую точку света. Лента разглаживается в атласный слой, и этот слой растворяется в кадре у зеркала.</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -7658,7 +7657,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>Вид сверху в открытую банку в верхних ~45% экрана, семь жемчужин по кольцу. Ниже фраза со списком активов, RTL, метки 2×2. Липкая панель «איפה לקנות».</t>
+          <t>Открытая банка чуть сверху в верхних ~45% экрана, семь жемчужин по кольцу. Ниже фраза со списком активов, RTL, метки 2×2. Липкая панель с b6.label1.</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -7683,17 +7682,17 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Комфорт: лента крема разглаживает хлопья</t>
+          <t>Комфорт: сцена у зеркала</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Из наклонённой банки медленной волной выходит лента крема — тот же завиток, что напечатан на коробке. Она проходит сквозь сухие хлопья, и каждый хлопок, которого она коснулась, тает в мягкую точку света. Внизу кадра лента расстилается в гладкий атласный слой — образ поддержанного барьера влаги. Эффекты идут в порядке меток b3.label1–4: хлопья перестают кружиться (успокоение) → появляется слой (барьер) → его поверхность выглаживается (мягкость) → дым светлеет, и шалфейное свечение за банкой становится ровным и тёплым (здоровое сияние). Людей в кадре нет.</t>
+          <t>Сцена у зеркала: в storyboard.json у этого блока стоит «benefits (mirror scene)», а у утверждённого MASK на экране 4 — кадр с лицом. Утверждённый фотокадр: женщина у зеркала наносит крем на щёку, и лента крема из перехода ложится на кожу. Банка фасадом стоит у края кадра. Четыре метки b3.label1–4 по очереди загораются золотыми точками на лице, как точки-метки в образце MASK. Дальний дым светлеет, шалфейное свечение становится ровным и тёплым. Фото с людьми ставится только утверждённое заказчиком. В коллаже такого фото нет, поэтому генерация — один образец, цена и «ок» до запуска. Пока «ок» нет, работает запасной 3D-вариант без людей. В порядке b3.label1–4: хлопья перестают кружиться → появляется атласный слой → его поверхность выглаживается → свечение за банкой становится ровным.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Атласный слой сворачивается обратно в банку, крышка опускается на место. Банка выпрямляется и отъезжает вправо-вниз. Дым густеет до насыщенного зелёного BIOSPICULE, в нём проступает золотая M, а слева въезжают коробки линейки.</t>
+          <t>Фотокадр уходит в дым. Банка выпрямляется, отъезжает вправо в глубину и гаснет. Дым густеет до насыщенного #1E4634, в нём проступает золотая M, въезжают билборды коробок линейки.</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -7743,7 +7742,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>Банка и лента — в верхних ~50% экрана, атласный слой у нижнего края этой зоны. Текст ниже, RTL. Четыре метки загораются по очереди вместе с эффектами. Липкая панель «איפה לקנות».</t>
+          <t>Фотокадр (или запасная 3D-сцена) в верхних ~50% экрана, золотые точки-метки на лице. Ниже текст RTL. Четыре метки загораются по очереди вместе с точками. Липкая панель с b6.label1.</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -7768,27 +7767,27 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Протокол: последняя точка линейки BIOSPICULE</t>
+          <t>Протокол: две ветки BIOSPICULE сходятся к DERMA</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Экран с оттенком серии: самый насыщенный зелёный #1E4634, за объектами в дыму — крупная полупрозрачная золотая монограмма M. Справа, чуть в глубине, в ряд стоят билборды коробок: CELL RENEW 1.5% и CELLULAR AGE DEFENSE 2.5% (шаг 1 — после сывороток), за ними MICRO BOOST 10% (шаг 2 — после клиники). К MICRO BOOST 10% тонкой золотой линией привязана метка b4.label4. Банка DERMA встаёт в конец ряда, на шаг ближе к зрителю, как точка в конце фразы. Шаг 3 «утро и вечер»: над банкой дважды проходит тонкая дуга света — тёплая золотая (утро) и шалфейная (вечер). V-TECH и EXO-NAD — только текстом в b4.line.</t>
+          <t>Экран оттенка серии: самый насыщенный зелёный #1E4634, за объектами в дыму крупная полупрозрачная золотая M. Справа две ветки сходятся к коробке DERMA (кубоид, фасад), которая стоит на шаг ближе к зрителю. Домашняя ветка (метка b4.label1): CELL RENEW 1.5% и CELLULAR AGE DEFENSE 2.5% стоят на одном месте и сменяют друг друга — одна гаснет, другая проступает. Это «או» из b4.line и cat.steps[0], а не два шага подряд. Клиническая ветка (метка b4.label2): билборд MICRO BOOST 10% с маленьким бейджем home.tg (золотая заливка — средство профессиональное), к нему тонкой золотой линией привязана b4.label4. Тонкие золотые линии обеих веток сходятся к коробке DERMA. Шаг b4.label3: над коробкой дважды проходит дуга света — золотая (утро) и шалфейная (вечер). Высоту билбордов выравниваем условно: реальных размеров коробок 3 мл, 30 мл и 50 мл в источниках нет. V-TECH и EXO-NAD — только текстом в b4.line.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Коробки сывороток и MICRO BOOST 10% гаснут в дыму, золотая M растворяется, зелёный возвращается к шалфейному окружению. Из глубины выходит коробка DERMA и встаёт слева-сзади от банки.</t>
+          <t>Сыворотки и MICRO BOOST 10% гаснут в дыму, золотая M растворяется, зелёный возвращается к базовому окружению. Коробка DERMA уходит в глубину. Камера опускается к открытой банке, которая выходит из дыма.</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>סדרת BIOSPICULE™ · SNAIL COLLAGEN</t>
+          <t>מתי למרוח</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>50 מ״ל. בוקר וערב.</t>
+          <t>אחרי הסרומים. אחרי הקליניקה. מדי יום.</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
@@ -7808,7 +7807,7 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>50 ml. Morning and evening.</t>
+          <t>After serums. After the clinic. Daily.</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -7828,12 +7827,12 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>Ряд из трёх коробок и банки ужат по ширине и стоит в верхних ~40% экрана; золотая M — за ним. Шаги — вертикальным списком ниже, RTL, метка «חובה לאחר MICRO BOOST 10%» выделена золотым контуром. Липкая панель «איפה לקנות».</t>
+          <t>Ветки ужаты в верхних ~40% экрана: место сывороток со сменой, MICRO BOOST 10% с бейджем home.tg, золотые линии к коробке DERMA, за ними золотая M. Шаги — вертикальным списком ниже, RTL, b4.label4 выделена золотым контуром. Липкая панель с b6.label1.</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>cat.eyebrow | b5.title | b4.line | b4.label1,b4.label2,b4.label3,b4.label4 | b4.cta</t>
+          <t>cat.s02[1] | b4.title | b4.line | b4.label1,b4.label2,b4.label3,b4.label4 | b4.cta</t>
         </is>
       </c>
     </row>
@@ -7853,17 +7852,17 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Факты: коробка и банка рядом</t>
+          <t>Факты: крупный план открытой банки</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Справа стоят рядом коробка (анфас, чуть сзади) и закрытая банка (вполоборота, впереди). Банка медленно поворачивается в пределах ±30° и показывает фасад этикетки — только когда есть фото банки. До фото банка стоит открытой, и видна поверхность крема. Тонкими золотыми выносками к объектам привязаны четыре факта b5.label1–4: объём и 0% спикул — к банке, «дважды в день» и «для всех типов кожи» — к коробке. Свечение за объектами — ровный шалфей.</t>
+          <t>Крупный план открытой банки чуть сверху: поверхность крема с завитком, внизу кадра край этикетки фасада (фото 1). Коробки в кадре нет — набор впервые соберётся на экране 7. Тонкими золотыми выносками к поверхности крема и к банке привязаны четыре факта b5.label1–4. Свечение — ровный шалфей.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Коробка и банка разворачиваются анфас и собираются в композицию покупки: коробка чуть сзади, банка впереди с приподнятой крышкой. Выноски гаснут, золото бренда проступает в волосяных линиях.</t>
+          <t>Камера отъезжает. Крышка возвращается и зависает чуть над банкой. Слева-сзади из глубины выходит коробка анфас. Выноски гаснут, объекты собираются в набор, золото бренда проступает в волосяных линиях.</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -7913,7 +7912,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>Коробка и банка рядом в верхних ~45% экрана, без выносок. Факты — чипами 2×2 под фразой, RTL. Липкая панель «איפה לקנות».</t>
+          <t>Открытая банка в верхних ~45% экрана, без выносок. Факты — чипами 2×2 под фразой, RTL. Липкая панель с b6.label1.</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -7943,7 +7942,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Справа — рендер набора: коробка анфас чуть сзади, банка впереди с приподнятой крышкой и видимым белым кремом, лёгкое шалфейное свечение, покачивание ±5°. Слева, RTL, блок «что внутри» (заголовок nav[2]): строка состава cat.kit[0] (1× DERMA RECOVERY CREAM, 50 ml ℮ 1.69 fl.oz.) и под заголовком cat.s03[1] — список семи активов cat.ingredients. Бейджи: «домашний уход» золотым контуром (home.sl-3) и линейка (cat.eyebrow) с маленькой золотой M. Одна главная кнопка с золотой заливкой — b6.label1. Под ней мелкая текстовая ссылка для клиник (b6.label3) и общий ряд контактов сайта: WhatsApp · телефон · email (как в образце MASK), у WhatsApp заполнено сообщение wa.text. Пометки «только для специалистов» нет: средство домашнее.</t>
+          <t>Справа рендер набора, коробка и банка вместе впервые на странице. Коробка анфас слева-сзади, впереди банка фасадом (фото 1) с приподнятой крышкой, виден белый крем. Лёгкое шалфейное свечение, покачивание ±5°, alt рендера — kit.alt. Слева текст RTL. Ряд бейджей как на экране 1: cat.eyebrow с маленькой золотой M и ui.use_home с золотым контуром. Чипы только b6.label2 и b6.label4. Блок «что внутри»: заголовок nav[2] и строка cat.kit[0]. Под ней свёрнутый блок cat.s03[1] со списком cat.ingredients — целиком он уже прозвучал в b2.line на экране 3. Кнопки b6.cta. Главная b6.label1 с золотой заливкой ведёт к экрану 8: специалисты и клиники, через которые средство продаётся (b6.line). Вторичная контурная b6.label3 открывает форму заявки, как кнопка цены в образце MASK; поле «מקצוע» в форме отделяет клиники от клиентов. Запасной путь без формы — WhatsApp. Ряд контактов как в MASK: WhatsApp ui.wa_number с сообщением ui.wa_text_product ({name} = DERMA RECOVERY CREAM), телефон ui.phone, почта ui.email. Пометки «только для специалистов» нет: средство домашнее.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -7964,7 +7963,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>קליניקות שותפות · לקליניקות: בקשת הצעת מחיר · משתלב בכל פרוטוקול · טיפול ביתי</t>
+          <t>סדרת BIOSPICULE™ · SNAIL COLLAGEN · טיפוח ביתי · קליניקות שותפות · משתלב בכל פרוטוקול · מה בפנים · 1× · DERMA RECOVERY CREAM · קרם קולגן מזין לשימוש יומיומי – 50 ml ℮ 1.69 fl.oz. · הרכיבים הפעילים המרכזיים · 054-326-2182 · info@mitoderm.com</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr">
@@ -7984,7 +7983,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Partner clinics · For clinics: request price · Pairs with every protocol · HOME CARE</t>
+          <t>BIOSPICULE™ LINE · SNAIL COLLAGEN ·  · Partner clinics · Pairs with every protocol · Inside · 1× · DERMA RECOVERY CREAM · 50 ml ℮ 1.69 fl.oz. — daily nourishing collagen cream. · Key active ingredients · 054-326-2182 · info@mitoderm.com</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
@@ -7994,12 +7993,12 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>Рендер набора сверху (~40% экрана). Ниже, RTL: заголовок, фраза, строка состава; список активов свёрнут в раскрывающийся блок. Кнопка «איפה לקנות» во всю ширину, она же в липкой нижней панели. Контакты — ряд иконок 44×44, ссылка для клиник — под ними.</t>
+          <t>Рендер набора сверху (~40% экрана). Ниже RTL: заголовок, фраза, два бейджа, строка состава cat.kit[0], свёрнутый список активов. Главная кнопка b6.label1 во всю ширину, она же в липкой нижней панели. Под ней контурная кнопка b6.label3. Контакты — ряд иконок 44×44.</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>nav[6] | b6.title | b6.line | b6.label2,b6.label3,b6.label4,home.sl-3 | b6.cta</t>
+          <t>nav[6] | b6.title | b6.line | cat.eyebrow,ui.use_home,b6.label2,b6.label4,nav[2],cat.kit[0],cat.s03[1],ui.phone,ui.email | b6.cta</t>
         </is>
       </c>
     </row>
@@ -8104,17 +8103,17 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Ручка в шампанском дыму</t>
+          <t>Ручка в серебряном дыму</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Справа висит MITOPEN — билборд из прозрачного пакшота в позе пакшота: наклон ≈20°, конус вверху, картридж смотрит вниз, к тексту. Перо покачивается за курсором на ±8°, раз в несколько секунд по корпусу пробегает блик через вертикальную надпись MITOPEN. Розово-золотое кольцо коротко вспыхивает — это подсказка «סובבו את הטבעת» (вторая часть b0.cta). Метка b0.label1 «מקצועי» оформлена как значок назначения (золотая заливка), остальные три — обычные чипы. Текст слева, RTL.</t>
+          <t>Справа висит MITOPEN — билборд из прозрачного пакшота в его же позе. Поворот в плоскости 0°: наклон ≈12° уже есть в самом пакшоте, конус вверху, картридж смотрит вниз-влево, к тексту. Перо слегка покачивается за курсором (до ±8°). Раз в несколько секунд по корпусу пробегает блик через вертикальную надпись MITOPEN, кольцо коротко вспыхивает. Это просто блик, а не призыв его крутить. Метка b0.label1 «מקצועי» оформлена как бейдж назначения с золотой заливкой, остальные три — обычные чипы. Числовые диапазоны на всей странице выводятся в изоляции LTR (&lt;bdi dir="ltr"&gt;, в Figma — LRI…PDI), чтобы «0.25–2.5» и «0.25-2.5» везде читались в одном порядке. Кнопка — призрачная b0.cta[0]. Подсказка прокрутки — ui.scroll_hint «גללו». Подсказку b0.cta[1] «סובבו את הטבעת» включаем только после того, как заказчик подтвердит, что кольцо задаёт глубину (вопрос 2). Текст слева, RTL.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Скролл поворачивает кольцо: насечки бегут по кругу (текстура смещается внутри маски кольца). Перо выпрямляется в вертикаль картриджем вниз, камера опускается вдоль корпуса к кольцу, дым у кончика густеет.</t>
+          <t>Скролл поворачивает перо в плоскости на −12°, до вертикали картриджем вниз. Камера опускается вдоль корпуса к нижней части пера, дым у кончика густеет.</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -8139,7 +8138,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>לקבלת פרטים על מחירים · סובבו את הטבעת</t>
+          <t>לקבלת פרטים על מחירים · גללו</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -8159,17 +8158,17 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Contact for Price · Turn the ring</t>
+          <t xml:space="preserve">Contact for Price · </t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>Сверху кикер, заголовок, фраза, чипы в ряд с горизонтальной прокруткой. Перо ниже, вертикально, 45% ширины, у начала строки (справа, RTL). Поворот за курсором на телефоне отключён, движение только от скролла. Кнопка «לקבלת פרטים על מחירים» — в липкой нижней панели, подсказка «סובבו את הטבעת» — над первой прокруткой.</t>
+          <t>Сверху кикер, заголовок, фраза, чипы в ряд с горизонтальной прокруткой. Ниже перо, вертикально, высотой не больше 45% высоты экрана (размер задаём по высоте, не по ширине), у начала строки — справа, RTL. Поворот за курсором отключён, движение идёт только от скролла. Кнопка b0.cta[0] — в липкой нижней панели, «גללו» — над первой прокруткой.</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>cat.eyebrow | b0.title | b0.line | b0.label1,b0.label2,b0.label3,b0.label4 | b0.cta</t>
+          <t>cat.eyebrow | b0.title | b0.line | b0.label1,b0.label2,b0.label3,b0.label4 | b0.cta[0] + ui.scroll_hint</t>
         </is>
       </c>
     </row>
@@ -8194,12 +8193,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Перо стоит вертикально, картридж вниз. Позади, на среднем плане, три тонких контура цвета шампань: профиль лица, шея с декольте, кожа головы с пробором — плоская линейная графика, без фото и без людей. На скролле кончик пера по очереди наводится на каждую зону: она подсвечивается и рядом всплывает её метка (b1.label1–3). На каждой зоне кольцо делает щелчок в своё положение. На четвёртой метке «עומק לפי אינדיקציה» щелчки повторяются для всех трёх зон. Цифры глубины по зонам не показываем: в каталоге их нет.</t>
+          <t>Перо стоит вертикально, картридж вниз. Позади, на среднем плане, три тонких контура цвета шампань: профиль лица, шея с декольте, кожа головы с пробором. Это плоская линейная графика, без фото и без людей. Порядок справа налево, как b1.label1–3: лицо → шея и декольте → кожа головы. На скролле кончик пера по очереди наводится на каждую зону: зона подсвечивается, рядом всплывает её метка. На четвёртой метке «עומק לפי אינדיקציה» подсвечиваются все три зоны вместе. Щелчков кольца нет. Цифр глубины по зонам не показываем: в каталоге их нет.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Контуры зон гаснут и растворяются в дыму. Камера наезжает на кольцо и прозрачный картридж, перо наклоняется кончиком к центру — получается макроракурс.</t>
+          <t>Контуры зон гаснут и растворяются в дыму. Перо смещается в центр, кончик наклоняется к центру, камера подходит к нижней трети: кольцо, носик, картридж.</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -8241,7 +8240,7 @@
       <c r="O83" s="2" t="inlineStr"/>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>Три контура зон — горизонтальной лентой над текстом, активный контур по центру. Перо — 30% ширины сбоку от ленты. Чипы 2×2 под фразой.</t>
+          <t>Три контура зон — горизонтальной лентой над текстом, справа налево: лицо, шея и декольте, кожа головы; активный контур по центру. Перо сбоку от ленты, высотой с ленту. Чипы 2×2 под фразой.</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -8266,17 +8265,17 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Кольцо и картридж: 0.25–2.5 мм, 5 скоростей</t>
+          <t>0.25–2.5 мм, 5 скоростей</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Макроплан нижней части пера: кольцо, носик, прозрачный картридж. Скролл крутит кольцо. С одной стороны от картриджа шкала глубины 0.25 → 2.5: только цифры, единица «מ״מ», как в b2.label1. С другой — циферблат скоростей 1–5. Иглы выдвигаются из картриджа вместе со шкалой, но только по макрофото двух положений; без фото иглы не рисуем, движутся только кольцо и шкалы. На шагах скорости 1 → 5 под кончиком, на тёмной плоскости кожи, густеет сетка микроканалов из точек цвета шампань — это иллюстрация «скорость управляет плотностью микроканалов» (b2.line). Кнопка на корпусе подсвечивается на каждом шаге скорости, только если заказчик подтвердит, что скорость переключается ею.</t>
+          <t>Пока нет исходника высокого разрешения, макроплана нет. Перо показываем целиком, в обычном масштабе (не выше ~650 CSS px), а рядом крупно ставим два SVG-оверлея. Шкала глубины: подписаны только крайние значения 0.25 и 2.5 с единицей «מ״מ», как в b2.label1. Деления без цифр, потому что шаг регулировки в источниках не указан. Направление шкалы: мелко сверху, глубже снизу, по ходу иглы. Второй оверлей — циферблат скоростей 1–5. Оба выводятся в &lt;bdi dir="ltr"&gt; и движутся от скролла. По примечанию b2.cta скролл должен «крутить кольцо», но до ответа на вопрос 2 кольцо только бликует. Если окажется, что глубину задаёт носик или картридж, движется эта деталь. На шагах скорости 1 → 5 под кончиком, на абстрактной тёмной плоскости, густеет сетка микроканалов из точек цвета шампань — иллюстрация b2.line. Иглы не рисуем: на пакшоте их не видно. Кнопка подсвечивается на шагах скорости, только если заказчик подтвердит, что скорость переключается ею. Когда будет исходник от 2500 px (фото 56/57 из Figma или новый снимок), появится макро кольца и картриджа и иглы, которые выдвигаются по двум макрофото.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Перо отъезжает и поворачивается кончиком вниз-влево. Сетка микроканалов уплывает вниз и перетекает в щёку на фото-кадре следующего экрана.</t>
+          <t>Перо отъезжает и поворачивается кончиком вниз-влево. Сетка микроканалов уходит вниз и растворяется в дыму до того, как проявится фото: на кожу клиентки сетка не переносится.</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -8318,7 +8317,7 @@
       <c r="O84" s="2" t="inlineStr"/>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>Макро картриджа на всю ширину сверху. Под ним в две строки шкала глубины (0.25–2.5 מ״מ) и циферблат 1–5, оба двигаются от скролла. Затем заголовок, фраза, чипы 2×2.</t>
+          <t>Сверху перо целиком, высотой не больше 40% экрана, рядом крупно шкала глубины (только 0.25 и 2.5 מ״מ) и циферблат 1–5. Оба движутся от скролла, сетка точек под кончиком. Ниже заголовок, фраза, чипы 2×2.</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -8348,7 +8347,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>В правой половине проявляется утверждённый фото-кадр. На нём специалистка в перчатках ведёт MITOPEN по щеке клиентки, шнура нет (род — как в b3.line: «לקוסמטיקאית», «המטופלת»). 3D-перо опускается по дуге, совмещается с пером в руке на фото, и билборд растворяется в снимке. Дальний дым замедляется почти до покоя, серебряные частицы гаснут — так показано «שקט». Метки b3 всплывают по одной у руки.</t>
+          <t>В правой половине проявляется утверждённый фото-кадр: специалистка в перчатках ведёт MITOPEN по щеке клиентки, шнура нет. Род — как в b3.line: «לקוסמטיקאית», «המטופלת». Кожа на снимке чистая и спокойная, без точек и покраснения (правило review-board-exocell.md). 3D-перо опускается по дуге и совмещается с пером в руке, а затем растворяется в снимке. Совмещение делаем только если перо на фото снято в том же ракурсе, что на пакшоте: вид 3/4 спереди, кнопкой к зрителю, картридж вниз-влево, отличие только в повороте в плоскости. Иначе билборд просто растворяется в фото. Дальний дым замедляется почти до покоя, серебряные частицы гаснут — так показано «שקט». Метки b3 всплывают по одной у руки.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -8395,7 +8394,7 @@
       <c r="O85" s="2" t="inlineStr"/>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>Фото-кадр 4:5 на всю ширину, перо совмещается с рукой на снимке. Текст под фото, чипы в один ряд с прокруткой.</t>
+          <t>Фото-кадр 4:5 на всю ширину, перо совмещается с рукой на снимке или растворяется в нём. Текст под фото, чипы в один ряд с прокруткой.</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -8425,12 +8424,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Всё прежнее отступает в глубину и притухает, поверх идут три шага-карточки справа налево (RTL). Шаг 1, b4.label1: кольцо делает щелчок, рядом мелькают шкала и циферблат с экрана 3. Шаг 2, b4.label2: перо проходит над плоскостью кожи короткими ровными проходами и оставляет равномерную сетку микроканалов. Шаг 3, b4.label3: слева поднимается V-TECH SYSTEM (для лица), справа EXOSIGNAL HAIR (для кожи головы) — оба билборды из пакшотов. Прозрачная капля стекает в сетку, и точки по очереди загораются. Цвет капли не задаём — в источниках его нет. MICRO BOOST 10% — только в метке b4.label4. Призрачная кнопка b4.cta — под шагами.</t>
+          <t>Всё прежнее отступает в глубину и притухает. Поверх идут три шага-карточки справа налево (RTL). Шаг 1, b4.label1: шкала глубины и циферблат с экрана 3 вспыхивают и встают на значение, без щелчка кольца. Шаг 2, b4.label2: перо проходит над абстрактной тёмной плоскостью короткими ровными проходами и оставляет равномерную сетку микроканалов. Шаг 3, b4.label3: справа поднимается V-TECH SYSTEM (лицо), слева EXOSIGNAL HAIR (кожа головы). Это порядок чтения b4.line, оба предмета — билборды из пакшотов. Прозрачная капля стекает в сетку, и точки по очереди загораются. Цвет капли не задаём: в источниках его нет. MICRO BOOST 10% — только в метке b4.label4. Под шагами призрачная кнопка b4.cta с золотым контуром.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Сетка и средства-партнёры уходят вниз в дым. Перо встаёт вертикально на круглый постамент из матового металла цвета шампань.</t>
+          <t>Сетка и средства-партнёры уходят вниз в дым. Перо встаёт вертикально, а по сторонам снова проявляются контуры лица (справа) и кожи головы (слева) с экрана 2.</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -8480,7 +8479,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>Перо по центру, 40% ширины. Три шага — тремя строками под ним, V-TECH SYSTEM и EXOSIGNAL HAIR — горизонтальным рядом после шагов. Метка «משתלב עם…» и призрачная кнопка в конце.</t>
+          <t>Перо по центру, высотой не больше 35% экрана. Три шага — тремя строками под ним. Затем ряд партнёров: V-TECH SYSTEM первым справа, EXOSIGNAL HAIR слева. В конце метка «משתלב עם…» и призрачная кнопка.</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -8510,17 +8509,17 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN один стоит на постаменте. Поворачивается только на ±12°, потому что это билборд: полный оборот возможен лишь с моделью по фото сзади и сбоку. Вокруг по очереди всплывают четыре плитки фактов (b5.label1–4). На последней плитке, «פנים · קרקפת», перо наклоняется сначала к слову «פנים», потом к «קרקפת»: одна ручка — две зоны. Надпись «לשימוש מקצועי בלבד» стоит в конце фразы b5.line.</t>
+          <t>Перо стоит вертикально между двумя линейными контурами с экрана 2: справа лицо, слева кожа головы. Шеи и декольте здесь нет, потому что b5.label4 — «פנים · קרקפת». Вокруг по очереди всплывают четыре плитки фактов b5.label1–4, диапазон в &lt;bdi dir="ltr"&gt;. На последней плитке перо наклоняется (поворот в плоскости) к контуру лица, тот подсвечивается, затем перо наклоняется к контуру кожи головы. Так «עט אחד. פנים וקרקפת.» показан предметами, а не словами. Полного оборота нет: это билборд. «לשימוש מקצועי בלבד» стоит в конце фразы b5.line.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Плитки собираются в список «что внутри» под постаментом. Постамент и дальний дым светлеют до самого яркого шампань-серебра страницы, камера чуть отъезжает — начинается экран покупки.</t>
+          <t>Контуры гаснут, плитки собираются в список «что внутри». Под пером поднимается круглый постамент из матового металла цвета шампань с серебряной кромкой. Дым светлеет до самого яркого серебра страницы, камера чуть отъезжает — начинается экран покупки.</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>תכולת האריזה</t>
+          <t>ערכה ועובדות</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
@@ -8557,12 +8556,12 @@
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>Плитки фактов 2×2 сверху, ниже на всю ширину перо на постаменте. Наклон к «פנים»/«קרקפת» сохраняется, он идёт от скролла.</t>
+          <t>Плитки фактов 2×2 сверху. Ниже перо высотой не больше 35% экрана между двумя маленькими контурами. Наклон к лицу и к коже головы идёт от скролла.</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">cat.s04[0] | b5.title | b5.line | b5.label1,b5.label2,b5.label3,b5.label4 | </t>
+          <t xml:space="preserve">nav[5] | b5.title | b5.line | b5.label1,b5.label2,b5.label3,b5.label4 | </t>
         </is>
       </c>
     </row>
@@ -8587,13 +8586,13 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Справа то же перо на постаменте. Под ним «что внутри»: строка 1× MITOPEN (cat.kit[0]) и техданные (cat.ingredients) — у прибора они стоят вместо активов. Слева кикер — бейдж линейки «מכשור» (контур цвета шампань с серебром; это и есть явная метка серии), затем заголовок, фраза с «לשימוש מקצועי בלבד» и чипы. b6.label1 оформлен как золотой значок «только для специалистов». Одна главная кнопка «לקבלת פרטים על מחירים» (b4.cta: угольная заливка, текст цвета шампань). Ниже подпись «צרו קשר» (b6.label4) и ряд контактов WhatsApp · телефон · e-mail (новая строка s7.contacts). Дальний фон — самый яркий шампань-серебряный дым страницы. В простое по кольцу раз в несколько секунд пробегает блик.</t>
+          <t>Справа перо на постаменте. В простое по кольцу раз в несколько секунд пробегает блик. Дальний фон — самый яркий серебряный дым и серебряный контровой свет страницы, шампань вторым цветом: это оттенок серии DEVICES. Слева кикер nav[6], под ним ряд бейджей: «מכשור» (home.sl-2, серебряный контур — метка серии) и «מקצועי» (home.tg, золотая заливка — назначение). Затем заголовок b6.title и фраза b6.line: «לשימוש מקצועי בלבד» на экране один раз. Один чип — b6.label2. Карточка «что внутри»: заголовок cat.s04[1], строка cat.kit[0] (1× · MITOPEN · описание), подзаголовок cat.s03[0] и четыре строки cat.ingredients — у прибора они стоят вместо активов, диапазон в &lt;bdi dir="ltr"&gt;. Одна главная кнопка b6.cta[0]: золотая заливка #c9a24b, текст #0a0a0b. Она открывает WhatsApp с текстом ui.wa_text_product (вместо {name} — MITOPEN) и форму заявки, как на MASK. Ниже подпись b6.label4 «צרו קשר» и контакты по образцу MASK: «טלפון» + ui.phone (ссылка tel:) и «דוא״ל» + ui.email (ссылка mailto:). b6.label1 и b6.label3 здесь не показываем: они повторяют b6.line и cat.ingredients[3]. Пока экран 7 в кадре, призрачная кнопка цены в шапке скрыта: кнопка цены на экране одна. Следом идёт экран 8 «Кто делает процедуру» — его добавляет сборщик, метки פנים и קרקפת.</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>מכשור</t>
+          <t>הצעה</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
@@ -8608,7 +8607,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>לשימוש מקצועי בלבד · הדרכה ופרוטוקולים · V-TECH · EXOSIGNAL HAIR · ⏳ перевод на иврит и две проверки идут</t>
+          <t>מכשור · מקצועי · הדרכה ופרוטוקולים · מה באריזה · 1× · MITOPEN · עט מיקרונידלינג מקצועי ואלחוטי עם עומק מחט ומהירות מתכווננים. · מפרט טכני · עומק מחט מתכוונן 0.25-2.5 מ״מ · עד 5 מהירויות · אלחוטי, ארגונומי ושקט · תומך בפרוטוקולי V-TECH SYSTEM ו-EXOSIGNAL HAIR · צרו קשר · טלפון · 054-326-2182 · דוא״ל · info@mitoderm.com</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr">
@@ -8628,7 +8627,7 @@
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Professional use only · Training &amp; protocols · V-TECH · EXOSIGNAL HAIR · WhatsApp · Phone · Email</t>
+          <t>DEVICES · PRO · Training &amp; protocols · In the box · 1× · MITOPEN · Professional cordless microneedling pen with adjustable depth and speed. · SPECIFICATIONS · Needle depth 0.25–2.5 mm, adjustable · Up to 5 speeds · Cordless, ergonomic, quiet · Supports V-TECH SYSTEM and EXOSIGNAL HAIR protocols · Contact · Phone · 054-326-2182 · Email · info@mitoderm.com</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
@@ -8638,12 +8637,12 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>Сверху перо на постаменте, 50% ширины, под ним 1× MITOPEN и техданные списком. Затем бейдж линейки, заголовок, фраза и кнопка на всю ширину, контакты — строкой из трёх иконок с подписями. Липкая нижняя панель с той же кнопкой (третья часть b6.cta) прячется, когда главная кнопка в кадре.</t>
+          <t>Порядок: бейджи «מכשור» и «מקצועי», кикер, заголовок, фраза, главная кнопка на всю ширину. Затем перо, положенное горизонтально (поворот в плоскости) на постамент: около 70% ширины и меньше 30% высоты экрана. Под ним «что внутри» одной колонкой, подпись «צרו קשר», телефон и e-mail в ряд с иконками. Липкая нижняя панель b6.cta[2] доходит до экрана 7, встаёт в главную кнопку и исчезает, пока та в кадре.</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>home.sl-2 | b6.title | b6.line | b6.label1,b6.label2,b6.label3,s7.contacts | b4.cta</t>
+          <t>nav[6] | b6.title | b6.line | home.sl-2,home.tg,b6.label2,cat.s04[1],cat.kit[0],cat.s03[0],cat.ingredients,b6.label4,exocell-mask:b6.cta[2],ui.phone,exocell-mask:b6.cta[3],ui.email | b6.cta[0]</t>
         </is>
       </c>
     </row>
@@ -8748,17 +8747,17 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Система на столе — «поднимите камеру»</t>
+          <t>Система на столе — «הרימו את המצלמה»</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Справа система стоит в композиции пакшота, камера низко, ракурс 3/4 как на фото. Планшет на подставке показывает экран с логотипом (бирюзово-фиолетовая мишень, 'Mitoscan', 'By Mitoderm Ltd'). Щуп сидит в держателе на правом боку планшета, серебряная база лежит спереди, спиральный кабель — на столе. Вся группа поворачивается за указателем на ±8°. По хрому базы проходит шампань-блик, синяя капля — только свечение экрана на белом корпусе щупа. Щуп «дышит» в держателе, приподнимаясь на 2–3 мм: это подсказка к призыву из b0.cta. Оттенок серии: за системой тёплое шампань-металлическое гало и серебряный дым, над заголовком бейдж линейки «מכשור» (home.sl-2, шампань-контур) и бейдж назначения «מקצועי» (home.tg, золотая заливка). Внизу док из 7 блоков (nav[0]–nav[6]).</t>
+          <t>Справа целый пакшот системы одним биллбордом (исходник protocols/print/img/mitoscan.webp), ракурс 3/4 как на фото. Планшет на белой подставке показывает экран-логотип, щуп стоит в держателе справа, серебряный цилиндр лежит спереди, спиральный кабель — на столе. Биллборд поворачивается за указателем на ±8°, части не двигаются. По щупу и хрому цилиндра проходит шампань-блик (маска по пакшоту), синяя капля — только свечение экрана. Оттенок серии: за системой тёплое шампань-гало и серебряный дым, над заголовком бейдж линейки «מכשור» (home.sl-2, шампань-контур) и бейдж назначения «מקצועי» (home.tg, золотая заливка). Чипов три, b0.label1–3. b0.label4 «מקצועית» не выводим: назначение показывает бейдж, а «מקצועי» и «מקצועית» в двух родах на одном экране читаются как ошибка. Первая часть b0.cta — контурная кнопка цены, вторая — подсказка прокрутки. Внизу док из 7 блоков (nav[0]–nav[6]).</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Щуп поднимается из держателя вертикально вверх, спиральный кабель растягивается, щуп наклоняется к зрителю на ~20°. Планшет и база уходят вправо-назад и теряют резкость, логотип на экране гаснет до чёрного.</t>
+          <t>Камера поднимается и наезжает на щуп, не дальше ~1,5× от исходника, иначе картинка поплывёт. Щуп растёт навстречу зрителю, будто его подняли. Планшет и цилиндр по маскам уходят в дымку и расфокус, экран гаснет. Из держателя щуп не выходит, пока нет фото пустого держателя (вопрос 2).</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -8778,7 +8777,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>×50 / ×200 · הדמיית HD · מעקב לפני / אחרי · מקצועית</t>
+          <t>×50 / ×200 · הדמיית HD · מעקב לפני / אחרי</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr">
@@ -8798,7 +8797,7 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>×50 / ×200 · HD imaging · Before / after tracking · Professional</t>
+          <t>×50 / ×200 · HD imaging · Before / after tracking</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -8808,12 +8807,12 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>Текст сверху (RTL), под ним 3D на ~45% высоты экрана, группа уменьшена. Поворот за указателем заменён лёгким наклоном по гироскопу; если гироскоп недоступен, группа стоит. Чипы идут одной прокручиваемой строкой. Внизу липкая панель с кнопкой цены (b4.cta), над ней точки дока из 7 блоков.</t>
+          <t>Текст сверху (RTL), под ним целый пакшот на ~45% высоты экрана. Поворот за указателем заменён лёгким наклоном по гироскопу; если гироскопа нет, пакшот стоит. Три чипа идут одной прокручиваемой строкой. Внизу липкая панель с кнопкой цены (b4.cta), над ней точки дока из 7 блоков.</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>cat.name | b0.title | b0.line | b0.label1,b0.label2,b0.label3,b0.label4 | b0.cta</t>
+          <t>cat.name | b0.title | b0.line | b0.label1,b0.label2,b0.label3 | b0.cta</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8837,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Щуп висит в воздухе перед потухшим планшетом, к зрителю обращена передняя панель 'Mitoscan'. Экран чёрный, как на пакшоте. Передний слой дыма сгущается, и вся сцена уходит в мягкую дымку с малой глубиной резкости: так выглядит «впечатление». Четыре метки b1.label1–4 — тонкие золотые выноски, направленные в пустой чёрный экран. Они приглушены до ~40%: параметры есть, но глазом их не видно. Синей капли на этом экране нет.</t>
+          <t>Камера держит щуп крупно, лицевая панель 'Mitoscan' обращена к зрителю. Планшет за левым краем кадра или целиком растворён в дымке: экран прибора на ступени проблемы не показываем, чтобы негатив не лёг на сам прибор. Размытие делается по маскам на одном биллборде, части при этом не сдвигаются. Передний слой дыма густеет, глубина резкости малая — так выглядит «впечатление». Четыре метки b1.label1–4 — тонкие золотые выноски, направленные в дымку, то есть во «взгляд на глаз». Они приглушены до ~40%: параметры есть, но глазом их не видно. Щуп — единственный намёк на решение. Синей капли на этом экране нет.</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Щуп поворачивается торцом с линзой к зрителю и приближается, пока линза не встанет в центр. От неё расходится тонкое шампань-кольцо, и внутри кольца дымка рассеивается. Сквозь кольцо выезжает планшет и разворачивается экраном прямо к зрителю. Если фото торца с линзой не будет, щуп просто уходит наклоном вниз из кадра, линзу не показываем.</t>
+          <t>Камера смещается со щупа влево, на экран планшета. Дымка расходится шампань-кольцом от центра экрана, экран загорается. Щуп не поворачивается линзой к зрителю, пока нет фото торца (вопрос 2).</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -8885,7 +8884,7 @@
       <c r="O91" s="2" t="inlineStr"/>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>Щуп и планшет крупнее, дымка та же. Выноски заменены чипами 2×2 под текстом.</t>
+          <t>Щуп крупно во всю ширину, дымка та же. Выноски заменены чипами 2×2 под текстом.</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -8910,17 +8909,17 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>×50 → ×200 на экране</t>
+          <t>×50 → ×200</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Планшет стоит прямо, экран занимает ~60% правой половины. Щуп стоит у правого края экрана с наклоном, кабель уходит вниз. На экране настоящий снимок прибора при ×50. Скролл ведёт переключатель ×50 / ×200 (микровзаимодействие из b2.cta; сегменты — b2.label1 и b2.label2 под экраном): к середине секции изображение плавно увеличивается и сменяется настоящим снимком ×200 того же участка. Синяя капля — активный сегмент и узкое свечение рамки экрана. Метки b2.label3 и b2.label4 идут чипами в тексте слева. Пока снимков прибора нет, на экране логотип с пакшота, а переключатель скрыт.</t>
+          <t>Экран планшета крупно, на ~60% правой половины: это наезд по целому биллборду, ракурс экрана как на фото. Поверх экрана лежит отдельная плоскость, выпрямленная по перспективе. Если снимки заказчика есть, на ней настоящий снимок ×50, а скролл ведёт переключатель ×50 / ×200 (сегменты b2.label1 и b2.label2 под экраном; микровзаимодействие из EN-раскадровки блока 2). К середине секции снимок плавно увеличивается и сменяется настоящим ×200 того же участка. Пока снимков нет (вопрос 1), экран остаётся с логотипом и притушен. Перед ним крупная типографика ×50 → ×200 из тех же b2.label1 и b2.label2, причём это слой страницы, а не изображение прибора: цифры растут от скролла и передают увеличение без выдуманного снимка. Синяя капля — активный сегмент переключателя и узкое свечение рамки экрана. b2.label3 и b2.label4 идут чипами в тексте слева.</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Планшет поворачивается вокруг вертикальной оси на ~25° к тексту, то есть к «пациенту»; снимок ×200 остаётся на экране. Позади планшета проявляется скруглённый фото-кадр, щуп опускается ниже.</t>
+          <t>Камера немного отъезжает, дым светлеет, глубина резкости возвращается. Если фото-кадр есть, позади системы проявляется скруглённый фото-кадр; если нет, экран остаётся крупным для варианта «зеркало».</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -8962,7 +8961,7 @@
       <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>Экран планшета во всю ширину. Переключатель ×50 / ×200 стоит двухсегментным контролом под заголовком и работает и от скролла, и от касания. Чипы 2×2.</t>
+          <t>Экран планшета во всю ширину. Переключатель ×50 / ×200 стоит двухсегментным контролом под заголовком и работает и от скролла, и от касания. Без снимков вместо них та же крупная типографика. Чипы идут в строку.</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -8992,12 +8991,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Позади 3D-планшета стоит фото-кадр, по аналогии с утверждённым кадром с лицом у MASK: специалист держит щуп у пробора пациента, оба смотрят на экран. 3D-планшет стоит впереди, повёрнут к зрителю, на экране тот же снимок ×200. Вокруг экрана по одной появляются четыре золотые выноски-итога b3.label1–4. Дым светлеет, глубина резкости возвращается — после дымки экрана 2 наступает ясность. Запасной вариант без людей — «зеркало»: планшет разворачивается экраном прямо к зрителю, и зритель оказывается на месте пациента.</t>
+          <t>Вариант с фото: позади целого пакшота стоит фото-кадр, по аналогии с утверждённым кадром лица у MASK. Специалист держит щуп у пробора пациента, оба смотрят на экран. Экран в фото-кадре развёрнут от камеры или показывает только логотип с пакшота. Настоящий ×200 стоит только на экране 3D-пакшота впереди. Вариант без людей, «зеркало»: камера держит экран прибора крупно, и зритель оказывается на месте пациента. Вокруг экрана по одной появляются четыре золотые выноски-итога b3.label1–4. После дымки экрана 2 наступает ясность: дым светлый, всё в фокусе. Пока снимков нет, на экране логотип.</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Всё отступает в глубину и уменьшается до ~60%, фото-кадр гаснет. Планшет, щуп и база выстраиваются в ряд в глубине и освобождают место трём шагам.</t>
+          <t>Камера отъезжает: система уменьшается до ~60% и уходит в глубину правой половины, фото-кадр гаснет и освобождает место трём шагам.</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -9039,7 +9038,7 @@
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>Фото-кадр 4:5 во всю ширину, планшет поверх его нижнего угла. Выноски стоят чипами под текстом. В варианте «зеркало» во всю ширину только экран планшета.</t>
+          <t>Фото-кадр 4:5 во всю ширину, пакшот поверх его нижнего угла. Выноски стоят чипами 2×2 под текстом. В варианте «зеркало» во всю ширину только экран.</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -9064,17 +9063,17 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Сканирование · объяснение · отслеживание над отступившей системой</t>
+          <t>Сканирование · объяснение · отслеживание</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Над отступившей системой стоят три шага b4.label1–3. По мере скролла каждый подсвечивает свой объект. Шаг 1: щуп делает короткую дугу вниз, «к коже», с шампань-контровым бликом. Шаг 2: экран загорается снимком ×200. Шаг 3: экран делится пополам — тот же участок в начале и в конце курса (настоящая пара), разделитель двигается скроллом, подпись cat.stats[3][0]. Под каждым шагом мелко идёт его описание: cat.steps[0][1], cat.steps[1][1], cat.steps[2][1]. Внизу строка b4.label4 и три маленьких биллборда-пакшота EXOSIGNAL HAIR, EXOSIGNAL SPRAY и MITOPEN, каждый ведёт на свою страницу. Их упаковки остаются своего цвета, но окружение страницы не меняют. Кнопка цены здесь — контурная (ghost).</t>
+          <t>Над отступившей системой стоят три шага b4.label1–3 и одна фраза b4.line. Строк каталога cat.steps нет: b4.line говорит то же самое, а каталожные строки принесли бы X50 рядом с ×50. По мере скролла каждый шаг подсвечивает свою часть по маске на целом пакшоте. Шаг 1 — щуп, шампань-контровой блик. Шаг 2 — экран загорается снимком ×200 или логотипом. Шаг 3 — экран. Если есть настоящая пара «до / после», на шаге 3 экран делится пополам, разделитель двигается скроллом, подпись cat.stats[3][0]. Без пары сплита нет. Внизу строка b4.label4 — только текст, без ссылок и пакшотов, чтобы на ступени «убеждён» посетитель не уходил на другие страницы до цены. Кнопка цены b4.cta здесь контурная (ghost).</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Шаги складываются, система выходит в центр и раскрывается в разнесённый вид: планшет уходит назад, щуп вправо, база вперёд, кабель натягивается между ними.</t>
+          <t>Шаги складываются, камера отъезжает к целой системе в центре правой половины, вокруг неё проступают золотые волосяные линии будущих выносок.</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -9124,7 +9123,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>Три шага идут стопкой, у каждого свой маленький кадр объекта; «до / после» — слайдер касанием. Строка «работает с» — горизонтальная прокрутка из трёх пакшотов.</t>
+          <t>Три шага идут стопкой, у каждого маленький кадр с подсвеченной частью. «До / после», если пара есть, — слайдер касанием. b4.label4 — строка текста.</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -9149,17 +9148,17 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Разнесённый вид — одна система</t>
+          <t>Одна система — четыре факта</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Три части показаны врозь. Планшет с экраном-логотипом стоит в глубине, щуп справа повёрнут передней панелью. Серебряная база впереди (токарная модель) покачивается на ±30° вокруг своей оси, и хромовый шильдик 'Mitoscan' проходит перед камерой. Полный оборот — только после фото тыльной стороны. Метки-характеристики стоят на золотых волосяных выносках: b5.label1 и b5.label2 указывают на щуп (это камера, «המצלמה» в b0.cta), b5.label3 и b5.label4 — на экран. Подписей с названиями частей нет, пока заказчик не подтвердит состав. Капля — только синее свечение экрана.</t>
+          <t>Целый пакшот, поворот за указателем ±8°. Разнесённого вида нет, пока нет фото щупа и планшета по отдельности (вопрос 2): вырезанный щуп или цилиндр оставит дыры в планшете и подставке. Золотые волосяные выноски стоят прямо на целом пакшоте. b5.label1 ×50, b5.label2 ×200 и b5.label3 «הדמיית HD» указывают на щуп: это камера («המצלמה» в b0.cta), и HD в источниках относится к съёмке (cat.ingredients[1], cat.lead), а не к дисплею. b5.label4 «מעקב לפני / אחרי» указывает на экран. Цилиндр без выноски и без подписи, по маске чуть приглушён, потому что его назначение не подтверждено (вопрос 3). Шампань-блик проходит по щупу, не по цилиндру. Подписей с названиями частей нет до ответа на вопрос 4. Синяя капля — только свечение экрана.</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Части сходятся обратно в композицию пакшота: щуп входит в держатель с коротким шампань-бликом «щелчка», база встаёт спереди, кабель сворачивается. Камера возвращается к ракурсу 3/4 и уводит систему в правую половину.</t>
+          <t>Выноски сворачиваются, система смещается в правую половину, дым стихает, камера возвращается к ракурсу экрана 1.</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
@@ -9201,7 +9200,7 @@
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>Разнесённый вид вертикальный: планшет сверху, щуп посередине, база снизу. Выноски заменены чипами 2×2 под 3D.</t>
+          <t>Пакшот во всю ширину. Выноски заменены чипами 2×2 под ним.</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -9231,7 +9230,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Справа собранная система в композиции пакшота медленно поворачивается за указателем. Дым тише, синяя капля — только экран. Слева заголовок и фраза. Под ними блок «что внутри» с заголовком cat.s04[1]: 1× MITOSCAN — cat.kit[0], ниже характеристики cat.ingredients. Бейджи: линейка «מכשור» (home.sl-2) и назначение «מקצועי» (home.tg). Метки b6.label1–4, первой стоит «לשימוש מקצועי בלבד» (b6.label1). Одна главная кнопка — b4.cta (золотая кнопка цены). Под ней строка контактов как на утверждённой странице MASK: WhatsApp (текст по шаблону wa_text_product с именем MITOSCAN), телефон, e-mail. Вторую кнопку «שאלו על הדרכה» из b6.cta не ставим: тему обучения ведут метка b6.label2 и WhatsApp.</t>
+          <t>Справа собранная система (целый пакшот) медленно поворачивается за указателем. Дым тише, синяя капля — только экран. Слева заголовок b6.title и фраза b6.line, которая начинается с «לשימוש מקצועי בלבד»: это и есть обязательная пометка. Блок «что внутри»: заголовок cat.s04[1] и одна строка cat.kit[0] (1× · MITOSCAN · מערכת מתקדמת לאבחון הקרקפת והשיער.) рядом с рендером системы. Ниже отдельная подгруппа с заголовком cat.s03[1] и одной строкой характеристик b5.label1–4 (×50 · ×200 · הדמיית HD · מעקב לפני / אחרי). Каталожные cat.ingredients не выводим: под «מה כלול» они читались бы как предметы комплекта и принесли бы X50. Бейджи: «מכשור» (home.sl-2) и «מקצועי» (home.tg). Метки три, b6.label2–4. b6.label1 убран, потому что та же мысль уже стоит в b6.line и в бейдже. Одна главная кнопка — b4.cta, золотая. Под ней строка контактов как на MASK: WhatsApp с текстом запроса цены (ui.wa_text_price с MITOSCAN, см. new_strings), телефон, e-mail. Вторую кнопку «שאלו על הדרכה» из b6.cta не ставим: тему обучения ведут метка b6.label2 и WhatsApp. После экрана 7, как на MASK, идут общий блок S8 «Кто делает процедуру» (Figma 118:2, фильтр קרקפת, данные специалистов только в Figma) и ряд связок под заголовком «משלימים את הטיפול» (related_more_h шаблона MASK): EXOSIGNAL HAIR, EXOSIGNAL SPRAY, MITOPEN, каждый ведёт на свою страницу. Карточки связок открывают WhatsApp по wa_text_product, как на MASK.</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
@@ -9252,7 +9251,7 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>לשימוש מקצועי בלבד · הדרכה · תוכניות לטיפול בנשירה · מעקב לאחר השתלת שיער</t>
+          <t>הדרכה · תוכניות לטיפול בנשירה · מעקב לאחר השתלת שיער</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr">
@@ -9272,7 +9271,7 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Professional use only · Training · Hair-loss programmes · Hair transplant follow-up</t>
+          <t>Training · Hair-loss programmes · Hair transplant follow-up</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -9282,12 +9281,12 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>Сверху текст и блок «что внутри», под ними система во всю ширину. Главная кнопка во всю ширину, контакты в ряд иконками. Липкая нижняя панель с кнопкой цены остаётся.</t>
+          <t>Сверху текст и блок «что внутри», под ними система во всю ширину. Главная кнопка во всю ширину, контакты в ряд иконками. Липкая нижняя панель с кнопкой цены остаётся. Ниже идут M8 со специалистами по образцу MASK и ряд связок с горизонтальной прокруткой.</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>nav[6] | b6.title | b6.line | b6.label1,b6.label2,b6.label3,b6.label4 | b4.cta</t>
+          <t>nav[6] | b6.title | b6.line | b6.label2,b6.label3,b6.label4 | b4.cta</t>
         </is>
       </c>
     </row>
@@ -9397,12 +9396,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Дальний слой: база #0a0a0b, медленный тёплый дым #c9a24b и золотая пыль; весь слой доворачивается за курсором (±6°). Ближний слой справа: настоящие упаковки пятью группами на пологой дуге, уходящей вглубь; порядок по дуге — порядок экранов 2–6. Ближе всех V-TECH FACE (золотой картон V-TECH SYSTEM, бирюзовая коробка EXOCELL MASK, золотой куб и шар EXOTECH GEL), затем PEELING (квадратная золотая коробка EXO-NAD), BIOSPICULE (четыре узкие кремовые коробки), DEVICES (MITOPEN стоя, MITOSCAN), HAIR (чёрные коробки EXOSIGNAL HAIR и SPRAY). Под каждой группой золотая волосяная линия и подпись линейки (те же ключи, что в доке экранов 2–6). Цвета линеек здесь не включаются. Дуга медленно дрейфует (≈2°/с), курсор её чуть разворачивает. Наведение или тап на упаковку выдвигает её вперёд на ~8% и показывает название и описание из карточек главной (home.card…); клик ведёт на страницу средства. Слева: кикер, заголовок, лид, две кнопки, внизу ряд из четырёх цифр.</t>
+          <t>Дальний слой: база #0a0a0b, медленный графитовый дым и редкая кремовая пыль (не больше 8%); весь слой доворачивается за курсором (±6°). Ближний слой справа: настоящие упаковки пятью группами на пологой дуге, уходящей вглубь; порядок по дуге — порядок экранов 2–6. Ближе всех V-TECH FACE: золотой картон V-TECH SYSTEM, бирюзовая коробка EXOCELL MASK, золотой куб и шар EXOTECH GEL. Затем PEELING — квадратная золотая коробка EXO-NAD. Затем BIOSPICULE — три узкие кремовые коробки (MICRO BOOST 10%, CELL RENEW 1.5%, CELLULAR AGE DEFENSE 2.5%) и более широкая DERMA RECOVERY CREAM. Затем DEVICES — MITOPEN и MITOSCAN. Последней HAIR — плоская чёрная коробка EXOSIGNAL HAIR и маленькая коробка SPRAY в глубине. Под каждой группой золотая волосяная линия и подпись линейки (те же ключи, что в доке экранов 2–6). Цвета линеек здесь не включаются. Дуга медленно дрейфует (≈2°/с), курсор её чуть разворачивает. Наведение или тап на упаковку выдвигает её вперёд на ~8% и показывает название, описание и бейдж назначения. Для V-TECH, EXO-NAD, MASK, MITOPEN, MITOSCAN, CELL RENEW, CELLULAR AGE DEFENSE и DERMA это пары home.card… (card · card-4, card-2 · card-5, card-3 · card-6, card-8 · card-11, card-9 · card-12, card-15 · card-18, card-16 · card-20, card-17 · card-19). Для EXOTECH GEL, EXOSIGNAL HAIR, EXOSIGNAL SPRAY и MICRO BOOST 10% — slug:cat.name · slug:cat.tagline. Бейдж — home.tg (заливка) или catalog.chips[6] (контур). Клик ведёт на страницу средства. Слева кикер, заголовок, лид, две кнопки, внизу ряд из трёх цифр.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Дуга поворачивается, группа V-TECH FACE выезжает вперёд и укрупняется, остальные четыре уходят в дым и размываются по глубине; пыль собирается в блики на золотой фольге. Слева сначала гаснет ряд цифр, затем меняется заголовок.</t>
+          <t>Дуга поворачивается, группа V-TECH FACE выезжает вперёд и укрупняется, остальные четыре уходят в дым и размываются по глубине. Графитовый дым теплеет до золотого, кремовая пыль желтеет и собирается в блики на золотой фольге. Слева сначала гаснет ряд цифр, затем меняется заголовок.</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
@@ -9422,12 +9421,12 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>IL · נוסדה בישראל · IT · KR · מעבדות שותפות · מעל 100 · מדינות שבהן משווקת VM · 4 · עקרונות ליבה</t>
+          <t>IL · נוסדה בישראל · IT · KR · מעבדות שותפות · מעל 100 · מדינות שבהן משווקת VM</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>צרו קשר · מוצרים מקצועיים · ⏳ перевод на иврит и две проверки идут</t>
+          <t>צרו קשר · מוצרים מקצועיים · מקצועי · הכל · ⏳ перевод на иврит и две проверки идут</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -9442,22 +9441,22 @@
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>IL · Founded in Israel · IT · KR · Laboratory partners · 100+ · Countries where VM is used · 4 · Core principles</t>
+          <t>IL · Founded in Israel · IT · KR · Laboratory partners · 100+ · Countries where VM is used</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Contact us · Professional products · Scroll</t>
+          <t>Contact us · Professional products · מקצועי · All · Scroll</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>Сцена сверху (~55% высоты), текст ниже. Дуга превращается в горизонтальную ленту из пяти групп, которую листают пальцем; в каждой группе на телефоне 1–2 главные упаковки (V-TECH SYSTEM, EXO-NAD, CELL RENEW, MITOPEN, EXOSIGNAL HAIR), остальные открываются по тапу. Цифры — сетка 2×2. Дым — статичная текстура, частиц вдвое меньше; вместо курсора гироскоп, если разрешён. При prefers-reduced-motion и без JS — статичный ключевой кадр каждого экрана. Нижний док — 7 точек, подпись видна только у активного пункта.</t>
+          <t>Сцена сверху (~55% высоты), текст ниже. Дуга превращается в горизонтальную ленту из пяти групп, которую листают пальцем. В каждой группе на телефоне 1–2 главные упаковки (V-TECH SYSTEM, EXO-NAD, CELL RENEW, MITOPEN, EXOSIGNAL HAIR), остальные открываются по тапу. Цифры — ряд из трёх. Дым — статичная текстура, частиц вдвое меньше; вместо курсора гироскоп, если разрешён. При prefers-reduced-motion и без JS — статичный ключевой кадр каждого экрана. Нижний док — 7 точек, подпись видна только у активного пункта.</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>home.eb | home.where-science-meets-beauty | home.lead | home.s / home.s-5,home.s-2 / home.s-6,home.s-3 / home.s-7,home.s-4 / home.s-8 | home.b1 (основная, золотая заливка → экран 7) · home.b2 (контур → прокрутка к экрану 2) · new:home.scroll над доком</t>
+          <t>home.eb | home.where-science-meets-beauty | home.lead | home.s / home.s-5,home.s-2 / home.s-6,home.s-3 / home.s-7 | home.b1 (основная, золотая заливка) сразу запускает то же действие, что кнопка экрана 7 (WhatsApp + форма), без прокрутки · home.b2 (контур) ведёт на страницу каталога (цель home.nav-2); фильтра «מקצועי» в каталоге нет, поэтому каталог открывается на catalog.chips[0] (см. вопрос) · new:home.scroll над доком — единственная подсказка прокрутки к экрану 2</t>
         </is>
       </c>
     </row>
@@ -9482,12 +9481,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Окружение чёрно-золотое: дым плотнее и теплее, в зеркальной фольге V-TECH SYSTEM отражается дым (env-map). Три средства стоят справа налево по маршруту заголовка: клиника → финиш → дом. 1) Картон V-TECH SYSTEM разворачивается фасадом со знаком V; рядом поднимаются одна янтарная виала и золотое саше гель-маски — это лишь намёк на набор, полный сюжет остаётся на его странице. 2) Коробка EXOCELL MASK выдвигается вторым планом, под ней узкое бирюзовое свечение-капля #6fb7ba; окружение остаётся чёрно-золотым. 3) Из-за золотого куба EXOTECH GEL выкатывается шар-банка и останавливается, по шву пробегает блик. Каждая метка-карточка привязана к своей упаковке. Бейдж «מקצועי» (заливка) — у V-TECH и MASK, золотой контур домашнего ухода — у GEL.</t>
+          <t>Окружение чёрно-золотое: впервые на странице тёплый золотой дым и золотая пыль, в зеркальной фольге V-TECH SYSTEM отражается дым (env-map). Под волосяной линией группы — бейдж линейки new:home.line.vtech-face: золотая точка и название. Три средства стоят справа налево по маршруту заголовка: клиника → финиш → дом. 1) Картон V-TECH SYSTEM разворачивается фасадом со знаком V; рядом поднимаются одна янтарная виала и золотое саше гель-маски. Это только намёк на набор, полный сюжет остаётся на странице V-TECH. 2) Коробка EXOCELL MASK выдвигается вторым планом, под ней узкое бирюзовое свечение-капля #6fb7ba; окружение остаётся чёрно-золотым. 3) Из-за золотого куба EXOTECH GEL выкатывается шар-банка и останавливается, по шву пробегает блик. Каждая метка-карточка привязана к своей упаковке. Бейдж «מקצועי» (заливка) — у V-TECH и MASK, золотой контур домашнего ухода — у GEL.</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Виала и саше уходят за картон, группа V-TECH FACE отъезжает влево-назад и тает. В зоне перехода дым меняет тон с золота на шампань #d8c48a; по дуге из глубины выезжает квадратная коробка EXO-NAD, по её грани проходит блик.</t>
+          <t>Виала и саше уходят за картон, группа V-TECH FACE отъезжает влево-назад и тает. В зоне перехода дым меняет тон с золота на шампань #d8c48a. По дуге из глубины выезжает квадратная коробка EXO-NAD, по её грани проходит блик.</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -9507,7 +9506,7 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>V-TECH SYSTEM · ערכה מקצועית מבוססת אקסוזומים סינתטיים להתחדשות עורית ברמת הדרמיס. · מקצועי · EXOCELL MASK · מסכת ביו-צלולוז עם אקסוזומים – השלב המסכם של הטיפול. · מקצועי · EXOTECH GEL · טיפול ביתי משלים לשיקום, לחות והתחדשות העור · ⚠ нет ключа: catalog.chips[6]</t>
+          <t>V-TECH SYSTEM · ערכה מקצועית מבוססת אקסוזומים סינתטיים להתחדשות עורית ברמת הדרמיס. · מקצועי · EXOCELL MASK · מסכת ביו-צלולוז עם אקסוזומים – השלב המסכם של הטיפול. · מקצועי · EXOTECH GEL · טיפול ביתי משלים לשיקום, לחות והתחדשות העור · טיפוח ביתי</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr">
@@ -9527,7 +9526,7 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>V-TECH SYSTEM · Professional synthetic-exosome kit for dermal regeneration. · PRO · EXOCELL MASK · Bio-cellulose exosome mask — the post-treatment finish. · PRO · EXOTECH GEL · Cellular recovery &amp; advanced skin renewal · ⚠ нет ключа: catalog.chips[6]</t>
+          <t>V-TECH SYSTEM · Professional synthetic-exosome kit for dermal regeneration. · PRO · EXOCELL MASK · Bio-cellulose exosome mask — the post-treatment finish. · PRO · EXOTECH GEL · Cellular recovery &amp; advanced skin renewal · Home care</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
@@ -9567,17 +9566,17 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Окружение шампань-золотое #d8c48a: светлый дым по чёрному, в дальнем слое медленно оседают мелкие золотые хлопья, как в жидкости флакона. Коробка EXO-NAD поворачивается фасадом. Крышка — верхняя часть до линии у дна — приподнимается; внутри нейтральная тёмная пустота без печати. Из коробки лесенкой, по стадиям, поднимаются: прозрачный квадратный флакон Biphasic Peel с золотой крышкой (хлопья внутри мерцают), янтарная виала PH NORMALIZER и сине-бирюзовая виала LONGEVITY SERUM. За каждой виалой встают ещё четыре копии (инстансы), потому что в наборе их по пять. Каждый предмет становится на ступень у своей метки. Наведение на коробку показывает описание из home.card-5, клик ведёт на страницу EXO-NAD.</t>
+          <t>Окружение шампань-золотое #d8c48a: светлый дым по чёрному, в дальнем слое медленно оседают мелкие золотые хлопья, как в жидкости флакона. Под волосяной линией — бейдж линейки catalog.chips[2] цвета шампань. Коробка EXO-NAD остаётся закрытой и поворачивается фасадом. Перед ней, как на настоящем пакшоте, стоят по одному предмету в порядке стадий: прозрачный квадратный флакон Biphasic Peel с золотой крышкой (хлопья внутри мерцают), янтарная виала PH NORMALIZER и сине-бирюзовая виала LONGEVITY SERUM. Когда загорается метка, её предмет выходит на полшага вперёд. Копий виал нет: количество (1 × 15, 5 × 5, 5 × 5 מ״ל) дают метки. Коробка не открывается — открытие остаётся странице EXO-NAD. Наведение на коробку показывает home.card-5, клик ведёт на страницу EXO-NAD.</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Флаконы опускаются в коробку, крышка закрывается, EXO-NAD уходит назад. Шампань-дым темнеет и переходит в зелёный #1E4634 → #12382A, хлопья вытягиваются в тонкие светлые иглы-спикулы, из глубины выходит ряд из четырёх кремовых коробок.</t>
+          <t>Флакон и две виалы отступают за коробку, EXO-NAD уходит назад. Шампань-дым темнеет и переходит в зелёный #1E4634 → #12382A, хлопья вытягиваются в тонкие светлые иглы-спикулы. Из глубины выходит ряд: три узкие кремовые коробки и более широкая DERMA RECOVERY CREAM.</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>⚠ нет ключа: catalog.chips[2]</t>
+          <t>פילינג</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
@@ -9622,7 +9621,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>Коробка и три флакона в один ряд, без лесенки и без пятёрок-инстансов. Метки набора — столбиком под сценой.</t>
+          <t>Коробка и три предмета в один ряд, без шага вперёд. Метки набора — столбиком под сценой.</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -9647,27 +9646,27 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Биоспикулы: клиника, дом, восстановление</t>
+          <t>Биоспикулы: четвёртое поколение</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Окружение зелёное: дым #1E4634 / #12382A, в дальнем слое медленно поворачивается золотая монограмма M (билборд) и дрейфуют тонкие светлые иглы-спикулы. Четыре узкие кремовые коробки стоят по маршруту строки: MICRO BOOST 10% (клиника) чуть впереди → CELL RENEW 1.5% → CELLULAR AGE DEFENSE 2.5% (между ними золотая волосяная стрелка шага 1.5% → 2.5%) → DERMA RECOVERY CREAM на подложке шалфея #9AA889. Пока читается строка, коробки по очереди делают шаг вперёд и доворачиваются на ~20°, показывая медальон со спикулами. Под CELL RENEW — узкое зелёное свечение-капля #4fb285. Бейдж «מקצועי» (заливка) только у MICRO BOOST 10%, у трёх домашних средств золотой контур. На главной показываются только коробки, без шприца, флакона и банки.</t>
+          <t>Окружение зелёное: дым #1E4634 / #12382A, в дальнем слое медленно поворачивается золотая монограмма M (билборд) и дрейфуют тонкие светлые иглы-спикулы. Под волосяной линией — бейдж линейки catalog.chips[5]. Четыре коробки стоят по маршруту строки. MICRO BOOST 10% (клиника) — чуть впереди. Затем CELL RENEW 1.5% и CELLULAR AGE DEFENSE 2.5%, между ними золотая волосяная стрелка шага 1.5% → 2.5%. Последней — DERMA RECOVERY CREAM: коробка шире (пропорции фото 688×945), стоит на подложке шалфея #9AA889. Пока читается строка, коробки по очереди делают шаг вперёд и доворачиваются фасадом к зрителю (~20°). У трёх узких виден медальон со спикулами, у DERMA — завиток крема и SNAIL COLLAGEN. Иглы-частицы к DERMA не подлетают: в креме 0% спикул. Под CELL RENEW — узкое зелёное свечение-капля #4fb285. Бейдж «מקצועי» (заливка) только у MICRO BOOST 10%, у трёх домашних средств золотой контур. На главной показываются только коробки, без шприца, флакона и банки.</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Коробки биоспикул опускаются и уходят назад, зелёный дым гаснет до чёрного и светлеет в холодный шампань-металл #d8c48a / серебро #d9d4cc. Иглы-спикулы сходятся в одну вертикальную линию, она становится корпусом MITOPEN, а справа из глубины выезжает MITOSCAN.</t>
+          <t>Коробки опускаются и уходят назад. Зелёный дым гаснет до чёрного и светлеет в холодный шампань-металл #d8c48a / серебро #d9d4cc. Иглы-спикулы сходятся в одну наклонную линию по оси пакшота MITOPEN, на её месте проявляется билборд MITOPEN, а справа из глубины выезжает MITOSCAN.</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>⚠ нет ключа: catalog.chips[5]</t>
+          <t>ביו-ספיקולות</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>קליניקה, בית, שיקום</t>
+          <t>ביו-מיקרונידלינג, הדור הרביעי</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
@@ -9677,7 +9676,7 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>MICRO BOOST 10% · הסרום המקצועי והמרוכז ביותר בסדרת BIOSPICULE™ · מקצועי · CELL RENEW 1.5% · סרום ספיקולות לחידוש והבהרה. · ⚠ нет ключа: catalog.chips[6] · CELLULAR AGE DEFENSE 2.5% · סרום ספיקולות עם בקוצ׳יול וחמישה פפטידים. · ⚠ нет ключа: catalog.chips[6] · DERMA RECOVERY CREAM · קרם SNAIL COLLAGEN לתמיכה במחסום העור, לאחר כל פרוטוקול. · ⚠ нет ключа: catalog.chips[6]</t>
+          <t>MICRO BOOST 10% · הסרום המקצועי והמרוכז ביותר בסדרת BIOSPICULE™ · מקצועי · CELL RENEW 1.5% · סרום ספיקולות לחידוש והבהרה. · טיפוח ביתי · CELLULAR AGE DEFENSE 2.5% · סרום ספיקולות עם בקוצ׳יול וחמישה פפטידים. · טיפוח ביתי · DERMA RECOVERY CREAM · קרם SNAIL COLLAGEN לתמיכה במחסום העור, לאחר כל פרוטוקול. · טיפוח ביתי</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr">
@@ -9687,7 +9686,7 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>Clinic, home, recovery</t>
+          <t>Bio-microneedling, fourth generation</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -9697,7 +9696,7 @@
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>MICRO BOOST 10% · The most concentrated serum in the BIOSPICULE™ range · PRO · CELL RENEW 1.5% · Spicule serum for renewal and brightening. · ⚠ нет ключа: catalog.chips[6] · CELLULAR AGE DEFENSE 2.5% · Spicule serum with Bakuchiol and five peptides. · ⚠ нет ключа: catalog.chips[6] · DERMA RECOVERY CREAM · Snail-collagen barrier cream after every protocol. · ⚠ нет ключа: catalog.chips[6]</t>
+          <t>MICRO BOOST 10% · The most concentrated serum in the BIOSPICULE™ range · PRO · CELL RENEW 1.5% · Spicule serum for renewal and brightening. · Home care · CELLULAR AGE DEFENSE 2.5% · Spicule serum with Bakuchiol and five peptides. · Home care · DERMA RECOVERY CREAM · Snail-collagen barrier cream after every protocol. · Home care</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
@@ -9707,12 +9706,12 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>Четыре коробки в одну линию, мельче; шаг вперёд делает только коробка, чья метка в фокусе ленты. Монограмма M — статичный фон, игл-частиц втрое меньше.</t>
+          <t>Четыре коробки в одну линию, мельче, DERMA так же шире остальных. Шаг вперёд делает только коробка, чья метка в фокусе ленты. Монограмма M — статичный фон, игл-частиц втрое меньше.</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
         <is>
-          <t>catalog.chips[5] | biospicule:b4.title | biospicule:b4.line | micro-boost-10:cat.name · micro-boost-10:cat.tagline · бейдж home.tg,home.card-15 · home.card-18 · бейдж catalog.chips[6],home.card-16 · home.card-20 · бейдж catalog.chips[6] (описание CELLULAR AGE — card-20, в Figma оно ниже, y=3172),home.card-17 · home.card-19 · бейдж catalog.chips[6] (описание DERMA — card-19) | home.card-7 на каждой из четырёх коробок → страница средства</t>
+          <t>catalog.chips[5] | biospicule:b0.title | biospicule:b4.line | micro-boost-10:cat.name · micro-boost-10:cat.tagline · бейдж home.tg,home.card-15 · home.card-18 · бейдж catalog.chips[6],home.card-16 · home.card-20 · бейдж catalog.chips[6] (описание CELLULAR AGE — card-20, в Figma оно ниже, y=3172),home.card-17 · home.card-19 · бейдж catalog.chips[6] (описание DERMA — card-19) | home.card-7 на каждой из четырёх коробок → страница средства</t>
         </is>
       </c>
     </row>
@@ -9737,12 +9736,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Окружение шампань-серебряное: холодный светлый дым, тонкие металлические блики, мягкий верхний свет. Порядок как в заголовке: сначала диагностика, потом доставка. MITOSCAN — билборд из прозрачного пакшота (планшет на подставке, ручной сканер с витым кабелем, серебряная база), стоит дальше справа; по экрану планшета проходит мягкий свет, под ним узкое синее свечение-капля #5aa9e6. MITOPEN — билборд, стоит ближе и наклоняется к зрителю на ~30°; на кончике картриджа загорается тонкий шампань-блик. MITOTECH CELL BOOSTER в 3D не показывается, потому что фото нет: только метка-карточка с бейджами «חדש · בקרוב», без силуэта и без печати.</t>
+          <t>Окружение шампань-серебряное: холодный светлый дым, тонкие металлические блики, мягкий верхний свет. Под волосяной линией — бейдж линейки home.sl-2. Порядок как в заголовке и строке: сначала диагностика, потом доставка. MITOSCAN — билборд из прозрачного пакшота (планшет на подставке, ручной сканер с витым кабелем, серебряная база). Он стоит дальше справа; по экрану планшета проходит мягкий свет, под ним узкое синее свечение-капля #5aa9e6. MITOPEN — билборд, стоит ближе. Он выдвигается к зрителю и поворачивается только в плоскости экрана (не больше ±15°), без наклона вглубь, чтобы плоская карточка не выдала себя. На кончике картриджа загорается тонкий шампань-блик. MITOTECH CELL BOOSTER в 3D не показывается, потому что фото нет: только метка-карточка, без силуэта и без печати.</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN и MITOPEN уменьшаются и отъезжают к правому краю — на следующем экране они остаются шагами 1 и 2. Металлический дым темнеет до чёрного с золотом, из глубины поднимаются матовая чёрная плоская коробка EXOSIGNAL HAIR и высокая чёрная коробка SPRAY.</t>
+          <t>MITOSCAN и MITOPEN уменьшаются и отъезжают к правому краю — на следующем экране они остаются шагами 1 и 2. Металлический дым темнеет до чёрного с тёплым золотом. Из глубины крупно поднимается матовая чёрная плоская коробка EXOSIGNAL HAIR, а коробка SPRAY остаётся маленькой в глубине.</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -9757,17 +9756,17 @@
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>מסלול החדירה לרכיבים הפעילים.</t>
+          <t>MITOSCAN · אבחון שיער וקרקפת בהגדלה X50 ו-X200. · MITOPEN · עט מיקרונידלינג אלחוטי, 0.25–2.5 מ״מ.</t>
         </is>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>MITOSCAN · אבחון שיער וקרקפת בהגדלה X50 ו-X200. · מכשיר · MITOPEN · עט מיקרונידלינג אלחוטי, 0.25–2.5 מ״מ. · מכשיר · MITOTECH CELL BOOSTER · בוסטר תאי בשני בקבוקונים לפרוטוקולים בקליניקה בשילוב עם MITOPEN או MICRO BOOST 10%. · חדש · בקרוב</t>
+          <t>MITOSCAN · מקצועי · מכשיר · MITOPEN · מקצועי · מכשיר · MITOTECH CELL BOOSTER · בוסטר תאי בשני בקבוקונים לפרוטוקולים בקליניקה בשילוב עם MITOPEN או MICRO BOOST 10%. · מקצועי · חדש · בקרוב</t>
         </is>
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>לפרטי המוצר ←</t>
+          <t>לפרטי המוצר ← · עדכנו אותי ← · сообщить о выходе</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -9777,27 +9776,27 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>The pathway for active ingredients.</t>
+          <t>MITOSCAN · ×50 / ×200 scalp &amp; hair diagnostics. · MITOPEN · Cordless microneedling pen, 0.25–2.5 mm.</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN · ×50 / ×200 scalp &amp; hair diagnostics. · DEVICE · MITOPEN · Cordless microneedling pen, 0.25–2.5 mm. · DEVICE · MITOTECH CELL BOOSTER · Two-vial cell booster for in-clinic protocols with MITOPEN or MICRO BOOST 10%. · NEW · Coming soon</t>
+          <t>MITOSCAN · PRO · DEVICE · MITOPEN · PRO · DEVICE · MITOTECH CELL BOOSTER · Two-vial cell booster for in-clinic protocols with MITOPEN or MICRO BOOST 10%. · PRO · NEW · Coming soon</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>View product →</t>
+          <t>View product → · Notify me → · сообщить о выходе</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN над MITOPEN, без наклона. Карточка MITOTECH CELL BOOSTER — последней в ленте меток.</t>
+          <t>MITOSCAN над MITOPEN, MITOPEN без поворота. Карточка MITOTECH CELL BOOSTER — последней в ленте меток.</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
         <is>
-          <t>home.sl-2 | home.h2-2 | mitopen:b0.title | home.card-9 · home.card-12 · бейдж home.tg-2,home.card-8 · home.card-11 · бейдж home.tg-2,home.card-10 · home.card-13 · бейджи home.tg-3 + home.sd-2 | home.card-7 на MITOSCAN и MITOPEN → их страницы · home.card-14 на MITOTECH CELL BOOSTER → форма «сообщить о выходе»</t>
+          <t>home.sl-2 | home.h2-2 | home.card-9 + « – » + home.card-12 + « » + home.card-8 + « – » + home.card-11 (склейка проверенных строк, MITOSCAN первым, ≈95 знаков) | home.card-9 · бейджи home.tg + home.tg-2,home.card-8 · бейджи home.tg + home.tg-2,home.card-10 · home.card-13 · бейджи home.tg + home.tg-3 + home.sd-2 | home.card-7 на MITOSCAN и MITOPEN → их страницы · home.card-14 на MITOTECH CELL BOOSTER → форма «сообщить о выходе»</t>
         </is>
       </c>
     </row>
@@ -9822,17 +9821,17 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Окружение чёрно-золотое: дым ниже и плотнее, золотая пыль. Справа плоская чёрная коробка EXOSIGNAL HAIR; крышка сдвигается, внутри нейтральная тёмная пустота, и пять прозрачных ампул с белым кольцом поднимаются веером. Метки маршрута по очереди подсвечивают предметы: 1 — у края вспыхивает маленький MITOSCAN с прошлого экрана; 2 — наклоняется маленький MITOPEN; 3 — одна ампула выходит вперёд; «בבית» — флакон EXOSIGNAL SPRAY (матовое стекло, рифлёная золотая крышка) выпускает тонкое облачко тумана из частиц, рядом стоит его коробка. Подписи у упаковок: exosignal-hair:cat.name · exosignal-hair:cat.tagline · home.tg и exosignal-spray:cat.name · exosignal-spray:cat.tagline · catalog.chips[6].</t>
+          <t>Окружение чёрно-золотое: золотой дым ниже и плотнее, золотая пыль. Под волосяной линией — бейдж линейки catalog.chips[4]. Справа плоская чёрная коробка EXOSIGNAL HAIR, закрытая, фасадом к зрителю. Метки маршрута по очереди подсвечивают предметы. 1 — у края вспыхивает маленький MITOSCAN с прошлого экрана. 2 — маленький MITOPEN поворачивается в плоскости экрана. 3 — перед коробкой встаёт ровно одна прозрачная ампула с белым кольцом, как на пакшоте и в метке «אמפולה אחת». «בבית» — подсвечивается маленькая коробка EXOSIGNAL SPRAY в глубине. Флакон SPRAY и облачко тумана из частиц включаются только после студийного пакшота флакона. Бейдж «מקצועי» (заливка) стоит на метке 3, золотой контур домашнего ухода — на метке «בבית». Отдельных подписей у упаковок нет: названия напечатаны на коробках и есть в строке.</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Ампулы возвращаются в коробку, MITOSCAN и MITOPEN — в свою группу. Все пять групп снова выстраиваются дугой, теперь ниже, ближе и мельче, как общая полка; дым возвращается к базе бренда.</t>
+          <t>Ампула отступает за коробку, MITOSCAN и MITOPEN возвращаются в свою группу. Все пять групп снова выстраиваются дугой, теперь ниже, ближе и мельче, как общая полка. Золотой дым остывает до графитового дыма базы бренда.</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>⚠ нет ключа: catalog.chips[4]</t>
+          <t>שיער</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
@@ -9847,7 +9846,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>1 · אבחון · MITOSCAN · 2 · מיקרונידלינג · MITOPEN · 3 · החדרה · אמפולה אחת · בבית · EXOSIGNAL SPRAY</t>
+          <t>1 · אבחון · MITOSCAN · 2 · מיקרונידלינג · MITOPEN · 3 · החדרה · אמפולה אחת · מקצועי · בבית · EXOSIGNAL SPRAY · טיפוח ביתי</t>
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr">
@@ -9867,7 +9866,7 @@
       </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
-          <t>1 · Diagnose · MITOSCAN · 2 · Microneedle · MITOPEN · 3 · Apply · one ampoule · Home · EXOSIGNAL SPRAY</t>
+          <t>1 · Diagnose · MITOSCAN · 2 · Microneedle · MITOPEN · 3 · Apply · one ampoule · PRO · Home · EXOSIGNAL SPRAY · Home care</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
@@ -9877,12 +9876,12 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>Веер из трёх ампул вместо пяти. MITOSCAN и MITOPEN — маленькие билборды-иконки у меток 1 и 2. Туман спрея — около 30 частиц.</t>
+          <t>Одна ампула, как на десктопе. MITOSCAN и MITOPEN — маленькие билборды-иконки у меток 1 и 2. Коробка SPRAY — маленький билборд у метки «בבית»; после пакшота — флакон и туман, около 30 частиц.</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
         <is>
-          <t>catalog.chips[4] | exosignal-hair:b4.title | exosignal-hair:b4.line | exosignal-hair:b4.label1,exosignal-hair:b4.label2,exosignal-hair:b4.label3,exosignal-hair:b4.label4 | home.card-7 на коробке EXOSIGNAL HAIR и на флаконе SPRAY → страницы средств</t>
+          <t>catalog.chips[4] | exosignal-hair:b4.title | exosignal-hair:b4.line | exosignal-hair:b4.label1,exosignal-hair:b4.label2,exosignal-hair:b4.label3 · бейдж home.tg,exosignal-hair:b4.label4 · бейдж catalog.chips[6] | home.card-7 на коробке EXOSIGNAL HAIR и на коробке SPRAY (после пакшота — на флаконе) → страницы средств</t>
         </is>
       </c>
     </row>
@@ -9897,17 +9896,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Контакт · пункт дока: home.nav-5</t>
+          <t>Покупка · пункт дока: home.nav-5</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Вся полка и одна кнопка</t>
+          <t>Вся полка, состав и одна кнопка</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Окружение — база бренда: чёрный #0a0a0b, тёплый золотой дым, цвета линеек выключены. Справа вся линейка на одной полке-дуге: пять групп, уменьшенных и отодвинутых назад, чтобы не спорить с кнопкой; под группами подписи линеек. У профессиональных средств бейдж «מקצועי» (заливка), у края полки строка v-tech-system:b6.label4 («לשימוש מקצועי בלבד»); у домашних — золотой контур. Наведение или тап на упаковку показывает, что в ней (количество и объём из блока inside), клик ведёт на страницу средства. Слева: кикер, заголовок, строка, три принципа работы и строка об импортёре, одна золотая кнопка, под ней WhatsApp, телефон и e-mail; ниже подвал home.footer-2.</t>
+          <t>Окружение — нейтральная база бренда: чёрный #0a0a0b, графитовый дым, редкая кремовая пыль. Цвета линеек выключены, золото только в линиях и кнопке. Справа вся линейка на одной полке-дуге: пять групп, уменьшенных и отодвинутых назад, чтобы не спорить с кнопкой; под каждой группой волосяная линия и бейдж линейки. Под полкой — «что внутри»: аккордеон из пяти линеек. У каждой линейки всегда видны названия её средств (home.card… или slug:cat.name) и бейдж назначения. Одна линейка раскрыта по умолчанию (V-TECH FACE) и показывает состав каждого средства — количество × объём из блока inside. Наведение или тап на группу на полке или на заголовок линейки раскрывает её. Тап на название или упаковку ведёт на страницу средства (home.card-7). Рядом с бейджами — легенда: «מקצועי» (заливка) с пояснением v-tech-system:b6.label4 и «טיפוח ביתי» (контур). Так «только для профессионалов» относится только к средствам с заливкой. Слева: кикер, заголовок, строка, строка об импортёре, одна золотая кнопка цены, под ней WhatsApp, телефон и e-mail; ниже подвал home.footer-2. Принципов работы (home.st…) здесь нет — они на странице About, блок b4.</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
@@ -9928,12 +9927,12 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>ידע · מיטודרם נוסדה מתוך היכרות עמוקה עם ביולוגיית העור ועם הצרכים הקליניים האמיתיים. · פרוטוקולים · פרוטוקולי טיפול מדויקים והבנה ברורה של מנגנוני הפעולה. · הדרכה · הדרכות מקצועיות וידע מדעי לצד הפצת המוצרים. · היבואנית הבלעדית של VM בישראל</t>
+          <t>היבואנית הבלעדית של VM בישראל · מקצועי · לשימוש מקצועי בלבד · טיפוח ביתי</t>
         </is>
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>צרו קשר</t>
+          <t>לקבלת פרטים על מחירים · ⏳ перевод на иврит и две проверки идут · טלפון · דוא״ל · צרו קשר · צרו קשר</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -9948,22 +9947,22 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Knowledge · Founded on in-depth knowledge of skin biology and real clinical needs. · Protocols · Precise treatment protocols and a clear understanding of mechanisms of action. · Training · Professional training and scientific education alongside distribution. · Exclusive VM importer, Israel</t>
+          <t>Exclusive VM importer, Israel · PRO · Professional use only · Home care</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Contact us</t>
+          <t>Contact for price · WhatsApp · Phone · Email · Contact us · צרו קשר</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>Полка свёрнута в тонкую золотую линию с пятью подписями линеек. Вместо дока — липкая нижняя панель с кнопкой home.b1, контакты одной строкой значков. Описания принципов (home.st-4…6) скрыты, остаются только их заголовки.</t>
+          <t>Полка — тонкая золотая линия с пятью бейджами линеек над аккордеоном того же состава. Тап на линейку раскрывает названия и количество × объём, тап на средство ведёт на его страницу. Вместо дока — липкая нижняя панель с кнопкой v-tech-system:b6.label1, контакты одной строкой значков.</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
         <is>
-          <t>home.sl-4 | home.cta | home.cta-2 | home.st · home.st-4,home.st-2 · home.st-5,home.st-3 · home.st-6,v-tech-system:b6.label3 | home.b1 — одна основная кнопка (золотая заливка; WhatsApp + форма) · под ней new:home.contact.whatsapp, exocell-mask:b6.cta#3 (טלפון), exocell-mask:b6.cta#4 (דוא״ל)</t>
+          <t>home.sl-4 | home.cta | home.cta-2 | v-tech-system:b6.label3,home.tg + « — » + v-tech-system:b6.label4 (легенда бейджа с заливкой),catalog.chips[6] (легенда контурного бейджа) | v-tech-system:b6.label1 — одна основная кнопка (= exocell-mask:b6.cta#1; золотая заливка; WhatsApp + форма) · под ней new:home.contact.whatsapp, exocell-mask:b6.cta#3 (טלפון), exocell-mask:b6.cta#4 (דוא״ל) · home.b1 «צרו קשר» остаётся в доке (home.nav-5) и на герое</t>
         </is>
       </c>
     </row>
@@ -10073,12 +10072,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Дальний слой: чёрный #0a0a0b, медленный тёплый золотой дым #c9a24b и редкие частицы. Весь слой поворачивается за курсором (±6°). Ближний слой справа: пять представителей линеек стоят пологой дугой на тонкой золотой линии — коробки V-TECH SYSTEM, EXO-NAD, EXOSIGNAL HAIR, MICRO BOOST 10% (кубоиды) и MITOPEN (билборд), все в ракурсе 3/4. Сами объекты неподвижны, за курсором доворачивается только вся дуга (±8°). Других анимаций нет. Текст слева (RTL): кикер, заголовок, лид, три метки назначения (מקצועי — золотая заливка, טיפול ביתי — золотой контур, מכשור) и кнопка. Нижний док — 7 точек этой страницы с подписями home.nav-2 · home.nav · catalog.line.vtech-face/catalog.line.hair · catalog.line.peeling · cat[biospicule].name · home.sl-2 · home.nav-5.</t>
+          <t>Дальний слой: чёрный #0a0a0b, медленный тёплый золотой дым #c9a24b и редкие частицы; весь слой поворачивается за курсором на ±6°. Ближний слой справа: пять представителей линеек стоят пологой дугой на тонкой золотой линии. Это коробки V-TECH SYSTEM, EXO-NAD, EXOSIGNAL HAIR и MICRO BOOST 10% (кубоиды) и MITOPEN (билборд). Боковины коробок неизвестны, поэтому кубоиды стоят почти фасадом (не больше 12°), а MITOPEN — строго фронтально. Объекты неподвижны. За курсором доворачивается только вся дуга (±6°), так что боковина никогда не открывается больше чем на 18°. Других анимаций нет. Текст слева (RTL): кикер, заголовок, лид и два бейджа назначения — home.tg (золотая заливка) и catalog.chips[6] (золотой контур). «מכשור» как назначение не показываем: о приборах говорит лид. Одна главная кнопка — кнопка цены, как на страницах средств (WhatsApp и форма). Нижний док: 7 точек с подписями home.nav-2 · home.nav · home:home.line.vtech-face + catalog.chips[4] · catalog.chips[2] · catalog.chips[5] · home.sl-2 · home.nav-5. На экранах 3–6 подписи дока совпадают со словами чипов.</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Дуга выпрямляется в ряд и опускается к низу экрана. Снизу поднимаются ещё два объекта — коробка EXOCELL MASK и сфера EXOTECH GEL. Все семь встают полкой над семью чипами категорий, текст героя уходит вверх.</t>
+          <t>Дуга выпрямляется в ряд и опускается к низу экрана. Снизу поднимаются ещё два объекта — коробка EXOCELL MASK и сфера EXOTECH GEL. Все семь встают полкой над чипами категорий, текст героя уходит вверх.</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -10088,7 +10087,7 @@
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>מוצרים</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
@@ -10098,17 +10097,17 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>מקצועי · טיפול ביתי · מכשור</t>
+          <t>מקצועי · טיפוח ביתי</t>
         </is>
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>צרו קשר</t>
+          <t>לקבלת פרטים על מחירים</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>Our products</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
@@ -10118,22 +10117,22 @@
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>PROFESSIONAL · HOME CARE · DEVICES</t>
+          <t>PRO · Home care</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Contact us</t>
+          <t>Contact for price</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>Текст сверху по правому краю. Под ним горизонтальная лента из пяти объектов: видно три, остальные выглядывают, лента листается пальцем. Поворот за курсором выключен, дым медленнее. Кнопка на всю ширину, док — 7 точек без подписей.</t>
+          <t>Текст сверху, по правому краю. Под ним горизонтальная лента из пяти объектов: видно три, остальные выглядывают, лента листается пальцем. Поворот за курсором выключен, дым медленнее. Кнопка цены на всю ширину. Дока на телефоне нет: с экрана 2 по экран 6 внизу висит липкая панель с той же кнопкой, как на страницах средств.</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
         <is>
-          <t>home.nav-2 | catalog.hero.title | home.lead | home.sl,home.sl-3,home.sl-2 | home.b1</t>
+          <t>home.nav-2 | home.nav | home.lead | home.tg,catalog.chips[6] | sb[v-tech-system].b6.label1</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10157,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Над каждым чипом стоит его объект: Exosomes — коробка V-TECH SYSTEM, Peels — EXO-NAD, Masks — EXOCELL MASK, Hair — EXOSIGNAL HAIR, Bio-Spicules — MICRO BOOST 10%, Home care — сфера EXOTECH GEL, Devices — MITOPEN. Чип «הכל» стоит первым справа и объекта не имеет. При наведении или фокусе на чип его объект поворачивается из 3/4 фасадом к зрителю (450 мс) и приподнимается, а дальний дым за 600 мс перетекает в цвет линейки этой категории. По клику фильтр действует на экраны 3–6: лишние карточки схлопываются, экран линейки без совпадений сворачивается целиком, страница плавно едет к первому совпадению. Полка уходит, чипы прилипают текстовой строкой под шапкой до конца экрана 6. Одновременно поворачивается не больше одного объекта. Кнопки нет — действие делают чипы.</t>
+          <t>Над каждым чипом стоит его объект: Exosomes — коробка V-TECH SYSTEM, Peels — EXO-NAD, Masks — EXOCELL MASK, Hair — EXOSIGNAL HAIR, Bio-Spicules — MICRO BOOST 10%, Home care — сфера EXOTECH GEL, Devices — MITOPEN. Чип «All» стоит первым справа и объекта не имеет. При наведении или фокусе объект поворачивается из позы покоя к фасаду, не дальше (450 мс), и приподнимается. MITOPEN и другие билборды не вращаются, а наклоняются на ±10° с бликом. Одновременно движется не больше одного объекта. Дым за 600 мс перетекает в цвет линейки категории. Чип выбирает все средства своей категории, а не одно значение поля filter. Exosomes — 6 средств из cat[synthetic-exosomes].ingredients: V-TECH SYSTEM, EXO-NAD, EXOCELL MASK, EXOSIGNAL HAIR, EXOTECH GEL, EXOSIGNAL SPRAY. Peels — EXO-NAD. Masks — EXOCELL MASK. Hair — EXOSIGNAL HAIR и EXOSIGNAL SPRAY. Bio-Spicules — 4 средства линейки BIOSPICULE: MICRO BOOST 10%, CELL RENEW 1.5%, CELLULAR AGE DEFENSE 2.5%, DERMA RECOVERY CREAM. Home care — 5 домашних средств по design-rules: EXOTECH GEL, EXOSIGNAL SPRAY, CELL RENEW 1.5%, CELLULAR AGE DEFENSE 2.5%, DERMA RECOVERY CREAM. Devices — MITOPEN и MITOSCAN. MITOTECH CELL BOOSTER до ответа на вопрос 2 виден только в «All». В листе Catalog колонку [filter] нужно сделать списком чипов. По клику лишние карточки на экранах 3–6 схлопываются, экран без совпадений сворачивается целиком, и страница плавно едет к первому совпадению. Полка уходит, чипы прилипают строкой под шапкой до конца экрана 6. Кнопки на экране нет — действие делают чипы.</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -10166,24 +10165,16 @@
           <t>Объекты полки растворяются, кроме коробки V-TECH SYSTEM: она перелетает в большую карточку экрана 3 и становится её объектом. За сеткой разгорается тёплое золотое свечение линейки V-TECH FACE.</t>
         </is>
       </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>מוצרים</t>
-        </is>
-      </c>
+      <c r="G107" s="3" t="inlineStr"/>
       <c r="H107" s="3" t="inlineStr">
         <is>
           <t>⏳ перевод на иврит и две проверки идут</t>
         </is>
       </c>
-      <c r="I107" s="3" t="inlineStr">
-        <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
-        </is>
-      </c>
+      <c r="I107" s="3" t="inlineStr"/>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>הכל · אקסוזומים · פילינג · מסכות · שיער · ביו-ספיקולות · טיפוח ביתי · מכשור</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr"/>
@@ -10192,11 +10183,7 @@
           <t>Choose a category</t>
         </is>
       </c>
-      <c r="M107" s="2" t="inlineStr">
-        <is>
-          <t>Each line has its own colour.</t>
-        </is>
-      </c>
+      <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
           <t>All · Exosomes · Peels · Masks · Hair · Bio-Spicules · Home care · Devices</t>
@@ -10205,12 +10192,12 @@
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>Полки нет. Чипы идут горизонтальной строкой, листаются справа налево и прилипают под шапкой. Выбор чипа меняет цвет дыма и прокручивает страницу к первому совпадению.</t>
+          <t>Полки нет. Чипы идут горизонтальной строкой, листаются справа налево и прилипают под шапкой. Выбор чипа меняет цвет дыма и прокручивает страницу к первому совпадению. Внизу липкая панель с кнопкой цены.</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">home.nav | catalog.filters.title | catalog.filters.line | catalog.chips | </t>
+          <t xml:space="preserve"> | catalog.filters.title |  | catalog.chips | </t>
         </is>
       </c>
     </row>
@@ -10235,7 +10222,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Оттенок серии — тёплое золото V-TECH FACE на чёрном, у подзаголовка бейдж линейки. В сетке большая карточка V-TECH SYSTEM (2×2): золотая коробка, перед ней пять флаконов и саше гель-маски, как на пакшоте. Со скроллом группа доворачивается на 0→20° — это единственное движение без наведения. Рядом EXOCELL MASK (коробка, под ней узкое бирюзовое свечение-капля) и EXOTECH GEL (кубическая коробка и сфера). Под подзаголовком HAIR: EXOSIGNAL HAIR (плоская чёрная коробка) и EXOSIGNAL SPRAY (коробка и флакон, пока плоский билборд). При наведении объект карточки поворачивается из 3/4 к фасаду и ещё на 15° дальше (450 мс), карточка поднимается на 6 px, под ней загорается золотое свечение. Когда курсор уходит, объект возвращается. В карточке: бейдж назначения, бейдж линейки, название, строка и ссылка; на PRO-карточках при наведении появляется «לשימוש מקצועי בלבד». Техника: один WebGL-холст на страницу, карточки — его окна, рендер идёт только при движении. При prefers-reduced-motion — статичные пакшоты без дыма, без JS — обычная сетка с картинками.</t>
+          <t>Оттенок серии — тёплое золото V-TECH FACE на чёрном. Подзаголовки групп — home:home.line.vtech-face и catalog.chips[4]; они же служат бейджами линейки на карточках. Большая карточка V-TECH SYSTEM (2×2): золотая коробка, перед ней пять флаконов (lathe), справа веером пять саше гель-маски — пять билбордов одной текстуры с пакшота, всегда лицом к камере. Так 3D совпадает с составом 5 + 5. Со скроллом группа доворачивается на 0→12°; это единственное движение без наведения. Рядом EXOCELL MASK (коробка в 3/4: её левая боковина известна; под ней узкая бирюзовая капля) и EXOTECH GEL (кубическая коробка в 3/4 и сфера). Группа HAIR: EXOSIGNAL HAIR (плоская чёрная коробка, почти фасадом) и EXOSIGNAL SPRAY (коробка-кубоид и флакон-lathe по фото заказчика). При наведении объект поворачивается из позы покоя к фасаду, не дальше (450 мс), карточка поднимается на 6 px, под ней загорается золотое свечение. Когда курсор уходит, объект возвращается. В карточке: бейдж назначения (home.tg или catalog.chips[6]), бейдж линейки, название, строка, строка состава (ключи из inside) и ссылка home.card-7. На PRO-карточках (V-TECH SYSTEM, EXOCELL MASK, EXOSIGNAL HAIR) под бейджем «מקצועי» всегда стоит мелкая строка sb[v-tech-system].b6.label4, на любой ширине экрана; наведение управляет только 3D. Техника: один WebGL-холст на страницу, карточки — его окна, рендер идёт только при движении. При prefers-reduced-motion — статичные пакшоты без дыма, без JS — обычная сетка с картинками.</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -10245,14 +10232,14 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
+          <t>⏳ перевод на иврит и две проверки идут · שיער</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
           <t>אקסוזומים סינתטיים</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>מערכת נשא מתוכננת – לא ממקור חי</t>
-        </is>
-      </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
           <t>מערכות נשא מתוכננות בהשראת בועיות טבעיות: הן משלבות בתוכן רכיבים פעילים נבחרים ומובילות אותם אל העור.</t>
@@ -10260,7 +10247,7 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут · V-TECH SYSTEM · ערכה מקצועית מבוססת אקסוזומים סינתטיים להתחדשות עורית ברמת הדרמיס. · EXOCELL MASK · מסכת ביו-צלולוז עם אקסוזומים – השלב המסכם של הטיפול. · EXOTECH GEL · טיפול ביתי משלים לשיקום, לחות והתחדשות העור · ⏳ перевод на иврит и две проверки идут · EXOSIGNAL HAIR · מערכת אקסוזומים סינתטיים מקצועית לטיפולי הקרקפת · EXOSIGNAL SPRAY · ספריי ביתי מתקדם לטיפוח הקרקפת ולתמיכה בשיער · מקצועי · טיפול ביתי · לשימוש מקצועי בלבד</t>
+          <t>V-TECH SYSTEM · ערכה מקצועית מבוססת אקסוזומים סינתטיים להתחדשות עורית ברמת הדרמיס. · 5× · סרום · 5× · מסכת ג׳ל · 5 מ״ל · לאמפולה · EXOCELL MASK · מסכת ביו-צלולוז עם אקסוזומים – השלב המסכם של הטיפול. · 5× · מסכות · EXOTECH GEL · טיפול ביתי משלים לשיקום, לחות והתחדשות העור · לשימוש ביתי · 30 מ״ל · EXOSIGNAL HAIR · מערכת אקסוזומים סינתטיים מקצועית לטיפולי הקרקפת · 5× · אמפולות · 5 מ״ל · לאמפולה · EXOSIGNAL SPRAY · ספריי ביתי מתקדם לטיפוח הקרקפת ולתמיכה בשיער · לשימוש ביתי · 15 מ״ל · מקצועי · טיפוח ביתי · לשימוש מקצועי בלבד</t>
         </is>
       </c>
       <c r="K108" s="3" t="inlineStr">
@@ -10270,7 +10257,7 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>Engineered delivery, not biology</t>
+          <t>Synthetic exosomes</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -10280,7 +10267,7 @@
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>V-TECH FACE · V-TECH SYSTEM · Professional synthetic-exosome kit for dermal regeneration. · EXOCELL MASK · Bio-cellulose exosome mask — the post-treatment finish. · EXOTECH GEL · Cellular recovery &amp; advanced skin renewal · HAIR · EXOSIGNAL HAIR · Professional synthetic-exosome system for the scalp · EXOSIGNAL SPRAY · Follicular support &amp; scalp maintenance · PRO · HOME CARE · Professional use only</t>
+          <t>V-TECH SYSTEM · Professional synthetic-exosome kit for dermal regeneration. · 5× · Serum · 5× · Gel Mask · 5 ml · Per ampoule · EXOCELL MASK · Bio-cellulose exosome mask — the post-treatment finish. · 5× · Masks · EXOTECH GEL · Cellular recovery &amp; advanced skin renewal · HOME CARE · 30 ML · EXOSIGNAL HAIR · Professional synthetic-exosome system for the scalp · 5× · Ampoules · 5 ml · Per ampoule · EXOSIGNAL SPRAY · Follicular support &amp; scalp maintenance · HOME USE · 15 ML · PRO · Home care · Professional use only</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
@@ -10290,12 +10277,12 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>Одна колонка. Большая карточка на всю ширину (объект 240 px), остальные идут по одной, объект слева от текста. Наведения нет: объект поворачивается один раз, когда карточка проходит середину экрана, тап по объекту повторяет поворот.</t>
+          <t>Одна колонка. Большая карточка на всю ширину (объект 240 px), остальные идут по одной, объект слева от текста. Наведения нет: объект поворачивается к фасаду один раз, когда карточка проходит середину экрана, тап повторяет поворот; билборды только наклоняются. Строка sb[v-tech-system].b6.label4 на PRO-карточках видна всегда. Чипы прилипли сверху, внизу липкая панель с кнопкой цены.</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
         <is>
-          <t>cat[synthetic-exosomes].name | sb[synthetic-exosomes].b0.title | sb[synthetic-exosomes].b0.line | catalog.line.vtech-face,home.card,home.card-4,home.card-3,home.card-6,cat[exotech-gel].name,cat[exotech-gel].tagline,catalog.line.hair,cat[exosignal-hair].name,cat[exosignal-hair].tagline,cat[exosignal-spray].name,cat[exosignal-spray].tagline,home.tg,home.sl-3,sb[v-tech-system].b6.label4 | home.card-7</t>
+          <t>home:home.line.vtech-face · catalog.chips[4] | cat[synthetic-exosomes].name | sb[synthetic-exosomes].b0.line | home.card,home.card-4,cat[v-tech-system].kit[0][0] + cat[v-tech-system].kit[0][1] + cat[v-tech-system].kit[1][0] + cat[v-tech-system].kit[1][1] + cat[v-tech-system].stats[1],home.card-3,home.card-6,cat[exocell-mask].kit[0][0] + cat[exocell-mask].kit[0][1],cat[exotech-gel].name,cat[exotech-gel].tagline,cat[exotech-gel].hero_sub,cat[exosignal-hair].name,cat[exosignal-hair].tagline,cat[exosignal-hair].kit[0][0] + cat[exosignal-hair].kit[0][1] + cat[exosignal-hair].stats[1],cat[exosignal-spray].name,cat[exosignal-spray].tagline,cat[exosignal-spray].hero_sub,home.tg,catalog.chips[6],sb[v-tech-system].b6.label4 | home.card-7</t>
         </is>
       </c>
     </row>
@@ -10320,7 +10307,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Окружение шампань-золото #d8c48a на чёрном. Одна карточка-витрина на всю ширину: квадратная золотая коробка EXO-NAD, перед ней слева квадратный флакон пилинга с золотыми хлопьями (билборд), янтарная бутылочка PH NORMALIZER и сине-бирюзовая LONGEVITY SERUM — как на пакшоте. Со скроллом композиция доворачивается на 0→15°. При наведении три ёмкости слегка расходятся веером и появляется метка «3 · שלבי טיפול», так три этапа видны без лишних слов. Когда курсор уходит, ёмкости сходятся обратно. Текст слева, бейджи PEELING и מקצועי, строка «לשימוש מקצועי בלבד».</t>
+          <t>Окружение шампань-золото #d8c48a на чёрном. Одна карточка-витрина на всю ширину: квадратная золотая коробка EXO-NAD, слева от неё, как на пакшоте, флакон пилинга с золотыми хлопьями (билборд, всегда лицом к камере), янтарная бутылочка PH NORMALIZER и сине-бирюзовая LONGEVITY SERUM (lathe). Со скроллом композиция доворачивается на 0→12°. При наведении ёмкости расходятся веером (сдвиг, а не поворот), и появляется метка cat[exo-nad].stats[0] — три этапа процедуры. Под карточкой всегда стоит строка состава из cat[exo-nad].kit (1× · 5× · 5×), чтобы три ёмкости не читались как «три флакона в коробке». Когда курсор уходит, ёмкости сходятся обратно. Текст слева. Бейджи catalog.chips[2] и home.tg, под ними постоянная строка sb[v-tech-system].b6.label4, как на всех PRO-карточках.</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -10345,7 +10332,7 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут · מקצועי · 3 · שלבי טיפול · לשימוש מקצועי בלבד</t>
+          <t>פילינג · מקצועי · לשימוש מקצועי בלבד · 3 · שלבי טיפול · 1× · Biphasic Peel · 5× · pH Normalizer · 5× · Longevity Serum</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr">
@@ -10365,7 +10352,7 @@
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>PEELING · PRO · 3 · Treatment stages · Professional use only</t>
+          <t>Peels · PRO · Professional use only · 3 · Treatment stages · 1× · Biphasic Peel · 5× · pH Normalizer · 5× · Longevity Serum</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
@@ -10375,12 +10362,12 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>Карточка на всю ширину, композиция 260 px над текстом, веер раскрывается по тапу.</t>
+          <t>Карточка на всю ширину, композиция 260 px над текстом, веер раскрывается по тапу. Строка состава и sb[v-tech-system].b6.label4 видны всегда. Внизу липкая панель с кнопкой цены.</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
         <is>
-          <t>cat[exo-nad].eyebrow | home.card-2 | home.card-5 | catalog.line.peeling,home.tg,cat[exo-nad].stats[0],sb[v-tech-system].b6.label4 | home.card-7</t>
+          <t>cat[exo-nad].eyebrow | home.card-2 | home.card-5 | catalog.chips[2],home.tg,sb[v-tech-system].b6.label4,cat[exo-nad].stats[0],cat[exo-nad].kit[0][0] + cat[exo-nad].kit[0][1] + cat[exo-nad].kit[1][0] + cat[exo-nad].kit[1][1] + cat[exo-nad].kit[2][0] + cat[exo-nad].kit[2][1] | home.card-7</t>
         </is>
       </c>
     </row>
@@ -10405,7 +10392,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Окружение линейки: зелёный #1E4634 и глубокий #12382A. Золотая монограмма M в дальнем слое медленно поворачивается за курсором вместе с дымом. Карточки идут в порядке ухода: большая MICRO BOOST 10% (высокая узкая коробка, PRO), затем CELL RENEW 1.5% (коробка, под ней капля #4fb285), CELLULAR AGE DEFENSE 2.5% (коробка) и DERMA RECOVERY CREAM (коробка, свечение шалфея #9AA889). Наведение — тот же поворот из 3/4 к фасаду. Монограмма как знак линейки появляется только на этом экране.</t>
+          <t>Окружение линейки: зелёный #1E4634 и глубокий #12382A. Золотая монограмма M в дальнем слое медленно поворачивается за курсором вместе с дымом. Как знак линейки она появляется только на этом экране. Карточки идут в порядке ухода: большая MICRO BOOST 10% (высокая узкая коробка, PRO), затем CELL RENEW 1.5% (под ней капля #4fb285), CELLULAR AGE DEFENSE 2.5% и DERMA RECOVERY CREAM (свечение шалфея #9AA889). В карточках только коробки: шприц MICRO BOOST не показываем, потому что его печать неизвестна, а баночка и флаконы показываются на страницах средств. Боковины коробок неизвестны, поэтому они стоят почти фасадом (не больше 12°), и наведение поворачивает их только к фасаду. Под строкой каждой карточки — строка состава: у MICRO BOOST 10% из cat[micro-boost-10].kit и stats[1], у домашних средств — cat[slug].hero_sub с объёмом. У MICRO BOOST 10% под бейджем «מקצועי» всегда стоит sb[v-tech-system].b6.label4, у домашних средств — бейдж catalog.chips[6].</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -10415,7 +10402,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>BIOSPICULE™</t>
+          <t>ביו-ספיקולות</t>
         </is>
       </c>
       <c r="H110" s="3" t="inlineStr">
@@ -10430,7 +10417,7 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>MICRO BOOST 10% · הסרום המקצועי והמרוכז ביותר בסדרת BIOSPICULE™ · CELL RENEW 1.5% · סרום ספיקולות לחידוש והבהרה. · CELLULAR AGE DEFENSE 2.5% · סרום ספיקולות עם בקוצ׳יול וחמישה פפטידים. · DERMA RECOVERY CREAM · קרם SNAIL COLLAGEN לתמיכה במחסום העור, לאחר כל פרוטוקול. · מקצועי · טיפול ביתי · לשימוש מקצועי בלבד</t>
+          <t>MICRO BOOST 10% · הסרום המקצועי והמרוכז ביותר בסדרת BIOSPICULE™ · 1× · מזרק · 3 מ״ל · CELL RENEW 1.5% · סרום ספיקולות לחידוש והבהרה. · סרום BIOSPICULE™ · 30 מ״ל · CELLULAR AGE DEFENSE 2.5% · סרום ספיקולות עם בקוצ׳יול וחמישה פפטידים. · סרום BIOSPICULE™ · 30 מ״ל · DERMA RECOVERY CREAM · קרם SNAIL COLLAGEN לתמיכה במחסום העור, לאחר כל פרוטוקול. · קרם משקם · 50 מ״ל · מקצועי · טיפוח ביתי · לשימוש מקצועי בלבד</t>
         </is>
       </c>
       <c r="K110" s="3" t="inlineStr">
@@ -10450,7 +10437,7 @@
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>MICRO BOOST 10% · The most concentrated serum in the BIOSPICULE™ range · CELL RENEW 1.5% · Spicule serum for renewal and brightening. · CELLULAR AGE DEFENSE 2.5% · Spicule serum with Bakuchiol and five peptides. · DERMA RECOVERY CREAM · Snail-collagen barrier cream after every protocol. · PRO · HOME CARE · Professional use only</t>
+          <t>MICRO BOOST 10% · The most concentrated serum in the BIOSPICULE™ range · 1× · Syringe · 3 ml · CELL RENEW 1.5% · Spicule serum for renewal and brightening. · BIOSPICULE™ SERUM · 30 ML · CELLULAR AGE DEFENSE 2.5% · Spicule serum with Bakuchiol and five peptides. · BIOSPICULE™ SERUM · 30 ML · DERMA RECOVERY CREAM · Snail-collagen barrier cream after every protocol. · RESTORATIVE CREAM · 50 ML · PRO · Home care · Professional use only</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
@@ -10460,12 +10447,12 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>Монограмма неподвижна за заголовком (прозрачность 30%). Карточки в одну колонку, объект поворачивается один раз при появлении.</t>
+          <t>Монограмма неподвижна за заголовком (прозрачность 30%). Карточки в одну колонку, коробка поворачивается к фасаду один раз при появлении. Строки состава и sb[v-tech-system].b6.label4 у MICRO BOOST 10% видны всегда. Внизу липкая панель с кнопкой цены.</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
         <is>
-          <t>cat[biospicule].name | sb[biospicule].b0.title | sb[biospicule].b6.line | cat[micro-boost-10].name,cat[micro-boost-10].tagline,home.card-15,home.card-18,home.card-16,home.card-20,home.card-17,home.card-19,home.tg,home.sl-3,sb[v-tech-system].b6.label4 | home.card-7</t>
+          <t>catalog.chips[5] | sb[biospicule].b0.title | sb[biospicule].b6.line | cat[micro-boost-10].name,cat[micro-boost-10].tagline,cat[micro-boost-10].kit[0][0] + cat[micro-boost-10].kit[0][1] + cat[micro-boost-10].stats[1][0],home.card-15,home.card-18,cat[cell-renew-1-5].hero_sub,home.card-16,home.card-20,cat[cellular-age-defense-2-5].hero_sub,home.card-17,home.card-19,cat[derma-recovery-cream].hero_sub,home.tg,catalog.chips[6],sb[v-tech-system].b6.label4 | home.card-7</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10477,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Окружение DEVICES: шампань-металл #d8c48a и серебро #d9d4cc, по дыму раз в несколько секунд проходит холодный блик. MITOPEN — билборд из прозрачного пакшота: у билборда нет боков, поэтому при наведении он не вращается, а наклоняется на ±10°, и по корпусу пробегает блик. MITOSCAN — билборд планшета, сканера и основания с узкой синей каплей #5aa9e6 под ним, наведение — тот же наклон. MITOTECH CELL BOOSTER — карточка без 3D: тонкий контур-заглушка, бейджи מקצועי и בקרוב, ссылка «עדכנו אותי ←».</t>
+          <t>Окружение DEVICES: шампань-металл #d8c48a и серебро #d9d4cc, по дыму раз в несколько секунд проходит холодный блик. MITOPEN — билборд из прозрачного пакшота: он не вращается, а наклоняется на ±10°, и по корпусу пробегает блик. MITOSCAN — билборд планшета, сканера и основания, под ним узкая синяя капля #5aa9e6; наведение даёт тот же наклон. Характеристики уже стоят в строках карточек: в home.card-11 — глубина иглы, в home.card-12 — увеличение ×50 и ×200. MITOTECH CELL BOOSTER — карточка без 3D: тонкий контур-заглушка, бейджи home.tg и home.sd-2, ссылка home.card-14. До ответа на вопрос 2 она видна только при чипе «All». На всех трёх PRO-карточках под бейджем «מקצועי» всегда стоит sb[v-tech-system].b6.label4.</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -10545,7 +10532,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>Карточки в колонку. Блик проходит один раз, когда карточка появляется, наклон — по тапу.</t>
+          <t>Карточки в колонку. Блик проходит один раз, когда карточка появляется, наклон — по тапу. sb[v-tech-system].b6.label4 видна всегда. Внизу липкая панель с кнопкой цены.</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -10570,12 +10557,12 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Связаться</t>
+          <t>Цена и связь</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>База бренда: чёрный с золотом, дым тише, чем на героe. Справа тот же ряд пяти представителей из экрана 1, уменьшенный, притушенный и неподвижный: страница замыкается, новых объектов нет. Слева: кикер, заголовок, фраза, одна главная золотая кнопка «צרו קשר» и ряд контактов WhatsApp · טלפון · דוא״ל, под ними строка «היבואנית הבלעדית של VM בישראל».</t>
+          <t>База бренда: чёрный с золотом, дым тише, чем на герое. Справа тот же ряд из пяти представителей с экрана 1, уменьшенный, притушенный и неподвижный: страница замыкается, новых объектов нет. Слева кикер, заголовок, фраза и одна главная золотая кнопка — кнопка цены sb[v-tech-system].b6.label1, как на страницах средств (WhatsApp и форма). Если выбран чип Home care, на её месте стоит sb[exotech-gel].b6.cta[0], как на страницах домашних средств. Под кнопкой ряд контактов: home:home.contact.whatsapp · sb[v-tech-system].b6.cta[2] · sb[v-tech-system].b6.cta[3] (индексы считаются с нуля). Ниже строка sb[v-tech-system].b6.label3. Таблицу «что внутри» здесь не повторяем: состав стоит строкой в каждой карточке на экранах 3–6.</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
@@ -10596,12 +10583,12 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>WhatsApp / התקשרו · טלפון · דוא״ל · היבואנית הבלעדית של VM בישראל</t>
+          <t>⏳ перевод на иврит и две проверки идут · טלפון · דוא״ל · היבואנית הבלעדית של VM בישראל</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>צרו קשר</t>
+          <t>לקבלת פרטים על מחירים</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -10616,22 +10603,22 @@
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp / call · Phone · Email · Exclusive VM importer, Israel</t>
+          <t>WhatsApp · Phone · Email · Exclusive VM importer, Israel</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Contact us</t>
+          <t>Contact for price</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>Всё в одну колонку: заголовок, фраза, кнопка на всю ширину, контакты иконками в ряд. Ряд объектов скрыт.</t>
+          <t>Всё в одну колонку: заголовок, фраза, кнопка цены на всю ширину (липкая панель на этом экране скрыта), контакты иконками в ряд. Ряд объектов скрыт.</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>home.sl-4 | home.cta | home.cta-2 | sb[micro-boost-10].b6.cta[1],sb[v-tech-system].b6.cta[2],sb[v-tech-system].b6.cta[3],sb[v-tech-system].b6.label3 | home.b1</t>
+          <t>home.sl-4 | home.cta | home.cta-2 | home:home.contact.whatsapp,sb[v-tech-system].b6.cta[2],sb[v-tech-system].b6.cta[3],sb[v-tech-system].b6.label3 | sb[v-tech-system].b6.label1</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11298,7 +11285,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Airless-флакон с помпой CELLULAR AGE DEFENSE 2.5% (BIOSPICULE SERUM)</t>
+          <t>CELLULAR AGE DEFENSE 2.5% — сыворотка BIOSPICULE в белом airless-флаконе с помпой, домашний уход (коробка — это картинка, а не компонент)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -11313,7 +11300,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>cat.kit[0]; cat.stats[0]; cat.ingredients[0]; packaging-text.json → airless pump bottle, нижняя строка '30ml ℮ 1.0 fl.oz.'</t>
+          <t>cat.kit[0]; cat.stats[0]; cat.ingredients[0]; airless-флакон — packaging-text.json → cellular-age-defense-2-5 и фото №9 в Figma. На пакшоте protocols/print/img/cellular-age-25.webp напечатано '30 ml ℮ 1.0 fl.oz.' с пробелом; в packaging-text.json записано '30ml' — это надо поправить там</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -11331,42 +11318,50 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CELLULAR AGE DEFENSE 2.5%</t>
+          <t>DERMA RECOVERY CREAM</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Коробка: высокая узкая, ивори, тёмно-зелёная полоса, золотая M</t>
+          <t>DERMA RECOVERY CREAM — банка 50 мл в коробке. Банка матовая белая, материал не указан, матовая крышка над чёрным пояском. Коробка цвета слоновой кости с шалфейной полосой.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1×</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>на коробке напечатано '30ml ℮ 1.0 fl.oz.' и 'ADVANCED / BIOSPICULE TECHNOLOGY'</t>
+          <t>50 ml ℮ 1.69 fl.oz. Утром и вечером на чистую кожу: b4.label3 и b4.line (HE и EN), EN cat.steps[2]. В HE cat.steps[2] только «יומיומי… על עור נקי», поэтому строку о применении брать из b4.label3. Доза на одно нанесение в источниках не указана.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>packaging-text.json → tall slim box; пакшот protocols/print/img/cellular-age-25.webp</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
+          <t>cat.kit[0]; packaging-text.json derma-recovery-cream (нижняя строка коробки и банки: '50 ml ℮ 1.69 fl.oz.')</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Panthenol – פנתנול (פרו־ויטמין B5) · Madecassoside – מצמח הסנטלה האסיאתית · Allantoin – אלנטואין · Shea Butter – חמאת שיאה · Niacinamide – ניאצינאמיד · Hydrolyzed Collagen – קולגן מפורק · Snail Secretion Filtrate – פוליסכריד מטוהר מריר החילזון</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>איפה לקנות</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>DERMA RECOVERY CREAM</t>
+          <t>MITOPEN</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>DERMA RECOVERY CREAM — банка 50 мл в коробке (матовая белая банка с прозрачной матовой крышкой над чёрным пояском; коробка цвета слоновой кости с шалфейной полосой)</t>
+          <t>MITOPEN — профессиональная беспроводная ручка для микронидлинга с регулируемыми глубиной иглы и скоростью; на пакшоте — с установленным прозрачным картриджем</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -11376,35 +11371,39 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>50 ml ℮ 1.69 fl.oz.; утром и вечером на чистую кожу (cat.steps[2], b4.label3); доза на одно нанесение в источниках не указана</t>
+          <t>Объёма и дозы нет (прибор). Глубина иглы 0.25–2.5 мм, до 5 скоростей</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>cat.kit[0]; packaging-text.json derma-recovery-cream (нижняя строка коробки и банки: '50 ml ℮ 1.69 fl.oz.')</t>
+          <t>product-pages.json kit[0] (1× MITOPEN) и ingredients[0–1]; storyboard b5.line; packaging-text.json → mitopen: в источниках только сам прибор, коробки и комплектующих нет</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Panthenol – פנתנול (פרו־ויטמין B5) · Madecassoside – מצמח הסנטלה האסיאתית · Allantoin – אלנטואין · Shea Butter – חמאת שיאה · Niacinamide – ניאצינאמיד · Hydrolyzed Collagen – קולגן מפורק · Snail Secretion Filtrate – פוליסכריד מטוהר מריר החילזון</t>
+          <t>עומק מחט מתכוונן 0.25-2.5 מ״מ · עד 5 מהירויות · אלחוטי, ארגונומי ושקט · תומך בפרוטוקולי V-TECH SYSTEM ו-EXOSIGNAL HAIR</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>איפה לקנות</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>לקבלת פרטים על מחירים</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN</t>
+          <t>MITOSCAN</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN — профессиональная беспроводная ручка для микронидлинга с регулируемой глубиной иглы и скоростью; на фото с установленным прозрачным картриджем</t>
+          <t>MITOSCAN — система диагностики волос и кожи головы</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -11414,17 +11413,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Объёма и дозы нет (прибор). Глубина иглы 0.25–2.5 мм регулируется, скоростей до 5.</t>
+          <t>×50 и ×200, HD (b5.label1–3)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>product-pages.json kit[0] (1× MITOPEN), ingredients[0–1]; storyboard b5.line; packaging-text.json → mitopen: в источниках только сам прибор, без коробки и комплектующих</t>
+          <t>cat.kit[0]; b5.line</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>עומק מחט מתכוונן 0.25-2.5 מ״מ · עד 5 מהירויות · אלחוטי, ארגונומי ושקט · תומך בפרוטוקולי V-TECH SYSTEM ו-EXOSIGNAL HAIR</t>
+          <t>×50 · ×200 · הדמיית HD · מעקב לפני / אחרי · מפרט המערכת</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -11441,32 +11440,32 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN</t>
+          <t>Home — MITODERM</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN — система диагностики волос и кожи головы</t>
+          <t>v-tech-system:b5.label1 (V-TECH SYSTEM, сыворотка)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1×</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>×50 и ×200, HD-изображение (cat.ingredients[0], cat.ingredients[1])</t>
+          <t>5 мл каждая</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>cat.kit[0]; cat.ingredients; b5.line</t>
+          <t>product-pages kit[0]; packaging-text: 5 amber vials</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>הגדלה גבוהה X50 ו-X200 · צילום באיכות HD · צפיפות שיער, מספר זקיקים, קוטר שערה ומצב הקרקפת · מעקב עקבי אחר האזור והשוואה לאורך זמן</t>
+          <t>אקסוזומים סינתטיים, פפטידים ו-PDRN, NAD⁺ ורכיבים ביומימטיים, ספיקולות BIOSPICULE™ והמכשירים MITOPEN ו-MITOSCAN.</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -11474,36 +11473,32 @@
           <t>לקבלת פרטים על מחירים</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN</t>
+          <t>Home — MITODERM</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Планшет на белой подставке, экран с логотипом (видно на пакшоте)</t>
+          <t>v-tech-system:b5.label2 (V-TECH SYSTEM, гель-маска)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>на пакшоте 1 — в каталоге не указан, ждёт подтверждения</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 мл в саше</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>packaging-text.json → mitoscan.objects[0]; protocols/assets/img/mitoscan.webp</t>
+          <t>product-pages kit[1]; packaging-text: gel mask sachet</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
@@ -11513,27 +11508,27 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN</t>
+          <t>Home — MITODERM</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Щуп-сканер со спиральным кабелем («המצלמה» в b0.cta)</t>
+          <t>exocell-mask:b5.label1 + new:home.kit.mask-net</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>на пакшоте 1 — в каталоге не указан, ждёт подтверждения</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>камера ×50 / ×200 (cat.lead, иврит: «מצלמה בהגדלה גבוהה X50 ו-X200»)</t>
+          <t>25 мл каждая (Net 5 x 25 ml ℮ 5 x 0.84 fl.oz)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>packaging-text.json → mitoscan.objects[1]; cat.lead</t>
+          <t>product-pages kit[0] (5×); объём только на коробке (packaging-text exocell-mask objects[0].front[4]), в проверенном иврите его нет, поэтому new:home.kit.mask-net</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
@@ -11543,27 +11538,27 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN</t>
+          <t>Home — MITODERM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>База — серебряный цилиндр с хромовыми торцами и шильдиком 'Mitoscan'</t>
+          <t>exotech-gel:cat.kit[0]</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>на пакшоте 1 — в каталоге не указан, ждёт подтверждения</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>— (назначение в источниках не указано)</t>
+          <t>30 мл</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>packaging-text.json → mitoscan.objects[2]</t>
+          <t>product-pages kit[0]</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
@@ -11578,34 +11573,26 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>v-tech-system:b5.label1 (V-TECH SYSTEM, сыворотка)</t>
+          <t>exo-nad:b5.label1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5 мл в ампуле</t>
+          <t>15 мл</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[0]; packaging-text: 5 amber vials</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>אקסוזומים סינתטיים, פפטידים ו-PDRN, NAD⁺ ורכיבים ביומימטיים, ספיקולות BIOSPICULE™ והמכשירים MITOPEN ו-MITOSCAN.</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>צרו קשר</t>
-        </is>
-      </c>
+          <t>product-pages kit[0]</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
@@ -11616,7 +11603,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>v-tech-system:b5.label2 (V-TECH SYSTEM, гель-маска)</t>
+          <t>exo-nad:b5.label2</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -11626,12 +11613,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>5 мл в саше</t>
+          <t>5 мл</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[1]; packaging-text: gel mask sachet</t>
+          <t>product-pages kit[1]</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr"/>
@@ -11646,7 +11633,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>exocell-mask:b5.label1</t>
+          <t>exo-nad:b5.label3</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -11656,12 +11643,12 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25 мл каждая (Net 5 x 25 ml ℮ 5 x 0.84 fl.oz)</t>
+          <t>5 мл</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[0]; packaging-text carton</t>
+          <t>product-pages kit[2]</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr"/>
@@ -11676,22 +11663,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>exotech-gel:cat.kit[0]</t>
+          <t>exosignal-hair:b5.label1 · exosignal-hair:b5.label2</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>30 мл</t>
+          <t>5 мл каждая (Net 5 x 5 ml ℮ 5 x 0.17 fl.oz.)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[0]</t>
+          <t>product-pages kit[0]; packaging-text flat box</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr"/>
@@ -11706,7 +11693,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>exo-nad:b5.label1</t>
+          <t>exosignal-spray:cat.kit[0]</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -11736,22 +11723,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>exo-nad:b5.label2</t>
+          <t>micro-boost-10:b0.label2</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5 мл</t>
+          <t>шприц 3 мл (3 ml ℮ 0.10 fl.oz.)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[1]</t>
+          <t>product-pages kit[0]; packaging-text box</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr"/>
@@ -11766,22 +11753,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>exo-nad:b5.label3</t>
+          <t>cell-renew-1-5:cat.kit[0]</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5 мл</t>
+          <t>30 ml ℮ 1.0 fl.oz.</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[2]</t>
+          <t>product-pages kit[0]; packaging-text box</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr"/>
@@ -11796,22 +11783,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>exosignal-hair:b5.label1 · exosignal-hair:b5.label2</t>
+          <t>cellular-age-defense-2-5:cat.kit[0]</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>5 мл каждая (Net 5 x 5 ml ℮ 5 x 0.17 fl.oz.)</t>
+          <t>30 ml ℮ 1.0 fl.oz.</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[0]; packaging-text flat box</t>
+          <t>product-pages kit[0]; packaging-text box</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr"/>
@@ -11826,7 +11813,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>exosignal-spray:cat.kit[0]</t>
+          <t>derma-recovery-cream:cat.kit[0]</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -11836,12 +11823,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>15 мл</t>
+          <t>50 ml ℮ 1.69 fl.oz.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[0]</t>
+          <t>product-pages kit[0]; packaging-text box</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr"/>
@@ -11856,7 +11843,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>micro-boost-10:b0.label2</t>
+          <t>mitopen:cat.kit[0]</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -11866,12 +11853,12 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>шприц 3 мл (3 ml ℮ 0.10 fl.oz.)</t>
+          <t>глубина иглы 0.25–2.5 мм, 5 скоростей (mitopen:cat.stats[0], cat.stats[1])</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[0]; packaging-text box</t>
+          <t>product-pages kit[0], stats (needle depth)</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr"/>
@@ -11886,22 +11873,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>cell-renew-1-5:cat.kit[0]</t>
+          <t>mitoscan:cat.kit[0]</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 система (планшет, ручной сканер, база)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>30 ml ℮ 1.0 fl.oz.</t>
+          <t>×50 / ×200 (mitoscan:cat.stats[0], cat.stats[1])</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[0]; packaging-text box</t>
+          <t>product-pages kit[0], stats; packaging-text objects</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr"/>
@@ -11916,22 +11903,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>cellular-age-defense-2-5:cat.kit[0]</t>
+          <t>home.card-10 · home.tg-3 + home.sd-2 (MITOTECH CELL BOOSTER, скоро)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2 флакона</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>30 ml ℮ 1.0 fl.oz.</t>
+          <t>объём неизвестен — на экране 7 без объёма, уточнить у заказчика</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[0]; packaging-text box</t>
+          <t>home.en.json card-13; лист Catalog, Card 13</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr"/>
@@ -11941,57 +11928,61 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Home — MITODERM</t>
+          <t>CATALOG</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>derma-recovery-cream:cat.kit[0]</t>
+          <t>V-TECH SYSTEM — ампулы сыворотки и саше гель-маски</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5 + 5</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>50 ml ℮ 1.69 fl.oz.</t>
+          <t>по 5 ml</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[0]; packaging-text box</t>
+          <t>cat[v-tech-system].kit; на карточке: cat[v-tech-system].kit[0][0] + cat[v-tech-system].kit[0][1] + cat[v-tech-system].kit[1][0] + cat[v-tech-system].kit[1][1] + cat[v-tech-system].stats[1]</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>לקבלת פרטים על מחירים</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Home — MITODERM</t>
+          <t>CATALOG</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>mitopen:cat.kit[0]</t>
+          <t>EXOCELL MASK — маски в саше</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>игла 0.25–2.5 мм, 5 скоростей (mitopen:cat.stats[0], cat.stats[1])</t>
+          <t>5 × 25 ml (Net 5 x 25 ml ℮ 5 x 0.84 fl.oz)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[0], stats</t>
+          <t>cat[exocell-mask].kit; packaging-text exocell-mask (коробка); на карточке: cat[exocell-mask].kit[0][0] + cat[exocell-mask].kit[0][1]</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr"/>
@@ -12001,27 +11992,27 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Home — MITODERM</t>
+          <t>CATALOG</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>mitoscan:cat.kit[0]</t>
+          <t>EXOTECH GEL — гель в сферической баночке</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>1 система (планшет, ручной сканер, база)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>×50 / ×200 (mitoscan:cat.stats[0], cat.stats[1])</t>
+          <t>30 ml</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>product-pages kit[0], stats; packaging-text objects</t>
+          <t>cat[exotech-gel].kit; на карточке: cat[exotech-gel].hero_sub</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr"/>
@@ -12031,27 +12022,27 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Home — MITODERM</t>
+          <t>CATALOG</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>home.card-10 · home.card-13 (MITOTECH CELL BOOSTER, скоро)</t>
+          <t>EXOSIGNAL HAIR — ампулы</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>2 флакона</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>объём неизвестен — уточнить у заказчика</t>
+          <t>5 × 5 ml (Net 5 x 5 ml ℮ 5 x 0.17 fl.oz.)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>home.en.json card-13; лист Catalog, Card 13</t>
+          <t>cat[exosignal-hair].kit; packaging-text exosignal-hair; на карточке: cat[exosignal-hair].kit[0][0] + cat[exosignal-hair].kit[0][1] + cat[exosignal-hair].stats[1]</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr"/>
@@ -12066,34 +12057,26 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>V-TECH SYSTEM — сыворотка в ампулах и гель-маска в саше</t>
+          <t>EXOSIGNAL SPRAY — флакон-спрей</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>5 + 5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>по 5 ml</t>
+          <t>15 ml</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>cat[v-tech-system].kit; packaging-text v-tech-system</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>פתרונות מקצועיים מבוססי אקסוזומים ו-BIOSPICULE™ לקליניקות ולאנשי מקצוע באסתטיקה – מערכות לשימוש בקליניקה, טיפול ביתי ומכשור אבחון.</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>צרו קשר</t>
-        </is>
-      </c>
+          <t>cat[exosignal-spray].kit; на карточке: cat[exosignal-spray].hero_sub</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
@@ -12104,22 +12087,22 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>EXOCELL MASK — маски в саше</t>
+          <t>EXO-NAD — Biphasic Peel, pH Normalizer, Longevity Serum</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1 + 5 + 5</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>5 × 25 ml (Net 5 x 25 ml)</t>
+          <t>15 ml; по 5 ml; по 5 ml</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>cat[exocell-mask].kit; packaging-text exocell-mask (коробка)</t>
+          <t>cat[exo-nad].kit; packaging-text exo-nad; на карточке: cat[exo-nad].kit[0][0] + cat[exo-nad].kit[0][1] + cat[exo-nad].kit[1][0] + cat[exo-nad].kit[1][1] + cat[exo-nad].kit[2][0] + cat[exo-nad].kit[2][1]</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr"/>
@@ -12134,7 +12117,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>EXOTECH GEL — гель в сферической баночке</t>
+          <t>MICRO BOOST 10% — шприц</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -12144,12 +12127,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>30 ml</t>
+          <t>3 ml ℮ 0.10 fl.oz.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>cat[exotech-gel].kit</t>
+          <t>cat[micro-boost-10].kit; packaging-text micro-boost-10; на карточке: cat[micro-boost-10].kit[0][0] + cat[micro-boost-10].kit[0][1] + cat[micro-boost-10].stats[1][0]</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr"/>
@@ -12164,22 +12147,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>EXOSIGNAL HAIR — ампулы</t>
+          <t>CELL RENEW 1.5% — сыворотка</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>5 × 5 ml (Net 5 x 5 ml)</t>
+          <t>30 ml ℮ 1.0 fl.oz.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>cat[exosignal-hair].kit; packaging-text exosignal-hair</t>
+          <t>cat[cell-renew-1-5].kit; packaging-text cell-renew-1-5; на карточке: cat[cell-renew-1-5].hero_sub</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr"/>
@@ -12194,7 +12177,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>EXOSIGNAL SPRAY — флакон-спрей</t>
+          <t>CELLULAR AGE DEFENSE 2.5% — сыворотка</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -12204,12 +12187,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>15 ml</t>
+          <t>30 ml ℮ 1.0 fl.oz.</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>cat[exosignal-spray].kit</t>
+          <t>cat[cellular-age-defense-2-5].kit; packaging-text cellular-age-defense-2-5; на карточке: cat[cellular-age-defense-2-5].hero_sub</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr"/>
@@ -12224,22 +12207,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>EXO-NAD — Biphasic Peel, pH Normalizer, Longevity Serum</t>
+          <t>DERMA RECOVERY CREAM — крем</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>1 + 5 + 5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>15 ml; по 5 ml; по 5 ml</t>
+          <t>50 ml ℮ 1.69 fl.oz.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>cat[exo-nad].kit; packaging-text exo-nad</t>
+          <t>cat[derma-recovery-cream].kit; packaging-text derma-recovery-cream; на карточке: cat[derma-recovery-cream].hero_sub</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr"/>
@@ -12254,7 +12237,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>MICRO BOOST 10% — шприц</t>
+          <t>MITOPEN — аппарат для микронидлинга</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -12264,12 +12247,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3 ml ℮ 0.10 fl.oz.</t>
+          <t>глубина иглы 0.25–2.5 mm</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>cat[micro-boost-10].kit; packaging-text micro-boost-10</t>
+          <t>cat[mitopen].kit; cat[mitopen].stats[0]; на карточке: home.card-11</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr"/>
@@ -12284,22 +12267,22 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CELL RENEW 1.5% — сыворотка</t>
+          <t>MITOSCAN — планшет, ручной сканер, основание</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 система</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>30 ml ℮ 1.0 fl.oz.</t>
+          <t>увеличение ×50 и ×200</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>cat[cell-renew-1-5].kit; packaging-text cell-renew-1-5</t>
+          <t>cat[mitoscan].kit; cat[mitoscan].stats[0], cat[mitoscan].stats[1]; packaging-text mitoscan; на карточке: home.card-12</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr"/>
@@ -12314,147 +12297,27 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>CELLULAR AGE DEFENSE 2.5% — сыворотка</t>
+          <t>MITOTECH CELL BOOSTER — флаконы</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>30 ml ℮ 1.0 fl.oz.</t>
+          <t>нет данных (нет ни пакшота, ни текста упаковки)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>cat[cellular-age-defense-2-5].kit; packaging-text cellular-age-defense-2-5</t>
+          <t>home.card-13; строки состава на карточке нет</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="3" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>DERMA RECOVERY CREAM — крем</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>50 ml ℮ 1.69 fl.oz.</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>cat[derma-recovery-cream].kit; packaging-text derma-recovery-cream</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>MITOPEN — аппарат для микронидлинга</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>глубина иглы 0.25–2.5 mm</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>cat[mitopen].kit; cat[mitopen].stats[0]</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>MITOSCAN — планшет, ручной сканер, основание</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>1 система</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>увеличение ×50 и ×200</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>cat[mitoscan].kit; cat[mitoscan].stats; packaging-text mitoscan</t>
-        </is>
-      </c>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>MITOTECH CELL BOOSTER — флаконы</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>нет данных (упаковки и текста упаковки нет)</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>home.card-13</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12467,7 +12330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E164"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14537,7 +14400,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Коробка CELLULAR AGE DEFENSE 2.5% (высокая узкая, ивори)</t>
+          <t>Коробка CELLULAR AGE DEFENSE 2.5% (высокая узкая, ивори; экраны 1–7)</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -14547,7 +14410,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Фасад — protocols/print/img/cellular-age-25.webp (308×1023, RGBA), запасной вариант site/img/cellular-age-25.png (217×720). Печать по packaging-text.json → tall slim box. Боковины и верх — гладкий ивори без печати, пока нет фото. Глубина условно равна ширине.</t>
+          <t>Фасад — protocols/print/img/cellular-age-25.webp (308×1023, RGBA), углы выпрямить; запасной вариант — site/img/cellular-age-25.png (217×720). Печать — по packaging-text.json → tall slim box. Боковины и верх неизвестны, глубина условная. Пока нет фото, поворот не больше ±20°, чтобы боковина не была видна крупно.</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -14564,7 +14427,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Airless-флакон с помпой 30 мл</t>
+          <t>Airless-флакон с помпой 30 мл (не входит в сборку по умолчанию; после ответа — экраны 4 и 7)</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -14574,7 +14437,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Рендер заказчика: печать расшифрована в packaging-text.json → airless pump bottle, но файла в репозитории нет. Строка 'CELL CELLULAR / AGE DEFENSE / 2.5%' ждёт подтверждения. Пока фото нет, экраны 4–7 собираются с одной коробкой.</t>
+          <t>Фото №9 в Figma (файл KcOGIzO76mDODxjwIrkGyo, узел 93:8095), в репозитории файла нет. Печать — по packaging-text.json → airless pump bottle, строка 'CELL CELLULAR / AGE DEFENSE / 2.5%' ждёт подтверждения. До ответа корпус крупно не показываем; на экране 4 крупно только белая головка помпы без печати.</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -14591,7 +14454,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Коробка CELL RENEW 1.5% (экраны 2 и 5)</t>
+          <t>Коробка CELL RENEW 1.5% (только экран 2; на экране 5 — 2D-карточка)</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -14601,7 +14464,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>protocols/print/img/cell-renew-15.webp (309×1012, RGBA); печать по packaging-text.json → cell-renew-1-5</t>
+          <t>protocols/print/img/cell-renew-15.webp (309×1012, RGBA); печать — по packaging-text.json → cell-renew-1-5. Поворот не больше ±20°, на подступенке золотая цифра из cat[cell-renew-1-5].stats[0][0].</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -14618,7 +14481,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Коробка DERMA RECOVERY CREAM (экраны 5 и 7)</t>
+          <t>Коробка DERMA RECOVERY CREAM (только экран 5)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -14628,7 +14491,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>protocols/print/img/derma-recovery.webp (688×945, RGBA); печать по packaging-text.json → derma-recovery-cream → box. Банку не строим: её фото в репозитории нет.</t>
+          <t>protocols/assets/img/derma-recovery.webp (642×1000, RGBA, прямой фасад, шалфейная полоса — как в packaging-text.json); обрезать по альфе 9,10–633,991. Вариант protocols/print/img/derma-recovery.webp (тёмно-зелёная полоса, лёгкая перспектива) не используем. Поворот не больше ±20°. Банку не строим.</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -14655,7 +14518,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Процедурное веретено, инстансы. Вид по site/img/spicules-macro.png, цвет — тёмно-зелёные спикулы медальона на фасаде коробки.</t>
+          <t>Процедурное веретено, инстансы. Вид — по site/img/spicules-macro.png, цвет — как тёмно-зелёные спикулы медальона на фасаде коробки.</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -14736,7 +14599,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>site/img/mitoderm-m-gold.png</t>
+          <t>site/img/mitoderm-m-gold.png — растр 566×600. Резко — не выше ~300 CSS px; крупнее — только размытой внутри слоя дыма. Для крупной резкой M нужен векторный файл заказчика.</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -14753,7 +14616,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Поверхность кожи под каплей (экран 4)</t>
+          <t>Кожа под каплей (экран 4)</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -14763,7 +14626,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>По умолчанию — процедурная тёплая изогнутая плоскость без лица. Фото-кадр (пальцы у линии челюсти) — только после ответа и снимка заказчика.</t>
+          <t>Вариант (а): кадр с человеком — пальцы у линии челюсти, одно мягкое круговое движение, по образцу утверждённого кадра MASK. Это платная генерация после «утверждаю», в публичный репозиторий кадр не идёт. Вариант (б): процедурная тёплая изогнутая поверхность без лица. Выбор за заказчиком.</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -14790,7 +14653,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Без печати: матовый тёмный камень с зеленью #12382A, золотая волосяная кромка</t>
+          <t>Матовый тёмный камень с зеленью #12382A, золотая волосяная кромка. На экране 2 на подступенках золотые цифры из cat[cell-renew-1-5].stats[0][0] и cat.stats[0][0].</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -14844,7 +14707,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/derma-recovery.webp: прямой фасад 624×981 px по альфе (пропорция ~1:1,57), актуальная шалфейная полоса. Не брать protocols/print/img/derma-recovery.webp: там старая тёмно-зелёная полоса.</t>
+          <t>protocols/assets/img/derma-recovery.webp: 642×1000, по альфе 624×981, актуальная шалфейная полоса. Не брать protocols/print/img/derma-recovery.webp: там старая тёмно-зелёная полоса.</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -14871,7 +14734,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Печать неизвестна. До фото — нейтральный картон цвета слоновой кости без надписей, поворот коробки не больше ±20°, клапан изнутри — чистый картон. Нужны фото граней и верха (закрытого и открытого) или хотя бы размеры Ш×В×Г: глубина коробки неизвестна.</t>
+          <t>Печать новой коробки неизвестна. Опора только по геометрии — protocols/print/img/derma-recovery.webp (688×945, старая версия с тёмной полосой, вид ¾): левая грань гладкая, без надписей, сверху клапан-язычок. Печать с него не брать. До фото — гладкий картон цвета слоновой кости, поворот коробки не больше ±20°, глубина условная, по пропорции старого пакшота. Нужны фото граней и верха (закрытого и открытого) или размеры Ш×В×Г.</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -14888,7 +14751,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Банка 50 мл — корпус</t>
+          <t>Банка 50 мл — корпус и фасад с этикеткой</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -14898,12 +14761,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Матовый белый пластик. Текст этикетки известен из packaging-text.json (вертикально MITODERM / BIOSPICULE SYSTEM, M, DERMA / RECOVERY / CREAM, SNAIL COLLAGEN, рамка, MADE IN KOREA, 50 ml ℮ 1.69 fl.oz.), но его вид и расположение — только с фото. Фото клиента от 10/10 в репозитории нет. До фото банка показывается открытой или сверху, этикетку не рисуем.</t>
+          <t>Фото заказчика в Figma: фото 1, файл KcOGIzO76mDODxjwIrkGyo, узел 93:8080 (site/photo-catalog.md), заливка по хешу. На фото фасад: вертикально MITODERM / BIOSPICULE SYSTEM, M, DERMA / RECOVERY / CREAM, SNAIL COLLAGEN, рамка, MADE IN KOREA, 50 ml ℮ 1.69 fl.oz. — совпадает с packaging-text.json. Текстура ложится только на фасадную половину, поворот не больше ±20°. Материал не указан, рендерим матовый белый. Разрешение заливки проверить при выгрузке.</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>needs photo</t>
+          <t>ready</t>
         </is>
       </c>
     </row>
@@ -14915,7 +14778,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Крышка банки</t>
+          <t>Банка — задняя сторона и вид сверху на закрытую крышку</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -14925,7 +14788,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Прозрачный матовый пластик над чёрным пояском (packaging-text.json). Пропорции и печать на верху крышки неизвестны — нужно фото сбоку и сверху.</t>
+          <t>Не сняты. Не показываем: поворот ограничен ±20°, камера над закрытой банкой не встаёт. Для свободного поворота нужны фото сзади, с боков и сверху на крышку.</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -14942,17 +14805,17 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Крем в банке (поверхность с завитком)</t>
+          <t>Крышка и обод открытой банки</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>procedural mesh</t>
+          <t>lathe model</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Белый крем, цвет взят с напечатанного завитка на фасаде protocols/assets/img/derma-recovery.webp; без надписей</t>
+          <t>Фото 73 (узел 113:8211, открытая банка, крышка рядом) и фото 1 (крышка над чёрным пояском, вид сбоку). В packaging-text.json крышка clear frosted, на фото 1 выглядит белой — цвет берём с фото.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -14969,22 +14832,22 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Кремовая лента и атласный слой барьера</t>
+          <t>Кадр у зеркала (экран 4)</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>procedural mesh</t>
+          <t>photo frame</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Форма — по завитку на фасаде коробки; белый с шалфейным отсветом #9AA889</t>
+          <t>Утверждённого фото нет: в коллаже site/photo-catalog.md нет нанесения DERMA. Фото с людьми — только с согласия заказчика и не в публичный репозиторий. Генерация — один образец, цена и «ок» до запуска. До этого работает запасная 3D-сцена без людей.</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>ready</t>
+          <t>needs photo</t>
         </is>
       </c>
     </row>
@@ -14996,7 +14859,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Семь жемчужин активов</t>
+          <t>Крем в банке (поверхность с завитком)</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -15006,7 +14869,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Полупрозрачные сферы цвета слоновой кости, без надписей и острых форм</t>
+          <t>Белый крем, цвет с напечатанного завитка на фасаде protocols/assets/img/derma-recovery.webp, без надписей.</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -15023,7 +14886,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Иглы-спикулы (экран 2) и сухие хлопья (экраны 2–4)</t>
+          <t>Кремовая лента и атласный слой барьера</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -15033,7 +14896,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Вид игл — по site/img/spicules-macro.png, в шалфейном тоне; хлопья — матовые, цвета слоновой кости</t>
+          <t>Форма по завитку на фасаде коробки, белый с шалфейным отсветом #9AA889.</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -15050,17 +14913,17 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Золотая монограмма M (шапка, дым экрана 5, бейдж экрана 7)</t>
+          <t>Семь жемчужин активов</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>procedural mesh</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>site/img/mitoderm-m-gold.png (566×600, прозрачный)</t>
+          <t>Полупрозрачные сферы цвета слоновой кости, без надписей и острых форм.</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -15077,17 +14940,17 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Коробка CELL RENEW 1.5% (экран 5)</t>
+          <t>Иглы-спикулы (экран 2) и сухие хлопья (экраны 2–3, переход 3→4)</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>procedural mesh</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>site/img/cell-renew-15.png (220×720, прозрачный, вид вполоборота)</t>
+          <t>Иглы по site/img/spicules-macro.png, в естественном серо-оливковом цвете (без шалфея), в отдельном дальнем плане. Хлопья матовые, цвета слоновой кости.</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -15104,7 +14967,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Коробка CELLULAR AGE DEFENSE 2.5% (экран 5)</t>
+          <t>Золотая монограмма M (шапка, кикер-бейдж, дым экрана 5)</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -15114,7 +14977,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>site/img/cellular-age-25.png (217×720, прозрачный, вид вполоборота)</t>
+          <t>site/img/mitoderm-m-gold.png (566×600, прозрачный)</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -15131,7 +14994,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Коробка MICRO BOOST 10% (экран 5)</t>
+          <t>Коробка CELL RENEW 1.5% (экран 5, домашняя ветка)</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -15141,7 +15004,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/micro-boost-10.webp (264×1000, прозрачный, анфас)</t>
+          <t>site/img/cell-renew-15.png (220×720, прозрачный). Высота условная, реальный размер неизвестен.</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -15158,17 +15021,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Дальний слой: дым и искры</t>
+          <t>Коробка CELLULAR AGE DEFENSE 2.5% (экран 5, домашняя ветка, сменяет CELL RENEW)</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>procedural mesh</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Шейдер дыма из образца MASK (site/proto/exocell-3d-template.html) в новых цветах #12382A / #1E4634 / #9AA889, искры #f6f3ec; на экране 5 — насыщенный #1E4634</t>
+          <t>site/img/cellular-age-25.png (217×720, прозрачный). Высота условная.</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -15180,22 +15043,22 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN</t>
+          <t>DERMA RECOVERY CREAM</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN целиком (экраны 1, 2, 4–7)</t>
+          <t>Коробка MICRO BOOST 10% (экран 5, клиническая ветка)</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>billboard из прозрачного пакшота, разрезанный на 3 слоя: верх корпуса с конусом и кнопкой, кольцо, носик с картриджем</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/mitopen.webp (RGBA, 297×915). Надписи только с фото: вертикальная белая MITOPEN и гравированная V у конуса. Для ретины на 80% высоты экрана разрешения мало — нужен исходник от 2500 px по высоте</t>
+          <t>protocols/assets/img/micro-boost-10.webp (264×1000, прозрачный, анфас) плюс маленький бейдж home.tg с золотой заливкой. Высота условная.</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -15207,22 +15070,22 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN</t>
+          <t>DERMA RECOVERY CREAM</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Кольцо глубины — анимация поворота</t>
+          <t>Дальний слой: дым и искры</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>billboard: слой кольца из пакшота, текстура насечек скользит внутри маски кольца</t>
+          <t>procedural mesh</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>тот же пакшот, полоса розово-золотого кольца</t>
+          <t>Шейдер дыма из образца MASK (site/proto/exocell-3d-template.html) в цветах #12382A / #1E4634 / #9AA889, искры #f6f3ec; на экране 5 насыщенный #1E4634.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -15239,22 +15102,22 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Прозрачный картридж с иглами: иглы убраны и выдвинуты (экран 3, макро)</t>
+          <t>MITOPEN целиком, обычный масштаб (экраны 1, 2, 3 без макро, 4–7)</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>billboard из двух макрофото с плавной сменой по скроллу</t>
+          <t>Билборд из прозрачного пакшота, разрезанный на 3 слоя: верх корпуса с конусом и кнопкой, кольцо рукоятки, носик с картриджем. Наклон ≈12° заложен в самом пакшоте, допускается только поворот в плоскости</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>На пакшоте картридж шириной около 70 px: число игл и их вид не читаются, рисовать нельзя. Нужен макроснимок картриджа на минимальной и максимальной глубине, на прозрачном или ровном фоне</t>
+          <t>protocols/assets/img/mitopen.webp (RGBA, 297×915; ось ≈12° от вертикали по альфа-каналу). Надписи только с фото: вертикальная белая MITOPEN и гравированная V у конуса. На экране не выше ~650 CSS px, это около 1.4× исходника на ретине; крупнее — только с исходником высокого разрешения</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>needs photo</t>
+          <t>ready</t>
         </is>
       </c>
     </row>
@@ -15266,22 +15129,22 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Фото-кадр процедуры: специалистка в перчатках ведёт MITOPEN по щеке клиентки (экран 4)</t>
+          <t>Кольцо рукоятки — блик в простое (экраны 1, 3, 7)</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>photo frame</t>
+          <t>Слой кольца из билборда, блик скользит внутри маски кольца. Поворот насечек (кольцо как регулятор) включаем только после ответа на вопрос 2</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Нужно утверждённое фото: съёмка заказчика или генерация по пакшоту, но только после образца и «утверждаю». Фото с людьми в репозиторий не кладём</t>
+          <t>Тот же пакшот, полоса розово-золотого кольца около 115×75 px</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>needs photo</t>
+          <t>ready</t>
         </is>
       </c>
     </row>
@@ -15293,22 +15156,22 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>V-TECH SYSTEM (экран 5, шаг «החדרה»)</t>
+          <t>Макро кольца и прозрачного картриджа, иглы убраны и выдвинуты (экран 3, когда будет исходник)</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>Билборд из двух макрофото с плавной сменой по скроллу</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/vtech-system.webp (RGBA, 1000×918): золотая коробка, 5 янтарных флаконов, саше гель-маски; надписи — по packaging-text.json</t>
+          <t>На пакшоте картридж около 65 px в ширину: иглы не читаются, рисовать их нельзя. Сначала проверить фото заказчика № 56 и 57 в Figma (113:8175, 113:8176, фрейм HeroArt 88:2). В коллаже это слои 59×83, скриншот MCP ограничен размером слоя, поэтому исходник нужно выгрузить по imageHash и записать его размер и ракурс. По миниатюре на 56 перо лежит почти горизонтально, на 57 стоит по диагонали с надписью. Нужно от 2500 px по высоте и макро картриджа на минимальной и максимальной глубине</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>ready</t>
+          <t>needs photo</t>
         </is>
       </c>
     </row>
@@ -15320,22 +15183,22 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>EXOSIGNAL HAIR (экран 5, шаг «החדרה»)</t>
+          <t>Фото-кадр процедуры: специалистка в перчатках ведёт MITOPEN по щеке клиентки (экран 4)</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>photo frame</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/exosignal-hair.webp (RGBA, 1000×665): чёрная коробка и 5 ампул; надписи — по packaging-text.json</t>
+          <t>Нужно утверждённое фото: съёмка заказчика или генерация по пакшоту, но только после образца и «утверждаю». В брифе указать: перо в ракурсе пакшота (3/4 спереди, кнопкой к зрителю, картридж вниз-влево, отличие только в повороте в плоскости), высота пера в процентах кадра и точка кончика на щеке в правой половине. Кожа чистая, без точек и покраснения. Фото № 25 (113:8131) не подходит: на миниатюре рука в перчатке с пипеткой, MITOPEN там нет. Фото с людьми в репозиторий не кладём</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>ready</t>
+          <t>needs photo</t>
         </is>
       </c>
     </row>
@@ -15347,17 +15210,17 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Постамент (экраны 5–7)</t>
+          <t>V-TECH SYSTEM (экран 5, шаг «החדרה», справа)</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>lathe model</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Процедурный матовый металл цвета шампань #d8c48a с серебряной кромкой #d9d4cc, без надписей</t>
+          <t>protocols/assets/img/vtech-system.webp (RGBA, 1000×918): золотая коробка, 5 янтарных флаконов, саше гель-маски; надписи по packaging-text.json</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -15374,17 +15237,17 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Шкала глубины 0.25–2.5 и циферблат скоростей 1–5 (экраны 3 и 5)</t>
+          <t>EXOSIGNAL HAIR (экран 5, шаг «החדרה», слева)</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>плоский SVG-оверлей поверх сцены, не 3D</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Только цифры из cat.ingredients / b2.label1–2, единица «מ״מ» (примечание к b2.cta)</t>
+          <t>protocols/assets/img/exosignal-hair.webp (RGBA, 1000×665): чёрная коробка и 5 прозрачных ампул; надписи по packaging-text.json</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -15401,17 +15264,17 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Плоскость кожи и сетка микроканалов (экраны 3 и 5)</t>
+          <t>Постамент (появляется в переходе 6→7, экран 7)</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>процедурные частицы на плоскости, плотность привязана к циферблату скоростей</t>
+          <t>lathe model</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Без фото: точки цвета шампань на тёмной матовой плоскости</t>
+          <t>Процедурный матовый металл цвета шампань #d8c48a с серебряной кромкой #d9d4cc, без надписей</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -15428,17 +15291,17 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Контуры зон: лицо, шея с декольте, кожа головы (экран 2)</t>
+          <t>Шкала глубины и циферблат скоростей 1–5 (экраны 3 и 5)</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>плоская линейная SVG-графика на среднем плане</t>
+          <t>Плоский SVG-оверлей поверх сцены, не 3D, в &lt;bdi dir="ltr"&gt;</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Рисуем сами тонкой линией цвета шампань, без людей и без цифр</t>
+          <t>Подписаны только крайние значения 0.25 и 2.5 из b2.label1 / cat.ingredients, единица «מ״מ» (примечание к b2.cta), деления без цифр; циферблат 1–5 по b2.label2</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -15455,17 +15318,17 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Дальний фон: дым и частицы</t>
+          <t>Абстрактная плоскость и сетка микроканалов (экраны 3 и 5)</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>процедурный шейдер, поворачивается за курсором</t>
+          <t>Процедурные частицы на плоскости, плотность привязана к циферблату скоростей</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>#0a0a0b, дым #d8c48a, частицы #d9d4cc</t>
+          <t>Без фото: точки цвета шампань на тёмной матовой плоскости. На фото кожи не накладывается</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -15482,44 +15345,44 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Объёмная модель MITOPEN для полного оборота (по желанию, экран 6)</t>
+          <t>Контуры зон: лицо, шея с декольте, кожа головы (экраны 2 и 6)</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>lathe model: профиль по силуэту пакшота, текстура лицевой стороны с фото</t>
+          <t>Плоская линейная SVG-графика на среднем плане</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Есть только вид спереди в 3/4. Заднюю сторону (кнопка, надписи) додумывать нельзя — нужны фото сбоку и сзади</t>
+          <t>Рисуем сами тонкой линией цвета шампань, без людей и цифр. Порядок справа налево — лицо, шея и декольте, кожа головы; на экране 6 только лицо и кожа головы</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>needs photo</t>
+          <t>ready</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN</t>
+          <t>MITOPEN</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Вся система одним кадром (пакшот целиком)</t>
+          <t>Дальний фон: дым и частицы</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>Процедурный шейдер, поворачивается за курсором</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/mitoscan.webp — прозрачный, 1000×685; экран 1 до разделения, мобильная версия, prefers-reduced-motion</t>
+          <t>#0a0a0b; серебряный дым #d9d4cc ведущий, прожилки шампань #d8c48a; самый яркий — на экране 7</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -15536,7 +15399,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Планшет на подставке</t>
+          <t>Вся система одним кадром (целый пакшот)</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -15546,12 +15409,12 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Вырезается из mitoscan.webp; экран — отдельная плоскость для смены снимков. Низ рамки и подставку закрывает база, правый край — щуп в держателе. Тыльную сторону не показываем (камера в пределах ±35°)</t>
+          <t>protocols/print/img/mitoscan.webp — 1145×777, RGBA, прозрачный; это исходник, по которому записан packaging-text. Веб-копия: protocols/assets/img/mitoscan.webp, 1000×685. На этом кадре держатся все экраны 1–7. Маски слоёв (щуп, экран, цилиндр, остальное) нужны для бликов и размытия без сдвига частей. Наезд камеры — не больше ~1,5×. alt: cat.name + « – » + cat.hero_sub</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>needs photo</t>
+          <t>ready</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15426,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Экран с логотипом (мишень, 'Mitoscan', 'By Mitoderm Ltd')</t>
+          <t>Плоскость экрана (логотип: мишень, 'Mitoscan', 'By Mitoderm Ltd')</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -15573,7 +15436,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Четырёхугольник экрана из mitoscan.webp, выпрямленный по перспективе</t>
+          <t>Четырёхугольник экрана из protocols/print/img/mitoscan.webp, выпрямленный по перспективе и наложенный поверх биллборда. На него ставятся снимки, если они будут</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -15600,7 +15463,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Настоящие снимки с экрана MITOSCAN от заказчика; генерировать нельзя — это была бы выдуманная работа прибора</t>
+          <t>Настоящие снимки с экрана MITOSCAN от заказчика. Генерировать нельзя: это была бы выдуманная работа прибора. Пока снимков нет — типографика ×50 → ×200 из b2.label1 и b2.label2</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -15627,7 +15490,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Настоящие снимки MITOSCAN одного участка в начале и в конце курса, с согласием пациента</t>
+          <t>Настоящие снимки MITOSCAN одного участка в начале и в конце курса, с согласием пациента. Пока пары нет, экран 5 обходится без сплита</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -15644,17 +15507,17 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Щуп-сканер</t>
+          <t>Фото-кадр экрана 4: специалист со щупом у пробора пациента</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>photo frame</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Передняя сторона из mitoscan.webp (чёрная овальная панель 'Mitoscan' / 'By Mitoderm Ltd'). Для поворота линзой к зрителю нужны фото торца с линзой и бока, иначе используем запасной ход «наклоном вниз»</t>
+          <t>Съёмка в клинике или генерация после цены и «утверждаю». В промпте экран прибора развёрнут от камеры или показывает только логотип, плюс блок PACKAGING TEXT из packaging-text.json → mitoscan.objects[0..1]. Фото с людьми в репозиторий не кладём, только в Figma</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -15671,22 +15534,22 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>База — серебряный цилиндр</t>
+          <t>Щуп отдельно (подъём из держателя, поворот линзой)</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>lathe model</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Профиль, шлифованное серебро, хромовые торцы, перфорированный диск на правом торце и хромовый шильдик 'Mitoscan' — всё из mitoscan.webp. Тыльная сторона не снята: только покачивание ±30°</t>
+          <t>Лицевая сторона вырезается из пакшота целиком, потому что щуп стоит впереди. Но если его поднять, в планшете откроется держатель, которого нет ни на одном фото. Нужны фото торца с линзой, бока и обратной стороны</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>ready</t>
+          <t>needs photo</t>
         </is>
       </c>
     </row>
@@ -15698,22 +15561,22 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Спиральный белый кабель</t>
+          <t>Планшет отдельно (для разнесённого вида)</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>needs model</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Процедурная трубка по спирали и сплайну, матовый белый, форма как на mitoscan.webp (от низа щупа к спирали на столе). Тянется за щупом</t>
+          <t>На пакшоте правую рамку и держатель закрывает щуп, низ подставки закрывает цилиндр. Нужно фото планшета без щупа, с пустым держателем и подставкой целиком</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>needs model</t>
+          <t>needs photo</t>
         </is>
       </c>
     </row>
@@ -15725,22 +15588,22 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Фото-кадр экрана 4: специалист со щупом у пробора пациента перед экраном</t>
+          <t>Серебряный цилиндр</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>photo frame</t>
+          <t>lathe model</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Съёмка в клинике или генерация после цены и «утверждаю»; фото с людьми не попадают в репозиторий</t>
+          <t>Профиль, шлифованное серебро, хромовые торцы, перфорированный диск на правом торце и шильдик 'Mitoscan' — всё из protocols/print/img/mitoscan.webp. Тыльная сторона не снята. Отдельно используется только в разнесённом виде, после вопросов 2–3</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>needs photo</t>
+          <t>ready</t>
         </is>
       </c>
     </row>
@@ -15752,44 +15615,44 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Пакшоты-связки EXOSIGNAL HAIR, EXOSIGNAL SPRAY, MITOPEN (экран 5)</t>
+          <t>Спиральный белый кабель</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>needs model</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/exosignal-hair.webp; site/img/exosignal-spray.png; protocols/assets/img/mitopen.webp</t>
+          <t>Процедурная трубка по спирали, матовая белая, форма как на пакшоте. Нужна только в разнесённом виде</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>ready</t>
+          <t>needs model</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Home — MITODERM</t>
+          <t>MITOSCAN</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>V-TECH SYSTEM — высокий картон (зеркальная золотая фольга)</t>
+          <t>Ряд связок после экрана покупки: EXOSIGNAL HAIR, MITOPEN</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>cuboid from packshot</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>protocols/print/img/vtech-system.webp (1200×1100): выпрямить фасад. Бока на фото не видны — гладкий золотой и чёрный цвет, взятый с фото, без печати; материал зеркальный с env-map</t>
+          <t>protocols/assets/img/exosignal-hair.webp (1000×665, RGBA); protocols/assets/img/mitopen.webp (297×915, RGBA)</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -15801,27 +15664,27 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Home — MITODERM</t>
+          <t>MITOSCAN</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>V-TECH SYSTEM — янтарная виала</t>
+          <t>Ряд связок после экрана покупки: EXOSIGNAL SPRAY</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>lathe model</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>вырезка одной из пяти виал с protocols/print/img/vtech-system.webp</t>
+          <t>site/img/exosignal-spray.png не годится: это непрозрачный скриншот 400×300 на светлом фоне (alpha 254–255), а в packaging-text указано «no studio packshot yet». Источник — фото заказчика из Figma, №2/3/21 (узлы 93:8081, 93:8083, 104:8121 по photo-catalog.md), с удалённым фоном, в PNG. Пока вырезки нет, вместо картинки текстовый чип «EXOSIGNAL SPRAY» со ссылкой</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>ready</t>
+          <t>needs photo</t>
         </is>
       </c>
     </row>
@@ -15833,17 +15696,17 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>V-TECH SYSTEM — золотое саше гель-маски</t>
+          <t>V-TECH SYSTEM — высокий картон (зеркальная золотая фольга)</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>cuboid from packshot</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>вырезка саше с protocols/print/img/vtech-system.webp</t>
+          <t>protocols/print/img/vtech-system.webp (1200×1100): выпрямить фасад. Правый нижний угол фасада (x≈700–790, y≈770–1060, вместе с чёрной полосой) закрыт саше: залить ровной золотой фольгой и продолжением чёрной полосы, текст не клонировать. Бока на фото не видны — гладкий золотой и чёрный цвет с фото, без печати; материал зеркальный с env-map</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -15860,17 +15723,17 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>EXOCELL MASK — бирюзовая коробка</t>
+          <t>V-TECH SYSTEM — янтарная виала</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>cuboid from packshot</t>
+          <t>lathe model</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>site/img/exocell-box-front.jpg + site/img/exocell-box-side.jpg (те же, что в утверждённом образце)</t>
+          <t>вырезка одной из двух передних виал с protocols/print/img/vtech-system.webp (задние перекрыты)</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -15887,17 +15750,17 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>EXOTECH GEL — золотой куб-коробка</t>
+          <t>V-TECH SYSTEM — золотое саше гель-маски</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>cuboid from packshot</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>protocols/print/img/exotech-gel.webp: видны фасад и левая грань с чёрной диагональю</t>
+          <t>вырезка саше с protocols/print/img/vtech-system.webp (видно целиком)</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -15914,17 +15777,17 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>EXOTECH GEL — золотая шар-банка</t>
+          <t>EXOCELL MASK — бирюзовая коробка</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>lathe model</t>
+          <t>cuboid from packshot</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>protocols/print/img/exotech-gel.webp (шар справа)</t>
+          <t>site/img/exocell-box-front.jpg + site/img/exocell-box-side.jpg (те же, что в утверждённом образце)</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -15941,7 +15804,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>EXO-NAD — квадратная золотая коробка</t>
+          <t>EXOTECH GEL — золотой куб-коробка</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -15951,7 +15814,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>protocols/print/img/exo-nad.webp: видны фасад и правая грань</t>
+          <t>protocols/print/img/exotech-gel.webp: видны фасад, левая грань с чёрной диагональю и чёрный верх</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -15968,17 +15831,17 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>EXO-NAD — квадратный флакон Biphasic Peel</t>
+          <t>EXOTECH GEL — золотая шар-банка</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>lathe model</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>вырезка с protocols/print/img/exo-nad.webp. Флакон мелкий (~80 px шириной): годится только до средней величины, для крупного плана нужно фото крупнее</t>
+          <t>protocols/print/img/exotech-gel.webp (шар справа)</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -15995,17 +15858,17 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>EXO-NAD — янтарная виала PH NORMALIZER (×5 инстансов)</t>
+          <t>EXO-NAD — квадратная золотая коробка (на главной закрыта)</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>lathe model</t>
+          <t>cuboid from packshot</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>вырезка с protocols/print/img/exo-nad.webp</t>
+          <t>protocols/print/img/exo-nad.webp: виден только фасад, градиент идёт до самого края. Боковые грани, верх и линия крышки — ровный цвет с фото, без печати</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -16022,17 +15885,17 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>EXO-NAD — сине-бирюзовая виала LONGEVITY SERUM (×5 инстансов)</t>
+          <t>EXO-NAD — квадратный флакон Biphasic Peel</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>lathe model</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>вырезка с protocols/print/img/exo-nad.webp</t>
+          <t>вырезка с protocols/print/img/exo-nad.webp. Флакон ~100 px шириной: годится до средней величины, для крупного плана нужно фото крупнее</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -16049,17 +15912,17 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>EXOSIGNAL HAIR — плоская чёрная коробка</t>
+          <t>EXO-NAD — янтарная виала PH NORMALIZER (на главной одна)</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>cuboid from packshot</t>
+          <t>lathe model</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>protocols/print/img/exosignal-hair.webp: фасад; верх и бока — матовый чёрный без печати</t>
+          <t>вырезка с protocols/print/img/exo-nad.webp (стоит отдельно, не перекрыта)</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -16076,7 +15939,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>EXOSIGNAL HAIR — прозрачные ампулы (×5)</t>
+          <t>EXO-NAD — сине-бирюзовая виала LONGEVITY SERUM (на главной одна)</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -16086,7 +15949,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>вырезка ампулы с protocols/print/img/exosignal-hair.webp (вертикальная надпись EXOSIGNAL HAIR)</t>
+          <t>вырезка с protocols/print/img/exo-nad.webp (стоит отдельно, не перекрыта)</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -16103,22 +15966,22 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>EXOSIGNAL SPRAY — флакон (матовое стекло, золотая крышка)</t>
+          <t>EXOSIGNAL HAIR — плоская чёрная коробка (на главной закрыта)</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>lathe model</t>
+          <t>cuboid from packshot</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>студийного пакшота нет: есть только фото в руке (site/img/exosignal-spray-hand.jpg) и снимок 400×300 (site/img/exosignal-spray.png). Нужен пакшот флакона на прозрачном фоне, без руки, фасадом с этикеткой</t>
+          <t>protocols/print/img/exosignal-hair.webp: фасад. Правая нижняя часть фасада закрыта ампулами — залить матовым чёрным, текст не клонировать. Верх и бока — матовый чёрный без печати</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>needs photo</t>
+          <t>ready</t>
         </is>
       </c>
     </row>
@@ -16130,22 +15993,22 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>EXOSIGNAL SPRAY — высокая чёрная коробка</t>
+          <t>EXOSIGNAL HAIR — прозрачная ампула (на главной одна)</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>cuboid from packshot</t>
+          <t>lathe model</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>есть только site/img/exosignal-spray.png 400×300 — слишком мелко. Нужен фронтальный пакшот коробки; до него — маленький билборд в глубине сцены</t>
+          <t>Процедурное прозрачное стекло (transmission) с белым кольцом на горлышке. Декаль — только вертикальная надпись EXOSIGNAL HAIR с крайней левой ампулы protocols/print/img/exosignal-hair.webp; мелкие строки рядом — тонкие серые линии ([unreadable]). Текстуру целиком с фото не брать: ампулы перекрывают друг друга, и сквозь стекло видны коробка и соседние надписи. Годится для мелкого и среднего плана; для крупного нужно фото одной ампулы на прозрачном фоне</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>needs photo</t>
+          <t>ready</t>
         </is>
       </c>
     </row>
@@ -16157,22 +16020,22 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>MICRO BOOST 10% — узкая кремовая коробка</t>
+          <t>EXOSIGNAL SPRAY — флакон (матовое стекло, рифлёная золотая крышка)</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>cuboid from packshot</t>
+          <t>lathe model</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>protocols/print/img/micro-boost-10.webp (385×1252): фасад; бока — кремовый цвет без печати</t>
+          <t>Студийного пакшота нет: есть фото в руке (site/img/exosignal-spray-hand.jpg, низ флакона закрыт пальцами) и снимок 400×300 (site/img/exosignal-spray.png), где флакон ~40 px и выглядит непрозрачно-белым, а не матовым стеклом. Замену из него не делать: до пакшота флакон и туман на главной не показываются. Нужен пакшот флакона на прозрачном фоне, без руки, фасадом с этикеткой</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>ready</t>
+          <t>needs photo</t>
         </is>
       </c>
     </row>
@@ -16184,22 +16047,22 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>CELL RENEW 1.5% — узкая кремовая коробка</t>
+          <t>EXOSIGNAL SPRAY — высокая чёрная коробка</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>cuboid from packshot</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>protocols/print/img/cell-renew-15.webp (309×1012): фасад и узкая правая грань</t>
+          <t>До пакшота — маленький билборд коробки из site/img/exosignal-spray.png (≈95×280 px), только в глубине сцены, крупно не выводить. После фронтального пакшота — cuboid</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>ready</t>
+          <t>needs photo</t>
         </is>
       </c>
     </row>
@@ -16211,7 +16074,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>CELLULAR AGE DEFENSE 2.5% — узкая кремовая коробка</t>
+          <t>MICRO BOOST 10% — узкая кремовая коробка</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -16221,7 +16084,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>protocols/print/img/cellular-age-25.webp (308×1023): фасад и узкая правая грань</t>
+          <t>protocols/print/img/micro-boost-10.webp (385×1252): фасад; бока — кремовый цвет без печати</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -16238,7 +16101,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>DERMA RECOVERY CREAM — коробка с полосой шалфея</t>
+          <t>CELL RENEW 1.5% — узкая кремовая коробка</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -16248,7 +16111,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>protocols/print/img/derma-recovery.webp (688×945): фасад и правая грань</t>
+          <t>protocols/print/img/cell-renew-15.webp (309×1012): фасад и узкая правая грань без печати</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -16265,17 +16128,17 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN — микронидлинг-ручка</t>
+          <t>CELLULAR AGE DEFENSE 2.5% — узкая кремовая коробка</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>cuboid from packshot</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>прозрачный пакшот protocols/print/img/mitopen.webp. Корпус цилиндрический, позже возможна лейтон-модель; обратная сторона не снята</t>
+          <t>protocols/print/img/cellular-age-25.webp (308×1023): фасад и узкая правая грань без печати</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -16292,17 +16155,17 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN — планшет, ручной сканер, серебряная база</t>
+          <t>DERMA RECOVERY CREAM — широкая коробка с тёмно-зелёной полосой</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>cuboid from packshot</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>прозрачный пакшот protocols/print/img/mitoscan.webp (один кадр на весь комплект)</t>
+          <t>protocols/print/img/derma-recovery.webp (688×945): кубоид в пропорциях фото, виден только фасад (завиток крема, SNAIL COLLAGEN, медальона со спикулами нет). Бока и верх — ровный кремовый без печати. Полоса тёмно-зелёная (~#1D3A2C); в packaging-text.json и .md она ошибочно названа sage-green — поправить. Шалфей #9AA889 — только подложка на экране 4</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -16319,7 +16182,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Золотая монограмма M (дальний слой, экран 4)</t>
+          <t>MITOPEN — микронидлинг-ручка</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -16329,7 +16192,7 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>site/img/mitoderm-m-gold.png (600 px, файл заказчика)</t>
+          <t>Прозрачный пакшот protocols/print/img/mitopen.webp, снят наискось. Только поворот в плоскости экрана (не больше ±15°) и масштаб, без наклона вглубь. Корпус цилиндрический, позже возможна лейтон-модель; обратная сторона не снята</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -16346,17 +16209,17 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Белый логотип MITODERM (пункт 1 дока, подвал)</t>
+          <t>MITOSCAN — планшет, ручной сканер, серебряная база</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>photo frame</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>site/img/mitoderm-logo-white.png</t>
+          <t>прозрачный пакшот protocols/print/img/mitoscan.webp (один кадр на весь комплект)</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -16373,44 +16236,44 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>MITOTECH CELL BOOSTER (два флакона, скоро)</t>
+          <t>Золотая монограмма M (дальний слой, экран 4)</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>needs model</t>
+          <t>billboard</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>фото упаковки нет ни в одном источнике; пока на главной только карточка без 3D. Нужен пакшот обоих флаконов и коробки, если она есть</t>
+          <t>site/img/mitoderm-m-gold.png (600 px, файл заказчика)</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>needs photo</t>
+          <t>ready</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>CATALOG</t>
+          <t>Home — MITODERM</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Дальний слой: дым и частицы (все экраны)</t>
+          <t>Белый логотип MITODERM (пункт 1 дока, подвал)</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>billboard (дальняя плоскость с шейдером дыма + точки-частицы)</t>
+          <t>photo frame</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Шейдер дыма и частицы из утверждённого образца EXOCELL MASK (site/proto/exocell-3d-template.html), перекраска по токенам линеек из design-rules.md</t>
+          <t>site/img/mitoderm-logo-white.png</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -16422,27 +16285,27 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>CATALOG</t>
+          <t>Home — MITODERM</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Коробка V-TECH SYSTEM (высокая, зеркальная золотая фольга)</t>
+          <t>MITOTECH CELL BOOSTER (два флакона, скоро)</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>cuboid from packshot</t>
+          <t>needs model</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/vtech-system.webp, фасад снят прямо. Печать боковин неизвестна: боковины из гладкой золотой фольги с чёрными полосами сверху и снизу, без надписей</t>
+          <t>Фото упаковки нет ни в одном источнике, пока на главной только карточка без 3D. Нужен пакшот обоих флаконов и коробки, если она есть</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>ready</t>
+          <t>needs photo</t>
         </is>
       </c>
     </row>
@@ -16454,17 +16317,17 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>5 флаконов V-TECH и саше гель-маски (только в большой карточке экрана 3)</t>
+          <t>Дальний слой: дым и частицы (все экраны)</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>lathe model (флаконы) + billboard (саше)</t>
+          <t>billboard (дальняя плоскость с шейдером дыма и точками-частицами)</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/vtech-system.webp; нечитаемая строка под V-TECH на флаконе рисуется тонкой линией</t>
+          <t>Шейдер дыма и частицы из утверждённого образца EXOCELL MASK (site/proto/exocell-3d-template.html), перекраска по токенам линеек из design-rules.md</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -16481,7 +16344,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Коробка EXOCELL MASK</t>
+          <t>Коробка V-TECH SYSTEM (высокая, зеркальная золотая фольга); одна на экранах 1–2, в группе на экране 3</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -16491,7 +16354,7 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>site/img/exocell-box-front.jpg + site/img/exocell-box-side.jpg (уже собрана в образце MASK)</t>
+          <t>protocols/print/img/vtech-system.webp (1200×1100, RGBA). Саше перекрывает правый нижний угол фасада вместе с нижней чёрной полосой. В этой зоне печати нет («S Y S T E M» кончается выше), поэтому её заливают соседней фольгой и полосой. Другой путь — фасад с фото заказчика в Figma №40/42. Боковины: гладкая золотая фольга без надписей, поза покоя не больше 12°</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -16508,17 +16371,17 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Кубическая коробка EXOTECH GEL</t>
+          <t>5 флаконов V-TECH и 5 саше гель-маски (большая карточка экрана 3)</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>cuboid from packshot</t>
+          <t>lathe model (флаконы) + 5 billboard одной текстуры (саше, всегда лицом к камере)</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/exotech-gel.webp: фасад и левая чёрная грань с золотой диагональю, выпрямить по перспективе</t>
+          <t>protocols/print/img/vtech-system.webp. Нечитаемые строки на флаконе и саше рисуются тонкими линиями ([unreadable] в packaging-text v-tech-system)</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -16535,17 +16398,17 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Сферическая баночка EXOTECH GEL</t>
+          <t>Коробка EXOCELL MASK</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>lathe model</t>
+          <t>cuboid from packshot</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/exotech-gel.webp: золотая сфера со швом, надпись EXOTECH / GEL</t>
+          <t>site/img/exocell-box-front.jpg (740×1000) и site/img/exocell-box-side.jpg (150×1000), уже собрана в образце MASK. Ракурс 3/4 только на левую боковину</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -16562,7 +16425,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Плоская коробка EXOSIGNAL HAIR</t>
+          <t>Кубическая коробка EXOTECH GEL</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -16572,7 +16435,7 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/exosignal-hair.webp, фасад. Боковины матовые чёрные без надписей. Ампулы на каталоге не показываются</t>
+          <t>protocols/print/img/exotech-gel.webp (1065×567): фасад и левая чёрная грань с золотой диагональю, выпрямить по перспективе. Ракурс 3/4 только на левую грань</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -16589,22 +16452,22 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>EXOSIGNAL SPRAY: коробка и флакон</t>
+          <t>Сферическая баночка EXOTECH GEL</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>billboard (временно); после фото — коробка как кубоид, флакон как lathe</t>
+          <t>lathe model</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Пока только site/img/exosignal-spray.png (рендер 400×300 на белом, нужно вырезать фон). Нужен прозрачный студийный пакшот коробки и флакона в высоком разрешении</t>
+          <t>protocols/print/img/exotech-gel.webp: золотая сфера со швом, надпись EXOTECH / GEL только спереди, поэтому поворот только к фасаду</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>needs photo</t>
+          <t>ready</t>
         </is>
       </c>
     </row>
@@ -16616,7 +16479,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Коробка EXO-NAD (квадратная, золотая)</t>
+          <t>Плоская коробка EXOSIGNAL HAIR (одна, без ампул)</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -16626,7 +16489,7 @@
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/exo-nad.webp, фасад прямой (795×489 — для большой карточки на пределе). Боковины из гладкого золота</t>
+          <t>protocols/print/img/exosignal-hair.webp (1087×714). Пять ампул закрывают правую часть фасада и правый край коробки. Текст кончается левее ампул, поэтому зону заливают матовым чёрным, а край достраивают. Другой путь — фото заказчика в Figma №36/47. Боковины матовые чёрные без надписей, поза покоя не больше 12°</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -16643,17 +16506,17 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Флакон пилинга EXO-NAD (квадратное стекло, золотые хлопья)</t>
+          <t>EXOSIGNAL SPRAY: коробка и флакон</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>cuboid from packshot (коробка) + lathe model (флакон)</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/exo-nad.webp</t>
+          <t>Фото заказчика в Figma: №2, 3, 21 (узлы 93:8081, 93:8083, 104:8121; фон белый, его нужно вырезать), флакон по №33 и 34. Надписи сверить с packaging-text exosignal-spray, нечитаемые строки рисовать тонкими линиями. site/img/exosignal-spray.png (400×300, без прозрачности) не используется</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -16670,17 +16533,17 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Бутылочки PH NORMALIZER (янтарь) и LONGEVITY SERUM (сине-бирюзовая)</t>
+          <t>Коробка EXO-NAD (квадратная, золотая)</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>lathe model</t>
+          <t>cuboid from packshot</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/exo-nad.webp, этикетки сняты с фото</t>
+          <t>protocols/print/img/exo-nad.webp (795×488, сама коробка шириной около 480 px — для карточки во всю ширину на пределе). Фасад не перекрыт, боковины из гладкого золота, поза покоя не больше 12°</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -16697,17 +16560,17 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Коробка MICRO BOOST 10%</t>
+          <t>Флакон пилинга EXO-NAD (квадратное стекло, золотые хлопья)</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>cuboid from packshot</t>
+          <t>billboard (всегда лицом к камере)</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/micro-boost-10.webp (264×1000). Шприц не показывается: его печать неизвестна</t>
+          <t>protocols/print/img/exo-nad.webp</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -16724,17 +16587,17 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Коробка CELL RENEW 1.5%</t>
+          <t>Бутылочки PH NORMALIZER (янтарь) и LONGEVITY SERUM (сине-бирюзовая)</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>cuboid from packshot</t>
+          <t>lathe model</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>site/img/cell-renew-15.png (220×720, хватает только для карточки)</t>
+          <t>protocols/print/img/exo-nad.webp, этикетки сняты с фото</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -16751,7 +16614,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Коробка CELLULAR AGE DEFENSE 2.5%</t>
+          <t>Коробка MICRO BOOST 10%</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -16761,7 +16624,7 @@
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>site/img/cellular-age-25.png (217×720). Флакон airless не показывается: фото в репозитории нет</t>
+          <t>protocols/print/img/micro-boost-10.webp (385×1252, RGBA). Шприц не показывается: его печать неизвестна</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -16778,7 +16641,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Коробка DERMA RECOVERY CREAM</t>
+          <t>Коробка CELL RENEW 1.5%</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -16788,7 +16651,7 @@
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/derma-recovery.webp (фасад 642×1000). Баночка не показывается: её фото нет</t>
+          <t>protocols/print/img/cell-renew-15.webp (309×1012, RGBA) вместо site/img/cell-renew-15.png (220×720, палитра, альфа фона 1). Флакон (Figma №70/75) — на странице средства</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -16805,17 +16668,17 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN</t>
+          <t>Коробка CELLULAR AGE DEFENSE 2.5%</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>cuboid from packshot</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/mitopen.webp (прозрачный пакшот)</t>
+          <t>protocols/print/img/cellular-age-25.webp (308×1023, RGBA) вместо site/img/cellular-age-25.png. Флакон airless (Figma №9) — на странице средства</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -16832,17 +16695,17 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN: планшет, ручной сканер, основание</t>
+          <t>Коробка DERMA RECOVERY CREAM</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>billboard</t>
+          <t>cuboid from packshot</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>protocols/assets/img/mitoscan.webp</t>
+          <t>protocols/print/img/derma-recovery.webp (688×945, RGBA). Баночка (Figma №1/73) — на странице средства</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -16859,22 +16722,22 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>MITOTECH CELL BOOSTER (2 флакона)</t>
+          <t>MITOPEN</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>needs model</t>
+          <t>billboard (фронтально, наклон ±10° с бликом)</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Нет ни пакшота, ни текста упаковки; до фото — карточка без 3D</t>
+          <t>protocols/assets/img/mitopen.webp (297×915, прозрачный пакшот; крупнее, чем версия в protocols/print/img)</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>needs photo</t>
+          <t>ready</t>
         </is>
       </c>
     </row>
@@ -16886,20 +16749,74 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
+          <t>MITOSCAN: планшет, ручной сканер, основание</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>billboard (фронтально, наклон ±10° с бликом)</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>protocols/print/img/mitoscan.webp (1145×777, RGBA)</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>MITOTECH CELL BOOSTER (2 флакона)</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>needs model</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Нет ни пакшота, ни текста упаковки; до фото — карточка без 3D</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>needs photo</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>Золотая монограмма M (экран 5)</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>billboard</t>
         </is>
       </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>site/img/mitoderm-m-gold.png</t>
-        </is>
-      </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>site/img/mitoderm-m-gold.png (566×600, RGBA)</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>ready</t>
         </is>
@@ -16916,7 +16833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17523,17 +17440,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CELLULAR AGE DEFENSE 2.5%</t>
+          <t>DERMA RECOVERY CREAM</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>s7.contacts</t>
+          <t>kit.alt</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp · Call · Email</t>
+          <t>DERMA RECOVERY CREAM box and 50 ml jar</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -17543,51 +17460,51 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Экран 7, строка контактов под главной кнопкой. Номера и адрес — общие контакты сайта, как в образце EXOCELL MASK.</t>
+          <t>Screen 7 — alt text of the kit render (box and jar). Hebrew goes through review, following the pattern of ui.kitshot_alt.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CELLULAR AGE DEFENSE 2.5%</t>
+          <t>MITOSCAN</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>badge.use</t>
+          <t>ui.wa_text_price</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Home care</t>
+          <t>Hello, I'd like to get details on MITOSCAN prices</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>שלום, אשמח לקבל פרטים על מחירי EXOCELL MASK</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Бейдж назначения (золотой контур) на экранах 1 и 7. На иврите по design-rules — «טיפוח ביתי», а не «טיפול ביתי» из home.sl-3.</t>
+          <t>Предзаполненный текст WhatsApp для главной кнопки b4.cta, липкой панели и контакта WhatsApp на экране 7. Это параметризация проверенной строки wa_text_price со страницы MASK (proto/exocell-he-ui.json), меняется только имя: «שלום, אשמח לקבל פרטים על מחירי MITOSCAN»</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CELLULAR AGE DEFENSE 2.5%</t>
+          <t>Home — MITODERM</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>badge.line</t>
+          <t>home.line.vtech-face</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>BIOSPICULE</t>
+          <t>V-TECH FACE</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -17597,24 +17514,24 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Бейдж линейки на экранах 1 и 7, латиницей и в иврите — как на коробке.</t>
+          <t>Марка серии латиницей, не переводится: кикер и бейдж линейки на экране 2, подпись группы на экранах 1 и 7, пункт 2 дока. Для остальных линеек подписи уже есть: catalog.chips[2] / [5] / [4] и home.sl-2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>DERMA RECOVERY CREAM</t>
+          <t>Home — MITODERM</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>wa.text</t>
+          <t>home.s2.line</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Hello, where can I buy DERMA RECOVERY CREAM?</t>
+          <t>V-TECH SYSTEM in the clinic, EXOCELL MASK to finish, EXOTECH GEL at home.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -17624,24 +17541,24 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Screen 7 — prefilled message of the WhatsApp contact link</t>
+          <t>Строка экрана 2. Сокращение synthetic-exosomes:b4.line: иврит вырезается из проверенной строки, убираются EXO-NAD и часть про кожу головы</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>DERMA RECOVERY CREAM</t>
+          <t>Home — MITODERM</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>kit.alt</t>
+          <t>home.kit.mask-net</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>DERMA RECOVERY CREAM box and 50 ml jar</t>
+          <t>Net 5 x 25 ml</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -17651,24 +17568,24 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Screen 7 — alt text of the kit render (box and jar)</t>
+          <t>Экран 7, состав EXOCELL MASK в аккордеоне, после exocell-mask:b5.label1. Напечатано на коробке (packaging-text exocell-mask objects[0].front[4]); LTR, без перевода</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN</t>
+          <t>Home — MITODERM</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>s7.contacts</t>
+          <t>home.contact.whatsapp</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp · Phone · Email</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -17678,24 +17595,24 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Экран 7 (покупка): ряд контактов под главной кнопкой «לקבלת פרטים על מחירים», после подписи «צרו קשר» (b6.label4). Каждая часть — ссылка: wa.me, tel:, mailto:.</t>
+          <t>Экран 7, ряд контактов под главной кнопкой, рядом с сегментами exocell-mask:b6.cta#3 (телефон) и #4 (e-mail). Латиница, название бренда</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN</t>
+          <t>Home — MITODERM</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>alt.system</t>
+          <t>home.scroll</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN: tablet on a stand, handheld scanner and base</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -17705,51 +17622,51 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Alt text of the 3D system and packshot on screens 1 and 7</t>
+          <t>Экран 1, подсказка прокрутки над нижним доком</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN</t>
+          <t>CATALOG</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>alt.scan</t>
+          <t>catalog.chips</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>The same scalp area on the MITOSCAN screen at ×50 and ×200</t>
+          <t>All · Exosomes · Peels · Masks · Hair · Bio-Spicules · Home care · Devices</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>הכל · אקסוזומים · פילינג · מסכות · שיער · ביו-ספיקולות · טיפוח ביתי · מכשור</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Alt text of the screen images on screens 3–5</t>
+          <t>Экран 2: строка чипов и липкая строка фильтра на экранах 3–6. Фрагменты [2], [4], [5] — бейджи линеек и подписи дока, [6] — бейдж домашнего ухода (как на главной). Иврит уже есть дословно в листе Catalog (строка Filters · Chips HE) — перенести без изменений</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Home — MITODERM</t>
+          <t>CATALOG</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>home.line.vtech-face</t>
+          <t>catalog.filters.title</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>V-TECH FACE</t>
+          <t>Choose a category</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -17759,277 +17676,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Марка серии латиницей, не переводится: кикер экрана 2, подпись группы на экранах 1 и 7, пункт 2 дока. Для остальных линеек подписи уже есть: catalog.chips[2] / [5] / [4] и home.sl-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Home — MITODERM</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>home.s2.line</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>V-TECH SYSTEM in the clinic, EXOCELL MASK to finish, EXOTECH GEL at home.</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Строка экрана 2. Это сокращение synthetic-exosomes:b4.line: иврит вырезается из проверенной строки — убрать EXO-NAD и часть про кожу головы</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Home — MITODERM</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>home.contact.whatsapp</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Экран 7, ряд контактов под кнопкой home.b1, рядом с сегментами exocell-mask:b6.cta#3 (телефон) и #4 (e-mail)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Home — MITODERM</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>home.scroll</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Scroll</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Экран 1, подсказка прокрутки над нижним доком</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>catalog.hero.title</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Our products</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Экран 1, заголовок (лист Catalog, Hero · Title; проверенного иврита нет)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>catalog.chips</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>All · Exosomes · Peels · Masks · Hair · Bio-Spicules · Home care · Devices</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Экран 2, строка чипов, и липкая строка фильтра на экранах 3–6. Иврит уже есть в листе Catalog (строка Chips HE), нужна сверка</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>catalog.filters.title</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Choose a category</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
           <t>Экран 2, заголовок над полкой и чипами</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>catalog.filters.line</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Each line has its own colour.</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Экран 2, фраза под заголовком: объясняет, почему меняется цвет фона</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>catalog.line.vtech-face</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>V-TECH FACE</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Экран 3: подзаголовок и бейдж линейки на карточках V-TECH SYSTEM, EXOCELL MASK, EXOTECH GEL; подпись в доке</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>catalog.line.hair</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>HAIR</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Экран 3: подзаголовок и бейдж линейки на карточках EXOSIGNAL HAIR и EXOSIGNAL SPRAY</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>catalog.line.peeling</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>PEELING</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Экран 4: бейдж линейки на карточке EXO-NAD; подпись в доке</t>
         </is>
       </c>
     </row>
@@ -21190,7 +20837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -22019,7 +21666,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Флакон: в репозитории нет файла airless-флакона, есть только описание печати с вашего рендера. Пришлите, пожалуйста, пакшот флакона на прозрачном фоне. Без него экраны 4–7 собираются только с коробкой.</t>
+          <t>Флакон: в Figma есть фото №9 (белый airless-флакон, узел 93:8095), в репозитории файла нет. На нём напечатано 'CELL CELLULAR / AGE DEFENSE / 2.5%'. Это опечатка макета или так на настоящем флаконе? Пришлите, пожалуйста, пакшот настоящего флакона на прозрачном фоне. До ответа страница собирается только с коробкой. Потом флакон добавим на экраны 4 (крупно только головка помпы) и 7.</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
@@ -22032,7 +21679,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>На рендере флакона напечатано 'CELL CELLULAR / AGE DEFENSE / 2.5%'. Это опечатка макета или так на настоящем флаконе? Пока нет ответа, фасад флакона крупно не показываем.</t>
+          <t>В коробке только один флакон 30 мл, без вкладышей и аксессуаров? От этого зависит строка «что внутри» на экране покупки.</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
@@ -22045,7 +21692,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>В коробке только один флакон 30 мл, без вкладышей и аксессуаров? Это строка «что внутри» на экране покупки.</t>
+          <t>Боковые и верхние грани коробок CELLULAR AGE DEFENSE 2.5%, CELL RENEW 1.5% и DERMA RECOVERY CREAM: нужны фото (по ним видна и настоящая глубина) или подтверждение, что печати там нет. До этого все три коробки поворачиваются не больше чем на ±20°.</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
@@ -22058,7 +21705,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Боковые и верхняя грани коробки: нужна фотография или подтверждение, что они без печати. Пока поворот коробки ограничен ±20°.</t>
+          <t>DERMA RECOVERY CREAM: в репозитории две версии коробки — с тёмно-зелёной полосой (protocols/print/img) и с шалфейной (protocols/assets/img). Какая сейчас в продаже? Пока ставим шалфейную, как в packaging-text.json и design-rules.</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
@@ -22071,7 +21718,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Экран 4 «Feel it»: капля падает на абстрактную поверхность кожи без лица — или нужен фото-кадр, как утверждённый кадр с лицом у MASK (пальцы у линии челюсти)? Если фото, то какой снимок использовать?</t>
+          <t>Экран 4 «Feel it», выберите вариант. (а) Кадр с человеком: пальцы у линии челюсти, одно мягкое круговое движение, как утверждённый кадр с лицом у MASK. Это платная генерация, цену и баланс назову до вашего «утверждаю». (б) Абстрактная тёплая поверхность кожи без человека, без генерации. Если (а) — есть ли снимок-референс?</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
@@ -22097,7 +21744,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Куда ведёт кнопка «איפה לקנות» — на список клиник-партнёров или в WhatsApp? «לקליניקות: לקבלת הצעת מחיר» оставляем текстовой ссылкой рядом с контактами?</t>
+          <t>Подтверждаете схему кнопок? «איפה לקנות» открывает экран «Ask your clinic» (решение 17). «לקליניקות: לקבלת הצעת מחיר» открывает WhatsApp с готовым текстом и кодом #CAD-HE-6. Липкая панель на телефоне включается только вместе с этой схемой.</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -22114,7 +21761,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Коробка CELL RENEW 1.5% появляется на этой странице на экранах 2 и 5 (ступень ниже, «начните с 1.5%»). Можно показывать соседнее средство?</t>
+          <t>Коробка CELL RENEW 1.5% стоит ступенью ниже на экране 2, а на экране 5 есть её карточка со ссылкой. Можно показывать соседнее средство на этой странице?</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr"/>
@@ -22127,7 +21774,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Фото банки. 10/10 клиент присылал фото банки DERMA RECOVERY (по нему расшифрован текст), но файла в репозитории нет. Нужно прямое фото банки на ровном фоне (лучше 4 ракурса через 90° и вид сверху на крышку) и фото открытой банки с кремом. Без него банку показываем только открытой или сверху, этикетку не рисуем.</t>
+          <t>Банка. Фасад банки есть у вас в Figma: фото 1 (узел 93:8080), открытая банка — фото 73 (узел 113:8211). По ним строим банку и поворачиваем её не больше чем на ±20°. Если банку нужно крутить свободнее, пришлите фото сзади, с боков и сверху на крышку. И подскажите: банка стеклянная или пластиковая?</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr"/>
@@ -22140,7 +21787,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Коробка. Фасад есть, но нужны фото боковых граней, задней грани и верха (с закрытым и открытым клапаном) или хотя бы размеры коробки Ш×В×Г в мм — глубина неизвестна. Пока поворот коробки ограничен ±20°, грани без печати.</t>
+          <t>Коробка. Нужны фото боковых граней, задней грани и верха (с закрытым и открытым клапаном) или размеры Ш×В×Г в мм. На старом пакшоте (тёмная полоса) боковины чистые и сверху клапан-язычок. У новой коробки так же?</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
@@ -22153,7 +21800,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Экран 4 сейчас полностью 3D, без людей: лента крема разглаживает сухие хлопья. Нужен ли здесь, как на экране 4 у MASK, кадр с женщиной, которая наносит крем? Если да — нужно утверждённое фото.</t>
+          <t>Экран 4 по раскадровке — сцена у зеркала, женщина наносит крем. В коллаже такого фото нет. У вас есть своё утверждённое фото, или сделать один образец генерацией? Цену назову до запуска. Пока «ок» нет, ставим 3D-вариант без людей.</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr"/>
@@ -22166,7 +21813,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Экран 5: показываем коробки CELL RENEW 1.5%, CELLULAR AGE DEFENSE 2.5% и MICRO BOOST 10%, а V-TECH и EXO-NAD — только текстом, потому что их золотые упаковки смешали бы цвета двух линеек. Согласны?</t>
+          <t>Экран 5: CELL RENEW 1.5% и CELLULAR AGE DEFENSE 2.5% показаны как «или» (сменяют друг друга), MICRO BOOST 10% — отдельной клинической веткой с бейджем «מקצועי». V-TECH и EXO-NAD — только текстом, чтобы не смешивать цвета линеек. Согласны?</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr"/>
@@ -22179,20 +21826,24 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Бейдж назначения: в design-rules написано «טיפוח ביתי», а в вычитанном тексте сайта (home.sl-3) — «טיפול ביתי». Какой вариант ставить на бейдж?</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr"/>
+          <t>Главная кнопка «איפה לקנות» ведёт к блоку специалистов и клиник (экран 8). Кнопка «לקליניקות: בקשת הצעת מחיר» открывает форму заявки, где поле «מקצוע» отделяет клиники. Так правильно?</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Таблицу специалистов заказчик пришлёт позже (11/10). До неё кнопка ведёт на форму заявки, без JS — в WhatsApp.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN</t>
+          <t>DERMA RECOVERY CREAM</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Есть ли у MITOPEN коробка или кейс и что в нём кроме ручки: картриджи, зарядка или кабель, подставка? В каталоге и на пакшоте только «1× MITOPEN», поэтому на экране покупки пока показываем только ручку. Если коробка есть — нужно её фото со всех сторон.</t>
+          <t>Бейдж назначения для всего сайта: «טיפוח ביתי» (design-rules, образец MASK, eyebrow сывороток BIOSPICULE) или «טיפול ביתי» (глоссарий, home.sl-3)? Пока ставим «טיפוח ביתי».</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr"/>
@@ -22200,12 +21851,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN</t>
+          <t>DERMA RECOVERY CREAM</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Что делает розово-золотое кольцо — задаёт глубину иглы? Чем переключаются 5 скоростей — кнопкой? Что означает маленькая точка над кнопкой — индикатор? Сюжет «поверните кольцо» должен повторять работу настоящего прибора.</t>
+          <t>К вычитке: в b5.line объём записан «1.69 fl. oz.» (EN) и «1.69 fl. oz» (HE), а на упаковке и в cat.kit — «50 ml ℮ 1.69 fl.oz.». Привести b5.line к печати?</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
@@ -22218,7 +21869,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Нужны пакшот MITOPEN в высоком разрешении (от 2500 px по высоте, сейчас 297×915) и макроснимок картриджа с иглами на минимальной и максимальной глубине. Без него иглы на экране 3 не показываем: их число и вид с фото не читаются.</t>
+          <t>Есть ли у MITOPEN коробка или кейс, и что в нём кроме ручки: картриджи, зарядка или кабель, подставка? В каталоге и на пакшоте только «1× MITOPEN», поэтому на экране покупки пока показываем одну ручку. Если коробка есть, нужно её фото со всех сторон.</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr"/>
@@ -22231,7 +21882,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Фото для экрана 4 (специалистка в перчатках ведёт MITOPEN по щеке клиентки): есть своя съёмка или генерируем по пакшоту? Генерация платная: сначала один образец, цена и «утверждаю».</t>
+          <t>Чем на MITOPEN задаётся глубина иглы: розово-золотым кольцом, носиком или картриджем? Чем переключаются 5 скоростей — кнопкой? Что означает точка над кнопкой? В раскадровке есть подсказка «סובבו את הטבעת» и «скролл крутит кольцо», но на упаковке кольцо описано как кольцо рукоятки. Пока ответа нет, кольцо только бликует, шкалы движутся от скролла, подсказка — «גללו».</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
@@ -22244,14 +21895,10 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Какие контакты ставить на экран покупки: номер WhatsApp, телефон, e-mail?</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Как на mitoderm.com (заказчик 11/10): кнопка WhatsApp +972-54-762-1889, телефон 054-326-2182, почта info@mitoderm.com (Mitoderm@gmail.com — только для мероприятий). Срок обратного звонка не пишем.</t>
-        </is>
-      </c>
+          <t>Если фото MITOPEN № 56 и 57 в Figma окажутся меньше 2500 px по высоте или без крупного плана картриджа: можете прислать пакшот в высоком разрешении и макроснимок картриджа с иглами на минимальной и максимальной глубине? Без него на экране 3 нет макро, а иглы не показываем.</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -22261,7 +21908,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>В еврейском каталоге диапазон написан через дефис («0.25-2.5»), в раскадровке через тире («0.25–2.5»). На экране 7 рядом стоят обе строки — выровнять каталог по раскадровке?</t>
+          <t>Фото для экрана 4 (специалистка в перчатках ведёт MITOPEN по щеке клиентки): есть своя съёмка или генерируем по пакшоту? Перо на снимке должно быть в том же ракурсе, что на пакшоте. Генерация платная: сначала один образец, цена и «утверждаю».</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
@@ -22269,12 +21916,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>MITOSCAN</t>
+          <t>MITOPEN</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Есть ли настоящие снимки с экрана MITOSCAN — один и тот же участок кожи головы при ×50 и ×200 и пара «до / после» этого участка за курс — и согласие пациента на показ на сайте? Генерировать «снимок прибора» нельзя, а без этих снимков экраны 3–5 покажут только экран с логотипом.</t>
+          <t>В каталоге диапазон написан через дефис («0.25-2.5»), в раскадровке через тире («0.25–2.5»). Порядок чисел на сайте мы выравниваем изоляцией LTR, но сам знак остаётся разным. Привести каталог к тире, как в раскадровке?</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr"/>
@@ -22287,7 +21934,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Нужны фото щупа: торец с линзой, бок и обратная сторона. И фото планшета без щупа — пустой держатель и подставка целиком. Без них щуп в 3D не отделить от планшета.</t>
+          <t>Это блокирует экраны 3–5. Есть ли настоящие снимки с экрана MITOSCAN — один и тот же участок кожи головы при ×50 и ×200 — и пара «до / после» этого участка за курс, с согласием пациента на показ на сайте? Генерировать «снимок прибора» нельзя. Пока ответа нет, экраны 3–5 в Figma на заглушках не собираю. Если снимков не будет, ставлю запасной вариант: крупная типографика ×50 → ×200 перед экраном с логотипом, «зеркало» с логотипом и три шага без «до / после».</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr"/>
@@ -22300,7 +21947,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Что за серебряный цилиндр с сеткой на торце, и соединён ли он кабелем со щупом? Пока не подтвердите, на сайте называем его только «база» и функцию не пишем.</t>
+          <t>Нужны фото щупа (торец с линзой, бок, обратная сторона) и фото планшета без щупа (пустой держатель, подставка целиком). Без них вся история идёт движением камеры по одному целому пакшоту: щуп не выходит из держателя, и система не разбирается на части.</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr"/>
@@ -22313,7 +21960,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Каталог пишет «1× MITOSCAN». Входят ли в комплект все три предмета с пакшота — планшет на подставке, щуп со спиральным кабелем и база? Если да, подпишем части на экранах 6–7 (нужны три короткие новые строки).</t>
+          <t>Что за серебряный цилиндр с сеткой на торце? В каталоге фото он назван подставкой-цилиндром, в описании упаковки — базой. Соединён ли он кабелем со щупом? Пока не подтвердите, на сайте он остаётся без названия, без функции и без выносок.</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr"/>
@@ -22326,7 +21973,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Фото-кадр для экрана 4 (специалист со щупом у пробора пациента перед экраном): снимаем в клинике или генерируем с ценой и вашим «утверждаю»? Если ни то ни другое — ставим вариант «зеркало» без людей.</t>
+          <t>Каталог пишет «1× MITOSCAN». Входят ли в комплект все три предмета с пакшота: планшет на подставке, щуп со спиральным кабелем и цилиндр? Если да, подпишем части на экранах 6–7, для этого нужны три короткие новые строки.</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr"/>
@@ -22339,24 +21986,20 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Кнопка цены: в проверенном иврите сайта «לקבלת פרטים על מחירים» (b4.cta), в каталоге «לקבלת הצעת מחיר». Ставлю сайтовый вариант — верно? И знак увеличения: сайт пишет ×50, каталог X50 — на экранах 5 и 7 строки из каталога придут с X50. Привести их к ×50?</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Да: «לקבלת פרטים על מחירים» — как на mitoderm.com.</t>
-        </is>
-      </c>
+          <t>Фото-кадр для экрана 4 (специалист со щупом у пробора пациента): снимаем в клинике или генерируем, назвав цену и получив ваше «утверждаю»? При генерации экран прибора в кадре развёрнут от камеры или показывает только логотип. Если ни то ни другое, ставлю вариант «зеркало» без людей.</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Home — MITODERM</t>
+          <t>MITOSCAN</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Обозначения ключей: «slug:ключ» — ключ другой страницы в storyboard.he.json; «slug:cat.поле» — та же страница в product-pages.he.json (по индексу, совпадающему с product-pages.json); «catalog.chips[i]» — i-й пункт строки «Chips HE» листа Catalog (0 הכל … 2 פילינג, 4 שיער, 5 ביו-ספיקולות, 6 טיפוח ביתי, 7 מכשור); «#n» — n-й сегмент строки, разделённой « · »; «new:» — строка из new_strings. Сборщик примет такую адресацию?</t>
+          <t>Блок «Кто делает процедуру» после экрана покупки: показываем всех специалистов с меткой קרקפת или только тех, у кого уже есть MITOSCAN?</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr"/>
@@ -22369,7 +22012,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Порядок линеек: предлагаю V-TECH FACE → PEELING → BIOSPICULE → DEVICES → HAIR. Так цвет окружения меняется на каждом шаге, а приборы идут сразу перед HAIR, где они шаги 1–2 протокола. Оставить так или взять порядок из таблицы палитры (V-TECH FACE, HAIR, PEELING, BIOSPICULE, DEVICES)?</t>
+          <t>Обозначения ключей: «slug:ключ» — ключ другой страницы в storyboard.he.json; «slug:cat.поле» — та же страница в product-pages.he.json (индекс тот же, что в product-pages.json); «catalog.chips[i]» — i-й пункт строки «Chips HE» листа Catalog (0 הכל … 2 פילינג, 4 שיער, 5 ביו-ספיקולות, 6 טיפוח ביתי, 7 מכשור); «#n» — n-й сегмент строки, разделённой « · »; «A + « – » + B» — склейка проверенных строк в одну (строка экрана 5, легенда экрана 7); «new:» — строка из new_strings. Сборщик примет такую адресацию?</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr"/>
@@ -22382,7 +22025,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Подписи линеек в доке и под группами: сейчас это ивритские названия фильтров каталога (פילינג, ביו-ספיקולות, מכשור, שיער) плюс латинская марка V-TECH FACE. Или везде латинские марки серий (V-TECH FACE · PEELING · BIOSPICULE · DEVICES · HAIR), как бейдж на странице MASK?</t>
+          <t>Порядок линеек: предлагаю V-TECH FACE → PEELING → BIOSPICULE → DEVICES → HAIR. Так цвет окружения меняется на каждом шаге, а приборы идут сразу перед HAIR, где они шаги 1–2 протокола. Оставить так или взять порядок из таблицы палитры (V-TECH FACE, HAIR, PEELING, BIOSPICULE, DEVICES)?</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr"/>
@@ -22395,7 +22038,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Бейдж домашнего ухода: в правилах палитры, в фильтрах каталога и в eyebrow товаров — «טיפוח ביתי», а проверенный home.sl-3 по глоссарию — «טיפול ביתי». Какое слово оставить на главной?</t>
+          <t>Подписи линеек в доке и бейджах: сейчас это ивритские названия фильтров каталога (פילינג, ביו-ספיקולות, מכשור, שיער) плюс латинская марка V-TECH FACE. Или везде латинские марки серий (V-TECH FACE · PEELING · BIOSPICULE · DEVICES · HAIR), как бейдж на странице MASK?</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr"/>
@@ -22408,14 +22051,10 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>MITOTECH CELL BOOSTER: к какой линейке он относится? В Figma главной он в ряду приборов, в Excel стоит «уточнить». Есть ли фото упаковки (два флакона) и их объём? Пока он показан только карточкой «חדש · בקרוב» без 3D.</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>В протоколах заказчика: два флакона — бустер и концентрат-порошок, смешать до прозрачного раствора, до 2 мл на лицо, шею и декольте. Линейка там не указана.</t>
-        </is>
-      </c>
+          <t>Бейдж домашнего ухода: в правилах палитры, в фильтрах каталога и в eyebrow товаров — «טיפוח ביתי», а проверенный home.sl-3 по глоссарию — «טיפול ביתי». Какое слово оставить на главной?</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -22425,10 +22064,14 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Нужны фото: студийный пакшот EXOSIGNAL SPRAY — флакон и коробка, без руки (сейчас только фото в руке и снимок 400×300). По желанию: EXO-NAD Biphasic Peel крупнее и боковые грани коробок V-TECH SYSTEM, EXOSIGNAL HAIR и BIOSPICULE — без них бока будут гладкого цвета без печати.</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr"/>
+          <t>MITOTECH CELL BOOSTER: к какой линейке он относится? В Figma главной он в ряду приборов, а в листе Catalog (Card 13) — PRO, фильтр [Exosomes], линейка «уточнить». Есть ли фото упаковки (два флакона) и их объём? Пока он показан только карточкой «חדש · בקרוב» без 3D.</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>В протоколах заказчика: два флакона — бустер и концентрат-порошок, смешать до прозрачного раствора, до 2 мл на лицо, шею и декольте. Линейка там не указана.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -22438,14 +22081,10 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Контакты на экране 7 (номер WhatsApp, телефон, e-mail): берём те же, что на утверждённом образце EXOCELL MASK?</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Как на mitoderm.com (заказчик 11/10): кнопка WhatsApp +972-54-762-1889, телефон 054-326-2182, почта info@mitoderm.com (Mitoderm@gmail.com — только для мероприятий). Срок обратного звонка не пишем.</t>
-        </is>
-      </c>
+          <t>Нужны фото: студийный пакшот EXOSIGNAL SPRAY — флакон и коробка, без руки. До него на главной флакона и тумана нет, только маленькая коробка в глубине. Для крупного плана — одна ампула EXOSIGNAL HAIR на прозрачном фоне. По желанию: Biphasic Peel крупнее и боковые грани коробок V-TECH SYSTEM, EXOSIGNAL HAIR, EXO-NAD и BIOSPICULE — без них бока будут ровного цвета без печати.</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -22455,20 +22094,24 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>В герое 12 упаковок сразу. Оставить всю линейку или на десктопе тоже показывать по одной главной упаковке на линейку, а остальные — по наведению?</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr"/>
+          <t>Контакты на экране 7 (номер WhatsApp, телефон, e-mail): берём те же, что на утверждённом образце EXOCELL MASK?</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Как на mitoderm.com (заказчик 11/10): кнопка WhatsApp +972-54-762-1889, телефон 054-326-2182, почта info@mitoderm.com (Mitoderm@gmail.com — только для мероприятий). Срок обратного звонка не пишем.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>CATALOG</t>
+          <t>Home — MITODERM</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Пять линеек на четыре экрана: V-TECH FACE и HAIR стоят на одном экране, потому что у обеих чёрный с золотом и обе — синтетические экзосомы VM. Оставляем так или объединить героя с полкой категорий, чтобы у каждой линейки был свой экран?</t>
+          <t>Герой: (а) показывать все 12 упаковок сразу или на десктопе тоже по одной главной на линейку, а остальные — по наведению? (б) Кнопка home.b2 «מוצרים מקצועיים» ведёт в каталог, но фильтра «מקצועי» в каталоге нет: открывать на «הכל» или добавить такой фильтр? (в) Цифру «4 עקרונות ליבה» убрали из ряда доверия, потому что сами принципы раскрыты только на странице About. Согласны?</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr"/>
@@ -22481,14 +22124,10 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>MITOTECH CELL BOOSTER: линейка не подтверждена, фото и надписей упаковки нет. Сейчас он стоит на экране приборов карточкой «בקרוב» без 3D, как на главной. Это верно или его место в V-TECH FACE (в листе Catalog у него фильтр Exosomes)? И для 3D нужен пакшот двух флаконов.</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>В протоколах заказчика: два флакона — бустер и концентрат-порошок, смешать до прозрачного раствора, до 2 мл на лицо, шею и декольте. Линейка там не указана.</t>
-        </is>
-      </c>
+          <t>Пять линеек на четыре экрана: V-TECH FACE и HAIR стоят на одном экране, потому что у обеих чёрный с золотом и обе — синтетические экзосомы VM. Оставляем так или дать HAIR свой экран, а героя объединить с полкой категорий?</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -22498,10 +22137,14 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Домашний уход: в листе Catalog и в design-rules бейдж и чип — «טיפוח ביתי», а на главной (home.sl-3) и в глоссарии — «טיפול ביתי». Какое слово ставим везде?</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr"/>
+          <t>MITOTECH CELL BOOSTER: линейка не подтверждена, пакшота и текста упаковки нет. Сейчас он стоит на экране приборов карточкой «בקרוב» без 3D, как на главной, и виден только при чипе «All»; в листе Catalog у него фильтр Exosomes. К какой линейке и каким чипам его отнести? Для 3D нужен пакшот двух флаконов.</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>В протоколах заказчика: два флакона — бустер и концентрат-порошок, смешать до прозрачного раствора, до 2 мл на лицо, шею и декольте. Линейка там не указана.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -22511,7 +22154,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Бейджи линеек: V-TECH FACE, HAIR и PEELING — латиницей, как в листе Catalog, BIOSPICULE™ — как в каталоге, у приборов — «מכשור». Оставить HAIR и PEELING латиницей или писать «שיער» и «פילינג», как в чипах?</t>
+          <t>Домашний уход: в листе Catalog и в design-rules стоит «טיפוח ביתי», а на главной (home.sl-3) и в глоссарии — «טיפול ביתי». На каталоге бейдж и чип берутся из одного ключа catalog.chips[6], так что один ответ поменяет оба. Какое слово ставим на всём сайте?</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr"/>
@@ -22524,10 +22167,14 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Фильтр «Masks»: на каталоге окружение линейки V-TECH FACE (чёрный с золотом) и узкое бирюзовое свечение под коробкой, а бирюзовое окружение MASK остаётся на её странице. Согласны?</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr"/>
+          <t>Главная кнопка каталога — «לקבלת פרטים על מחירים», как на страницах средств; при чипе Home care вместо неё стоит «איפה לקנות». В листе Catalog и на главной стоит «Contact us / צרו קשר». Исправить лист под кнопку цены или оставить «צרו קשר»?</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Таблицу специалистов заказчик пришлёт позже (11/10). До неё кнопка ведёт на форму заявки, без JS — в WhatsApp.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -22537,7 +22184,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>EXOSIGNAL SPRAY: студийного пакшота нет, есть только рендер 400×300 на белом и фото в руке. Пришлёте прозрачный пакшот коробки и флакона в высоком разрешении?</t>
+          <t>Бейджи линеек сделаны как на главной: V-TECH FACE латиницей, остальные — словами чипов (פילינג, שיער, ביו-ספיקולות, מכשור). Так подходит или PEELING, HAIR и BIOSPICULE™ писать латиницей, как в листе Catalog?</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr"/>
@@ -22550,7 +22197,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Боковины коробок: печать известна только у EXOCELL MASK (есть фото боковины) и EXOTECH GEL (видна на пакшоте). У остальных при повороте боковины будут гладкими в цвет коробки, без надписей. Пришлёте фото боковин или оставить так?</t>
+          <t>Чип «Masks»: на каталоге дым остаётся в чёрном с золотом V-TECH FACE, а бирюза EXOCELL — только каплей под коробкой; бирюзово-синее окружение MASK остаётся на её собственной странице. Согласны?</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr"/>
@@ -22563,7 +22210,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>DERMA RECOVERY CREAM и CELLULAR AGE DEFENSE 2.5% в карточках показаны только коробками: фото баночки и флакона в репозитории нет, а на рендере флакона ещё и «CELL CELLULAR». Нужна ли ёмкость рядом с коробкой?</t>
+          <t>Печать боковин известна только у EXOCELL MASK и EXOTECH GEL, поэтому только они стоят в 3/4. Остальные коробки стоят почти фасадом (до 12°) и поворачиваются только к фасаду. Пришлёте фото боковин, чтобы и их поставить в 3/4?</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr"/>
@@ -22576,10 +22223,14 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>У четырёх карточек (EXOSIGNAL HAIR, MICRO BOOST 10%, EXOTECH GEL, EXOSIGNAL SPRAY) у текста из листа Catalog нет проверенного иврита, поэтому стоят проверенные слоганы с их страниц. Подходит?</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr"/>
+          <t>Контакты на экране 7 (WhatsApp, телефон, e-mail) — те же, что на образце EXOCELL MASK?</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Как на mitoderm.com (заказчик 11/10): кнопка WhatsApp +972-54-762-1889, телефон 054-326-2182, почта info@mitoderm.com (Mitoderm@gmail.com — только для мероприятий). Срок обратного звонка не пишем.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -22589,27 +22240,10 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Какие номер WhatsApp, телефон и адрес почты ставить на экран связи? В источниках их нет.</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Как на mitoderm.com (заказчик 11/10): кнопка WhatsApp +972-54-762-1889, телефон 054-326-2182, почта info@mitoderm.com (Mitoderm@gmail.com — только для мероприятий). Срок обратного звонка не пишем.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Техническое, для сборщика Excel: каталог берёт тексты других страниц — cat[slug].поле, sb[slug].ключ и sb[slug].b6.cta[i] (i-й фрагмент через « · »). site/tools/story3d_xlsx.py пока понимает только ключи своей страницы: без доработки в Excel будет «⚠ нет ключа».</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr"/>
+          <t>Техническое, для сборщика Excel: site/tools/story3d_xlsx.py уже понимает cat[slug].…, sb[slug].…, b6.cta[i] (счёт с нуля) и home:ключ. Но индекс внутри новой строки он не берёт: catalog.chips[i] выходит как «⚠ нет ключа» (на главной то же самое). Нужно доработать: поддержать [i] для новых строк и искать catalog.* с любой страницы.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mitoderm-catalog/site/MITODERM-3D-story.xlsx
+++ b/mitoderm-catalog/site/MITODERM-3D-story.xlsx
@@ -438,22 +438,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,60 +463,55 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Статус</t>
+          <t>Slug</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Slug</t>
+          <t>Линейка</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Линейка</t>
+          <t>Назначение</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Назначение</t>
+          <t>Цветовое окружение</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Цветовое окружение</t>
+          <t>Экран с оттенком серии</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Экран с оттенком серии</t>
+          <t>Герой-объект</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Герой-объект</t>
+          <t>Сюжет одной строкой</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Сюжет одной строкой</t>
+          <t>Метки специалистов</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Метки специалистов</t>
+          <t>Фото заказчика (№ в коллаже)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Фото заказчика (№ в коллаже)</t>
+          <t>Новых строк</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Новых строк</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Вопросов</t>
         </is>
@@ -531,56 +525,51 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>v-tech-system</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>v-tech-system</t>
+          <t>V-TECH FACE</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>V-TECH FACE</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
           <t>Линейка V-TECH FACE: чёрный с золотом. Фон бренда #0a0a0b. Дальний слой — медленный золотой дым и золотые искры: золото #c9a24b, светлое #d8bd7e, глубокое #9c7a2f. Весь слой поворачивается за курсором. За коробкой — узкое тёплое золотое свечение. Своей «капли» у V-TECH нет, поэтому по правилу акцент несёт цвет линейки. Янтарь флаконов и золото фольги — цвета самих упаковок, страницу в них не красим. Плоскость кожи тёплая и тёмная, её освещает золото линейки, нового цвета она не вводит. Коробка в зеркальной фольге отражает дальний слой, так что окружение видно и в самом герое. Страница чёрная, поэтому ставим белый логотип, а не монограмму M. Цветов других линеек на странице нет: финиш EXOCELL MASK и DERMA RECOVERY CREAM дан чипами-ссылками в цветах страницы, без бирюзы MASK, без зелени BIOSPICULE и без 3D-объектов. Самое яркое золото дыма — на экране 4, это сияние результата. Цвет V-TECH FACE совпадает с базой бренда и с линейкой HAIR, поэтому серию называет бейдж: тройка бейджей образца MASK (ui.line_mark, ui.line_name, home.tg) стоит на экране 1 и повторяется на экране 7.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Высокая коробка в зеркальной золотой фольге с чёрными полосами сверху и снизу. На фасаде серебряное VM, большой чёрный знак V с треугольником и V-TECH / S Y S T E M. Внутри чёрный ложемент (фото заказчика №44, Figma 113:8161): саше гель-маски из золотой фольги лежат плашмя (на фото видно верхнее), пять янтарных флаконов стоят в гнёздах. В наборе 5 флаконов сыворотки и 5 саше гель-маски.</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Высокая коробка в зеркальной золотой фольге с чёрными полосами сверху и снизу. На фасаде серебряное VM, большой чёрный знак V с треугольником и V-TECH / S Y S T E M. Внутри чёрный ложемент (фото заказчика №44, Figma 113:8161): саше гель-маски из золотой фольги лежат плашмя (на фото видно верхнее), пять янтарных флаконов стоят в гнёздах. В наборе 5 флаконов сыворотки и 5 саше гель-маски.</t>
+          <t>Зеркальная золотая коробка ложится и открывает чёрный ложемент, из гнёзд поднимаются пять янтарных флаконов, капля сыворотки с экзосомами уходит в открытые иглами микроканалы, золотое саше кладёт поверх слой геля без смывания, и рельеф кожи под ним выравнивается; в коробке пять флаконов и пять саше, курс — не меньше четырёх процедур раз в две недели.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Зеркальная золотая коробка ложится и открывает чёрный ложемент, из гнёзд поднимаются пять янтарных флаконов, капля сыворотки с экзосомами уходит в открытые иглами микроканалы, золотое саше кладёт поверх слой геля без смывания, и рельеф кожи под ним выравнивается; в коробке пять флаконов и пять саше, курс — не меньше четырёх процедур раз в две недели.</t>
+          <t>פנים</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>פנים</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
           <t>40, 42, 44–50, 53, 54, 60, 78–80, 82, 83</t>
         </is>
       </c>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="2" t="n">
         <v>9</v>
       </c>
     </row>
@@ -592,56 +581,51 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>exo-nad</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>exo-nad</t>
+          <t>PEELING</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>PEELING</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
           <t>Линейка PEELING по правилу «лицо / волосы / пилинг — чёрное с золотом». Фон — база бренда #0a0a0b, поверхности #111114 / #1a1a1f, текст крем #f6f3ec. Цвет линейки по таблице палитры — шампань-золото #d8c48a. Им окрашены дым и свечение дальнего слоя, свечение за коробкой и бейдж линейки. Частицы фона — мелкие шампань-золотые искры самого фона, а не хлопья из флакона: хлопья остаются внутри стекла, потому что золота нет в cat.ingredients. На экране 2 искры тускнеют до серо-бежевой матовой пыли, на экране 4 ложатся ровной вуалью. Волосяные линии, кикеры, выносные линии, линия шагов, подсветка гнёзд ложемента и кнопка цены — золото бренда #c9a24b (светлое #d8bd7e). Своей капли у EXO-NAD в правилах нет, поэтому работает цвет линейки. Янтарь и голубизна есть только на самих флаконах. Бирюзового дыма и свечения нет: это окружение MASK, а два цвета линеек на одной странице запрещены. Чёрный ложемент с золотой печатью (фото заказчика 29) сам лежит в этой гамме. Страница чёрная, поэтому логотип белый; монограммы M нет, она для BIOSPICULE. Бейдж линейки: без рамки и без заливки, текст PEELING цветом #d8c48a с маленькой шампань-точкой впереди, отделён промежутком от залитого золотом «מקצועי». Золотой контур не используется: он означает «טיפוח ביתי». Бейдж одинаковый на экранах 1 и 7. Оттенок серии впервые появляется на экране 1 (шампань-свечение за коробкой и бейдж PEELING), на экране 7 повторяется и становится сильнее всего.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Квадратная коробка EXO-NAD из брашированного золота. Крышка поднимается прямо вверх, как на фото заказчика 26 и 32, и открывает чёрный ложемент (фото 29). Слева в высоком гнезде стоит флакон пилинга с золотым колпачком, в верхнем ряду — 5 флаконов pH Normalizer, в нижнем — 5 флаконов Longevity Serum. На самом ложементе золотом напечатаны шаги ① EXO-NAD PEELING, ② PH NORMALIZER, ③ LONGEVITY SERUM. Для экранов 3–5 используются отдельные модели, по одной каждого вида: флакон пилинга, флакон pH Normalizer и флакон Longevity Serum.</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Квадратная коробка EXO-NAD из брашированного золота. Крышка поднимается прямо вверх, как на фото заказчика 26 и 32, и открывает чёрный ложемент (фото 29). Слева в высоком гнезде стоит флакон пилинга с золотым колпачком, в верхнем ряду — 5 флаконов pH Normalizer, в нижнем — 5 флаконов Longevity Serum. На самом ложементе золотом напечатаны шаги ① EXO-NAD PEELING, ② PH NORMALIZER, ③ LONGEVITY SERUM. Для экранов 3–5 используются отдельные модели, по одной каждого вида: флакон пилинга, флакон pH Normalizer и флакон Longevity Serum.</t>
+          <t>Закрытая золотая коробка стоит в тусклой пыли, из-за неё по порядку выходят три жидкости одного визита, их общий свет превращает пыль в ровное шампань-сияние, а в конце крышка поднимается, как на фото заказчика, и показывает ложемент с напечатанными шагами 1-2-3: 1 флакон и 5 + 5 флаконов.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Закрытая золотая коробка стоит в тусклой пыли, из-за неё по порядку выходят три жидкости одного визита, их общий свет превращает пыль в ровное шампань-сияние, а в конце крышка поднимается, как на фото заказчика, и показывает ложемент с напечатанными шагами 1-2-3: 1 флакон и 5 + 5 флаконов.</t>
+          <t>פנים</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>פנים</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
           <t>26–32, 35, 39, 51, 63, 64, 84</t>
         </is>
       </c>
+      <c r="K3" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -653,58 +637,53 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>exocell-mask</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>exocell-mask</t>
+          <t>V-TECH FACE</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>V-TECH FACE</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
           <t>MASK — исключение из правила линейки: вместо чёрно-золотого окружения V-TECH FACE у неё своё бирюзово-синее. Фон страницы — база бренда #0a0a0b. Дальний слой: медленный бирюзовый дым (EXOCELL #6fb7ba, фасад коробки #5ca0a5) и редкие светлые частицы, вместе поворачиваются за указателем. Передний план: прозрачные бирюзовые капли сыворотки, слои маски #dcf0f5 и бледно-голубой. Золото бренда #c9a24b — только волосяные линии кикеров, бейдж «מקצועי» (home.tg, золотая заливка) и кнопка цены. Чипы-ссылки на другие средства (экраны 2 и 6) — кремовый контур #f6f3ec, не золото: на шаге «зачем» они не должны выглядеть главным действием. Оттенок серии: бейдж line.mark «V-TECH FACE» на экране 1, а на экране 7 за карточкой «что внутри» горит тёплое золотое свечение V-TECH FACE (эллипс ~900 px) и стоит бейдж линейки, чтобы посетитель видел серию. Зелёный BIOSPICULE не смешивается; бирюза капли не заливает плоскости сверх окружения.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="F4" s="2" t="n">
         <v>7</v>
       </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Коробка EXOCELL MASK — тёмно-бирюзовый портретный картон (#5ca0a5) с тёмно-синей печатью, версия «Your Second Skin» (как на пакшоте и на утверждённом 03-mirror). Кубоид: фасад site/img/exocell-box-front.jpg и левая боковина site/img/exocell-box-side.jpg, обе выпрямлены из protocols/assets/img/exocell-mask.webp. Правая грань, верх, низ и оборот — гладкий #5ca0a5 без печати (их печать неизвестна). Ракурс как на пакшоте: коробка повёрнута вправо, видна левая боковина.</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Коробка EXOCELL MASK — тёмно-бирюзовый портретный картон (#5ca0a5) с тёмно-синей печатью, версия «Your Second Skin» (как на пакшоте и на утверждённом 03-mirror). Кубоид: фасад site/img/exocell-box-front.jpg и левая боковина site/img/exocell-box-side.jpg, обе выпрямлены из protocols/assets/img/exocell-mask.webp. Правая грань, верх, низ и оборот — гладкий #5ca0a5 без печати (их печать неизвестна). Ракурс как на пакшоте: коробка повёрнута вправо, видна левая боковина.</t>
+          <t>Коробка EXOCELL MASK среди капель сыворотки открывается, из неё поднимается двойная маска из биоцеллюлозы и ложится на лицо; потом из коробки разлетаются все пять саше, поверх встают три коротких шага протокола, и всё собирается в экран покупки с тёплым золотом линейки V-TECH FACE.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Коробка EXOCELL MASK среди капель сыворотки открывается, из неё поднимается двойная маска из биоцеллюлозы и ложится на лицо; потом из коробки разлетаются все пять саше, поверх встают три коротких шага протокола, и всё собирается в экран покупки с тёплым золотом линейки V-TECH FACE.</t>
+          <t>פנים</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>פנים</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
           <t>11–24 (саше, двойная маска, нанесение)</t>
         </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="M4" s="2" t="n">
-        <v>7</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -714,56 +693,51 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>exosignal-hair</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>exosignal-hair</t>
+          <t>HAIR</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>HAIR</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
           <t>Линейка HAIR: чёрный и золото. По design-rules.md это тот же цвет, что у V-TECH FACE и у базы бренда. Фон #0a0a0b, тёплый золотой дым малой плотности (#9c7a2f → #c9a24b), золотые частицы #d8bd7e, свечение за коробкой #c9a24b. Капли цвета нет: жидкость в ампулах бесцветная (это видно на пакшоте), поэтому работает цвет линейки (правило «Капля средства»). Стекло ампул даёт только холодный белый блик. Проблема на экране 2 показана тусклым кремово-серым (#f6f3ec, прозрачность около 30%). Золото включается только там, где начинается решение. MITOSCAN и MITOPEN стоят в холодном нейтральном свете своих материалов, без золотой подсветки и без окружения DEVICES: смешивать на одной странице цвета двух линеек нельзя. Золото HAIR совпадает с базой, поэтому оттенок серии передаётся контрастом, а не цветом всей страницы. На экране 5 дым почти гаснет, устройства приглушены, и тёплое золотое пятно остаётся только под ампулой и флаконом EXOSIGNAL SPRAY (оба средства линейки HAIR). Над ними стоит бейдж линейки line.mark. Тот же бейдж есть в ряду бейджей на экранах 1 и 7. Это штатное окружение линейки, а не исключение, как у MASK.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="F5" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Стеклянная ампула EXOSIGNAL HAIR на 5 мл: прозрачное стекло, бесцветная жидкость, белое кольцо на горлышке. Крупная вертикальная надпись 'EXOSIGNAL' ('EXO' жирным), рядом мелкие вертикальные строки: 'EXOSIGNAL HAIR', 'Siero nutriente per il cuoio capelluto' и другие, нечитаемые. На обороте тоже есть печать, сквозь стекло она видна зеркально. Ампула стоит на фоне плоской матово-чёрной коробки с золотыми 'EXOSIGNAL' / 'H A I R'.</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Стеклянная ампула EXOSIGNAL HAIR на 5 мл: прозрачное стекло, бесцветная жидкость, белое кольцо на горлышке. Крупная вертикальная надпись 'EXOSIGNAL' ('EXO' жирным), рядом мелкие вертикальные строки: 'EXOSIGNAL HAIR', 'Siero nutriente per il cuoio capelluto' и другие, нечитаемые. На обороте тоже есть печать, сквозь стекло она видна зеркально. Ампула стоит на фоне плоской матово-чёрной коробки с золотыми 'EXOSIGNAL' / 'H A I R'.</t>
+          <t>Из чёрной коробки выходит одна ампула; на фоне тусклых падающих нитей золотой прицел измерения задаёт точку отсчёта; у ампулы отламывается горлышко, и капля становится экзосомой с PDRN и восемью пептидами; из кожи головы вырастают четыре золотые пряди; путь «измерить → открыть → доставить → дома» отмечен золотом линейки HAIR; в конце пять запечатанных ампул, пять сеансов, собираются в одну коробку.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Из чёрной коробки выходит одна ампула; на фоне тусклых падающих нитей золотой прицел измерения задаёт точку отсчёта; у ампулы отламывается горлышко, и капля становится экзосомой с PDRN и восемью пептидами; из кожи головы вырастают четыре золотые пряди; путь «измерить → открыть → доставить → дома» отмечен золотом линейки HAIR; в конце пять запечатанных ампул, пять сеансов, собираются в одну коробку.</t>
+          <t>קרקפת · טריכולוג/ית</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>קרקפת · טריכולוג/ית</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
           <t>36, 47, 55, 58</t>
         </is>
       </c>
+      <c r="K5" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="L5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" s="2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -775,56 +749,51 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>exosignal-spray</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>exosignal-spray</t>
+          <t>HAIR</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>HAIR</t>
+          <t>home care</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>home care</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
           <t>Линейка HAIR: чёрный фон #0a0a0b и золото #c9a24b (светлое #d8bd7e, глубокое #9c7a2f). Дальний слой — медленный тёплый золотисто-коричневый дым и золотые частицы на чёрном, он поворачивается за курсором. Туман спрея — матово-белые капли: это цвет самого стекла, а не отдельный цвет. Своей «капли» у спрея нет, поэтому работает цвет линейки (правило палитры). Серебро #d9d4cc из старого site/prompts/exosignal-spray.md не используем: это цвет линейки DEVICES, а два цвета линеек на одной странице смешивать запрещено. Исключением, как MASK, страница не является. Цвет HAIR совпадает с базой бренда и с V-TECH FACE, поэтому одним цветом серию не показать. Серию обозначает знак: пара бейджей ui.line_mark «HAIR» + ui.line_name рядом с ui.use_home «טיפוח ביתי» (золотой контур) на экранах 1, 2 и 7, а на экране 2 — пакшот EXOSIGNAL HAIR, на котором читается надпись, с подписью b6.label4. Самый яркий золотой контровой свет на странице бывает только на экране 7.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Флакон-спрей EXOSIGNAL SPRAY HOME на 15 мл: цилиндр из матового полупрозрачного стекла, золотой металлический рифлёный колпачок, вертикальная надпись EXOSIGNAL. Колпачок надет на всех экранах: распылитель под ним не снят на фото. Второй объект — высокая матовая чёрная коробка с золотой и белой печатью. Знак линейки — пакшот EXOSIGNAL HAIR в глубине на экранах 2 и 5.</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Флакон-спрей EXOSIGNAL SPRAY HOME на 15 мл: цилиндр из матового полупрозрачного стекла, золотой металлический рифлёный колпачок, вертикальная надпись EXOSIGNAL. Колпачок надет на всех экранах: распылитель под ним не снят на фото. Второй объект — высокая матовая чёрная коробка с золотой и белой печатью. Знак линейки — пакшот EXOSIGNAL HAIR в глубине на экранах 2 и 5.</t>
+          <t>Матовый стеклянный флакон с золотым колпачком выходит из тени своей чёрной коробки и превращается в золотую нить между двумя визитами EXOSIGNAL HAIR; облачко тумана, входящее в кадр сверху, решает три задачи и ложится на проборы без смывания, а в конце флакон возвращается к своей коробке на экране покупки.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Матовый стеклянный флакон с золотым колпачком выходит из тени своей чёрной коробки и превращается в золотую нить между двумя визитами EXOSIGNAL HAIR; облачко тумана, входящее в кадр сверху, решает три задачи и ложится на проборы без смывания, а в конце флакон возвращается к своей коробке на экране покупки.</t>
+          <t>קרקפת · טריכולוג/ית</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>קרקפת · טריכולוג/ית</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
           <t>2, 3, 21, 33, 34, 41, 43, 59, 65</t>
         </is>
       </c>
+      <c r="K6" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="L6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -836,56 +805,51 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>exotech-gel</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>exotech-gel</t>
+          <t>V-TECH FACE</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>V-TECH FACE</t>
+          <t>home care</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>home care</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
           <t>Линейка V-TECH FACE, поэтому чёрный с золотом. Фон #0a0a0b. Дальний слой — медленный тёплый дым от #0a0a0b к глубокому золоту #9c7a2f с бликами #c9a24b и частицами-пылинками #d8bd7e; слой поворачивается за указателем. За упаковкой узкое золотое свечение. Своей «капли» у средства нет: упаковка сама золотая, поэтому работает золото линейки. На объектах остаётся собственное, более жёлтое золото фольги с пакшота, брендовым золотом его не подменяем. Свет на предметах и фон разделены. Куб и сфера отражают отдельную тёплую студийную карту окружения с 2–3 крупными софтбоксами: блики сверху слева и справа, как на фото. Дым рендерится только фоном и подмешивается в отражения слабым слоем, поэтому дым только тёплый, без холодных и зелёных оттенков. У фасада куба roughness около 0,35–0,5. Проверка до сборки: один тестовый рендер экрана 1, на котором надписи EXOTECH / GEL на кубе и на сфере читаются на чёрном фоне. На экране 5 BIOSPICULE упоминается только текстом, без зелёного цвета: смешивать цвета линеек запрещено. Логотип белый, так как страница чёрная. Назначение показывает бейдж «טיפוח ביתי» (b0.label1) с золотым контуром, а не цвет фона. Элемент серии (line.mark «V-TECH FACE» с мелкой подписью «סדרת האקסוזומים הסינתטיים») стоит кикером на экране 1 и повторяется на экране 7. На экране 7 золото за упаковками разгорается теплее.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Золотая полированная сфера-банка EXOTECH GEL, 30 мл. Крышка — верхняя полусфера со всей надписью: 'EXOTECH' ('EXO' жирным, 'TECH' тонким) и под ним курсив с разрядкой 'GEL'. Шов — экватор. Пакшот снят чуть сверху, поэтому спереди шов проходит под 'GEL'. Основание — гладкое золото без печати. Рядом её внешняя упаковка — зеркально-золотой куб с чёрной левой гранью и золотым диагональным клином.</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Золотая полированная сфера-банка EXOTECH GEL, 30 мл. Крышка — верхняя полусфера со всей надписью: 'EXOTECH' ('EXO' жирным, 'TECH' тонким) и под ним курсив с разрядкой 'GEL'. Шов — экватор. Пакшот снят чуть сверху, поэтому спереди шов проходит под 'GEL'. Основание — гладкое золото без печати. Рядом её внешняя упаковка — зеркально-золотой куб с чёрной левой гранью и золотым диагональным клином.</t>
+          <t>Золотая сфера выходит вперёд от своего зеркального куба, приподнимает крышку со всей надписью над светящейся щелью и выпускает пять капель активов; капли сливаются в невесомую плёнку, которая ложится на зрителя, а свет обходит сферу от утра до вечера — протокол клиники каждый день продолжается дома.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Золотая сфера выходит вперёд от своего зеркального куба, приподнимает крышку со всей надписью над светящейся щелью и выпускает пять капель активов; капли сливаются в невесомую плёнку, которая ложится на зрителя, а свет обходит сферу от утра до вечера — протокол клиники каждый день продолжается дома.</t>
+          <t>פנים</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>פנים</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
           <t>37, 38, 52</t>
         </is>
       </c>
+      <c r="K7" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="L7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M7" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -897,56 +861,51 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>micro-boost-10</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>micro-boost-10</t>
+          <t>BIOSPICULE</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>BIOSPICULE</t>
+          <t>professional</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>professional</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
           <t>Окружение линейки BIOSPICULE (design-rules, «палитра по линейкам»: BIOSPICULE = зелёный). Дым #1E4634 на тёмном #12382A уходит в чёрный бренда #0a0a0b. Золото бренда #c9a24b (светлое #d8bd7e): волосяные линии, кикеры, кнопка цены, искры массажа, дуга-таймер, кольцо-ореол. Золотая монограмма M (site/img/mitoderm-m-gold.png) проступает в дыму. Частицы — тонкие полупрозрачные спикулы с тёмно-зелёным тоном, как на медальоне коробки, с золотыми бликами. Своей капли у MICRO BOOST нет: по design-rules у средства без своего цвета капли нет, работает цвет линейки. Мятный #4fb285 из старого промпта не используется, это капля CELL RENEW; вопрос решён в design-rules, заказчику его не задаём. Шалфей #9AA889 только на мини-коробке DERMA RECOVERY CREAM (та же линейка). Бирюзы MASK и цветов других линеек на странице нет: смешивать две линейки запрещено.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Высокая узкая коробка цвета слоновой кости. На ней тёмно-зелёная полоса с золотым «MICRO BOOST 10%» и круглый медальон в золотом кольце: светлый прозрачно-серебристый диск с тёмно-зелёными спикулами. Перед коробкой шприц 3 мл без иглы. Коробка — настоящий пакшот-герой, шприц — модель без печати до фото.</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Высокая узкая коробка цвета слоновой кости. На ней тёмно-зелёная полоса с золотым «MICRO BOOST 10%» и круглый медальон в золотом кольце: светлый прозрачно-серебристый диск с тёмно-зелёными спикулами. Перед коробкой шприц 3 мл без иглы. Коробка — настоящий пакшот-герой, шприц — модель без печати до фото.</t>
+          <t>Рой спикул из медальона на коробке сходится в шприц 3 мл. Спикулы проходят сквозь поверхность там, где пилинг останавливается. В капле они делятся на две длины и уходят на две глубины эпидермиса. Руки косметолога вмассировывают сыворотку, и спикулы могут работать до 72 часов. В конце коробка и шприц стоят на экране покупки.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Рой спикул из медальона на коробке сходится в шприц 3 мл. Спикулы проходят сквозь поверхность там, где пилинг останавливается. В капле они делятся на две длины и уходят на две глубины эпидермиса. Руки косметолога вмассировывают сыворотку, и спикулы могут работать до 72 часов. В конце коробка и шприц стоят на экране покупки.</t>
+          <t>פנים</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>פנים</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
           <t>6, 67–69, 72, 74, 77</t>
         </is>
       </c>
+      <c r="K8" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="L8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -958,56 +917,51 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>cell-renew-1-5</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>cell-renew-1-5</t>
+          <t>BIOSPICULE</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>BIOSPICULE</t>
+          <t>home care</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>home care</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
           <t>Окружение линейки BIOSPICULE: по правилу цвет линейки — главный акцент. Дальний фон — медленный зелёный дым от #12382A в глубине до #1E4634 у света. Частицы — те же иглы-веретёна в малом масштабе, редкие. Фото spicules-macro.png светлое, кремовое, поэтому в фон его не ставим; оно идёт только маской яркости в тоне #12382A с непрозрачностью не выше 15% на экране 3. Золото бренда #c9a24b появляется только в пяти местах. Первое — волосяные линии: выноски, тонкий кант зеркала, взятый с печати медальона, линия массажа на экране 4. Дальше — кикеры, главная кнопка, бейдж линейки и золотая монограмма M (site/img/mitoderm-m-gold.png) на экранах 1, 5 и 7. Капля средства — мятный #4fb285, не больше ~10% площади: узкое свечение медальона, редкие искры покалывания, контровой свет за каплей, точки меток. Сама капля сыворотки бесцветная, потому что цвет сыворотки нигде не задокументирован. Назначение показывает бейдж «טיפוח ביתי» с золотым контуром, а не цвет фона. Чёрной базы V-TECH и бирюзы MASK нет. Шалфей #9AA889 — только напечатанная полоса на коробке DERMA RECOVERY CREAM на экране 5, фон им не красим. Экран с оттенком серии — 5: за рядом коробок поднимаются золотая M и бейдж линейки «BIOSPICULE™», дым густеет до #1E4634, на двух передних коробках читается напечатанное «BIOSPICULE SYSTEM».</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="F9" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Высокая узкая коробка CELL RENEW 1.5% цвета слоновой кости — куб, фасад выпрямлен из protocols/print/img/cell-renew-15.webp. На ней зелёная полоса с золотой надписью «CELL RENEW / 1.5%» и круглый медальон в зелёном кольце с тёмно-зелёными спикулами. Медальон — сквозной мотив сюжета: его кольцо становится зеркалом, и через него зритель попадает внутрь. Кольцо строим геометрией, а не растягиваем из фото.</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Высокая узкая коробка CELL RENEW 1.5% цвета слоновой кости — куб, фасад выпрямлен из protocols/print/img/cell-renew-15.webp. На ней зелёная полоса с золотой надписью «CELL RENEW / 1.5%» и круглый медальон в зелёном кольце с тёмно-зелёными спикулами. Медальон — сквозной мотив сюжета: его кольцо становится зеркалом, и через него зритель попадает внутрь. Кольцо строим геометрией, а не растягиваем из фото.</t>
+          <t>Узкая коробка CELL RENEW 1.5% встаёт в зелёном дыму, её медальон становится тусклым зеркалом с узнаваемыми проблемами кожи, через него мы попадаем в редкое облако стеклянных игл и активов, после мягкого массажа дымка на стекле редеет и оно начинает сиять, коробка встаёт в ряд линии BIOSPICULE рядом с DERMA RECOVERY CREAM и следующим шагом 2.5%, а в конце идёт экран покупки, где показано, что внутри, и есть одна кнопка «Где купить».</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Узкая коробка CELL RENEW 1.5% встаёт в зелёном дыму, её медальон становится тусклым зеркалом с узнаваемыми проблемами кожи, через него мы попадаем в редкое облако стеклянных игл и активов, после мягкого массажа дымка на стекле редеет и оно начинает сиять, коробка встаёт в ряд линии BIOSPICULE рядом с DERMA RECOVERY CREAM и следующим шагом 2.5%, а в конце идёт экран покупки, где показано, что внутри, и есть одна кнопка «Где купить».</t>
+          <t>פנים</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>פנים</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
           <t>10, 70, 75, 67–69</t>
         </is>
       </c>
+      <c r="K9" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1019,56 +973,51 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>cellular-age-defense-2-5</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>cellular-age-defense-2-5</t>
+          <t>BIOSPICULE</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>BIOSPICULE</t>
+          <t>home care</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>home care</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
           <t>Окружение линейки BIOSPICULE зелёное. Фон #12382A, дым #1E4634, к краям он уходит в базу бренда #0a0a0b. Свечение за продуктом тоже зелёное и светлеет к центру. Частицы, нити пептидов и волосяные линии — золото бренда #c9a24b / #d8bd7e: оно повторяет золотую монограмму M и золотой текст на тёмно-зелёной полосе коробки. Своей капли у средства нет (по design-rules капля есть только у EXOCELL, CELL RENEW и MITOSCAN), поэтому акцент держит цвет линейки. Зелёный CELL RENEW #4fb285 как свечение не используем. Коробки CELL RENEW 1.5% (экран 2) и DERMA RECOVERY CREAM (экран 5; шалфейная полоса #9AA889 на её коробке) несут свой цвет только печатью, второго цвета линейки на странице нет. Шаг «Защита» — это временное потепление света, а не новый цвет. Оттенок серии показан на экране 1: глубокий зелёный, золотая монограмма M в дыму (размытая: файл — растр 600 px) и бейдж линейки. На экране 7 монограмма повторяется. Линейка и назначение передаются парой бейджей из cat.eyebrow: «סרום BIOSPICULE™» — бейдж линейки, «טיפוח ביתי» — золотой контур. Назначение цветом фона не передаём.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="F10" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Высокая узкая ивори-коробка CELLULAR AGE DEFENSE 2.5%: тёмно-зелёная полоса с золотым текстом, круглый медальон со спикулами, сверху золотая M. Это куб с фасадом из пакшота protocols/print/img/cellular-age-25.webp, поворот не больше ±20°. По умолчанию страница собирается только с коробкой. Белый airless-флакон 30 мл (фото №9 в Figma) раньше экрана 4 не появляется. Он добавляется только после ответа заказчика про печать 'CELL CELLULAR' и только на экранах 4 (крупно одна головка помпы) и 7.</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Высокая узкая ивори-коробка CELLULAR AGE DEFENSE 2.5%: тёмно-зелёная полоса с золотым текстом, круглый медальон со спикулами, сверху золотая M. Это куб с фасадом из пакшота protocols/print/img/cellular-age-25.webp, поворот не больше ±20°. По умолчанию страница собирается только с коробкой. Белый airless-флакон 30 мл (фото №9 в Figma) раньше экрана 4 не появляется. Он добавляется только после ответа заказчика про печать 'CELL CELLULAR' и только на экранах 4 (крупно одна головка помпы) и 7.</t>
+          <t>Коробка 2.5% встаёт на ступень выше CELL RENEW 1.5%, камера проходит сквозь её медальон, где через поле спикул идут пять золотых нитей пептидов, Bakuchiol и Adenosine (у 1.5% их нет), всё собирается в одну каплю, которая покалывает и требует мягких движений, а лестница ухода (2.5% → DERMA RECOVERY → дневная защита) ведёт к экрану покупки с одной коробкой 30 мл.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Коробка 2.5% встаёт на ступень выше CELL RENEW 1.5%, камера проходит сквозь её медальон, где через поле спикул идут пять золотых нитей пептидов, Bakuchiol и Adenosine (у 1.5% их нет), всё собирается в одну каплю, которая покалывает и требует мягких движений, а лестница ухода (2.5% → DERMA RECOVERY → дневная защита) ведёт к экрану покупки с одной коробкой 30 мл.</t>
+          <t>פנים</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>פנים</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
           <t>7, 9, 67–69</t>
         </is>
       </c>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1080,56 +1029,51 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>derma-recovery-cream</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>derma-recovery-cream</t>
+          <t>BIOSPICULE</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>BIOSPICULE</t>
+          <t>home care</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>home care</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
           <t>Зелёное окружение линейки BIOSPICULE (слово заказчика 11/10). База дальнего слоя — #12382A, дым — #1E4634. Подсветка за объектами — шалфей DERMA #9AA889: это цвет DERMA в таблице линеек и цвет полосы на коробке. Шалфей — «капля» средства, не больше ~10% площади. Он есть только у крема и барьера: свечение за банкой, лента крема, атласный слой, точки меток. Искры в дыму кремовые #f6f3ec. Иглы-спикулы на экране 2 естественного серо-оливкового цвета, как на site/img/spicules-macro.png. Шалфея в них нет, чтобы иглы не читались как часть крема. Золото бренда #c9a24b — волосяные линии, кикеры, главная кнопка, выноски. В шапке вместо белого логотипа стоит золотая монограмма M (site/img/mitoderm-m-gold.png). Оттенок серии — экран 5: дым густеет до насыщенного #1E4634, за объектами проступает крупная полупрозрачная золотая M. Исключений нет: бирюза MASK не используется. Мятный #4fb285 (капля CELL RENEW) тоже не используется, кроме печати на билборде её коробки. Золотые упаковки V-TECH и EXO-NAD в кадр не выводятся, эти средства есть только в тексте b4.line, чтобы на странице не было двух цветов линеек. Назначение показывает бейдж, а не цвет фона. Бейдж ui.use_home с золотым контуром стоит на экранах 1 и 7. У MICRO BOOST 10% на экране 5 маленький бейдж home.tg с золотой заливкой (по design-rules).</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="F11" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Матовая белая банка 50 мл. Материал в источниках не указан. Крышка матовая, над чёрным пояском: в packaging-text.json она clear frosted, на фото 1 выглядит белой. Банка лежит в коробке цвета слоновой кости с шалфейной полосой и золотой надписью DERMA RECOVERY / CREAM. Экран 1 открывает коробка, её фасад готов. Дальше герои — банка и сам белый крем. Фасад банки берётся с фото заказчика в Figma: фото 1, узел 93:8080, фасад с этикеткой. Открытая банка — фото 73, узел 113:8211. Поэтому банку показываем фасадом и поворачиваем не больше чем на ±20°. Задняя сторона банки не снята.</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Матовая белая банка 50 мл. Материал в источниках не указан. Крышка матовая, над чёрным пояском: в packaging-text.json она clear frosted, на фото 1 выглядит белой. Банка лежит в коробке цвета слоновой кости с шалфейной полосой и золотой надписью DERMA RECOVERY / CREAM. Экран 1 открывает коробка, её фасад готов. Дальше герои — банка и сам белый крем. Фасад банки берётся с фото заказчика в Figma: фото 1, узел 93:8080, фасад с этикеткой. Открытая банка — фото 73, узел 113:8211. Поэтому банку показываем фасадом и поворачиваем не больше чем на ±20°. Задняя сторона банки не снята.</t>
+          <t>После игл обновления приходит мягкость: банка поднимается из коробки и открывается без единой иглы, лента крема ложится на кожу у зеркала, а на зелёном экране серии обе ветки BIOSPICULE — домашние сыворотки и MICRO BOOST 10% в клинике — сходятся к DERMA.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>После игл обновления приходит мягкость: банка поднимается из коробки и открывается без единой иглы, лента крема ложится на кожу у зеркала, а на зелёном экране серии обе ветки BIOSPICULE — домашние сыворотки и MICRO BOOST 10% в клинике — сходятся к DERMA.</t>
+          <t>פנים</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>פנים</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
           <t>1, 5, 73</t>
         </is>
       </c>
+      <c r="K11" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" s="2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1141,56 +1085,51 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>mitopen</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>mitopen</t>
+          <t>DEVICES</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>DEVICES</t>
+          <t>device</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>device</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
           <t>Фон — тёмная база бренда #0a0a0b. Дальний слой поворачивается за курсором: медленный холодный серебряный дым #d9d4cc с тонкими прожилками шампань-металла #d8c48a и мелкая серебряная пыль. Это цвет линейки DEVICES, как на странице MITOSCAN. Серебро ведущее, потому что шампань #d8c48a у DEVICES совпадает с цветом линейки PEELING (EXO-NAD), и различить их можно только по серебру. К тому же перо цвета шампань лучше читается на серебре. По кромке пера идёт холодный серебряный контровой свет. Золото бренда #c9a24b используется только для волосяных линий, кикеров, бейджа назначения «מקצועי» (золотая заливка) и кнопок цены. Главная кнопка и кнопка в липкой панели — с заливкой #c9a24b и текстом #0a0a0b, как .btn.primary в proto/exocell-3d-template.html. Призрачные кнопки на экранах 1 и 5 — с золотым контуром. «Угольную заливку» из примечания к b6.cta не используем: #1a1a1f на #0a0a0b даёт контраст около 1.1:1. Своей капли у MITOPEN нет, поэтому работает цвет линейки. Единственное тёплое пятно на странице — розово-золотое кольцо и кнопка самого прибора. V-TECH SYSTEM и EXOSIGNAL HAIR на экране 5 стоят только как предметы, их цвета на фон не переносим: два цвета линеек на одной странице запрещены. MICRO BOOST 10% (зелёная BIOSPICULE) упоминается только меткой b4.label4. Оттенок серии — на экране 7: там самый яркий серебряный дым и контровой свет страницы, шампань идёт вторым цветом, а рядом с бейджем «מקצועי» стоит бейдж линейки «מכשור» (home.sl-2) с серебряным контуром.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="F12" s="2" t="n">
         <v>7</v>
       </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>MITOPEN — беспроводная ручка для микронидлинга. Корпус из металла цвета шампань-золото. Розово-золотое ребристое кольцо рукоятки (в packaging-text.json это «rose-gold knurled grip ring»; задаёт ли оно глубину, в источниках не сказано — вопрос 2). Такого же цвета кнопка с маленькой точкой над ней, прозрачный картридж с иглами. Надписи берём только с фото: вертикальная белая «MITOPEN» на корпусе и маленькая гравированная V у верхнего конуса. На пакшоте ось пера отклонена от вертикали примерно на 12° (замер по альфа-каналу mitopen.webp): конус вверху справа, картридж внизу слева. Коробки в источниках нет, поэтому героем идёт сам прибор.</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN — беспроводная ручка для микронидлинга. Корпус из металла цвета шампань-золото. Розово-золотое ребристое кольцо рукоятки (в packaging-text.json это «rose-gold knurled grip ring»; задаёт ли оно глубину, в источниках не сказано — вопрос 2). Такого же цвета кнопка с маленькой точкой над ней, прозрачный картридж с иглами. Надписи берём только с фото: вертикальная белая «MITOPEN» на корпусе и маленькая гравированная V у верхнего конуса. На пакшоте ось пера отклонена от вертикали примерно на 12° (замер по альфа-каналу mitopen.webp): конус вверху справа, картридж внизу слева. Коробки в источниках нет, поэтому героем идёт сам прибор.</t>
+          <t>MITOPEN задаёт глубину 0.25–2.5 мм и одну из пяти скоростей, прозрачный картридж оставляет ровную сетку временных микроканалов, а по ней уходят V-TECH SYSTEM в кожу лица и EXOSIGNAL HAIR в кожу головы: одна ручка — точная и повторяемая процедура.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>MITOPEN задаёт глубину 0.25–2.5 мм и одну из пяти скоростей, прозрачный картридж оставляет ровную сетку временных микроканалов, а по ней уходят V-TECH SYSTEM в кожу лица и EXOSIGNAL HAIR в кожу головы: одна ручка — точная и повторяемая процедура.</t>
+          <t>פנים · קרקפת</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>פנים · קרקפת</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
           <t>56, 57</t>
         </is>
       </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1202,56 +1141,51 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>mitoscan</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>mitoscan</t>
+          <t>DEVICES</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>DEVICES</t>
+          <t>device</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>device</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
           <t>База бренда: фон #0a0a0b. Дальний слой, дым и частицы, сделан в цвете линейки DEVICES по правилу «цветовое окружение по линейке»: холодный серебряный дым #d9d4cc с тёплыми прожилками шампань-металла #d8c48a и мелкая серебряная пыль. На белых корпусах и хроме лежит контровой свет шампань. MITOSCAN не исключение, в отличие от MASK. Капля средства — синий MITOSCAN #5aa9e6, не больше ~10% площади: свечение экрана, активный сегмент ×50 / ×200 и узкий рефлекс на щупе. Страницу целиком в синий не красим. Золото бренда #c9a24b идёт на волосяные выноски, кикеры, кнопку цены и бейдж «מקצועי» (home.tg, золотая заливка). Кнопка цены золотая по правилу палитры. Синяя заливка из EN-описания b6.cta противоречит правилу «капля ≤10%», её не берём. Бирюзово-фиолетовая мишень на экране — это печать экрана с пакшота: её не перекрашиваем и в фон не выносим. Белая клиническая студия и «blue on dark» из site/prompts/mitoscan.md написаны до правила линеек и сюда не идут. Белые объекты стоят на тёмном фоне.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Система MITOSCAN целиком, как на пакшоте. Белый планшет на белой подставке с экраном-логотипом (мишень, 'Mitoscan', 'By Mitoderm Ltd'). Справа в держателе щуп-сканер: белый корпус, чёрная овальная панель 'Mitoscan' / 'By Mitoderm Ltd', спиральный кабель. Спереди серебряный цилиндр с хромовым шильдиком 'Mitoscan'. Сюжет ведёт щуп, «המצלמה» из b0.cta, а результат появляется на экране. Пока нет фото частей по отдельности, всё строится одним биллбордом целого пакшота: части не двигаются, работают камера и маски.</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Система MITOSCAN целиком, как на пакшоте. Белый планшет на белой подставке с экраном-логотипом (мишень, 'Mitoscan', 'By Mitoderm Ltd'). Справа в держателе щуп-сканер: белый корпус, чёрная овальная панель 'Mitoscan' / 'By Mitoderm Ltd', спиральный кабель. Спереди серебряный цилиндр с хромовым шильдиком 'Mitoscan'. Сюжет ведёт щуп, «המצלמה» из b0.cta, а результат появляется на экране. Пока нет фото частей по отдельности, всё строится одним биллбордом целого пакшота: части не двигаются, работают камера и маски.</t>
+          <t>Камера поднимается к щупу MITOSCAN, сквозь дымку «на глаз» переходит к экрану, где открываются ×50 и ×200, показывает то, что видит пациент, проводит через «сканирование · объяснение · отслеживание» и отъезжает к целой системе на экране покупки.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Камера поднимается к щупу MITOSCAN, сквозь дымку «на глаз» переходит к экрану, где открываются ×50 и ×200, показывает то, что видит пациент, проводит через «сканирование · объяснение · отслеживание» и отъезжает к целой системе на экране покупки.</t>
+          <t>פנים</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>פנים</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
           <t>81</t>
         </is>
       </c>
+      <c r="K13" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1263,56 +1197,51 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>all lines: V-TECH FACE · PEELING · BIOSPICULE · DEVICES · HAIR (one line per screen 2–6)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>all lines: V-TECH FACE · PEELING · BIOSPICULE · DEVICES · HAIR (one line per screen 2–6)</t>
+          <t>page</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>page</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
           <t>Экраны 1 и 7 — нейтральная база бренда (design-rules, слой 1). Фон #0a0a0b, поверхности #111114 / #1a1a1f, графитовый дым, кремовая пыль #f6f3ec не больше 8%, текст крем #f6f3ec. Золото #c9a24b здесь только в волосяных линиях, кикерах и кнопке. Цветов линеек на этих экранах нет: группы в герое и на полке различаются расстановкой и подписями. Экраны 2–6 — каждый в окружении своей линейки, цвет меняется только в зоне перехода. 2 V-TECH FACE — чёрный, тёплый золотой дым #c9a24b, золотая пыль #d8bd7e, блики зеркальной фольги. 3 PEELING — шампань-золото #d8c48a. 4 BIOSPICULE — зелёный #1E4634 и тёмный #12382A, подложка шалфея #9AA889 под DERMA, золотая монограмма M. 5 DEVICES — холодный шампань-металл #d8c48a и серебро #d9d4cc. 6 HAIR — чёрный, золотой дым и пыль. Золотой дым есть только на экранах 2 и 6, поэтому на переходах 1→2 и 6→7 меняется цвет, а не только плотность дыма. V-TECH FACE и HAIR по правилам одного цвета, их различает бейдж линейки. Это подпись группы под волосяной линией: точка и название в цвете линейки, как бейдж серии на экране покупки MASK. Капля средства — только узкое свечение под упаковкой, не больше ~10% площади: EXOCELL MASK бирюза #6fb7ba на экране 2, CELL RENEW #4fb285 на экране 4, MITOSCAN #5aa9e6 на экране 5. На главной MASK стоит в чёрно-золотом окружении своей серии V-TECH FACE: её бирюзовое окружение — исключение только на её собственной странице. Назначение показывают бейджи, а не фон: «מקצועי» — золотая заливка, домашний уход — золотой контур. Оттенок серии виден на всех экранах 2–6; в поле ниже указан первый из них.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="F14" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Вся линейка: 12 настоящих упаковок пятью группами на пологой дуге (V-TECH FACE · PEELING · BIOSPICULE · DEVICES · HAIR). Ближе всех и в центре — золотой зеркальный картон V-TECH SYSTEM. MITOTECH CELL BOOSTER без фото в 3D не показывается. EXOSIGNAL SPRAY до студийного пакшота — только маленький билборд коробки в глубине, без флакона.</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Вся линейка: 12 настоящих упаковок пятью группами на пологой дуге (V-TECH FACE · PEELING · BIOSPICULE · DEVICES · HAIR). Ближе всех и в центре — золотой зеркальный картон V-TECH SYSTEM. MITOTECH CELL BOOSTER без фото в 3D не показывается. EXOSIGNAL SPRAY до студийного пакшота — только маленький билборд коробки в глубине, без флакона.</t>
+          <t>Главная — прогулка по полке MITODERM: вся линейка стоит дугой из пяти групп, с каждым экраном вперёд выходит одна серия в своём цветовом окружении (лицо, пилинг, биоспикулы, приборы, волосы) и ведёт на страницы своих средств, а в конце все упаковки возвращаются на общую полку с составом каждой линейки и одной кнопкой «לקבלת פרטים על מחירים».</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Главная — прогулка по полке MITODERM: вся линейка стоит дугой из пяти групп, с каждым экраном вперёд выходит одна серия в своём цветовом окружении (лицо, пилинг, биоспикулы, приборы, волосы) и ведёт на страницы своих средств, а в конце все упаковки возвращаются на общую полку с составом каждой линейки и одной кнопкой «לקבלת פרטים על מחירים».</t>
+          <t>פנים · קרקפת · טריכולוג/ית</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>פנים · קרקפת · טריכולוג/ית</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
           <t>66, 71, 76</t>
         </is>
       </c>
+      <c r="K14" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="L14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M14" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1324,25 +1253,20 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>готово</t>
+          <t>catalog</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>catalog</t>
+          <t>все линейки: V-TECH FACE · HAIR · PEELING · BIOSPICULE · DEVICES</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>все линейки: V-TECH FACE · HAIR · PEELING · BIOSPICULE · DEVICES</t>
+          <t>page</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>page</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Экраны 1, 2 и 7 стоят на базе бренда: фон #0a0a0b, медленный золотой дым #c9a24b, частицы цвета крема и золота, белый логотип. На каталоге есть все линейки, поэтому правило «не смешивать два цвета линеек» соблюдается поэкранно: на каждом экране только один цвет линейки, при переходе дым перетекает за 600 мс.
 Экран 3 (V-TECH FACE + HAIR): чёрный и тёплое золото V-TECH FACE, свечение сильнее, чем на базе. Бирюза EXOCELL #6fb7ba даётся только узкой каплей под её карточкой (не больше 10%), а бирюзово-синее окружение MASK остаётся на её странице.
@@ -1353,33 +1277,33 @@
 Назначение показывается бейджем, а не цветом: home.tg — золотая заливка, catalog.chips[6] — золотой контур. Бейдж и чип домашнего ухода берутся из одного ключа. Оттенок серии виден на каждом из экранов 3–6; в поле стоит экран 3, где он появляется впервые: тёплое золото V-TECH FACE, как на экране покупки MASK.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="F15" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Одного героя нет. На экране 1 стоит «витрина линеек» из пяти представителей: коробки V-TECH SYSTEM, EXO-NAD, EXOSIGNAL HAIR и MICRO BOOST 10% (кубоиды почти фасадом, рыскание не больше 12°, потому что печать их боковин неизвестна) и MITOPEN (строго фронтальный билборд). Дальше 3D работает в карточках: при наведении товар поворачивается к фасаду.</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Одного героя нет. На экране 1 стоит «витрина линеек» из пяти представителей: коробки V-TECH SYSTEM, EXO-NAD, EXOSIGNAL HAIR и MICRO BOOST 10% (кубоиды почти фасадом, рыскание не больше 12°, потому что печать их боковин неизвестна) и MITOPEN (строго фронтальный билборд). Дальше 3D работает в карточках: при наведении товар поворачивается к фасаду.</t>
+          <t>Каталог — спокойная витрина: пять представителей линеек встречают посетителя на чёрно-золотом фоне и спускаются на полку категорий; дальше каждая линейка идёт своим экраном в своём цвете, в каждой карточке видно, что лежит в коробке, а вся страница ведёт к одной кнопке цены.</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Каталог — спокойная витрина: пять представителей линеек встречают посетителя на чёрно-золотом фоне и спускаются на полку категорий; дальше каждая линейка идёт своим экраном в своём цвете, в каждой карточке видно, что лежит в коробке, а вся страница ведёт к одной кнопке цены.</t>
+          <t>פנים · קרקפת · טריכולוג/ית</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>פנים · קרקפת · טריכולוג/ית</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
           <t>пакшоты всех средств</t>
         </is>
       </c>
+      <c r="K15" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" s="2" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2201,7 +2125,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут · AHA + BHA ≈30% · NAD⁺ · אקסוזומים סינתטיים · פיצפטריק I–VI</t>
+          <t>PEELING · AHA + BHA ≈30% · NAD⁺ · אקסוזומים סינתטיים · פיצפטריק I–VI</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -2683,7 +2607,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>מקצועי · ⏳ перевод на иврит и две проверки идут · 1 × 15 מ״ל Biphasic Peel · 5 × 5 מ״ל pH Normalizer · 5 × 5 מ״ל Longevity Serum · שילוב חומצות AHA ו-BHA (כ־30%) · חומצה טרנקסמית ורכיבים נוגדי חמצון · קולגן ופפטידים ביומימטיים · ויטמין B12 · מבנים אקסוזומליים סינתטיים · NAD⁺ · Epitalon – אפיטלון · GHK-Cu · ⏳ перевод на иврит и две проверки идут</t>
+          <t>מקצועי · PEELING · 1 × 15 מ״ל Biphasic Peel · 5 × 5 מ״ל pH Normalizer · 5 × 5 מ״ל Longevity Serum · שילוב חומצות AHA ו-BHA (כ־30%) · חומצה טרנקסמית ורכיבים נוגדי חמצון · קולגן ופפטידים ביומימטיים · ויטמין B12 · מבנים אקסוזומליים סינתטיים · NAD⁺ · Epitalon – אפיטלון · GHK-Cu · WhatsApp · טלפון · דוא״ל</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -2853,7 +2777,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>מקצועי · ⏳ перевод на иврит и две проверки идут · שלב מסכם לאחר פרוצדורה · לחות וקרירות · תמיכה במחסום העור</t>
+          <t>מקצועי · V-TECH FACE · שלב מסכם לאחר פרוצדורה · לחות וקרירות · תמיכה במחסום העור</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -3185,7 +3109,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>5 · מסכות באריזה · ביו-צלולוז · מבנה דק וגמיש · חד-פעמית · סרום פעיל · ⏳ перевод на иврит и две проверки идут</t>
+          <t>5 · מסכות באריזה · ביו-צלולוז · מבנה דק וגמיש · חד-פעמית · סרום פעיל · מסכה כפולה: שכבה לבנה ושכבה כחולה, שמניחים בזו אחר זו.</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr"/>
@@ -3335,7 +3259,7 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут · מה באריזה · 5× · מסכות · מסכות ביו-צלולוז חד-פעמיות עם סרום פעיל. · ⏳ перевод на иврит и две проверки идут · ⏳ перевод на иврит и две проверки идут · רכיבים פעילים · מבנים אקסוזומליים סינתטיים · פולינוקלאוטידים · חומצה היאלורונית, גליצרול ושמנים צמחיים · תמציות צמחיות ותמצית אצה · Hexapeptide-8 · Ubiquinone – קו־אנזים Q10 · Nannochloropsis Oculata Extract · Spilanthes Acmella Extract · טלפון · ⏳ перевод на иврит и две проверки идут · דוא״ל · ⏳ перевод на иврит и две проверки идут · הוסיפו לפנייה על V-TECH / EXO-NAD</t>
+          <t>V-TECH FACE · מה באריזה · 5× · מסכות · מסכות ביו-צלולוז חד-פעמיות עם סרום פעיל. · כל מסכה מורכבת משתי שכבות – לבנה וכחולה – שמניחים בזו אחר זו. · Net 5 x 25 ml · רכיבים פעילים · מבנים אקסוזומליים סינתטיים · פולינוקלאוטידים · חומצה היאלורונית, גליצרול ושמנים צמחיים · תמציות צמחיות ותמצית אצה · Hexapeptide-8 · Ubiquinone – קו־אנזים Q10 · Nannochloropsis Oculata Extract · Spilanthes Acmella Extract · טלפון · 054-326-2182 · דוא״ל · info@mitoderm.com · הוסיפו לפנייה על V-TECH / EXO-NAD</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
@@ -4778,7 +4702,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>V-TECH FACE</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -5252,7 +5176,7 @@
       <c r="F48" s="2" t="inlineStr"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>V-TECH FACE</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">
@@ -9426,7 +9350,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>צרו קשר · מוצרים מקצועיים · מקצועי · הכל · ⏳ перевод на иврит и две проверки идут</t>
+          <t>צרו קשר · מוצרים מקצועיים · מקצועי · הכל · גללו</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -9491,7 +9415,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>V-TECH FACE</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
@@ -9501,7 +9425,7 @@
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>בקליניקה – V-TECH SYSTEM, ולסיום EXOCELL MASK; בבית – EXOTECH GEL.</t>
         </is>
       </c>
       <c r="J99" s="3" t="inlineStr">
@@ -9932,7 +9856,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>לקבלת פרטים על מחירים · ⏳ перевод на иврит и две проверки идут · טלפון · דוא״ל · צרו קשר · צרו קשר</t>
+          <t>לקבלת פרטים על מחירים · WhatsApp · טלפון · דוא״ל · צרו קשר · צרו קשר</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -10168,7 +10092,7 @@
       <c r="G107" s="3" t="inlineStr"/>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>בחרו קטגוריה</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr"/>
@@ -10232,7 +10156,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут · שיער</t>
+          <t>V-TECH FACE · שיער</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
@@ -10583,7 +10507,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут · טלפון · דוא״ל · היבואנית הבלעדית של VM בישראל</t>
+          <t>WhatsApp · טלפון · דוא״ל · היבואנית הבלעדית של VM בישראל</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr">
@@ -16888,7 +16812,7 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>אריזת V-TECH SYSTEM עם 5 אמפולות סרום ו-5 שקיות מסכת ג׳ל</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -16915,7 +16839,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>PEELING</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -16942,7 +16866,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>WhatsApp · טלפון · דוא״ל</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -16969,7 +16893,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>V-TECH FACE</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -16996,7 +16920,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>מסכה כפולה: שכבה לבנה ושכבה כחולה, שמניחים בזו אחר זו.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -17023,7 +16947,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>כל מסכה מורכבת משתי שכבות – לבנה וכחולה – שמניחים בזו אחר זו.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -17050,7 +16974,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>Net 5 x 25 ml</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -17077,7 +17001,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>054-326-2182</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -17104,7 +17028,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>info@mitoderm.com</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -17158,7 +17082,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>HAIR</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -17185,7 +17109,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>שלום, אשמח לקבל פרטים על מחירי EXOSIGNAL HAIR</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -17212,7 +17136,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>שלום, אשמח לתאם הדגמת MITOSCAN עבור EXOSIGNAL HAIR</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -17293,7 +17217,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>V-TECH FACE</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -17320,7 +17244,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>שלום! איפה אפשר לקנות את EXOTECH GEL?</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -17347,7 +17271,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>BIOSPICULE™</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -17374,7 +17298,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>אריזת MICRO BOOST 10% ומזרק של 3 מ״ל</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -17401,7 +17325,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>BIOSPICULE™</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -17428,7 +17352,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>טיפוח ביתי</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -17455,7 +17379,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>אריזת DERMA RECOVERY CREAM וצנצנת של 50 מ״ל</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -17509,7 +17433,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>V-TECH FACE</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -17536,7 +17460,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>בקליניקה – V-TECH SYSTEM, ולסיום EXOCELL MASK; בבית – EXOTECH GEL.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -17563,7 +17487,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>Net 5 x 25 ml</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -17590,7 +17514,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -17617,7 +17541,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>גללו</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -17671,7 +17595,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>⏳ перевод на иврит и две проверки идут</t>
+          <t>בחרו קטגוריה</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">

--- a/mitoderm-catalog/site/MITODERM-3D-story.xlsx
+++ b/mitoderm-catalog/site/MITODERM-3D-story.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mitoderm.com" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сверка с источниками" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4287,7 +4288,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Герой экрана — кожа головы, а не флакон. Справа в 3D под небольшим углом плавает фото-рамка: вид сверху на пробор, капли на коже впитываются (новый кадр, см. вопрос 3). Рамка слегка наклоняется за курсором. На её поверхность оседают последние капли дымки с экрана 3 и исчезают без следа — это «ללא שטיפה». Флакон маленький и тёмный, в глубине сбоку, стоит фасадом. Метки b3.label1–4 ложатся по краю рамки. Фото site/img/exosignal-spray-hand.jpg на странице не используется: на нём флакон у щеки, видно лицо, а кожи головы нет.</t>
+          <t>Герой экрана — кожа головы, а не флакон. Справа в 3D под небольшим углом плавает фото-рамка: вид сверху на пробор, капли на коже впитываются (новый кадр, см. вопрос 3). Рамка слегка наклоняется за курсором. На её поверхность оседают последние капли дымки с экрана 3 и исчезают без следа — это «ללא שטיפה». Флакон маленький и тёмный, в глубине сбоку, стоит фасадом. Метки b3.label1–4 ложатся по краю рамки. Фото фото флакона в руке (с человеком: хранится закрыто, не в репозитории) на странице не используется: на нём флакон у щеки, видно лицо, а кожи головы нет.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -13308,7 +13309,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Цилиндр из матового полупрозрачного стекла и рифлёный золотой колпачок. Наклейку снять с site/img/exosignal-spray-hand.jpg (565×1340) и выпрямить наклон. Видимые строки по packaging-text.json: VM-монограмма, вертикальная 'EXOSIGNAL' ('EXO' жирным), 'S P R A Y · H O M E', 'EXOSIGNAL SPRAY HOME', 'Deep nourishing scalp serum', 'HOME USE'. Строки, помеченные [unreadable], и строки под пальцами рисуются тонкими серыми линиями. Файл site/img/exosignal-spray.png не использовать: это скриншот 400×300, и флакон на нём непрозрачный белый с гладким колпачком, то есть не настоящий. Показывать только мелким планом. Нужен студийный пакшот флакона на прозрачном фоне.</t>
+          <t>Цилиндр из матового полупрозрачного стекла и рифлёный золотой колпачок. Наклейку снять с фото флакона в руке (с человеком: хранится закрыто, не в репозитории) (565×1340) и выпрямить наклон. Видимые строки по packaging-text.json: VM-монограмма, вертикальная 'EXOSIGNAL' ('EXO' жирным), 'S P R A Y · H O M E', 'EXOSIGNAL SPRAY HOME', 'Deep nourishing scalp serum', 'HOME USE'. Строки, помеченные [unreadable], и строки под пальцами рисуются тонкими серыми линиями. Файл site/img/exosignal-spray.png не использовать: это скриншот 400×300, и флакон на нём непрозрачный белый с гладким колпачком, то есть не настоящий. Показывать только мелким планом. Нужен студийный пакшот флакона на прозрачном фоне.</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -13389,7 +13390,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Полоса этикетки выпрямляется из site/img/exosignal-spray-hand.jpg (565×1340). Печать настоящая, но снята в перспективе, нижние строки у края частично закрыты пальцем, оборот не виден. Фото служит только источником текстуры и на странице не показывается. Поворот не больше ±30° от фасада. Для финала нужен пакшот флакона спереди и сзади на прозрачном фоне.</t>
+          <t>Полоса этикетки выпрямляется из фото флакона в руке (с человеком: хранится закрыто, не в репозитории) (565×1340). Печать настоящая, но снята в перспективе, нижние строки у края частично закрыты пальцем, оборот не виден. Фото служит только источником текстуры и на странице не показывается. Поворот не больше ±30° от фасада. Для финала нужен пакшот флакона спереди и сзади на прозрачном фоне.</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -13470,7 +13471,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Кадра пока нет. Подойдёт фото заказчика или генерация по промпту кадра «Why» (вид сверху на пробор) из site/prompts/exosignal-spray.md. Сначала один образец, цена и баланс — до запуска. site/img/exosignal-spray-hand.jpg не подходит: на нём флакон у щеки, видны лицо и шея, а кожи головы нет.</t>
+          <t>Кадра пока нет. Подойдёт фото заказчика или генерация по промпту кадра «Why» (вид сверху на пробор) из site/prompts/exosignal-spray.md. Сначала один образец, цена и баланс — до запуска. фото флакона в руке (с человеком: хранится закрыто, не в репозитории) не подходит: на нём флакон у щеки, видны лицо и шея, а кожи головы нет.</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -15954,7 +15955,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Студийного пакшота нет: есть фото в руке (site/img/exosignal-spray-hand.jpg, низ флакона закрыт пальцами) и снимок 400×300 (site/img/exosignal-spray.png), где флакон ~40 px и выглядит непрозрачно-белым, а не матовым стеклом. Замену из него не делать: до пакшота флакон и туман на главной не показываются. Нужен пакшот флакона на прозрачном фоне, без руки, фасадом с этикеткой</t>
+          <t>Студийного пакшота нет: есть фото в руке (фото флакона в руке (с человеком: хранится закрыто, не в репозитории), низ флакона закрыт пальцами) и снимок 400×300 (site/img/exosignal-spray.png), где флакон ~40 px и выглядит непрозрачно-белым, а не матовым стеклом. Замену из него не делать: до пакшота флакон и туман на главной не показываются. Нужен пакшот флакона на прозрачном фоне, без руки, фасадом с этикеткой</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -21258,7 +21259,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Фото site/img/exosignal-spray-hand.jpg (флакон у щеки, видно лицо) на странице не ставим и берём только как источник этикетки. Но это фото с человеком, и оно уже лежит в публичном репозитории, хотя по правилу проекта таким фото там не место. Убрать его из репозитория и хранить копию только локально?</t>
+          <t>Фото фото флакона в руке (с человеком: хранится закрыто, не в репозитории) (флакон у щеки, видно лицо) на странице не ставим и берём только как источник этикетки. Но это фото с человеком, и оно уже лежит в публичном репозитории, хотя по правилу проекта таким фото там не место. Убрать его из репозитория и хранить копию только локально?</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
@@ -22168,6 +22169,2861 @@
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Страница</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Экран</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Что</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>В сюжете</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>В источнике</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Предложение</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Проверка скептика</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>b4.line, b4.label2 «2 · סרום 1–1.5 מ״ל», cat.steps[1][1] (доза сыворотки и как наносится гель-маска)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>источники расходятся</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>b4.line: «המיקרונידלינג פותח את מסלול החדירה, 1–1.5 מ״ל סרום מוחדרים פנימה ומסכת הג׳ל נשארת על העור – ללא שטיפה.» / cat.steps[1][1]: «בין 1 ל־1.5 מ״ל סרום אקסוזומים סינתטיים לטיפול: פנים, צוואר, דקולטה או כפות ידיים.»</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Протокол: «לאזור טיפול אחד – פנים / צוואר / מחשוף:» «V-TECH Serum: עד 2 מ״ל» «V-TECH Gel Mask: עד 2 מ״ל»; про гель: «יש לעסות בעדינות עד לספיגה מלאה. אין צורך בשטיפה.» Каталог (проигрывает): «כמות: בין 1 ל1.5 מל לטיפול». PLAN §7: «до 2 мл сыворотки и до 2 мл гель-маски на зону».</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:35 (vtech-mitopen, «מינון מומלץ») и :46 (V-TECH GEL MASK); каталог source-texts.md:112; PLAN.md:118</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Побеждает протокол. Метка шага 2 — «2 · סרום עד 2 מ״ל לאזור». В b4.line «1–1.5 מ״ל סרום» заменить на «עד 2 מ״ל סרום לאזור טיפול». Про гель написать по протоколу: втирается мягкими движениями до полного впитывания, смывать не нужно («יש לעסות בעדינות עד לספיגה מלאה. אין צורך בשטיפה.»). В cat.steps[1][1] дозу дать по протоколу: до 2 мл на одну зону (лицо, шея или декольте). Кисти рук протокол не упоминает: зону из каталога не убирать без слова заказчика или задать ему вопрос. Новые строки на иврите — через переводчика и рецензентов.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В content.he.mjs:35 стоит «לאזור טיפול אחד – פנים / צוואר / מחשוף:», а ниже «V-TECH Serum: עד 2 מ״ל» и «V-TECH Gel Mask: עד 2 מ״ל». В :46 сказано «יש לעסות בעדינות עד לספיגה מלאה. אין צורך בשטיפה.». В каталоге (source-texts.md:112) «כמות: בין 1 ל1.5 מל לטיפול». PLAN.md:118 подтверждает, что главный источник — протокол: «до 2 мл сыворотки и до 2 мл гель-маски на зону». В сюжете действительно «1–1.5 מ״ל» в b4.line, b4.label2 и cat.steps[1][1], а гель «נשארת על העור». Поправка: протокол даёт дозу на зону «פנים / צוואר / מחשוף» и про кисти рук молчит. Значит, убирать кисти, которые есть в каталоге, без слова заказчика нельзя.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>b4.label4 «בסיום: EXOCELL MASK + SPF» и cat.steps[2][1] (чем заканчивается протокол)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>источники расходятся</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>b4.label4: «בסיום: EXOCELL MASK + SPF»; cat.steps[2][1]: «לאחר האמפולה, ללא שטיפה. בסיום הטיפול: EXOCELL MASK או DERMA RECOVERY ומקדם הגנה.»</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Протокол, «לאחר הסרום»: «מומלץ להניח מסכת EXOCELL MASK להחדרה של חומצה הילארונית , תמציות צמחים ואלוורה.» → «בסיום DERMA RECOVERY CREAM» → «מקדם הגנה חובה». PLAN §7: «финиш EXOCELL MASK → DERMA RECOVERY → SPF».</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:51-53 (vtech-mitopen, after); PLAN.md:118</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Финиш дать последовательностью протокола, а не через «или»: EXOCELL MASK (рекомендуется), затем DERMA RECOVERY CREAM, затем обязательно SPF. В b4.label4 добавить DERMA RECOVERY CREAM в этом порядке. В cat.steps[2][1] вместо «EXOCELL MASK או DERMA RECOVERY» написать порядок протокола. Два чипа-ссылки оставить в том же порядке: EXOCELL MASK, потом DERMA RECOVERY CREAM. Иврит — через переводчика.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В content.he.mjs:51–53 блок «לאחר הסרום» идёт по порядку: «מומלץ להניח מסכת EXOCELL MASK…», затем «בסיום DERMA RECOVERY CREAM», затем «מקדם הגנה חובה». В PLAN.md:118 тот же порядок: «финиш EXOCELL MASK → DERMA RECOVERY → SPF». В сюжете b4.label4 — «בסיום: EXOCELL MASK + SPF» (без DERMA RECOVERY), а в cat.steps[2][1] стоит «או». Уточнение: маска в протоколе «מומלץ» (рекомендуется), а SPF — «חובה» (обязательно).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>b4.title / b4.line («каждые две недели, 4 процедуры») вместе с cat.steps[0][1], где BIOSPICULE™ 10% стоит среди способов открыть каналы</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>источники расходятся</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>b4.title «שלושה שלבים, כל שבועיים»; b4.line «…4 טיפולים, בהפרש של שבועיים.»; cat.steps[0][1] «…מיקרונידלינג, RF microneedling, BIOSPICULE™ 10% או Laser CO₂ פותחים את מסלול החדירה.»</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Отдельный протокол «BIOSPICULE™ MICROBOOST 10% + VTECH»: «ניתן לבצע סדרה של 4–3 טיפולים, במרווח של 4 שבועות בין טיפול לטיפול.»; финиш там: «SPF   מסנן קרינה של 30 לפחות חובה». Ритм раз в 14 дней относится к протоколу «VTECH+ MITOPEN».</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:65-69 (biospicule-vtech, aside «סדרת טיפולים»), :91; :32, :56 (vtech-mitopen)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Не обещать «каждые две недели» для любого способа. Указать, что ритм 14 дней и курс 4–6 относятся к протоколу с MITOPEN / мезопеном. С BIOSPICULE™ MICRO BOOST 10% — 3–4 процедуры с интервалом 4 недели (протокол «BIOSPICULE™ MICROBOOST 10% + VTECH»). Достаточно уточнения в раскрытом шаге 1 (cat.steps[0][1]) или короткой сноски под b4.line. BIOSPICULE™ 10% из шага 1 не убирать. Иврит — через переводчика.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. У протокола «BIOSPICULE™ MICROBOOST 10% + VTECH» свой ритм (content.he.mjs:69): «ניתן לבצע סדרה של 4–3 טיפולים, במרווח של 4 שבועות בין טיפול לטיפול.» Ритм «каждые 14 дней» взят из протокола «VTECH+ MITOPEN» (:56). Сюжет ставит BIOSPICULE™ 10% среди способов шага 1 (b4.label1, cat.steps[0][1]) и при этом обещает «כל שבועיים» (b4.title, b4.line, b5.label4). Поправка к предложению: вариант «убрать BIOSPICULE™ 10%» не подходит. Этот способ есть и в каталоге, и в протоколах заказчика.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>b5.line (курс и поддержка), b5.label3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>источники расходятся</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>«5 אמפולות סרום של 5 מ״ל ו-5 שקיות מסכת ג׳ל של 5 מ״ל. סדרה מומלצת: לפחות 4 טיפולים; תחזוקה אחת לחצי שנה.» / b5.label3 «4 טיפולים בסדרה»</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Протокол: «טיפול אחד בכל 14 יום.» «סדרה מומלצת: 6-4טיפולים, בהתאם למצב העור ולמטרת הטיפול.» «פרוטוקול בסיס של 4 טיפולים רצופים: כל שבועיים» «לאחר השלמת הסדרה מומלץ לבצע טיפול תחזוקה אחת לחודשיים-שלושה, בהתאם למצב העור...» Каталог (проигрывает): «לפחות 4 טיפולים תחזוקה : אחת לחצי שנה».</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:56-59 (vtech-mitopen, «תדירות וסדרת טיפולים»); source-texts.md:112</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Заменить в b5.line по протоколу: «סדרה מומלצת: 4–6 טיפולים; טיפול תחזוקה אחת לחודשיים-שלושה». b5.label3 сделать «4–6 טיפולים בסדרה» (4 — это базовый протокол «4 טיפולים רצופים: כל שבועיים», поэтому так и подписать, если нужна одна цифра). Поддержку раз в полгода убрать со всей страницы. Иврит — через переводчика.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В content.he.mjs:56–59: «טיפול אחד בכל 14 יום.», «סדרה מומלצת: 6-4טיפולים», «פרוטוקול בסיס של 4 טיפולים רצופים: כל שבועיים» и «טיפול תחזוקה אחת לחודשיים-שלושה». В каталоге (:112) «לפחות 4 טיפולים … תחזוקה : אחת לחצי שנה». PLAN.md:118 — «курс 4–6». В сюжете b5.line: «סדרה מומלצת: לפחות 4 טיפולים; תחזוקה אחת לחצי שנה.» Поддержка раз в полгода прямо противоречит протоколу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>список «что внутри»: строка дозы cat.steps[1][1] под cat.kit[0]; cat.kit[1] без дозы («дозы в каталоге нет, её не пишем»)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>источники расходятся</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Доза сыворотки: «בין 1 ל־1.5 מ״ל סרום אקסוזומים סינתטיים לטיפול: פנים, צוואר, דקולטה או כפות ידיים.»; у гель-маски: «дозы в каталоге нет, её не пишем»</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>«לאזור טיפול אחד – פנים / צוואר / מחשוף:» «V-TECH Serum: עד 2 מ״ל» «V-TECH Gel Mask: עד 2 מ״ל»</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:35 (vtech-mitopen, «מינון מומלץ»)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>В списке «что внутри» под сывороткой написать «עד 2 מ״ל לאזור טיפול» вместо 1–1,5 мл. Под гель-маской добавить дозу из протокола: «עד 2 מ״ל לאזור טיפול». Иврит — через переводчика.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. На экране 7 сюжет ставит под сыворотку cat.steps[1][1] («בין 1 ל־1.5 מ״ל…»), а про гель-маску пишет «дозы в каталоге нет, её не пишем». В основном протоколе (content.he.mjs:35) есть обе дозы: «V-TECH Serum: עד 2 מ״ל» и «V-TECH Gel Mask: עד 2 מ״ל» на одну зону. Довод «в каталоге нет» больше не работает. Правка та же, что в находке 0, но поле другое — экран покупки.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>inside.components[0].volume_dose; inside.components[1].volume_dose</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>[0]: «5 мл во флаконе; на процедуру 1–1,5 мл (cat.steps[1][1])»; [1]: «5 мл в саше; наносится после сыворотки, без смывания. Дозы на процедуру в каталоге нет, на странице её не указываем»</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>«V-TECH Serum: עד 2 מ״ל», «V-TECH Gel Mask: עד 2 מ״ל» на одну зону; «יש לעסות בעדינות עד לספיגה מלאה. אין צורך בשטיפה.»; «יש להשתמש באמפולה עד חודש ממועד הפתיחה, בהתאם להנחיות האחסון של המוצר.»</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:35-36, :46</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>[0]: «5 мл во флаконе; до 2 мл на одну зону (лицо / шея / декольте); набирают шприцем 3 мл через иглу для набора; открытую ампулу использовать в течение месяца». [1]: «5 мл в саше; до 2 мл на одну зону; после сыворотки втирается до полного впитывания, без смывания».</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В inside.components[0] стоит «на процедуру 1–1,5 мл», в [1] — «Дозы … в каталоге нет». Протокол (content.he.mjs:35–36, 40, 46) даёт: до 2 мл сыворотки и до 2 мл гель-маски на зону; набор шприцем 3 мл через иглу для набора («מחט שאיבה למזרק 3 מ״ל»); открытую ампулу использовать до месяца; гель втирать до полного впитывания, без смывания.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[2] — как берут сыворотку из флакона (шприц, пипетка, пробка)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>«И как сыворотку берут из флакона: шприцем, пипеткой, снимают пробку? Пока ответа нет, колпачок закрыт, а капля возникает в воздухе над флаконом.»</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>«יש לשאוב את V-TECH Serum באמצעות מחט שאיבה למזרק 3 מ״ל.» «יש ליישם את הסרום באמצעות MITOPEN / מזופן או מכשור מקצועי מתאים אחר.»</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:40-41 (vtech-mitopen, шаг V-TECH SERUM); PLAN.md:118</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Ответ есть: сыворотку набирают шприцем 3 мл через иглу для набора и наносят MITOPEN / мезопеном (или другим подходящим профессиональным прибором). В вопросе оставить только цвет колпачка. Капля над флаконом в 3D может остаться схемой, а в раскрытом шаге 2 сказать про шприц 3 мл и MITOPEN / мезопен.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В content.he.mjs:40–41: «יש לשאוב את V-TECH Serum באמצעות מחט שאיבה למזרק 3 מ״ל.» и «יש ליישם את הסרום באמצעות MITOPEN / מזופן או מכשור מקצועי מתאים אחר.» PLAN.md:118: «сыворотку набирают шприцем 3 мл». Значит, на вопрос «шприцем, пипеткой, пробку снимают?» ответ есть. Цвет колпачка протокол не называет, этот вопрос остаётся.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[4] и экран 3 (cat.ingredients[7] отдельной строкой) — к какому компоненту относятся гиалуроновая кислота и алоэ</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>«Гиалуроновая кислота и алоэ вера (последний пункт состава) — в сыворотке или в гель-маске? Пока в раскрытом составе это отдельная строка после двух групп.»</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm.com, Gel Mask: «חומצה היאלורונית במשקל מולקולרי נמוך, אלוורה» (EN: «Low molecular weight hyaluronic acid, aloe vera»); каталог HE — под «מסכת גל לאחר האמפולה ללא שטיפה»: «חומצה היאלורונית / אלוורה»; каталог RU — под «Гелевая маска»: «Гиалуроновая кислота / Алоэ вера».</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>site/sources/mitoderm-com/products-he.json:11 (solution.main.item2textP5); source-texts.md:104-110; source-texts-ru-2026-09-18.md (Полоса 06, «Гелевая маска»)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Гиалуроновая кислота и алоэ — в гель-маске. На экране 3 перенести cat.ingredients[7] в группу гель-маски (после «PDRN 1% … – מסכת ג׳ל») и не давать его отдельной строкой. Вопрос закрыть.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. На mitoderm.com гиалуроновая кислота и алоэ стоят в блоке гель-маски: products-he.json:11, item2 «V-Tech Gel Mask 5ml», item2textP5 «חומצה היאלורונית במשקל מולקולרי נמוך, אלוורה»; на английской версии «Low molecular weight hyaluronic acid, aloe vera». В каталоге HE (source-texts.md:104–110) они стоят под «מסכת גל לאחר האמפולה ללא שטיפה». В каталоге RU (:111–118) — под «Гелевая маска». Отдельный пункт cat.ingredients[7] «חומצה היאלורונית ואלוורה» в сюжете идёт отдельной строкой — это подтверждено.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[5] — сколько уходит на процедуру и хватает ли коробки на курс</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>«Сколько флаконов и саше уходит на одну процедуру и хватает ли одной коробки на курс? … сыворотки на процедуру 1–1,5 мл из флакона на 5 мл.»</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>«V-TECH Serum: עד 2 מ״ל» / «V-TECH Gel Mask: עד 2 מ״ל» на одну зону; «יש להשתמש באמפולה עד חודש ממועד הפתיחה, בהתאם להנחיות האחסון של המוצר.»; «טיפול אחד בכל 14 יום.» «סדרה מומלצת: 6-4טיפולים».</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:35-36, :56-57</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Ответ частичный. Протокол даёт дозу (до 2 мл сыворотки и до 2 мл гель-маски на одну зону) и срок: открытую ампулу использовать до месяца. Сколько коробок нужно на курс, в протоколе не сказано, поэтому набор и курс по-прежнему показываем отдельными фактами. В факты (экран 6 или 7) добавить срок после вскрытия — до месяца. В тексте вопроса заменить «1–1,5 мл» на «до 2 мл на зону», а курс «не меньше четырёх» — на «4–6».</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено, ответ частичный. Протокол даёт дозу на зону (:35), срок открытой ампулы — до месяца (:36), ритм и курс (:56–57). Сколько коробок нужно на курс, не сказано. Вопрос в сюжете опирается на «1–1,5 мл», а это вытеснено протоколом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[6] — шаг 1: абстрактное поле или MITOPEN</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>«Шаг 1 протокола: оставить абстрактное поле микроканалов … или показать там MITOPEN как перекрёстную продажу?»</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Основной протокол называется «VTECH+ MITOPEN»: «יש ליישם את הסרום באמצעות MITOPEN / מזופן או מכשור מקצועי מתאים אחר.»; второй протокол — «BIOSPICULE™ MICROBOOST 10% + VTECH».</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:32, :41, :65</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>MITOPEN на шаге 1 — часть основного протокола заказчика, а не придуманная перекрёстная продажа. Можно назвать MITOPEN основным прибором (со ссылкой на его страницу) с подписью «או מזופן / מכשור מקצועי מתאים אחר». Для BIOSPICULE™ 10% остаётся свой протокол (см. находку 3). Открытым остаётся только одно: показывать ли сам прибор в 3D.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. Основной протокол называется «VTECH+ MITOPEN» (:32), на плитке ссылка «MITOPEN + VTECH» (:22), сыворотку наносят «באמצעות MITOPEN / מזופן או מכשור מקצועי מתאים אחר» (:41). Посылка вопроса («перекрёстная продажа») неверна: MITOPEN входит в протокол самого заказчика. Показывать ли прибор в 3D — по-прежнему решение по дизайну.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[7] — финиш: только EXOCELL MASK + SPF или и DERMA RECOVERY</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>«Финиш: в каталоге — «EXOCELL MASK или DERMA RECOVERY и защита от солнца», а в метке протокола на сайте только EXOCELL MASK + SPF … Попросить редактора иврита добавить DERMA RECOVERY в эту метку?»</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>«מומלץ להניח מסכת EXOCELL MASK…» → «בסיום DERMA RECOVERY CREAM» → «מקדם הגנה חובה»</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:51-53</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Да, DERMA RECOVERY CREAM добавить, и не через «или», а по порядку: EXOCELL MASK (рекомендуется) → DERMA RECOVERY CREAM → SPF (обязательно). Правка — в находке 2 (экран 5). Вопрос закрыть.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено (content.he.mjs:51–53; PLAN.md:118). Протокол даёт финиш последовательностью EXOCELL MASK → DERMA RECOVERY CREAM → SPF (обязательно), а не через «или». Это ответ на вопрос сюжета.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[1] — флакон или ампула в тексте</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>«Флакон или ампула? … в каталоге и текстах сайта — אמפולות. В 3D показываем как на фото. Слово в тексте оставляем или меняем?»</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Протокол: «יש להשתמש באמפולה עד חודש ממועד הפתיחה»; mitoderm.com: «5 אמפולות V-Tech Serum בנפח 5 מ׳׳ל כל אחת»; PLAN §7: «в коробке 5 ампул сыворотки по 5 мл»; только схема набора (фото 78/83) пишет «VIALS».</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:36; site/sources/mitoderm-com/products-he.json:11 (bundleText1); PLAN.md:119</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Протокол, сайт, каталог и слова заказчика в PLAN называют её ампулой, поэтому в тексте оставляем «אמפולות». Форма в 3D — как на фото (флакон). Вопрос снять.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В протоколе :36 — «יש להשתמש באמפולה עד חודש ממועד הפתיחה». На mitoderm.com (bundleText1): «5 אמפולות V-Tech Serum בנפח 5 מ׳׳ל כל אחת». В каталоге RU: «Сыворотка: 5 ампул × 5 мл». У заказчика в PLAN.md:79 и :119: «V-TECH — ампулы», «5 ампул сыворотки по 5 мл». «VIALS» есть только на схеме набора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>EXO-NAD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>b4.line и метки шагов b4.label1–3 (раскрытые шаги) — нет доз, времени и смывания</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>b4.line: «פילינג, נטרול והחדרת ה-Longevity Serum. טיפול בודד או סדרה, בכל ימות השנה; בסיום – EXOCELL MASK ומקדם הגנה.»; метки «1 · Biphasic Peel», «2 · pH Normalizer», «3 · Longevity Serum» — без доз и времени</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>«לפני השימוש יש לנער היטב את התמיסה הדו־פאזית.»; «אפשרות 1 – עור דק, רגיש או מעט מבוגר: יש לשאוב 1 מ״ל … יש להשאיר את התמיסה על העור עד 20 דקות»; «אפשרות 2 – עור עבה או מבוגר יותר: … 1 מ״ל … 15 דקות … 1 מ״ל נוסף … עד 15 דקות נוספות. זמן חשיפה כולל: עד 30 דקות.»; «יש לשאוב  1.5 -2 מ״ל מהמנטרל…» «יש להשאיר על העור למשך 2–3 דקות. לאחר מכן יש לשטוף היטב במים ולייבש את העור לחלוטין.»; «יש לשאוב כ 2 מל מ״ל מסרום ה־Longevity…» «יש לאפשר לסרום להיספג בעור. אין לשטוף.»; «יש להחליף כפפות, מחטים ומזרקים בין שלב לשלב»</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:167-179, :186 (exo-nad)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Добавить в метки шагов коротко время и смывание (это важно для безопасности), а дозы — в раскрытие шагов:
+- 1 — 1 мл пилинга до 20 мин (тонкая или чувствительная кожа); для плотной кожи 1 мл на 15 мин, затем ещё 1 мл до 15 мин, всего до 30 мин; перед работой встряхнуть.
+- 2 — 1,5–2 мл нейтрализатора на 2–3 мин, затем тщательно смыть водой и полностью высушить кожу.
+- 3 — около 2 мл Longevity Serum, нанести равномерно, дать впитаться, не смывать.
+Между шагами менять перчатки, иглы и шприцы. Слово «החדרת» в b4.line оставить: оно из каталога. Иврит — через переводчика.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Пропуск подтверждён. Протокол EXO-NAD (content.he.mjs:167–179, 186) даёт:
+- встряхнуть флакон;
+- 1 мл до 20 минут, а для плотной кожи — 1 мл на 15 минут и ещё 1 мл до 15 минут (всего до 30);
+- 1,5–2 мл нейтрализатора на 2–3 минуты, затем смыть и высушить;
+- около 2 мл Longevity Serum без смывания;
+- между шагами менять перчатки, иглы и шприцы.
+В сюжете метки только с названиями шагов, а страница V-TECH дозы показывает. Поправка к предложению: замену «החדרת» снимаю. Это слово каталога («ולבסוף החדרת סרום פעיל», source-texts.md), то есть вопрос стиля, а не ошибка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>EXO-NAD</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>b4.label4 «בסיום: EXOCELL MASK + SPF» и финиш в b4.line</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>ошибка</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>b4.label4: «בסיום: EXOCELL MASK + SPF»; b4.line: «…בסיום – EXOCELL MASK ומקדם הגנה.»</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Каталог HE: «בסיום: exocell mask | DERMA RECOVERY»; каталог RU: «По завершении процедуры: Солнцезащитное средство / EXOCELL MASK | DERMA RECOVERY CREAM»; cta каталога: «בסיום הטיפול – EXOCELL MASK או DERMA RECOVERY CREAM ומקדם הגנה.» В протоколе EXO-NAD финиша нет; в протоколе EXOCELL MASK «פילינג» назван среди процедур, после которых ставится маска.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>source-texts.md:154; source-texts-ru-2026-09-18.md:208-211; site/product-pages.he.json (EXO-NAD, cta[1]); protocols/src/content.he.mjs:212</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Вернуть DERMA RECOVERY CREAM дословно по cta каталога: «בסיום הטיפול – EXOCELL MASK או DERMA RECOVERY CREAM ומקדם הגנה.» На маркере финиша дать вторую ссылку — на DERMA RECOVERY CREAM.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В каталоге HE (source-texts.md:154) «בסיום: exocell mask | DERMA RECOVERY». В каталоге RU (:208–211) «Солнцезащитное средство / EXOCELL MASK | DERMA RECOVERY CREAM». В cta[1] каталога (product-pages.he.json, EXO-NAD) «בסיום הטיפול – EXOCELL MASK או DERMA RECOVERY CREAM ומקדם הגנה.» В протоколе EXO-NAD финиша нет. В протоколе EXOCELL MASK (:212) «פילינג» стоит среди процедур, после которых ставят маску. В сюжете b4.label4 и b4.line содержат только EXOCELL MASK + SPF, DERMA RECOVERY CREAM выпал.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>EXO-NAD</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>inside</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>inside.components[1].what и [2].what — цвет жидкости</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>ошибка</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>«pH Normalizer — флакон с янтарной жидкостью…», «Longevity Serum — флакон с голубой жидкостью…»</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>packaging-text.json: «amber vial» — «amber glass vial, silver crimp cap»; «teal vial» — «blue-teal glass vial, silver crimp cap»</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>site/packaging-text.json → exo-nad.objects[2], objects[3]</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Писать «флакон из янтарного стекла» (pH Normalizer) и «флакон из сине-бирюзового стекла» (Longevity Serum), оба с серебристым обжимным колпачком. Цвет самой жидкости в источниках не указан, в 3D его не придумывать.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В packaging-text.json (exo-nad.objects[2], [3]): «amber glass vial, silver crimp cap» и «blue-teal glass vial, silver crimp cap». Цветное здесь стекло, а не жидкость. В сюжете написано «флакон с янтарной жидкостью» и «флакон с голубой жидкостью». photo-catalog.md тоже говорит о цвете флаконов, не жидкости.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>EXO-NAD</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[4] — финиш протокола</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>«Финиш протокола: в раскадровке «EXOCELL MASK + SPF», в каталоге «EXOCELL MASK או DERMA RECOVERY CREAM ומקדם הגנה». Какой вариант верный?»</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Каталог HE «בסיום: exocell mask | DERMA RECOVERY»; RU «Солнцезащитное средство / EXOCELL MASK | DERMA RECOVERY CREAM». Протокол EXO-NAD финиша не называет и с каталогом не спорит.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>source-texts.md:154; source-texts-ru-2026-09-18.md:208-211</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Ответ на первую половину: верен вариант каталога — EXOCELL MASK или DERMA RECOVERY CREAM, плюс SPF. Добавляем вторую ссылку, на DERMA RECOVERY CREAM (правка — в находке 13). Вторая половина вопроса (не показывать саше MASK объектом) остаётся вопросом по дизайну.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено: все три текста каталога называют EXOCELL MASK и DERMA RECOVERY CREAM плюс SPF, протокол EXO-NAD финиша не называет и каталогу не противоречит. Поправка к предложению: «заказчику её можно не задавать» — это мнение, не вывод из источника. Вторая половина вопроса (саше MASK объектом не показываем) просто остаётся вопросом по дизайну.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>EXO-NAD</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[2] — сколько процедур на коробку (и экраны 6–7, где числа нет)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>«Сколько процедур рассчитано на одну коробку (15 мл пилинга, 5 + 5 флаконов по 5 мл)? В каталоге этого нет, поэтому на экране покупки число не пишем.»</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>«הערכה מאפשרת עד 15 טיפולים, בהתאם לכמות הנצרכת בכל טיפול.»; «לאחר הפתיחה ניתן להשתמש במוצר במשך עד חודש, באחסון במקום קריר ובהתאם להוראות האחסון.»</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:184-185 (exo-nad, «אחסון ושימוש לאחר פתיחה»)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Ответ есть: набора хватает до 15 процедур, в зависимости от расхода на каждую. На экран 6 (факты) или 7 (что внутри) добавить «עד 15 טיפולים בערכה, בהתאם לכמות הנצרכת בכל טיפול» и срок после вскрытия: до месяца, хранить в прохладном месте. Вопрос закрыть.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В content.he.mjs:184–185 «הערכה מאפשרת עד 15 טיפולים, בהתאם לכמות הנצרכת בכל טיפול.» и «לאחר הפתיחה ניתן להשתמש במוצר במשך עד חודש, באחסון במקום קריר…». В сюжете вопрос «В каталоге этого нет, поэтому … число не пишем» — а ответ есть в основном протоколе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>EXO-NAD</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[5] — контакты экрана покупки и бейдж PEELING</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>«Контакты для экрана покупки: номер WhatsApp, телефон и e-mail. Бейдж линейки: «PEELING» латиницей, как BIOSPICULE, или на иврите…?»</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>contacts.json: «"phone": "054-326-2182"», «"whatsapp": "+972-54-762-1889"», «"email": "info@mitoderm.com"», «callback_time: null». Протокол на иврите называет семейство латиницей: «nav: 'PEELING', title: 'PEELING'».</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>site/sources/mitoderm-com/contacts.json:3-8; protocols/src/content.he.mjs:154; PLAN.md:117</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Контакты: WhatsApp +972-54-762-1889 (wa.me/972547621889), телефон 054-326-2182, info@mitoderm.com; срок обратного звонка не пишем. Бейдж — латиницей «PEELING», как в ивритской версии протоколов заказчика. Вопрос закрыть.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. contacts.json: phone «054-326-2182», whatsapp «+972-54-762-1889», whatsapp_link «https://wa.me/972547621889», email «info@mitoderm.com», callback_time null. PLAN.md:117 повторяет это и запрещает срок обратного звонка. Протокол на иврите (:154) называет семейство латиницей: nav и title «PEELING».</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>b1.line и чипы b1.label2–5 — после каких процедур</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>b1.line «לאחר מיקרונידלינג, פילינגים וספיקולות, העור זקוק ללחות…»; чипы: V-TECH SYSTEM, פילינג EXO-NAD, MICRO BOOST 10%, מיקרונידלינג</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>«EXOCELL MASK מתאימה במיוחד כשלב מסיים ומרגיע לאחר טיפולים מקצועיים, לרבות:» chips: 'לייזר', 'פילינג', 'טיפולי הזרקה ופילרים', 'מזותרפיה רפואית', 'RF מיקרונידלינג', 'RF', 'מיקרונידלינג'</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:210-212 (exocell-mask, blocks[0])</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Добавить перечень из протокола строкой без ссылок под чипами (b1.line можно не трогать), дословно: «לייזר · פילינג · טיפולי הזרקה ופילרים · מזותרפיה רפואית · RF מיקרונידלינג · RF · מיקרונידלינג». Чипы-ссылки на свои средства оставить.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В content.he.mjs:211–212: «EXOCELL MASK מתאימה במיוחד כשלב מסיים ומרגיע לאחר טיפולים מקצועיים, לרבות:» и чипы «לייזר, פילינג, טיפולי הזרקה ופילרים, מזותרפיה רפואית, RF מיקרונידלינג, RF, מיקרונידלינג». В сюжете b1.line «לאחר מיקרונידלינג, פילינגים וספיקולות» и четыре чипа своих средств. Лазер, инъекции и филлеры, мезотерапия и RF пропущены — а это заметная часть применения для клиник.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>b4.label2 «2 · ספיגה» и b4.line — нет времени экспозиции</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Метка «2 · ספיגה» без времени; в action_3d_ru и в вопросе 6: «В каталоге нет времени экспозиции маски, поэтому шаг «ספיגה» на экране 6 идёт без времени.»</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>«יש להשאיר את המסכה על העור למשך עד־30 דקות.» PLAN §7: «EXOCELL MASK — до 30 минут».</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:206 (exocell-mask, use.steps[1]); PLAN.md:118</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Метка шага 2: «2 · ספיגה · עד 30 דקות» (время из протокола: «למשך עד־30 דקות»). Иврит — через переводчика.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В content.he.mjs:206 «יש להשאיר את המסכה על העור למשך עד־30 דקות.» (EN: «Leave the mask on the skin for up to 30 minutes.»). PLAN.md:118: «EXOCELL MASK — до 30 минут». В сюжете метка «2 · ספיגה» без времени, а в вопросе 6 стоит «В каталоге нет времени экспозиции».</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>b4.label3 «3 · סיום» — нет действия протокола</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>«3 · סיום» / «3 · Finish», без действия</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>«לאחר מכן יש להסיר את המסכה ולהספיג בעדינות את שאריות הסרום שנותרו על העור.»</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:207 (exocell-mask, use.steps[2])</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>В метке шага 3 сказать, что делают с остатком сыворотки, не выделяя снятие маски. Например: «3 · סיום · מספיגים בעדינות את שאריות הסרום לעור» — по фразе протокола «להספיג בעדינות את שאריות הסרום שנותרו על העור». Через переводчика и рецензентов.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В content.he.mjs:207 «לאחר מכן יש להסיר את המסכה ולהספיג בעדינות את שאריות הסרום שנותרו על העור.» (EN :207 — «gently pat the remaining serum into the skin»). В сюжете метка «3 · סיום» без действия. Предложение соблюдает слово заказчика «Снятие не выделять» (PLAN.md:81).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>b6.line «לשימוש מקצועי בלבד.»; use: professional; inside.pro_only: true</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>источники расходятся</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>«לשימוש מקצועי בלבד.» / «For professional use only.»</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Протокол: «sub: 'פרוטוקול שימוש מקצועי וביתי'» (EN: «Professional and home-use protocol»). PLAN §7, слово заказчика 11/10: «В клинике её снимает специалист; клиент может пользоваться маской и после процедуры.» packaging-text: «clients can also use it after the procedure (owner, 11/10)». Каталог HE: «ניתן להשתמש בה גם כטיפול עצמאי לעור יבש, עייף, רגיש או חסר חיוניות.»</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:202; PLAN.md:81; site/packaging-text.json → exocell-mask.objects[3].look; source-texts.md:164</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>«Только для профессионального использования» противоречит слову заказчика и подзаголовку протокола «מקצועי וביתי». Убрать «בלבד»: маска — для клиник, а клиент может пользоваться ею и после процедуры. Формулировку на иврите сделать через переводчика и подтвердить у заказчика, потому что это заявление о продаже. Флаг inside.pro_only пересмотреть вместе с ней. Текст про двойную маску не трогаем.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В подзаголовке протокола (:202) «פרוטוקול שימוש מקצועי וביתי» (EN: «Professional and home-use protocol»). Заказчик 11/10 (PLAN.md:81): «клиент может пользоваться маской и после процедуры»; то же в packaging-text exocell-mask.objects[3].look. Печатный каталог HE (source-texts.md:164) пишет «ניתן להשתמש בה גם כטיפול עצמאי…», а «לשימוש מקצועי בלבד» у EXOCELL в печатном тексте нет — оно есть только в веб-cta product-pages.he.json. В сюжете b6.line «לשימוש מקצועי בלבד.» и pro_only: true.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[5] — время экспозиции</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>«В каталоге нет времени экспозиции маски, поэтому шаг «ספיגה» на экране 6 идёт без времени. Если в техлисте VM время есть, добавить?»</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>«יש להשאיר את המסכה על העור למשך עד־30 דקות.»</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs:206</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Ответ есть в основных протоколах заказчика: до 30 минут. Добавить в шаг 2 (находка 18), вопрос закрыть.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено: в content.he.mjs:206 «יש להשאיר את המסכה על העור למשך עד־30 דקות.», в PLAN.md:118 — «EXOCELL MASK — до 30 минут». Вопрос сюжета исходит из того, что времени нет, а оно есть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[6] — WhatsApp 054-762-1889 и телефон 054-326-2182</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>«Главная кнопка WhatsApp ведёт на номер 054-762-1889, а на экране 7 указан телефон 054-326-2182 (оба из site/proto/exocell-he-ui.json). Так и задумано?»</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>contacts.json: «"phone": "054-326-2182"», «"whatsapp": "+972-54-762-1889"», «"whatsapp_link": "https://wa.me/972547621889"»; «Owner 11/10: everything on mitoderm.com is correct»</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>site/sources/mitoderm-com/contacts.json:2-7; PLAN.md:117</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Да, так задумано: на mitoderm.com WhatsApp +972-54-762-1889, телефон 054-326-2182, почта info@mitoderm.com. Вопрос закрыть; срок обратного звонка нигде не писать.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. contacts.json: «phone»: «054-326-2182», «whatsapp»: «+972-54-762-1889», «whatsapp_link»: «https://wa.me/972547621889»; в _source: «Owner 11/10: everything on mitoderm.com is correct». PLAN.md:117 — то же. Номер 054-762-1889 из сюжета совпадает с WhatsApp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>b2.label4 + b2.line + inside.actives_text (витамины)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>источники расходятся</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>«ויטמינים B5 · B7 · B6 · B1» / «Vitamins B5 · B7 · B6 · B1»; в составе «Vitamins B5, B7, B6, B1»</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Каталог HE: «ויטמינים ורכיבים תומכים : פנתנול – פרו־ויטמין B5, ביוטיו– ויטמין B7 פירידוקסין – ויטמין B6 תיאמין – ויטמין B1»; каталог RU: «Витамины: Panthenol — провитамин B5, Biotin — витамин B7, Pyridoxine — витамин B6, Thiamine — витамин B1». mitoderm.com: «ויטמינים (פנתנול, גלוטתיון, ביוטין)» / «Vitamins (panthenol glutathione biotin)».</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/source-texts.md → Стр. 10 EXOSIGNAL HAIR; mitoderm-catalog/source-texts-ru-2026-09-18.md → Полоса 12; site/sources/mitoderm-com/products-he.json и products-en.json → solution.signal.item5</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Текст не менять: оставить B5 · B7 · B6 · B1, как в обеих печатных редакциях. Глутатион, который есть только на mitoderm.com, без подтверждения заказчика не добавлять. По желанию задать один короткий вопрос: входит ли глутатион в формулу (в лиде каталога есть «ויטמינים ונוגדי חמצון»).</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Цитаты точные. Печатный каталог на иврите: «פנתנול – פרו־ויטמין B5, ביוטיו– ויטמין B7 פירידוקסין – ויטמין B6 תיאמין – ויטמין B1». Русская версия называет те же четыре витамина. mitoderm.com: «ויטמינים (פנתנול, גלוטתיון, ביוטין)». Страница следует обеим печатным редакциям, ошибки на ней нет. Это расхождение источников только для сведения, текст менять не нужно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>b4.label3 + transition_ru 5→6 + story_one_line (ампула «израсходована в сеансе»; связано с вопросом 3 об отламывании горлышка)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>ошибка</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>b4.label3: «3 · החדרה · אמפולה אחת» / «3 · Apply · one ampoule»; переход 5→6: «открытая ампула гаснут и уходят назад в темноту: ампула израсходована в сеансе»; story_one_line: «в конце пять запечатанных ампул, пять сеансов, собираются в одну коробку»</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>«יש להשתמש בכ־2–1.5 מ״ל מהסרום, בהתאם לגודל האזור המטופל.» / «Use about 1.5-2 ml of serum…»; «לאחר הפתיחה יש לשמור את האמפולה בקירור. עמידות לאחר פתיחה: עד חודש.» / «After opening, keep the ampoule refrigerated. Shelf life after opening: up to one month.»</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/protocols/src/content.he.mjs / content.en.mjs → protocol id 'exosignal-hair': steps[2] и aside 'Storage'</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>b4.label3 — по дозе протокола: «3 · EXOSIGNAL HAIR · 1.5–2 מ״ל» / «3 · EXOSIGNAL HAIR · 1.5–2 ml». В переходе 5→6 не говорить, что ампула израсходована. Факт хранения дать на экране 6 или в карточке экрана 7 дословно: «לאחר הפתיחה יש לשמור את האמפולה בקירור. עמידות לאחר פתיחה: עד חודש.» В story_one_line вместо «пять сеансов» — «пять ампул по 5 мл в одной коробке». Вопрос 3 (как вскрывается ампула) задать заказчику вместе с фактом о хранении вскрытой ампулы, до сборки перехода 2→3.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В истории b4.label3 — «3 · החדרה · אמפולה אחת» / «3 · Apply · one ampoule». Переход 5→6 говорит, что ампула «израсходована в сеансе», а story_one_line — «пять запечатанных ампул, пять сеансов». Протокол даёт дозу около 1,5–2 мл на процедуру и хранение вскрытой ампулы в холодильнике до месяца. Так что ампула за сеанс не расходуется. Как вскрывается ампула, источники не говорят. Но вскрытую ампулу хранят, поэтому сцену с отломанной и улетевшей головкой (вопрос 3) нужно согласовать.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>b4.title + b4.line + b4.label1–3 + action_3d_ru (порядок шагов: сначала MITOPEN, потом средство)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>ошибка</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>«מודדים, פותחים, מחדירים» / «Measure, open, deliver»; «MITOSCAN קובע את נקודת הפתיחה, MITOPEN פותח את מסלול החדירה, EXOSIGNAL HAIR מוחדר לקרקפת המטופלת…» / «MITOSCAN sets the baseline, MITOPEN opens the pathway, EXOSIGNAL HAIR goes on the treated scalp…»; метки «1 · Diagnose · MITOSCAN», «2 · Microneedle · MITOPEN», «3 · Apply · one ampoule»</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Протокол: шаг 1 «יש לנקות היטב את אזור הקרקפת…», «ניתן לבצע את החיטוי…», «ניתן להשתמש במצלמת MITOSCAN  לסקירת הקרקפת , מצב הזקיקים, דלילות ודלקות»; шаг 2 «יש לייבש את אזור הטיפול לחלוטין»; шаг 3 «הטיפול מתבצע בשילוב MITOPEN / מזופן.», «עומק עבודה: עד 0.6 מ״מ, בהתאם לאזור, למצב הקרקפת ולאבחון המקצועי.», «בסימולטניות עוברים ביחד עם החומר והמכשיר . לחלק את העבודה לאזורים : קודם לטפטף מעט מהחומר על אזור מסוים ואז לעשות סטמפינג» / «Product and device work at the same time. Divide the work into sections: first drip a little product onto a section, then stamp.»; шаг 4 «לאחר העבודה יש לעסות עם הכפפות את הקרקפת בעדינות עד לספיגה מלאה של החומר.» Каталог (product-pages.json steps) даёт ту же неверную последовательность: «Scalp microneedling with MITOPEN creates the pathway for the actives.» → «EXOSIGNAL HAIR on the treated scalp» — побеждает протокол.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/protocols/src/content.he.mjs / content.en.mjs → protocol id 'exosignal-hair' steps[0..3]; mitoderm-catalog/site/product-pages.json → exosignal-hair.steps</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Шаги по протоколу. 1 — очищение и дезинфекция кожи головы; MITOSCAN по желанию, для осмотра кожи головы и фолликулов. 2 — полностью высушить. 3 — EXOSIGNAL HAIR и MITOPEN (или мезопен) одновременно: по участкам сначала капнуть немного средства, затем стемпинг; глубина до 0,6 мм, около 1,5–2 мл. 4 — помассировать кожу головы руками в перчатках до полного впитывания. Дома — EXOSIGNAL SPRAY. В 3D ампула и MITOPEN работают в одном шаге: капля на участок, затем стемпинг. Заголовок и фраза не должны говорить, что средство наносят после микронидлинга на уже обработанную кожу. Иврит брать из протокола, например «קודם לטפטף מעט מהחומר על אזור מסוים ואז לעשות סטמפינג».</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В истории (экран 5): «MITOPEN פותח את מסלול החדירה, EXOSIGNAL HAIR מוחדר לקרקפת המטופלת» / «…goes on the treated scalp», шаги идут по порядку: MITOSCAN → MITOPEN → ампула. В протоколе шаг 3 другой: «הטיפול מתבצע בשילוב MITOPEN / מזופן», «בסימולטניות עוברים ביחד עם החומר והמכשיר . לחלק את העבודה לאזורים : קודם לטפטף מעט מהחומר על אזור מסוים ואז לעשות סטמפינג». Значит, средство и прибор работают в одном шаге, и средство капают до стемпинга. Глубина — до 0,6 мм, затем массаж в перчатках до впитывания. MITOSCAN в шаге 1 стоит как «ניתן להשתמש», то есть по желанию. Порядок «сначала прибор» есть в product-pages.json и на mitoderm.com («לאחר פציעה מבוקרת מטפטפים את החומר»), но по порядку шагов главный источник — протокол.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>частота и курс процедур (нет ни на одном экране)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Частоты процедур, числа процедур в курсе и поддерживающих процедур на странице нет; вместо курса — «пять сеансов» по числу ампул.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>«טיפול אחד בכל 14 יום.», «מומלץ לבצע לפחות 4 טיפולים רצופים.», «לאחר השלמת הסדרה ניתן לבצע טיפול תחזוקה אחת לחודשיים.» / «One treatment every 14 days.», «At least 4 consecutive treatments are recommended.», «After the course, a maintenance treatment can be done once every two months.»</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/protocols/src/content.he.mjs / content.en.mjs → protocol id 'exosignal-hair' → after 'תדירות וסדרת טיפולים / Frequency and treatment course'</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>На экран 5 или на экран 6 вместо «пяти сеансов» добавить строку курса дословно из протокола: «טיפול אחד בכל 14 יום · מומלץ לבצע לפחות 4 טיפולים רצופים · לאחר השלמת הסדרה ניתן לבצע טיפול תחזוקה אחת לחודשיים» / «One treatment every 14 days · at least 4 consecutive treatments · maintenance once every two months». По желанию добавить оговорку протокола «התדירות ומספר הטיפולים עשויים להשתנות…».</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. Ни на одном экране истории нет частоты процедур и длины курса. В протоколе exosignal-hair, в блоке «תדירות וסדרת טיפולים», дословно: «טיפול אחד בכל 14 יום.», «מומלץ לבצע לפחות 4 טיפולים רצופים.», «לאחר השלמת הסדרה ניתן לבצע טיפול תחזוקה אחת לחודשיים.» Для профессионального средства это важный факт протокола.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>b5.title + b5.line + action_3d_ru («пять запечатанных ампул — курс из пяти сеансов», цифры 1–5 под ампулами)</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>ошибка</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>«חמישה טיפולים באריזה אחת» / «Five sessions in one box»; «חמש אמפולות זכוכית של 5 מ״ל – אחת לכל טיפול מקצועי – …» / «Five 5 ml glass ampoules — one per professional session — …»; 3D: «пять запечатанных ампул — курс из пяти сеансов. Под каждой цифра от 1 до 5»</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Протокол, шаг EXOSIGNAL HAIR SERUM: «יש להשתמש בכ־2–1.5 מ״ל מהסרום, בהתאם לגודל האזור המטופל.» / «Use about 1.5-2 ml of serum, depending on the size of the area.» Хранение: «לאחר הפתיחה יש לשמור את האמפולה בקירור. עמידות לאחר פתיחה: עד חודש.» / «After opening, keep the ampoule refrigerated. Shelf life after opening: up to one month.» Печать коробки: 'Net 5 x 5 ml ℮ 5 x 0.17 fl.oz.'</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/protocols/src/content.he.mjs и content.en.mjs → protocol id 'exosignal-hair': steps[2] 'EXOSIGNAL HAIR SERUM' и aside 'אחסון / Storage'; mitoderm-catalog/site/packaging-text.json → exosignal-hair → flat box</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Убрать «одна ампула — один сеанс» и «пять сеансов в коробке». Заголовок экрана 6 — о составе коробки, например «5 אמפולות × 5 מ״ל» / «5 ampoules × 5 ml», как на печати 'Net 5 x 5 ml'. b5.line: «חמש אמפולות זכוכית של 5 מ״ל», затем дословно из протокола «יש להשתמש בכ־2–1.5 מ״ל מהסרום, בהתאם לגודל האזור המטופל», затем PDRN 2% (20 מ״ג/מ״ל) и восемь пептидов. В 3D убрать цифры 1–5 и «курс из пяти сеансов». Если курс показывать, то протокольный: процедура раз в 14 дней, не меньше 4 подряд.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В истории (экран 6) стоит «חמישה טיפולים באריזה אחת» / «Five sessions in one box», «אחת לכל טיפול מקצועי», а в 3D: «курс из пяти сеансов, цифры 1–5». Протокол exosignal-hair (content.he/en.mjs): шаг EXOSIGNAL HAIR SERUM — «יש להשתמש בכ־2–1.5 מ״ל מהסרום…», в aside — «לאחר הפתיחה יש לשמור את האמפולה בקירור. עמידות לאחר פתיחה: עד חודש.» Вскрытую ампулу 5 мл, значит, хранят и используют снова. При процедуре раз в 14 дней одна ампула идёт на 2–3 сеанса, а не на один. На коробке (packaging-text.json) напечатано 'Net 5 x 5 ml ℮ 5 x 0.17 fl.oz.'. «Один сеанс» встречается только в product-pages.json, а протокол важнее.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>карточка «что внутри»: cat.kit[0][2]; inside.components[0].volume_dose</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>источники расходятся</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>cat.kit[0][2]: «5 מ״ל כל אחת – הפורמולה המלאה לקרקפת לטיפול מקצועי אחד.» / «5 ml each — the full scalp formula for one professional session.»; inside.volume_dose: «5 мл каждая, одна ампула на один профессиональный сеанс»</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Протокол: «יש להשתמש בכ־2–1.5 מ״ל מהסרום, בהתאם לגודל האזור המטופל.» и «לאחר הפתיחה יש לשמור את האמפולה בקירור. עמידות לאחר פתיחה: עד חודש.» Печатный каталог HE говорит только «תכולת האריזה: 5 אמפולות *5 מל», RU — «5 ампул × 5 мл»; mitoderm.com — «5 ml x 5 Ampules». «Один сеанс» есть только в product-pages.json.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/site/product-pages.json и product-pages.he.json → exosignal-hair.kit[0]; mitoderm-catalog/protocols/src/content.he.mjs → 'exosignal-hair' steps[2], aside; mitoderm-catalog/source-texts.md → Стр. 10; site/sources/mitoderm-com/products-he.json → solution.signal.item1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>В карточке: «5× · אמפולות · 5 מ״ל כל אחת», без «לטיפול מקצועי אחד». По желанию добавить из протокола «כ־1.5–2 מ״ל לטיפול» и «לאחר הפתיחה – בקירור, עד חודש». inside.volume_dose: «5 мл каждая; на процедуру около 1,5–2 мл; после вскрытия — в холодильнике до одного месяца».</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. product-pages(.he).json → kit[0]: «5 מ״ל כל אחת – הפורמולה המלאה לקרקפת לטיפול מקצועי אחד.» / «…for one professional session». Печатный каталог говорит только «תכולת האריזה: 5 אמפולות *5 מל», русская версия — «5 ампул × 5 мл», mitoderm.com — «5 ml x 5 Ampules». Протокол даёт 1,5–2 мл на процедуру и хранение вскрытой ампулы до месяца. Источники расходятся, и по процедуре прав протокол.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[0] (фото коробки, открытая коробка с вкладышем) + assets (торцы коробки «needs photo», крупная ампула «needs photo») + экран 6 «фото вкладыша нет»</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>«Нужны фото коробки: фасад без ампул…, торцы, задняя сторона, глубина, а также открытая коробка с вкладышем»; экран 6: «Внутренность коробки не показываем: фото вкладыша нет.»</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>«| 36, 47 | 113:8145, 113:8164 | EXOSIGNAL HAIR | чёрная коробка с золотым «EXOSIGNAL HAIR» | текстура коробки |» и «| 55, 58 | 113:8174, 113:8177 | EXOSIGNAL HAIR | открытая чёрная коробка со стеклянными ампулами | раскрытие набора, 3D-ампулы |»</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/site/photo-catalog.md → строки 36, 47 и 55, 58</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Фото заказчика уже есть в Figma: коробка (113:8145, 113:8164) и открытая коробка со стеклянными ампулами (113:8174, 113:8177). Сначала посмотреть по ним фасад без ампул, торцы, вкладыш и ампулы крупно. У заказчика спрашивать только то, чего на этих снимках нет. Сцену с открытой коробкой на экранах 6–7 можно вернуть по фото 55/58.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В photo-catalog.md есть строки «36, 47 | 113:8145, 113:8164 | EXOSIGNAL HAIR | чёрная коробка с золотым «EXOSIGNAL HAIR» | текстура коробки» и «55, 58 | 113:8174, 113:8177 | … открытая чёрная коробка со стеклянными ампулами | раскрытие набора, 3D-ампулы». Сборщик (story3d_xlsx.py, PHOTOS) тоже относит к этой странице фото 36, 47, 55, 58. А история говорит «фото вкладыша нет» и просит у заказчика открытую коробку. Есть ли на этих снимках торцы и фасад без ампул, неизвестно, поэтому сначала их нужно посмотреть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>kicker (ui.line_mark + ui.line_name + ui.use_home), то же на экранах 2 и 7</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>ошибка</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>«V-TECH FACE · התחדשות הפנים · טיפוח ביתי» / «V-TECH FACE»</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>product-pages.he.json: «eyebrow»: «טיפוח ביתי · קרקפת»; product-pages.json: «filter»: «Hair», «eyebrow»: «HOME CARE · SCALP»; каталог: «ספריי ביתי מתקדם לטיפוח הקרקפת ולתמיכה בשיער». В самом сюжете new_strings: ui.line_mark = «HAIR».</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/site/product-pages.he.json и product-pages.json → EXOSIGNAL SPRAY; mitoderm-catalog/source-texts.md → Стр. 18; site/proto/exocell-he-ui.json (line_mark «V-TECH FACE», line_name «התחדשות הפנים»)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Для спрея значения ui.line_mark и ui.line_name из строк страницы (story3d.json: «HAIR» и вычитанное «שיער וקרקפת», ждёт вопроса 8) должны иметь приоритет над UI-файлом MASK. Это правка в resolve() или отдельный UI-файл спрея. До ответа заказчика ui.line_name не брать у MASK: ставить «שיער וקרקפת» с пометкой «на ответе» или показывать только «HAIR» + «טיפוח ביתי».</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В истории спрея кикер экрана 1 разрешился в «V-TECH FACE · התחדשות הפנים · טיפוח ביתי» / «V-TECH FACE», хотя в new_strings стоит ui.line_mark = «HAIR». Причина в коде: resolve() в story3d_xlsx.py берёт все ключи ui.* только из UI-файла MASK (exocell-he-ui.json: line_mark «V-TECH FACE», line_name «התחדשות הפנים»). Строки самой страницы спрея ему не видны, хотя в story3d.json для спрея уже есть HE «HAIR» и «שיער וקרקפת». Ошибка повторится в бейджах экранов 2 и 7. Средство для кожи головы подписано линейкой для лица. Предложение находки поставить «טיפוח ביתי · קרקפת» продублировало бы «טיפוח ביתי»: эта надпись уже есть в бейдже ui.use_home.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>b4.line + b4.label1–3 (как применять)</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>«לחלק את השיער כדי לחשוף את הקרקפת, להתיז ישירות עליה ולעסות בעדינות – ללא צורך בשטיפה. מדי יום…» / «Part the hair…, spray directly on, massage lightly — no rinsing. Daily…»; шаги «1 · Part · 2 · Spray · 3 · Massage»</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm.com: «פעם ביום, על קרקפת נקייה ויבשה. לנער לפני השימוש ולהתיז על האזור הרצוי בשורשים. לעסות בעדינות לפיזור. מומלץ בערב, למשך חודשיים.» / «Once a day, on a clean and dry scalp. Shake before use and spray on the desired area at the roots. Gently massage to distribute. Recommended for evening use, for a duration of two months.»</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/site/sources/mitoderm-com/products-he.json и products-en.json → solution.hair.bundleText2</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Дополнить способ применения данными mitoderm.com. Например, b4.line: «פעם ביום, על קרקפת נקייה ויבשה. לנער לפני השימוש, לחלק את השיער ולהתיז על האזור הרצוי בשורשים, לעסות בעדינות – ללא צורך בשטיפה. מומלץ בערב, למשך חודשיים.» Шаги можно начать с «לנער».</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В протоколах спрея нет. На mitoderm.com (products-he/en.json → solution.hair.bundleText2): «פעם ביום, על קרקפת נקייה ויבשה. לנער לפני השימוש ולהתיז על האזור הרצוי בשורשים. לעסות בעדינות לפיזור. מומלץ בערב, למשך חודשיים.» В b4.line истории есть только «разделить волосы → распылить → помассировать, без смывания, ежедневно». Нет того, что встряхивать, наносить на чистую сухую кожу у корней, раз в день, лучше вечером и курсом два месяца. Каталогу это не противоречит.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[6] (состав спрея) + inside.actives_key + экран 3 / карточка экрана 7</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>«Есть ли состав спрея (INCI или активы)? В каталоге есть только «что делает спрей»…»; inside.actives_key: «в каталоге только «что делает спрей», INCI нет»</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm.com: «קומפלקס פעיל לטיפול יומיומי»: «15 מל», «אקסוזומים סינתטיים», «PDRN במשקל מולקולרי נמוך», «פנתנול», «ביוטין», «פפטידים ביומימטיים 8 סוגים» / «Active complex for daily treatment»: «15 ml», «Synthetic exosomes», «PDRN with low molecular weight», «Panthenol», «Biotin», «Biomimetic peptides 8 types»</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/site/sources/mitoderm-com/products-he.json и products-en.json → solution.hair.itemTitle, item1–item6</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Вопрос снять. В карточку «מה בפנים» (экран 7) и на экран 3 добавить подзаголовок «רכיבים פעילים» и список с mitoderm.com: «אקסוזומים סינתטיים · PDRN במשקל מולקולרי נמוך · פנתנול · ביוטין · פפטידים ביומימטיים 8 סוגים». Блок «מה הספריי עושה» можно оставить рядом.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. Вопрос 7 истории («Есть ли состав спрея…? В каталоге только «что делает спрей»») закрывается mitoderm.com. В solution.hair (это ExoSignal Hair Spray, «בקבוק ספריי 15 מל») есть «קומפלקס פעיל לטיפול יומיומי» со списком: «אקסוזומים סינתטיים», «PDRN במשקל מולקולרי נמוך», «פנתנול», «ביוטין», «פפטידים ביומימטיים 8 סוגים». Английская версия совпадает.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[5] (нажатий на нанесение, на сколько хватает 15 мл)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>«Сколько нажатий нужно на одно нанесение и на сколько хватает 15 мл? В каталоге этого нет, поэтому на странице пишем только «15 מ״ל, ежедневно, без смывания»»</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm.com: «פעם ביום, … מומלץ בערב, למשך חודשיים.» / «Once a day, … Recommended for evening use, for a duration of two months.»</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/site/sources/mitoderm-com/products-he.json и products-en.json → solution.hair.bundleText2</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Частота (раз в день, лучше вечером) и курс (два месяца) есть на mitoderm.com — их можно писать на экранах 5–6. Заказчику оставить только вопрос о числе нажатий на одно нанесение.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Частично подтверждено. Вопрос 6 истории: «Сколько нажатий на одно нанесение и на сколько хватает 15 мл?» На mitoderm.com: «פעם ביום… מומלץ בערב, למשך חודשיים» — раз в день, лучше вечером, курс два месяца. Числа нажатий нет ни в одном источнике. Находка это и говорит и не утверждает, что 15 мл точно хватает на два месяца.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[0] (студийный пакшот) + assets: коробка «Фасад есть только на site/img/exosignal-spray.png», флакон «needs photo»</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>«Студийного пакшота EXOSIGNAL SPRAY нет… Пришлите его в чат или положите в Drive /products»; assets: «Фасад есть только на site/img/exosignal-spray.png (400×300…)»</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>«| 2, 3, 21 | 93:8081, 93:8083, 104:8121 | EXOSIGNAL SPRAY HOME | чёрная коробка с золотом + матовый флакон с золотой крышкой (белый фон) | пакшот спрея (замена слабого 49:6) |» и «| 33, 34, 41, 43, 59, 65 | 113:8141 … 113:8185 | EXOSIGNAL SPRAY HOME | матовый флакон, чёрная коробка; 65 — интерьерная сцена | пакшот, сцена |»</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/site/photo-catalog.md → строки 2, 3, 21 и 33, 34, 41, 43, 59, 65</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Фото заказчика (коробка + матовый флакон с золотым колпачком) уже есть в Figma: 93:8081, 93:8083, 104:8121 на белом фоне и 113:8141…113:8185. Фасад коробки и этикетку флакона брать с них, а не с exosignal-spray.png. У заказчика просить только то, чего на этих снимках не окажется после проверки: например, распылитель без колпачка, оборот флакона, бок и верх коробки.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. В photo-catalog.md есть строки «2, 3, 21 | 93:8081, 93:8083, 104:8121 | EXOSIGNAL SPRAY HOME | чёрная коробка с золотом + матовый флакон с золотой крышкой (белый фон) | пакшот спрея» и «33, 34, 41, 43, 59, 65 | 113:8141 … 113:8185 | … матовый флакон, чёрная коробка». Сборщик тоже относит их к спрею (PHOTOS). А история пишет, что студийного пакшота нет, просит прислать его в чат или Drive и берёт фасад коробки со скриншота exosignal-spray.png 400×300.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[3] (фото с человеком exosignal-spray-hand.jpg в публичном репозитории)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>«…это фото с человеком, и оно уже лежит в публичном репозитории… Убрать его из репозитория и хранить копию только локально?»</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>«Сами фото в репозиторий не кладутся: на части из них люди, репозиторий публичный.»; «**«люди»** — фото с людьми: в публичные файлы и рендеры не идёт, только в Figma и только с согласия заказчика.»</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/site/photo-catalog.md → вводный абзац; файл в git: mitoderm-catalog/site/img/exosignal-spray-hand.jpg (на фото щека, волосы и рука)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Вопрос не задавать: решение заказчика уже есть. Убрать site/img/exosignal-spray-hand.jpg из репозитория, копию держать локально или в Figma. Ссылки в packaging-text.json/.md и story3d.json перевести на фото 93:8081 / 93:8083 / 104:8121, этикетку брать с них.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. Файл mitoderm-catalog/site/img/exosignal-spray-hand.jpg лежит в git (git ls-files). На нём щека, шея, волосы и рука человека — проверено просмотром. Правило заказчика уже есть: photo-catalog.md — «Сами фото в репозиторий не кладутся: на части из них люди, репозиторий публичный», «люди… в публичные файлы и рендеры не идёт»; CLAUDE.md проекта — «Не в репозиторий: … фото с людьми». В репозитории на файл ссылаются только тексты: packaging-text.json/.md и story3d.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>EXOTECH GEL</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>b4.line + b4.label4 (с чем и когда применять)</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>«…משתלב עם V-TECH, EXO-NAD וסדרת BIOSPICULE™.» / «Works with V-TECH, EXO-NAD and the BIOSPICULE™ line.»; экран 2: «לאחר טיפול בקליניקה» / «After in-clinic treatments»</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Протокол (домашний протокол поддержки): «ניתן להשתמש באקסוטק גל לשימור התוצאה של האקסוזומים מיד לאחר סדרת ביומיקרונידלינג» / «EXOTECH GEL can be used to preserve the exosome results immediately after a biomicroneedling course.»; протокол BIOSPICULE MICRO BOOST 10% + V-TECH: «לבית ניתן להמליץ את הסדרה הביתית של ביוספיקול לחידוש , אקסוטק גל ללחות מיטבית וקרם רקברי להזנה ולחות אינטנסיבית.»</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/protocols/src/content.he.mjs / content.en.mjs → protocol 'exocell-mask' → home.maintain; protocol 'biospicule-vtech' → aside</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Добавить факт протокола дословно. Например, b4.line: «…בוקר וערב. ניתן להשתמש באקסוטק גל לשימור התוצאה של האקסוזומים מיד לאחר סדרת ביומיקרונידלינג.» По желанию добавить из протокола BIOSPICULE MICRO BOOST 10% + V-TECH: «אקסוטק גל ללחות מיטבית» в домашнем уходе после процедуры.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Подтверждено. Протокол exocell-mask → home.maintain: «ניתן להשתמש באקסוטק גל לשימור התוצאה של האקסוזומים מיד לאחר סדרת ביומיקרונידלינג». Протокол biospicule-vtech, aside: «לבית ניתן להמליץ את הסדרה הביתית של ביוספיקול לחידוש , אקסוטק גל ללחות מיטבית…». В истории есть только общее «לאחר טיפול בקליניקה» и «משתלב עם V-TECH, EXO-NAD וסדרת BIOSPICULE™». Протокольного момента применения — сразу после курса биомикронидлинга, чтобы сохранить результат экзосом — нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>EXOTECH GEL</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[2] (фото куба и сферы в высоком разрешении, другие грани; объём 30 мл)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>«Есть ли исходные фото куба и сферы в высоком разрешении…? И что напечатано на тыльной, правой и нижней гранях куба…? Объём 30 ml на видимых сторонах не виден, сейчас он взят из каталога.»</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>photo-catalog: «| 37, 38 | 113:8153, 113:8154 | EXOTECH GEL | золотой куб-коробка «EXOTECH GEL» | 3D-коробка |»; манифест фото каталога: «EXOTECH GEL (шар + коробка, 2 ракурса) | 2 фото»; mitoderm.com: «item1»: «30 ml», «bundleText1»: «V-Tech Gel 30 ml».</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/site/photo-catalog.md → строки 37, 38; mitoderm-catalog/source-texts.md → Приложение B; site/sources/mitoderm-com/products-en.json → solution.gel</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Сначала проверить в Figma два ракурса куба заказчика (113:8153, 113:8154): разрешение и видимые грани. Объём 30 мл подтверждён каталогом и mitoderm.com. У заказчика спрашивать только то, чего на этих фото нет: вероятно, тыльную, правую и нижнюю грани куба и обратную сторону сферы.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Частично подтверждено. В photo-catalog.md есть строка «37, 38 | 113:8153, 113:8154 | EXOTECH GEL | золотой куб-коробка «EXOTECH GEL» | 3D-коробка», сборщик тоже относит фото 37, 38 к этой странице. История берёт куб только с protocols/print/img/exotech-gel.webp и просит у заказчика исходники. Объём 30 мл, кроме каталога, подтверждён mitoderm.com («item1»: «30 ml», «V-Tech Gel 30 ml»). Есть ли на фото 37/38 сфера, обратные грани и высокое разрешение, неизвестно, поэтому их нужно сначала проверить.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10%</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>b3.label2 «עד 72 שעות»; b3.line; b5.label4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>источники расходятся</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>«...הספיקולות עשויות להמשיך לעורר את העור עד 72 שעות לאחר שהמטופלת עוזבת»</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Протокол: 'הספיקולות עשויות להישאר בשכבות החיצוניות של העור עד 72 שעות.' Русский каталог: 'Микроспикулы могут сохраняться в коже до 72 часов'. Ивритский каталог, разворот стр. 12–13: 'מיקרו-מחטים ביולוגיות נשארות בעור עד 24 שעות'.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs, протокол biospicule-vtech, строка 97; source-texts-ru-2026-09-18.md, строка 363; source-texts.md, стр. 12–13, строка 269</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>На странице MICRO BOOST 10% ничего не менять: «עד 72 שעות» совпадает с протоколом и русским каталогом, текущая формулировка b3.line подтверждена. Цифру 24 ч нигде на сайте не использовать (страница BIOSPICULE уже на 72 ч). Владельцу сообщить, что в печатном ивритском каталоге на развороте стр. 12–13 стоит «עד 24 שעות», а протокол и русский каталог говорят 72 ч: вероятно, это ошибка печати.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Расхождение есть. Протокол (строка 97) и русский каталог (строки 323, 363) — до 72 ч, ивритский каталог (разворот стр. 12–13, строка 269) — «עד 24 שעות». По процедуре решает протокол, так что 72 ч на странице верно. Поправка: переписывать b3.line ближе к протоколу не нужно. Формулировка «עשויות להמשיך לעורר את העור עד 72 שעות» опирается на русский каталог («могут сохраняться в коже до 72 часов, продолжая механическую стимуляцию») и на product-pages («להמשך גירוי וחידוש»), и смена слов — вопрос стиля.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10%</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>b4.label4 «+ DERMA RECOVERY בבית»; cat.steps[2][1]; b4.line</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>ошибка</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Метка «+ DERMA RECOVERY בבית» / «+ DERMA RECOVERY at home»; cat.steps[2][1]: «V-TECH או Longevity Serum, לאחר מכן EXOCELL MASK; בבית – DERMA RECOVERY CREAM ומקדם הגנה». DERMA RECOVERY CREAM показан только как домашний шаг, SPF 30 на экране не назван.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Протокол, «סיום הטיפול»: 'EXOCELL MASK  כמסכת סיום ושיקום' · 'DERMA RECOVERY CREAM להשלמת לחות הזנה ותמיכה במחסום העורי' · 'SPF   מסנן קרינה של 30 לפחות חובה' (EN: 'DERMA RECOVERY CREAM to complete hydration and nourishment and support the skin barrier', 'SPF 30 or higher sunscreen, mandatory'). Каталог, стр. 14: 'Derma Recovery סיום טיפול ובבית – חובה לאחר הטיפול לתמיכה במחסום הלחות ולהפחתת תחושת יובש ומתיחה'.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs, протокол biospicule-vtech, after «סיום הטיפול», строки 89–91; source-texts.md, стр. 14, строка 299</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Протокол и оба каталога ставят DERMA RECOVERY CREAM в финал процедуры в клинике, после EXOCELL MASK, и делают его обязательным дома. Метку b4.label4 заменить по смыслу каталога («סיום טיפול ובבית»), например «+ DERMA RECOVERY בסיום הטיפול ובבית». В cat.steps[2][1] финиш дать в порядке протокола: EXOCELL MASK → DERMA RECOVERY CREAM → מסנן קרינה SPF 30 לפחות (חובה). Защиту не переносить в «בבית». В b4.line микроканалы оставить для V-TECH / Longevity Serum, а EXOCELL MASK назвать финишной маской: протокол «כמסכת סיום ושיקום», русский каталог «Завершение процедуры».</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Цитаты точные (content.he.mjs стр. 89–91, source-texts.md стр. 14, строка 299). Русский каталог подтверждает: «Завершение процедуры: EXOCELL MASK / DERMA RECOVERY CREAM — также обязательное домашнее применение / Солнцезащитное средство». В ивритском каталоге есть ещё «הגנה בסיום טיפול». В сюжете метка «+ DERMA RECOVERY בבית», а cat.steps[2][1] (product-pages.he.json) — «בבית – DERMA RECOVERY CREAM ומקדם הגנה»: крем и защита уходят домой, SPF 30 не назван. По протоколу и обоим каталогам это ошибка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10%</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>b4.line; cat.steps[2][1] (активный продукт после MICRO BOOST)</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>«...the open micro-pathways then carry V-TECH or Longevity Serum and EXOCELL MASK» / «...מובילים פנימה את V-TECH או Longevity Serum ואת EXOCELL MASK». Есть два варианта, MITOTECH CELL BOOST не упомянут.</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>'לאחר ספיגת MICRO BOOST 10% ניתן, בהתאם לפרוטוקול שנבחר, לבחור בחומרים פעילים כגון:' — ['V-TECH Serum + V-TECH Gel Mask', 'MITOTECH CELL BOOST', 'LONGEVITY SERUM']. У владельца есть и отдельный протокол 'BIOSPICULE BOOST 10% + MITOTECH CELL BOOSTER': 'באמצעות גל הביוספיקולות – יש למרוח 1.5-2 מל על אזור הפנים ומיד לאחר הספיגה להניח את הcell  booster'.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs, протокол biospicule-vtech, шаг «שילוב חומרים פעילים», строки 83–84; протокол cell-booster, строка 109</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>В шаге 3 и b4.line перечислить варианты из протокола: «V-TECH Serum + V-TECH Gel Mask · MITOTECH CELL BOOSTER · LONGEVITY SERUM». Название брать по глоссарию, в протоколе оно написано «MITOTECH CELL BOOST». V-TECH давать парой «сыворотка + гель-маска». MITOTECH CELL BOOSTER — только текстом, без 3D: пакшота нет, на главной он идёт карточкой «בקרוב». Ссылку вести на эту карточку, а не на страницу: страницы нет.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Цитаты точные: строки 83–84 (три варианта) и строка 109 (протокол BIOSPICULE BOOST 10% + MITOTECH CELL BOOSTER). В b4.line сюжета названы только «V-TECH או Longevity Serum ואת EXOCELL MASK», V-TECH одним словом. Отдельный протокол владельца MICRO BOOST + CELL BOOSTER — одна из двух официальных связок MICRO BOOST, на странице её нет. Список в протоколе открытый («כגון»), но вторая связка — отдельный протокол владельца. Средство описано в PLAN как новое, пакшота нет, на главной оно карточкой «скоро».</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10%</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Курс и частота процедур (нет ни на одном экране)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>На экранах 5–7 не сказано, сколько процедур в курсе и с каким интервалом.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>'ניתן לבצע סדרה של 4–3 טיפולים, במרווח של 4 שבועות בין טיפול לטיפול.' · 'לאחר השלמת הסדרה ניתן לבצע טיפול תחזוקה בהתאם להערכת מצב העור, מטרות הטיפול ותגובת המטופל/ת.' (EN: 'A course of 3-4 treatments, 4 weeks apart.')</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs, протокол biospicule-vtech, aside «סדרת טיפולים», строки 69–70</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>На экран 5 добавить строку из протокола: «סדרה של 4–3 טיפולים, במרווח של 4 שבועות בין טיפול לטיפול; לאחר מכן ניתן לבצע טיפול תחזוקה בהתאם להערכת מצב העור». Это может быть отдельная строка или описание шага, раскрываемое тапом. Частоту V-TECH («каждые 14 дней», курс 4–6) сюда не переносить: у связки с MICRO BOOST интервал 4 недели.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Цитата точная (строки 69–70, EN строка 68). Ни в одном тексте сюжета MICRO BOOST (экраны 1–7, inside) нет числа процедур и интервала. Для профессионального средства это ключевой параметр протокола, а протоколы владельца решают по частоте и длине курса.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10%</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Домашний уход после процедуры (b4.label4, cat.cta[1] на экране 7)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Из домашнего ухода назван только DERMA RECOVERY CREAM.</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>'לבית ניתן להמליץ את הסדרה הביתית של ביוספיקול לחידוש , אקסוטק גל ללחות מיטבית וקרם רקברי להזנה ולחות אינטנסיבית.' (EN: 'For home use, recommend the BIOSPICULE home series for renewal, EXOTECH GEL for optimal hydration and DERMA RECOVERY CREAM for intensive nourishment and hydration.')</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs, протокол biospicule-vtech, aside «סדרת טיפולים», строка 71</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Домашние рекомендации после MICRO BOOST 10% дать по протоколу: домашняя серия BIOSPICULE (CELL RENEW 1.5% / CELLULAR AGE DEFENSE 2.5%) для обновления, EXOTECH GEL для увлажнения, DERMA RECOVERY CREAM для питания и увлажнения. Показать текстом со ссылками на страницы. EXOTECH GEL в 3D не показывать (другая линейка), в 3D оставить мини-коробку DERMA, как в сюжете.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Цитата точная (строка 71, EN строка 70). На экранах 5–7 сюжета из домашнего ухода назван только DERMA RECOVERY CREAM (b4.label4, cat.steps[2][1]). Протокол рекомендует три средства. Поправка к предложению: CELL RENEW / CAD 2.5% тоже из линейки BIOSPICULE, другая линейка только у EXOTECH GEL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10%</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>b5.title «מזרק אחד. טיפול אחד.»; b5.line; inside.components[0].volume_dose; экран 5, шаг 1 («цифр и шкалы нет»)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>«One syringe. One treatment.» / «3 ml ... professional dose control for one in-clinic treatment»; inside: «3 мл на одну процедуру в клинике. Количество... задаёт специалист»; доза на экранах нигде не названа.</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Протокол владельца (BIOSPICULE BOOST 10% + CELL BOOSTER): 'באמצעות גל הביוספיקולות – יש למרוח 1.5-2 מל על אזור הפנים' (EN: 'with the biospicule gel: apply 1.5-2 ml to the face'). В печатном каталоге про шприц сказано только: 'ומגיע במזרק של 3 מ״ל, המאפשר לקוסמטיקאית לשלוט בכמות החומר'. Слов «на одну процедуру» в каталоге нет, они есть только в черновике сайта product-pages kit.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs, протокол cell-booster, строка 109; source-texts.md, стр. 14, строка 280; site/product-pages.he.json, MICRO BOOST kit[0]</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Указать дозу из протокола владельца: «1.5–2 מ״ל לאזור הפנים». Её поставить в шаг 1 на экране 5 (по тапу) и в inside.volume_dose вместо «3 мл на одну процедуру»; «3 ml ℮ 0.10 fl.oz.» — это объём шприца по печати. Заголовок «מזרק אחד. טיפול אחד.» и «לטיפול אחד בקליניקה» в b5.line снять или заменить фактом печати. У владельца спросить, на сколько процедур и зон (лицо или лицо + шея + декольте) рассчитан шприц и подходит ли доза 1.5–2 мл для связки с V-TECH.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Цитата точная (строка 109). «גל הביוספיקולות» в протоколе MITOPEN/BIOSPICULE CELL BOOSTER 10% — это MICRO BOOST 10%: в шапке протокола «10%» и картинка micro-boost-10. Печатные каталоги HE и RU говорят только про шприц 3 мл и контроль количества, слов «на одну процедуру» в них нет. Они есть только в kit сайта product-pages, а project-council уже отметил «единицу продажи — шприц 3 ml» как допущение. При 1.5–2 мл на лицо из шприца 3 мл «один шприц — одна процедура» не следует ни из одного источника. Уточнение: доза взята из протокола связки с CELL BOOSTER, в основном протоколе MICRO BOOST + V-TECH числа нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10%</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[4]; b5.line «3 ml ℮ 0.10 fl. oz.»</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>«В b5.line написано «3 ml ℮ 0.10 fl. oz.» с пробелом, а на коробке «fl.oz.». Привести строку к печати?»</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>"bottom: '3 ml ℮ 0.10 fl.oz.'"</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>site/packaging-text.json, micro-boost-10 → front, строка 47</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Да, привести к печати. В b5.line (HE и EN) писать «3 ml ℮ 0.10 fl.oz.» без пробела в «fl.oz.». Вопрос 5 заказчику снять, правку внести через редактора иврита.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>packaging-text.json, строка 47: «bottom: '3 ml ℮ 0.10 fl.oz.'». На пакшоте protocols/print/img/micro-boost-10.webp (нижняя строка в увеличении) тоже «3 ml ℮ 0.10 fl.oz.» без пробела. Источник по объёмам однозначен, вопрос заказчику не нужен.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5%</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Когда начинать после процедуры в клинике (b1.line «בין הביקורים», b4.line)</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Страница продаёт средство для дома «между визитами» и называет кислоты в формуле (b2.line «חומצה סליצילית + חומצה ציטרית»). Паузы после процедуры в клинике на странице нет.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Протокол, домашние правила после процедуры: 'אין להשתמש בחומצות, רטינואידים, בנזואיל פרוקסיד, פילינג גרגרים או תכשירים מגרים במשך 5–7 ימים, או עד שהעור חזר למצבו ולתחושתו הרגילים.' Каталог: 'Salicylic Acid + Citric Acid'.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>protocols/src/content.he.mjs, exocell-mask → home.cards «חומרים פעילים», строка 223; source-texts.md, стр. 19</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Задать владельцу вопрос до публикации: распространяется ли правило протокола «אין להשתמש בחומצות… במשך 5–7 ימים, או עד שהעור חזר למצבו ולתחושתו הרגילים» на CELL RENEW 1.5% (в составе салициловая и лимонная кислоты, спикулы) и на CAD 2.5% (спикулы, Bakuchiol)? Если да, на экран 5 (или мелко на экран 7) добавить строку: «לאחר טיפול בקליניקה – לא לפני 5–7 ימים, או עד שהעור חזר למצבו ולתחושתו הרגילים». До ответа текст не добавлять.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Цитаты точные: строка 223 протокола (запрет на кислоты и раздражающие средства на 5–7 дней) и состав каталога (Salicylic Acid + Citric Acid). Страница позиционирует средство «בין הביקורים» (b1.line), а паузы после процедуры в клинике нет. Правило стоит в блоке домашних инструкций протокола EXOCELL MASK. Там же предлагается домашняя серия BIOSPICULE 1.5%/2.5% для поддержки, но без срока начала. Значит, распространяется ли правило на CELL RENEW, решает только владелец. Это вопрос к нему, а не готовый текст.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5%</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>b6.cta / ссылка «לקליניקות: לקבלת הצעת מחיר» → шаблон ui.wa_text_price</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>ошибка</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>«...открывает WhatsApp с текстом по шаблону wa_text_price. Оба шаблона берём из proto/exocell-he-ui.json с именем CELL RENEW 1.5%»</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>"wa_text_price": "שלום, אשמח לקבל פרטים על מחירי EXOCELL MASK". В шаблоне нет подстановки {name}, есть только в "wa_text_product": "שלום, אשמח לקבל פרטים על {name}".</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>site/proto/exocell-he-ui.json, строки 16 и 18</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Если взять шаблон буквально, клиника со страницы CELL RENEW 1.5% отправит в WhatsApp вопрос о ценах EXOCELL MASK. Для ссылки «לקליניקות: לקבלת הצעת מחיר» взять ui.wa_text_product с {name} = CELL RENEW 1.5% («שלום, אשמח לקבל פרטים על {name}»), как на странице CAD 2.5%, или завести общий шаблон цены с {name}. Номер 972547621889 верный.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Проверено: в exocell-he-ui.json строка 16 «wa_text_price»: «שלום, אשמח לקבל פרטים על מחירי EXOCELL MASK», подстановки {name} нет, она есть только в wa_text_product (строка 18). Сюжет CELL RENEW ведёт ссылку b6.label3 на wa_text_price «с именем CELL RENEW 1.5%», но шаблон имя не принимает. В сюжете CAD 2.5% та же ссылка идёт через ui.wa_text_product с {name}. Номер 972547621889 совпадает с contacts.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5%</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[0]; assets «Флакон CELL RENEW 1.5% 30 мл» (status: needs photo)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>«Фото флакона нет, печать неизвестна»; заказчика просят прислать фото флакона и спрашивают, такой ли это airless, как у CAD 2.5%.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>| 70, 75 | 113:8199, 113:8214 | CELL RENEW 1.5% | белый airless-флакон на полке | 3D-флакон |</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>site/photo-catalog.md, строка 42</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Фото флакона CELL RENEW 1.5% уже есть в Figma: №70 и №75 (узлы 113:8199, 113:8214), белый airless-флакон, как №9 у CAD 2.5%. Модель флакона строить по ним, assets перевести из «needs photo» в работу по Figma. У заказчика спросить только то, чего на снимках с полки не видно: вид сверху, печать крупно, цвет и прозрачность сыворотки.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Строка 42 photo-catalog.md процитирована точно: №70 и №75 (113:8199, 113:8214) — CELL RENEW 1.5%, «белый airless-флакон на полке», назначение «3D-флакон». В сюжете сказано «Фото флакона нет» и есть просьба прислать фото. Фото заказчика уже лежат в Figma, в репозитории их нет. Сходство с флаконом CAD (№9, «белый airless-флакон») видно по описанию.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5%</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[1] (фасад коробки в высоком разрешении); assets «Коробка CELL RENEW 1.5%»</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Текстура взята с protocols/print/img/cell-renew-15.webp (309×1012), заказчика просят прислать фасад от 2000 px.</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>| 10 | 93:8097 | CELL RENEW 1.5% | коробка: «BIOSPICULE SERUM», эмблема спикул, 30 ml | текстура коробки |</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>site/photo-catalog.md, строка 18</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Сначала проверить разрешение оригинала фото №10 (узел 93:8097) в Figma, он отмечен как текстура коробки. Если по высоте его хватает, брать фасад оттуда, а не из webp 309×1012. Новый фасад просить у заказчика, только если оригинал слабый. Вопрос о боковых гранях, верхе и заднике остаётся.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Строка 18 photo-catalog.md процитирована точно: №10 (93:8097) — коробка CELL RENEW 1.5%, назначение «текстура коробки». Сюжет берёт текстуру только с protocols/print/img/cell-renew-15.webp (309×1012) и просит у заказчика фасад от 2000 px, не проверив оригинал в Figma. Ответ частичный: фото граней, верха и задника в каталоге фото нет.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5%</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[4] (свой солнцезащитный крем MITODERM для шага 3)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>«есть ли у MITODERM свой солнцезащитный крем, который можно показать?»</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>В содержании каталога (все средства) солнцезащитного средства нет: '5. תכשירים משלימים לשימוש ביתי ... EXOTECH GEL • EXOSIGNAL SPRAY ... CELL RENEW 1.5% ... CELLULAR AGE DEFENSE 2.5% ... DERMA RECOVERY'. Протоколы называют только степень защиты: 'SPF   מסנן קרינה של 30 לפחות חובה' и 'יש להשתמש מדי בוקר במסנן קרינה SPF 50'.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>source-texts.md, стр. 02 (תוכן העניינים), строки 9–34; protocols/src/content.he.mjs, строки 91 и 221</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Своего солнцезащитного средства у MITODERM в источниках нет: ни в содержании каталога, ни на mitoderm.com. Вопрос «есть ли свой SPF» снять. Шаг «הגנה» показывать без упаковки, полосой дневного света, как в сюжете CAD 2.5%. Владельцу задать один общий вопрос на обе страницы: подходит ли такой показ шага.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>В содержании каталога (стр. 02) перечислены все средства, солнцезащитного среди них нет. На mitoderm.com его тоже нет. Протоколы называют только степень защиты (строки 91 и 221, цитаты точные). Поправка: в сюжете CAD 2.5% шаг «защита» полосой света ещё ждёт подтверждения владельца («Так подходит?»), то есть «уже решено» — преувеличение.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5%</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[5] (список клиник-партнёров для кнопки «איפה לקנות»); в сюжете нет экрана 8</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>«Есть ли список клиник-партнёров... (например, блок специалистов после экрана покупки)?» В сюжете 7 экранов.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>'**Блок «Кто делает процедуру»** на каждой странице — сразу после экрана с ценой. Дизайн — со страницы специалистов в Make, данные — со списка на сайте (имя, город, телефон).' · 'В каждый сюжет добавляется экран 8 «Кто делает процедуру» с меткой פנים/קרקפת.' · '**Таблицу специалистов** заказчик пришлёт позже.'</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>PLAN.md, раздел 7, строки 80, 94, 120</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Добавить в сюжеты CELL RENEW 1.5%, CAD 2.5% и MICRO BOOST 10% экран 8 «Кто делает процедуру» сразу после экрана покупки (метка פנים, фильтр по линейке BIOSPICULE). Дизайн — со страницы специалистов, данные — из таблицы, которую заказчик пришлёт позже. Вопрос заказчику сузить до одного: «איפה לקנות» ведёт на экран 8 или на «Ask your clinic» (решение 17)?</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>PLAN.md, строки 80, 94 и 120 процитированы точно. Экран 8 «Кто делает процедуру» с меткой פנים/קרקפת полагается на каждой странице, сразу после экрана цены, таблицу заказчик пришлёт позже. Во всех трёх сюжетах по 7 экранов, экрана 8 нет. Поправка: PLAN не говорит, что «איפה לקנות» ведёт на этот блок. По решению 17 (project-council) «Where to buy» открывает «Ask your clinic», так что маршрут кнопки остаётся отдельным вопросом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>b0.title + b0.line</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>ошибка</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>«כל פרוטוקול מסתיים כאן.» / «Every protocol ends here.»; «…השלב המשלים, בבית.» / «The finishing step, at home.»</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Протоколы: крем наносят в клинике в конце процедуры, а после него обязателен SPF. V-TECH+MITOPEN: «בסיום DERMA RECOVERY CREAM» → «מקדם הגנה חובה»; CELL BOOSTER: «מריחת קרם לחות דרמה רקברי.» → «ומעליו מקדם הגנה 30 SPF לפחות». Каталог: «Derma Recovery סיום טיפול ובבית»</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/protocols/src/content.he.mjs стр. 52–53, 111–112; mitoderm-catalog/source-texts.md стр. 299</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Заголовок заменить на дословную строку каталога «הקרם המשלים לכל פרוטוקול טיפול» (product-pages.he.json cta[0]; EN по смыслу: «The complementary cream for every treatment protocol»). Строку исправить на «…השלב המשלים – בסיום הטיפול ובבית.» (опора на каталог: «סיום טיפול ובבית»). Не писать, что протокол заканчивается кремом: последний шаг — обязательный SPF. Новые строки на иврите отдать на вычитку.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Тексты сюжета проверены: b0.title «כל פרוטוקול מסתיים כאן.» / «Every protocol ends here.», b0.line «…השלב המשלים, בבית.». По протоколам это неверно. Там, где крем есть, после него обязателен SPF: стр. 52–53 «בסיום DERMA RECOVERY CREAM» → «מקדם הגנה חובה», стр. 111–112 «מריחת קרם לחות דרמה רקברי.» → «ומעליו מקדם הגנה 30 SPF לפחות», стр. 90–91. В протоколах EXO-NAD и EXOSIGNAL HAIR крема нет вовсе. PLAN фиксирует финиш «EXOCELL MASK → DERMA RECOVERY → SPF». Крем наносят и в клинике, поэтому «בבית» без клиники неполно. Каталог: «Derma Recovery סיום טיפול ובבית» (source-texts.md стр. 299), а product-pages.he.json cta[0] — «הקרם המשלים לכל פרוטוקול טיפול».</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>b4.line / b4.label1–3 (где крем стоит в протоколе)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>«לאחר CELL RENEW 1.5% או CELLULAR AGE DEFENSE 2.5%; לאחר פרוטוקולי V-TECH, EXO-NAD ו-MICRO BOOST 10%; בוקר וערב, על עור נקי.» — EXOCELL MASK перед кремом и SPF после крема не упомянуты</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10% + V-TECH, «סיום הטיפול»: «EXOCELL MASK  כמסכת סיום ושיקום» → «DERMA RECOVERY CREAM להשלמת לחות הזנה ותמיכה במחסום העורי» → «SPF   מסנן קרינה של 30 לפחות חובה»; CELL BOOSTER: «בסיום ניתן להניח מסכת EXOCELL MASK» → «מריחת קרם לחות דרמה רקברי.» → «ומעליו מקדם הגנה 30 SPF לפחות»</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/protocols/src/content.he.mjs стр. 88–91, 110–112; content.en.mjs стр. 88–90, 109–111</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>В клинической ветке экрана 5 текстом, без пакшотов других линеек, показать порядок по протоколу: EXOCELL MASK (по протоколу рекомендуется) → DERMA RECOVERY CREAM → SPF 30+ (обязательно). Минимум — добавить строку на иврите дословно из протокола: «ומעליו מקדם הגנה 30 SPF לפחות». Сейчас обязательного SPF поверх крема нет ни на одном экране.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Цитаты дословны: стр. 89–91 и 110–112. В сюжете b4.line и метки экрана 5 действительно не упоминают ни EXOCELL MASK перед кремом, ни SPF после него. SPF нет ни на одном экране. PLAN (слово заказчика 11/10) фиксирует финиш «EXOCELL MASK → DERMA RECOVERY → SPF». Поправка к предложению: EXOCELL MASK в протоколах не всегда обязательна. В V-TECH+MITOPEN — «מומלץ», в CELL BOOSTER — «ניתן», и только в MICRO BOOST 10% это просто шаг. Обязателен только SPF. По правилу о линейках другие средства показывать текстом, а не пакшотами.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>5, 7</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>b4.label4 «חובה לאחר MICRO BOOST 10%»; b6.line «לאחר MICRO BOOST 10% הקרם חובה גם בבית.»</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>источники расходятся</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>После MICRO BOOST 10% крем обязателен и дома / «Mandatory home care after MICRO BOOST 10%»</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Протокол MICRO BOOST 10%: «לבית ניתן להמליץ את הסדרה הביתית של ביוספיקול לחידוש , אקסוטק גל ללחות מיטבית וקרם רקברי להזנה ולחות אינטנסיבית.» (EN: «For home use, recommend … DERMA RECOVERY CREAM for intensive nourishment and hydration.»). В завершении процедуры словом «חובה» помечен только SPF. Каталог: «Derma Recovery סיום טיפול ובבית – חובה לאחר הטיפול»</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/protocols/src/content.he.mjs стр. 71, 88–91; mitoderm-catalog/source-texts.md стр. 299; site/product-pages.he.json стр. 882</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Одной строкой спросить заказчика: «В протоколе MICRO BOOST 10% дома крем — ‘ניתן להמליץ’, в каталогах — ‘חובה גם בבית’. Что оставляем?» До ответа ставить формулировку протокола: заказчик назвал протоколы основными. b4.label4 → «בסיום טיפול MICRO BOOST 10%» (в клинике крем — шаг завершения после EXOCELL MASK, перед обязательным SPF). В b6.line вместо «הקרם חובה גם בבית» — рекомендация для дома с опорой на «לבית ניתן להמליץ … וקרם רקברי להזנה ולחות אינטנסיבית». Если заказчик подтвердит «חובה», вернуть каталожную строку. Новые строки на иврите отдать на вычитку.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Цитаты точные. Протокол MICRO BOOST 10%, стр. 71: «לבית ניתן להמליץ … וקרם רקברי להזנה ולחות אינטנסיבית». В «סיום הטיפול» (стр. 88–91) словом «חובה» помечен только SPF. Сюжет: b4.label4 «חובה לאחר MICRO BOOST 10%», b6.line «לאחר MICRO BOOST 10% הקרם חובה גם בבית.» — дословно product-pages.he.json cta[1]. «Обязательно» есть и в source-texts.md стр. 299 («חובה לאחר הטיפול»), и в русском каталоге («также обязательное домашнее применение»). Противоречие реальное, но в одной части: «обязательно дома» против протокольного «можно рекомендовать». В клинике крем — штатный шаг завершения протокола, поэтому называть его там «מומלץ», как в исходном предложении, неточно. «חובה» трижды написал сам заказчик, значит решать ему.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>questions_ru[6] — привести b5.line («1.69 fl. oz.» / «1.69 fl. oz») к печати?</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>ответ на вопрос</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Вопрос открыт: в b5.line «50 ml ℮ 1.69 fl. oz.» (EN) и «1.69 fl. oz» (HE)</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Упаковка, нижняя строка коробки и банки: «50 ml ℮ 1.69 fl.oz.»; каталог cat.kit[0]: «50 ml ℮ 1.69 fl.oz.»</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>site/packaging-text.json → derma-recovery-cream.objects[box|jar].front «bottom: '50 ml ℮ 1.69 fl.oz.'»; site/product-pages.json derma-recovery-cream.kit[0]</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>В b5.line (HE и EN) писать ровно как на коробке и банке: «50 ml ℮ 1.69 fl.oz.». Вопрос 6 у заказчика снять.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Проверено. В packaging-text.json → derma-recovery-cream нижняя строка и коробки, и банки: «50 ml ℮ 1.69 fl.oz.». Так же в каталоге: product-pages.json kit[0] «50 ml ℮ 1.69 fl.oz. — …» и product-pages.he.json kit[0] «…– 50 ml ℮ 1.69 fl.oz.». В сюжете b5.line: HE «1.69 fl. oz», EN «1.69 fl. oz.». Это расходится с печатью и со строкой cat.kit[0] на экране 7 того же сюжета. Ответ на questions_ru[6] уже есть в источниках, спрашивать заказчика не нужно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>MITOPEN</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2 (и 3)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>b1.label3 «קרקפת» / b1.label4 «עומק לפי אינדיקציה»; action_3d_ru экрана 2: «Цифр глубины по зонам не показываем: в каталоге их нет»</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>не хватает важного</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Глубина по зонам не указана; на странице только общий диапазон 0.25–2.5 мм</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR: «עומק עבודה: עד 0.6 מ״מ, בהתאם לאזור, למצב הקרקפת ולאבחון המקצועי.» (EN: «Working depth: up to 0.6 mm, depending on the area, scalp condition and the professional assessment.»); V-TECH (лицо): «עומק העבודה נקבע בהתאם למכשיר, לאזור המטופל, לעובי העור, למצבו ולאבחון המקצועי.»</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/protocols/src/content.he.mjs стр. 137 (exosignal-hair) и стр. 42 (vtech-mitopen); content.en.mjs стр. 136, 41</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>У метки кожи головы показать «קרקפת · עד 0.6 מ״מ» (EN: «Scalp · up to 0.6 mm»), число — в изоляции LTR. Опора дословно: «עומק עבודה: עד 0.6 מ״מ». Для лица, шеи и декольте числа не давать: глубину выбирает специалист («עומק העבודה נקבע בהתאם למכשיר, לאזור המטופל, לעובי העור, למצבו ולאבחון המקצועי.»). Пометку в action_3d_ru исправить: цифра для кожи головы есть в протоколах.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Цитата дословна: content.he.mjs стр. 137 «עומק עבודה: עד 0.6 מ״מ, בהתאם לאזור, למצב הקרקפת ולאבחון המקצועי.», стр. 42 — для лица числа нет. В сюжете (экран 2, action_3d_ru) сказано «Цифр глубины по зонам не показываем: в каталоге их нет», а метки — «קרקפת» и «עומק לפי אינדיקציה». В каталоге этого числа и правда нет, но в основном протоколе MITOPEN + EXOSIGNAL HAIR оно есть. Для пера с диапазоном 0.25–2.5 мм потолок 0.6 мм на коже головы — существенный рабочий параметр, а не вопрос стиля.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>MITOPEN</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>b4.title / b4.line / b4.label2–3 (порядок шагов) + action_3d_ru (сначала сетка микроканалов, потом капля стекает в сетку); то же в story_one_line</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>источники расходятся</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>«הגדרה. מיקרונידלינג. החדרה.» / «בחרו עומק ומהירות בהתאם לאזור, צרו מיקרו־תעלות אחידות ולאחר מכן יישמו את V-TECH SYSTEM בפנים או את EXOSIGNAL HAIR בקרקפת.» (EN: «create uniform micro-channels, then apply V-TECH SYSTEM on the face or EXOSIGNAL HAIR on the scalp»); метки «2 · מיקרונידלינג אחיד», «3 · החדרת הפורמולה»</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Протоколы: EXOSIGNAL HAIR — «בסימולטניות עוברים ביחד עם החומר והמכשיר . לחלק את העבודה לאזורים : קודם לטפטף מעט מהחומר על אזור מסוים ואז לעשות סטמפינג» (EN: «Product and device work at the same time. Divide the work into sections: first drip a little product onto a section, then stamp.»); V-TECH — «יש ליישם את הסרום באמצעות MITOPEN / מזופן או מכשור מקצועי מתאים אחר.»; CELL BOOSTER — «לטפטף מס טיפות ביחד עם המקרונידלינג    בכל אזור בפנים -בשיטת הסטמפינג». Против: каталог product-pages.json mitopen.steps «Needle — Create uniform micro-channels…» → «Deliver — Apply V-TECH SYSTEM on the face or EXOSIGNAL HAIR on the scalp.» и mitoderm.com «After a controlled injury, the material is dripped onto the skin»</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/protocols/src/content.he.mjs стр. 138 (exosignal-hair), 41 (vtech-mitopen), 109 (cell-booster); content.en.mjs стр. 137; site/product-pages.json стр. 972–976; site/sources/mitoderm-com/products-en.json solution.main.discountLabelText2</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Побеждают протоколы. Средство не наносят на готовую сетку: его капают на участок и сразу проходят MITOPEN по нему, участок за участком. Метки: «1 · הגדרת עומק ומהירות» → «2 · טפטוף החומר על האזור» → «3 · סטמפינג עם MITOPEN, אזור אחר אזור». Заголовок, например: «הגדרה. טפטוף. סטמפינג.». b4.line, например: «בחרו עומק ומהירות בהתאם לאזור, טפטפו מעט מהחומר על אזור אחד ובצעו סטמפינג עם MITOPEN – אזור אחר אזור: V-TECH SYSTEM בפנים, EXOSIGNAL HAIR בקרקפת.». Опора на иврите дословно: «קודם לטפטף מעט מהחומר על אזור מסוים ואז לעשות סטמפינג» (EXOSIGNAL HAIR), а для лица — «יש ליישם את הסרום באמצעות MITOPEN» (V-TECH). Для лица при желании добавить: после сыворотки V-TECH Gel Mask наносят на ту же зону и массируют до впитывания, без смывания («לאחר סיום העבודה עם הסרום, יש למרוח V-TECH Gel Mask על אותו אזור.»). В 3D сначала капля падает на участок, потом перо проходит через неё; сетку раньше капли не показывать. Тот же порядок поправить в story_one_line. Новые строки на иврите отдать на вычитку.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Цитаты проверены дословно: content.he.mjs стр. 138 («בסימולטניות עוברים ביחד עם החומר והמכשיר… קודם לטפטף מעט מהחומר על אזור מסוים ואז לעשות סטמפינג»), стр. 41 (V-TECH: «יש ליישם את הסרום באמצעות MITOPEN»), стр. 109 (CELL BOOSTER: «לטפטף מס טיפות ביחד עם המקרונידלינג… בשיטת הסטמפינג»). В сюжете действительно «צרו מיקרו־תעלות אחידות ולאחר מכן יישמו…», метки «2 · מיקרונידלינג אחיד» → «3 · החדרת הפורמולה», а в 3D капля стекает в уже готовую сетку. Порядок взят из каталога (steps) и mitoderm.com («After a controlled injury, the material is dripped»), но порядок шагов определяют протоколы. Там средство и перо работают одновременно, участок за участком. Конфликт настоящий. Одна оговорка: в протоколе V-TECH слова «капать» нет. Там сыворотку набирают в шприц 3 мл и наносят через MITOPEN. Прямо «капать, потом стемпинг» сказано в протоколах EXOSIGNAL HAIR и CELL BOOSTER (лицо).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>MITOPEN</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>b4.label4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>источники расходятся</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>«משתלב עם V-TECH · EXOSIGNAL HAIR · MICRO BOOST 10%» / «Works with V-TECH · EXOSIGNAL HAIR · MICRO BOOST 10%»</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Протоколы: связки «MITOPEN + VTECH», «MITOPEN +MITOTECH CELL BOOSTER», «MITOPEN + EXOSIGNAL HAIR»; MICRO BOOST 10% стоит вместо пера: «BIOSPICULE BOOST 10% + VTECH», «BIOSPICULE BOOST 10% + MITOTECH CELL BOOSTER», заголовок «MITOPEN/BIOSPICULE CELL BOOSTETR 10%», EN: «Alternatively, with the biospicule gel: apply 1.5-2 ml to the face…». Каталог: «יכול לשמש כטיפול ביומיקרונידלינג כתחליף לטיפול המסורתי במיקרונידלינג!». Против: каталожные чипы MITOPEN («Works with … MICRO BOOST 10%»)</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm-catalog/protocols/src/content.he.mjs стр. 22–26, 103; content.en.mjs стр. 108; mitoderm-catalog/source-texts.md стр. 245; site/product-pages.json стр. 1007 (mitopen.chips)</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Убрать MICRO BOOST 10% из «משתלב עם»: MITOPEN и MICRO BOOST 10% — два разных пути (микронидлинг пером или биомикронидлинг спикулами), вместе их не применяют. Метка: «משתלב עם V-TECH · EXOSIGNAL HAIR» (как в каталоге: «להחדרת חומרים: VTECH SYSTEM, EXOSIGNAL HAIR»). MITOTECH CELL BOOSTER (в протоколах есть связка «MITOPEN +MITOTECH CELL BOOSTER») добавлять только текстом, без ссылки, и только после слова заказчика: в PLAN MITOTECH отложен. Заодно убрать упоминание MICRO BOOST 10% / BIOSPICULE из colour_env и action_3d_ru экрана 5.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Проверено. В протоколах связки только «MITOPEN + VTECH», «MITOPEN +MITOTECH CELL BOOSTER», «MITOPEN + EXOSIGNAL HAIR». MICRO BOOST 10% стоит вместо пера: заголовок «MITOPEN/BIOSPICULE…», а в стр. 109 «…או באמצעות גל הביוספיקולות» — то есть «или». В протоколе MICRO BOOST 10% (стр. 74–85) MITOPEN нет. В каталоге (source-texts.md стр. 245): «יכול לשמש כטיפול ביומיקרונידלינג כתחליף לטיפול המסורתי במיקרונידלינג!». В печатном каталоге на странице MITOPEN (source-texts.md стр. 453–466) тоже указаны только «VTECH SYSTEM, EXOSIGNAL HAIR». MICRO BOOST 10% есть лишь в чипах product-pages(.he).json. Метка сюжета «משתלב עם … MICRO BOOST 10%» противоречит протоколам. Поправка к предложению: MITOTECH по PLAN отложен до пакшота и текстов («MITOTECH (ждёт пакшот и тексты)»), поэтому без слова заказчика его не добавлять.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/mitoderm-catalog/site/MITODERM-3D-story.xlsx
+++ b/mitoderm-catalog/site/MITODERM-3D-story.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -476,7 +476,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>סטטוס נכון ל-14/10</t>
+          <t>סטטוס נכון ל-17/10</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>התרגום לקראת סיום, חוברת העבודה בשלבי הרכבה</t>
+          <t>מוכן, עודכן ב-17/10</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>עמוד 3D לדוגמה של EXOCELL MASK: בטלפון הקופסה קטנה, ליד הכותרת; 5 שקיות עם הדפס קריא; המוצר בצבעיו האמיתיים, הטורקיז רק מסביב; פחות גלילה ריקה; כרטיסי «ראו גם»</t>
+          <t>עמוד 3D לדוגמה של EXOCELL MASK: מסכה אחת בשתי שכבות, ובמסך הערכה השכבות נפרדות, כל אחת עם שם; Rubik בכל העמוד; הטקסט מימין וה-3D משמאל; בלוק «מה באריזה» אחד</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>נבנה מחדש לפי ההערות מ-14/10, ממתין ל«אוקיי»</t>
+          <t>נבנה מחדש ב-17/10, ממתין ל«אוקיי»</t>
         </is>
       </c>
     </row>
@@ -542,22 +542,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>רנדר HD: מעקב מסלולי קרניים (path tracing) ב-Blender Cycles במקום רינדור בדפדפן – זכוכית ונוזל עם שבירת אור, רדיד, קצוות משופעים, תאורת סטודיו; הדוגמה – האובייקט המרכזי של V-TECH והערכה, ואחרי «אוקיי» – סדרת הרנדרים</t>
+          <t>V-TECH ב-HD ‏(Blender Cycles): הקופסה נפתחת כמו בצילומים – העטיפה המוזהבת עולה, הקופסה השחורה נפתחת, 5 אמפולות ו-5 שקיות; רדיד סאטן בלי צללים כבדים; תאי אקסוזום, מולקולות PDRN וסליל DNA; תנועה גם בטלפון</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>דוגמה 2 שעות, עמוד 1–2 שעות</t>
+          <t>הדוגמה מוכנה; רינדור סופי על ה-Mac כ-3–4 שעות</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>צילומים של כל אריזה מכל הצדדים, מ-3000 px ומעלה, מידות במ״מ, צילום של אריזה פתוחה</t>
+          <t>תיקונים לדוגמה, «אוקיי», הרצת הרינדור על ה-Mac</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Blender מותקן, הטקסטורות מוכנות, הדוגמה הבאה בתור</t>
+          <t>הדוגמה פורסמה ב-17/10, ממתינה לתיקונים</t>
         </is>
       </c>
     </row>
@@ -569,22 +569,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>השלמת V-TECH: מסך הפרוטוקול – בקצרה «איך זה עובד», בלי מינונים; הפרוטוקול המלא – אחרי הרכישה; בלוק «מאותה סדרה / משתלב עם»; פריימים ב-HD</t>
+          <t>Figma למתכנת: כל העמודים לפי ההחלטות האחרונות (טקסט מימין, 3D משמאל, Rubik, בלוק «מה באריזה» אחד), עם מפרט: מנוע הפריימים, הנכסים, נקודות השבירה והתנועה בטלפון</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2 שעות</t>
+          <t>יום אחד</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>«אוקיי» על V-TECH ועל MASK</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>העמוד ב-Figma הורכב, 2 סבבי בדיקה</t>
+          <t>בעבודה</t>
         </is>
       </c>
     </row>
@@ -596,22 +596,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>שאר עמודי המוצרים, אחד אחרי השני: MICRO BOOST 10% → DERMA RECOVERY CREAM → MITOPEN → EXO-NAD → EXOSIGNAL HAIR → EXOTECH GEL → EXOSIGNAL SPRAY → CELL RENEW 1.5% → CELLULAR AGE DEFENSE 2.5% → MITOSCAN</t>
+          <t>פיילוט של השיטה המהירה על EXOTECH GEL: פריימים מרכזיים מ-Firefly (של המזמין/ה) ומעברים ב-Kling, שהופכים לפריימים לאתר באותו מנוע; השוואה ל-Blender באיכות, בזמן ובמחיר</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2–3 שעות לכל עמוד</t>
+          <t>יום אחד</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>צילומי HD של האריזות, פקשוט של הספריי, צילומים של סריקות MITOSCAN</t>
+          <t>שני פריימים מ-Firefly ‏(2400×1500, המוצר משמאל); אישור להוצאה לפני כל יצירה</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>אחרי שלב 1</t>
+          <t>הבא בתור</t>
         </is>
       </c>
     </row>
@@ -623,22 +623,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>דף הבית – דף בית אמיתי: מסך פתיחה כמו ב-Make → כל המוצרים ב-3D מתכנסים ומתפזרים לפי סדרות → בחירת תחום למעלה → כל סדרה פעם אחת; לחיצה על סדרה פותחת את חלון הסדרה; «אודות» למטה; עמוד כל המוצרים</t>
+          <t>שאר עמודי המוצרים בשיטה הטובה מבין השתיים – קודם גרסה קלה לטלפון, אחר כך 3D: MICRO BOOST 10% → DERMA RECOVERY CREAM → MITOPEN → EXO-NAD → EXOSIGNAL HAIR → EXOSIGNAL SPRAY → CELL RENEW 1.5% → CELLULAR AGE DEFENSE 2.5% → MITOSCAN</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1 יום</t>
+          <t>יום עבודה לכל עמוד</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>דוגמה למסך הפתיחה מ-Make</t>
+          <t>צילומי HD של האריזות (גם פתוחות), מידות במ״מ, צילומי לפני/אחרי באישור הלקוחות</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>אחרי שלב 3</t>
+          <t>אחרי הפיילוט</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>חשבון ותוכנית נאמנות: בחירת תחום → הדגשים אישיים; הרשמה (שם, email, טלפון, תפקיד); אימות סטטוס מקצועי עבור המוצרים המקצועיים; קוד קופון, 5% על הבאת חבר/ה, מדרגות עד 15%; הפרוטוקולים של המוצרים שנרכשו – בחשבון ובדוא״ל</t>
+          <t>דף הבית – דף בית אמיתי: מסך פתיחה כמו ב-Make → כל המוצרים ב-3D מתכנסים ומתפזרים לפי סדרות → בחירת תחום למעלה → כל סדרה פעם אחת; לחיצה על סדרה פותחת את חלון הסדרה; «אודות» למטה; עמוד כל המוצרים</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>כללי התוכנית (מדרגות, מועדים), מי מאמת/ת את הסטטוס</t>
+          <t>דוגמה למסך הפתיחה מ-Make</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>אירועי האקדמיה בדף הבית וטופס להזמנת מקומות</t>
+          <t>חשבון ותוכנית נאמנות: בחירת תחום → הדגשים אישיים; הרשמה (שם, email, טלפון, תפקיד); אימות סטטוס מקצועי עבור המוצרים המקצועיים; קוד קופון, 5% על הבאת חבר/ה, מדרגות עד 15%; הפרוטוקולים של המוצרים שנרכשו – בחשבון ובדוא״ל</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3 שעות</t>
+          <t>1 יום</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>תאריכים, מחירים</t>
+          <t>כללי התוכנית (מדרגות, מועדים), מי מאמת/ת את הסטטוס</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>עמודי שירות: נגישות, פרטיות, תנאי שימוש, פאנל ניהול</t>
+          <t>אירועי האקדמיה בדף הבית וטופס להזמנת מקומות</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2 שעות</t>
+          <t>3 שעות</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>טקסטים משפטיים</t>
+          <t>תאריכים, מחירים</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>בסוף</t>
+          <t>אחרי שלב 6</t>
         </is>
       </c>
     </row>
@@ -731,20 +731,47 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>עמודי שירות: נגישות, פרטיות, תנאי שימוש, פאנל ניהול</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2 שעות</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>טקסטים משפטיים</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>בסוף</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>התוצר הסופי – קישור אחד: מפת האתר עם כל העמודים ומסלולי המשתמש</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>2 שעות</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>בסוף, טיוטה – מוקדם יותר</t>
         </is>

--- a/mitoderm-catalog/site/MITODERM-3D-story.xlsx
+++ b/mitoderm-catalog/site/MITODERM-3D-story.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>סטטוס נכון ל-17/10</t>
+          <t>סטטוס נכון ל-18/10</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>הדוגמה פורסמה ב-17/10, ממתינה לתיקונים</t>
+          <t>הדוגמה פורסמה ב-17/10; ב-18/10 נוספו מולקולות PDRN וסליל DNA; ממתינה לתיקונים</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>בעבודה</t>
+          <t>18/10: ב-Figma יש עמוד התחלה למתכנת, ועמודי V-TECH ו-MASK עודכנו; שאר העמודים — לפי התבנית</t>
         </is>
       </c>
     </row>

--- a/mitoderm-catalog/site/MITODERM-3D-story.xlsx
+++ b/mitoderm-catalog/site/MITODERM-3D-story.xlsx
@@ -7987,7 +7987,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>המצלמה יורדת לגובה התפר. המכסה – חצי הכדור העליון עם הכיתוב השלם 'EXOTECH / GEL' – מתרומם ישר למעלה בכמה מילימטרים: בלי סיבוב ביחס לבסיס, בלי הטיה לאחור. הסדק הצר לאורך קו המשווה מתמלא בזוהר זהוב חם, ולכן לא נראים לא פנים הצנצנת ולא הצד התחתון של המכסה (שאלה 1). הבסיס הזהוב החלק נשאר במקומו.</t>
+          <t>המצלמה יורדת לגובה התפר. המכסה – חצי הכדור העליון עם הכיתוב השלם 'EXOTECH / GEL' – נפתח בהברגה (תשובת המזמין/ה, 18/10: הכדור מתחלק לשני חצאים): מסתובב סביב הציר האנכי כרבע סיבוב ומתרומם בכמה מילימטרים, בלי הטיה לאחור. הסדק הצר לאורך קו המשווה מתמלא בזוהר זהוב חם, ולכן לא נראים לא פנים הצנצנת ולא הצד התחתון של המכסה (מראה הג׳ל – שאלה 2). הבסיס הזהוב החלק נשאר במקומו.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>המכסה עם הכיתוב השלם 'EXOTECH / GEL' מרחף מעל הבסיס, והסדק הצר זוהר בזהב חם. מהסדק עולות בזו אחר זו חמש טיפות ג׳ל שקופות – חמשת הרכיבים הפעילים מ-b2.line. ארבע טיפות נקיות, בלי מתכת, והן נבדלות בגודל, בצורה ובשבירת האור. ניצוצות זהב ונחושת מנצנצים רק בטיפת הפפטידים (b2.label3), כמו בהרכב. הטיפות חגות לאט סביב הכדור בגבהים שונים. ארבע טיפות מקושרות לארבעת הצ׳יפים של b2: ריחוף או הקשה על צ׳יפ מדגישים את הטיפה שלו בהילה בהירה (מיקרו-אינטראקציה מהסטוריבורד האנגלי של בלוק 2). הטיפה החמישית, cat.ingredients[4] (פוליסכרידים ממקור חלזון), מודגשת בריחוף מעל המשפט.</t>
+          <t>החצי העליון של הכדור, אחרי שנפתח בהברגה, מרחף עם הכיתוב השלם 'EXOTECH / GEL' מעל החצי התחתון, והסדק הצר זוהר בזהב חם. מהסדק עולות בזו אחר זו חמש טיפות ג׳ל שקופות – חמשת הרכיבים הפעילים מ-b2.line. ארבע טיפות נקיות, בלי מתכת, והן נבדלות בגודל, בצורה ובשבירת האור. ניצוצות זהב ונחושת מנצנצים רק בטיפת הפפטידים (b2.label3), כמו בהרכב. הטיפות חגות לאט סביב הכדור בגבהים שונים. ארבע טיפות מקושרות לארבעת הצ׳יפים של b2: ריחוף או הקשה על צ׳יפ מדגישים את הטיפה שלו בהילה בהירה (מיקרו-אינטראקציה מהסטוריבורד האנגלי של בלוק 2). הטיפה החמישית, cat.ingredients[4] (פוליסכרידים ממקור חלזון), מודגשת בריחוף מעל המשפט.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>הרצועה אינה חוזרת לצנצנת. היא עפה אל המצלמה ומתמוססת על פני כל הפריים באדוות אור זהובות וחמות: הג׳ל נספג בעור הצופה (הדימוי «לעסות עד לספיגה» מתוך b4.line). במקביל המכסה יורד ישר למטה אל הבסיס, בלי סיבוב, וזוהר הסדק כבה – הצנצנת סגורה.</t>
+          <t>הרצועה אינה חוזרת לצנצנת. היא עפה אל המצלמה ומתמוססת על פני כל הפריים באדוות אור זהובות וחמות: הג׳ל נספג בעור הצופה (הדימוי «לעסות עד לספיגה» מתוך b4.line). במקביל החצי העליון יורד אל החצי התחתון ונסגר בהברגה (רבע סיבוב), וזוהר הסדק כבה – הצנצנת סגורה.</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -24566,7 +24566,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>איך נפתח הכדור? המכסה – חצי הכדור העליון עם הכיתוב כולו 'EXOTECH / GEL', התפר – קו המשווה מתחת ל-'GEL'. הוא נפתח בהברגה או פשוט מורם? נדרשים צילומים של הצנצנת הפתוחה מלמעלה ובזווית שלושה רבעים, וצילום של המכסה מלמטה. בינתיים המכסה מתרומם ישר למעלה בכמה מילימטרים, הסדק מכוסה בזוהר, והפנים אינם נראים.</t>
+          <t>איך נפתח הכדור? המכסה – חצי הכדור העליון עם הכיתוב כולו 'EXOTECH / GEL', התפר – קו המשווה מתחת ל-'GEL'. הוא נפתח בהברגה או פשוט מורם? נדרשים צילומים של הצנצנת הפתוחה מלמעלה ובזווית שלושה רבעים, וצילום של המכסה מלמטה. בינתיים המכסה מתרומם ישר למעלה בכמה מילימטרים, הסדק מכוסה בזוהר, והפנים אינם נראים. תשובת המזמין/ה (18/10): נפתח בהברגה – הכדור הזהוב מתחלק לשני חצאים.</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr"/>

--- a/mitoderm-catalog/site/MITODERM-3D-story.xlsx
+++ b/mitoderm-catalog/site/MITODERM-3D-story.xlsx
@@ -7987,7 +7987,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>המצלמה יורדת לגובה התפר. המכסה – חצי הכדור העליון עם הכיתוב השלם 'EXOTECH / GEL' – נפתח בהברגה (תשובת המזמין/ה, 18/10: הכדור מתחלק לשני חצאים): מסתובב סביב הציר האנכי כרבע סיבוב ומתרומם בכמה מילימטרים, בלי הטיה לאחור. הסדק הצר לאורך קו המשווה מתמלא בזוהר זהוב חם, ולכן לא נראים לא פנים הצנצנת ולא הצד התחתון של המכסה (מראה הג׳ל – שאלה 2). הבסיס הזהוב החלק נשאר במקומו.</t>
+          <t>המצלמה יורדת לגובה התפר. המכסה – חצי הכדור העליון עם הכיתוב השלם 'EXOTECH / GEL' – נפתח בהברגה (תשובת המזמין/ה, 18/10: הכדור מתחלק לשני חצאים): מסתובב סביב הציר האנכי כרבע סיבוב ומתרומם בכמה מילימטרים, בלי הטיה לאחור. הסדק הצר לאורך קו המשווה מתמלא בזוהר זהוב חם, ולכן לא נראים לא פנים הצנצנת ולא הצד התחתון של המכסה. הבסיס הזהוב החלק נשאר במקומו.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>החצי העליון של הכדור, אחרי שנפתח בהברגה, מרחף עם הכיתוב השלם 'EXOTECH / GEL' מעל החצי התחתון, והסדק הצר זוהר בזהב חם. מהסדק עולות בזו אחר זו חמש טיפות ג׳ל שקופות – חמשת הרכיבים הפעילים מ-b2.line. ארבע טיפות נקיות, בלי מתכת, והן נבדלות בגודל, בצורה ובשבירת האור. ניצוצות זהב ונחושת מנצנצים רק בטיפת הפפטידים (b2.label3), כמו בהרכב. הטיפות חגות לאט סביב הכדור בגבהים שונים. ארבע טיפות מקושרות לארבעת הצ׳יפים של b2: ריחוף או הקשה על צ׳יפ מדגישים את הטיפה שלו בהילה בהירה (מיקרו-אינטראקציה מהסטוריבורד האנגלי של בלוק 2). הטיפה החמישית, cat.ingredients[4] (פוליסכרידים ממקור חלזון), מודגשת בריחוף מעל המשפט.</t>
+          <t>החצי העליון של הכדור, אחרי שנפתח בהברגה, מרחף עם הכיתוב השלם 'EXOTECH / GEL' מעל החצי התחתון, והסדק הצר זוהר בזהב חם. מהסדק עולות בזו אחר זו חמש טיפות של ג׳ל לבן כמו קרם (תשובת המזמין/ה, 18/10) – חמשת הרכיבים הפעילים מ-b2.line. ארבע טיפות בלי מתכת, והן נבדלות בגודל, בצורה ובברק. ניצוצות זהב ונחושת מנצנצים רק בטיפת הפפטידים (b2.label3), כמו בהרכב. הטיפות חגות לאט סביב הכדור בגבהים שונים. ארבע טיפות מקושרות לארבעת הצ׳יפים של b2: ריחוף או הקשה על צ׳יפ מדגישים את הטיפה שלו בהילה בהירה (מיקרו-אינטראקציה מהסטוריבורד האנגלי של בלוק 2). הטיפה החמישית, cat.ingredients[4] (פוליסכרידים ממקור חלזון), מודגשת בריחוף מעל המשפט.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>הטיפה הגדולה אינה נופלת, אלא נמתחת למעלה לרצועה שקופה ודקה – שכבת ג׳ל דקה. הרצועה מתנופפת כמו משי, לוכדת ברקים חמים, ודרכה נראה הכדור: השקיפות והעלייה למעלה מבטאות את «אף פעם לא מכביד» (b3.title). הסמן «נושף» קלות על הרצועה, וממנו יוצא גל. בזמן שהרצועה נפרשת, מופיעות בזו אחר זו ארבע התוויות של b3. זו «סצנת המראה» של בלוק 3: אין אנשים בפריים, העור הוא הצופה עצמו (ראו המעבר). פריים עם אדם – רק אחרי התשובה לשאלה 5.</t>
+          <t>הטיפה הגדולה אינה נופלת, אלא נמתחת למעלה לרצועה דקה ולבנה כמו קרם – שכבת ג׳ל דקה. הרצועה מתנופפת כמו משי, לוכדת ברקים חמים, ובשוליים היא דקה יותר וזוהרת: הדקות והעלייה למעלה מבטאות את «אף פעם לא מכביד» (b3.title). הסמן «נושף» קלות על הרצועה, וממנו יוצא גל. בזמן שהרצועה נפרשת, מופיעות בזו אחר זו ארבע התוויות של b3. זו «סצנת המראה» של בלוק 3: אין אנשים בפריים, העור הוא הצופה עצמו (ראו המעבר). פריים עם אדם – רק אחרי התשובה לשאלה 5.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>הכדור הסגור עומד במרכז החצי הימני. הגלילה מעבירה אותו דרך שלושה שלבים, בסנכרון עם התוויות של b4. «1 · ניקוי»: על פני הזהב עובר משמאל לימין ברק בהיר ונקי. «2 · מריחת שכבה דקה»: סביב הכדור מופיעה לרגע טבעת-שכבה שקופה ודקה, ונספגת. «3 · בוקר וערב»: הסופטבוקס הראשי של מפת הסטודיו מקיף את הכדור בקשת – בבוקר אור בגוון קרם-זהב מלמעלה מימין, בערב אור ענבר נמוך משמאל; גבול האור והצל מחליק על פני הכדור. תווית 4 «משתלב עם V-TECH · EXO-NAD · BIOSPICULE™» – טקסט בלבד: אריזות של מוצרים אחרים לא מציגים, והירוק של BIOSPICULE אינו מופיע בדף. הכפתור b4.cta – ghost, והוא גולל אל פרטי הקשר במסך 7 (b6.label4).</t>
+          <t>הכדור הסגור עומד במרכז החצי הימני. הגלילה מעבירה אותו דרך שלושה שלבים, בסנכרון עם התוויות של b4. «1 · ניקוי»: על פני הזהב עובר משמאל לימין ברק בהיר ונקי. «2 · מריחת שכבה דקה»: סביב הכדור מופיעה לרגע טבעת-שכבה דקה ולבנה כמו קרם, ונספגת. «3 · בוקר וערב»: הסופטבוקס הראשי של מפת הסטודיו מקיף את הכדור בקשת – בבוקר אור בגוון קרם-זהב מלמעלה מימין, בערב אור ענבר נמוך משמאל; גבול האור והצל מחליק על פני הכדור. תווית 4 «משתלב עם V-TECH · EXO-NAD · BIOSPICULE™» – טקסט בלבד: אריזות של מוצרים אחרים לא מציגים, והירוק של BIOSPICULE אינו מופיע בדף. הכפתור b4.cta – ghost, והוא גולל אל פרטי הקשר במסך 7 (b6.label4).</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>ללא פקשוט: פרופיל טיפה פרוצדורלי, חומר שקוף שובר אור (transmission). ארבע טיפות ללא מתכת, נבדלות בגודל, בצורה ובשבירת האור. ניצוצות זהב ונחושת – רק בטיפת הפפטידים. הצבע והשקיפות של הג׳ל – לפי צילום (שאלה 2).</t>
+          <t>ללא פקשוט: פרופיל טיפה פרוצדורלי, חומר לבן כמו קרם, אטום, עם פיזור רך מתחת לפני השטח וברקים מבריקים (תשובת המזמין/ה, 18/10: הג׳ל לבן כמו קרם). ארבע טיפות ללא מתכת, נבדלות בגודל, בצורה ובברק. ניצוצות זהב ונחושת – רק בטיפת הפפטידים.</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>ללא פקשוט: משטח גלי דק מאותו חומר של הג׳ל. במעבר 4→5 הוא עף אל המצלמה ומתמוסס באדוות אור. הצבע – לפי צילום הג׳ל (שאלה 2).</t>
+          <t>ללא פקשוט: משטח גלי דק מאותו חומר של הג׳ל. במעבר 4→5 הוא עף אל המצלמה ומתמוסס באדוות אור. הצבע – לבן כמו קרם (תשובת המזמין/ה, 18/10).</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -24579,7 +24579,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>באיזה צבע הג׳ל ועד כמה הוא שקוף? נדרש צילום של הג׳ל בצנצנת פתוחה או על האצבע. בינתיים הטיפות והשכבה הדקה שקופות בגוון ניטרלי, עם ברקים חמים.</t>
+          <t>באיזה צבע הג׳ל ועד כמה הוא שקוף? נדרש צילום של הג׳ל בצנצנת פתוחה או על האצבע. בינתיים הטיפות והשכבה הדקה שקופות בגוון ניטרלי, עם ברקים חמים. תשובת המזמין/ה (18/10): לבן כמו קרם.</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr"/>

--- a/mitoderm-catalog/site/MITODERM-3D-story.xlsx
+++ b/mitoderm-catalog/site/MITODERM-3D-story.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מפת דרכים" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סקירה כללית" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מסכים" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מה בפנים" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="נכסי 3D" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מחרוזות חדשות" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="טופס" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mitoderm.com" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="שאלות" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="הצלבה מול המקורות" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="מפת דרכים" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="סקירה כללית" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="מסכים" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="מה בפנים" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="נכסי 3D" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="מחרוזות חדשות" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="טופס" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="mitoderm.com" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="שאלות" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="הצלבה מול המקורות" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +476,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>סטטוס נכון ל-18/10</t>
+          <t>סטטוס נכון ל-18/10, ערב</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18/10: ב-Figma יש עמוד התחלה למתכנת, ועמודי V-TECH ו-MASK עודכנו; שאר העמודים — לפי התבנית</t>
+          <t>18/10: ב-Figma יש עמוד התחלה למתכנת, ועמודי V-TECH ו-MASK עודכנו; שאר העמודים — לפי התבנית; המתכנת בונה ב-React</t>
         </is>
       </c>
     </row>
@@ -606,12 +606,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>שני פריימים מ-Firefly ‏(2400×1500, המוצר משמאל); אישור להוצאה לפני כל יצירה</t>
+          <t>שישה פריימים מ-Firefly ‏(2400×1500, המוצר בחצי השמאלי ולפחות 10% מהשוליים, רקע שחור נקי, קו אור דק לאורך הקצוות של הפאות השחורות של הקופסה); אישור להוצאה לפני כל יצירה</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>הבא בתור</t>
+          <t>18/10: הכלי שהופך סרטוני Kling לפריימים לאתר מוכן ונבדק; טיוטת עמוד EXOTECH GEL על התבנית (תמונות זמניות מתמונת המוצר) ממתינה לבדיקה; ממתינים לשישה פריימים מ-Firefly</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>אחרי הפיילוט</t>
+          <t>אחרי הפיילוט; בונה העמודים כבר מתאים לכל מוצר, והדוגמה היא טיוטת EXOTECH GEL</t>
         </is>
       </c>
     </row>

--- a/mitoderm-catalog/site/MITODERM-3D-story.xlsx
+++ b/mitoderm-catalog/site/MITODERM-3D-story.xlsx
@@ -11,12 +11,13 @@
     <sheet name="סקירה כללית" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="מסכים" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="מה בפנים" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="נכסי 3D" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="מחרוזות חדשות" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="טופס" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="mitoderm.com" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="שאלות" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="הצלבה מול המקורות" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="דפי מדע ואודות" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="נכסי 3D" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="מחרוזות חדשות" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="טופס" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="mitoderm.com" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="שאלות" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="הצלבה מול המקורות" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -788,6 +789,1425 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C100"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>עמוד</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>שאלה למזמין/ה</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>תשובה / החלטה (מקור)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>איך נפתחת הקופסה של V-TECH SYSTEM? בצילום מס׳ 44 יש בפנים מגש פנימי שחור (השקיות מונחות שטוחות, 5 בקבוקונים בשקעים), ובפקשוט נראים פסים שחורים מעל הזהב ומתחתיו. חלק הזהב הוא שרוול שנשלף, או מכסה? נדרשים המקור של צילום 44 וצילום של פתיחת הקופסה, וכן החלק העליון, התחתית והצד האחורי של הקופסה. כל עוד אין תשובה, חלק הזהב פשוט מתרומם ונסוג לאחור.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>בקבוקון או אמפולה? בפקשוט – בקבוקונים, בתרשים הערכה (צילומים 78 ו-83) – VIALS ו-POUCHES, ובקטלוג ובטקסטים של האתר – אמפולות. ב-3D מציגים כמו בצילום. את המילה בטקסט משאירים או משנים?</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>בטקסט — «אמפולות», כמו ב-mitoderm.com («5 אמפולות V-Tech Serum בנפח 5 מ׳׳ל כל אחת»); ב-3D — בקבוקון, כמו בתמונה. המזמין/ה 11/10: «5 מסכות ו-5 אמפולות».</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>מכסה הבקבוקון: בפקשוט – flip-off לבן, בצילומים 45, 46, 48 ו-79 – כסוף. איזה להציג? ואיך לוקחים את הסרום מהבקבוקון: במזרק, בטפטפת, מסירים את הפקק? כל עוד אין תשובה, המכסה סגור, והטיפה מופיעה באוויר מעל הבקבוקון.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>כסוף, כמו בתמונה 79. את הסרום שואבים למזרק 3 מ״ל במחט שאיבה (פרוטוקולי המזמין/ה, V-TECH + MITOPEN, שלב 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>מה הצבע והמראה של הסרום ושל הג׳ל – שקופים, זהובים? בינתיים הטיפה והג׳ל שקופים, ללא חלקיקים.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>חומצה היאלורונית ואלוורה (הפריט האחרון ברשימת הרכיבים) – בסרום או במסכת הג׳ל? בינתיים, ברשימת הרכיבים הפתוחה זו שורה נפרדת אחרי שתי הקבוצות.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>במסכת הג׳ל: mitoderm.com, הרכב V-Tech Gel Mask 5ml — «חומצה היאלורונית במשקל מולקולרי נמוך, אלוורה».</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>כמה בקבוקונים ושקיות נדרשים לטיפול אחד, והאם קופסה אחת מספיקה לסדרת טיפולים? בערכה 5 + 5, סדרת הטיפולים – לפחות ארבעה טיפולים, סרום לטיפול – 1–1.5 מ״ל מבקבוקון של 5 מ״ל. בינתיים את הערכה ואת סדרת הטיפולים מציגים כעובדות נפרדות.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>פרוטוקולי המזמין/ה: לכל אזור (פנים, צוואר או דקולטה) עד 2 מ״ל סרום ועד 2 מ״ל מסכת ג׳ל; פעם ב-14 יום, סדרה של 4–6 טיפולים, ולאחר מכן תחזוקה פעם ב-2–3 חודשים. כמה טיפולים יש באריזה אחת — לא מופיע בפרוטוקולים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>שלב 1 בפרוטוקול: להשאיר את השדה המופשט של המיקרו-תעלות (אחת מארבע השיטות שבקטלוג – מיקרונידלינג, מיקרונידלינג RF, BIOSPICULE™ 10%, לייזר CO₂) או להציג שם את MITOPEN כמכירה צולבת?</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>הפרוטוקול של המזמין/ה נקרא «V-TECH + MITOPEN»: את הסרום מחדירים באמצעות MITOPEN, מזופן או ציוד מתאים אחר. את MITOPEN מציגים כמכירה צולבת.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>הסיום: בקטלוג – «EXOCELL MASK או DERMA RECOVERY ומקדם הגנה», ובתווית הפרוטוקול באתר רק EXOCELL MASK + SPF. בדף מציגים שני צ׳יפים-קישורים. לבקש מעורך/ת העברית להוסיף את DERMA RECOVERY לתווית הזו?</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>פרוטוקול המזמין/ה: מומלצת EXOCELL MASK, בסיום DERMA RECOVERY CREAM, הגנה מהשמש היא חובה. מציגים את שני הצ׳יפים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>צילומים 79 (הבקבוקון בתקריב), 80 (דופן הקופסה) ו-82 (השקית) מופיעים ב-Figma כתמונות ממוזערות בקולאז׳. אפשר לקבל את המקורות שלהם בגודל מלא, כדי לפענח את הכיתובים? הצד האחורי של השקית לא מופיע בצילומים – האם יש צילום כזה? שורות קטנות בלתי קריאות משרטטים כקווים אפורים דקים.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>EXO-NAD</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>הפקשוט exo-nad.webp הוא, כנראה, רנדר. בתמונות שלכם בקבוק הפילינג עם תווית אחרת: ב-28, 31 ו-35 – מונוגרמה VM, «EXO-NAD PEELING» ושורות קטנות בכמה שפות, ועל התושבת (תמונה 29) הוא גם מסומן «EXO-NAD PEELING». בפקשוט – «EXO-NAD / SKIN LONGEVITY PEELING». על מכסה הקופסה (תמונה 32) מתחת ל-«SKIN LONGEVITY PEELING» יש גוש של טקסט קטן שאינו מופיע בפקשוט. לפי איזו גרסה לבנות? את תמונה 64 עם הכיתוב «SKIN LONGEVITY PILING» לא לוקחים.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>EXO-NAD</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>לתקריבים נדרשים צילומי סטודיו: בקבוק הפילינג, pH Normalizer ו-Longevity Serum – מלפנים וב-3/4, לפחות 1500 px בגובה; הקופסה – דפנות, חלק עליון, גב ועומק. כל עוד אין אותם, הכלים על המסך אינם גדולים מהמקור (בקבוק ≈210 px, בקבוקונים ≈140 px), והקופסה מסתובבת לא יותר מ-10°.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>EXO-NAD</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>לכמה טיפולים מיועדת קופסה אחת (15 מ״ל פילינג, 5 + 5 בקבוקונים של 5 מ״ל)? בקטלוג אין את המידע הזה, ולכן במסך הרכישה לא כותבים מספר.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>פרוטוקולי המזמין/ה: הערכה מספיקה לעד 15 טיפולים, בהתאם לכמות השימוש.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>EXO-NAD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>מסך 4: להשאיר את מעטה השמפניה המופשט (ללא פנים) או להציב פריים של פנים, כמו ב-MASK? לפנים נדרש צילום מאושר; תמונה 30 – עם אדם, רק בהסכמתכם.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>EXO-NAD</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>סיום הפרוטוקול: בסטוריבורד «EXOCELL MASK + SPF», בקטלוג «EXOCELL MASK או DERMA RECOVERY CREAM ומקדם הגנה». איזו גרסה נכונה? אם זו של הקטלוג – נוסיף קישור שני, ל-DERMA RECOVERY CREAM. את שקית ה-MASK לא מציגים כאובייקט (טורקיז של סדרה אחרת) – מסכימים?</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>EXO-NAD</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>פרטי קשר למסך הרכישה: מספר WhatsApp, טלפון ודוא״ל. תג הסדרה: «PEELING» באותיות לטיניות, כמו BIOSPICULE, או בעברית, כמו «מכשור» בדף הבית?</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>כמו ב-mitoderm.com (המזמין/ה 11/10): כפתור WhatsApp +972-54-762-1889, טלפון 054-326-2182, דוא״ל info@mitoderm.com (Mitoderm@gmail.com — לאירועים בלבד). את זמן החזרה הטלפונית לא מציינים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>בפריימים המאושרים (03-mirror, הערכה) – הקופסה הכהה «Your Second Skin», ואותה משאירים. אם במכירה כבר נמצאת הבהירה (sources/exocell-box-v2-front.png, אין תמונה של הדופן שלה), אמרו לנו: טקסטורת החזית תוחלף ותתווסף השורה «Total 125 ml». שורת ה-Net זהה בשתי הקופסאות.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>שלחו בבקשה צילום של גב השקית: ההדפס שלו אינו ידוע. בינתיים הגב טורקיז חלק, ללא כיתובים.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>לקופסה נדרשים צילומים של הדופן הימנית, החלק העליון, הגב ושל הקופסה הפתוחה (איך היא נפתחת, הדש מבפנים, התושבת). כל עוד אין אותם, הפאות האלה טורקיז חלק ללא הדפס, הקופסה מסובבת כך שרואים רק את החזית ואת הדופן השמאלית, והפתיחה במסך 2 משוערת. זה מתאים?</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>במסך 7 אין את השורות המאומתות b6.label1–2 («הדרכה ופרוטוקולים», «היבואנית…»). משאירים את מסך הרכישה בלעדיהן (מה בפנים, כפתור אחד, פרטי קשר) או מחזירים אותן כשורה קטנה מתחת לפרטי הקשר?</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>כמו ב-mitoderm.com (המזמין/ה 11/10): כפתור WhatsApp +972-54-762-1889, טלפון 054-326-2182, דוא״ל info@mitoderm.com (Mitoderm@gmail.com — לאירועים בלבד). את זמן החזרה הטלפונית לא מציינים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>את שכבות המסכה מניחים בזו אחר זו (כך בטקסטים של הדוגמה s5.double ו-kit.double) או יחד, «2 ב-1»? אם בזו אחר זו – איזו שכבה מונחת על העור ראשונה, הלבנה או התכלת, והאם לכתוב זאת בשלב 01 של הפרוטוקול? בלי אישורכם את הטקסטים לא משנים.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>המזמין/ה 11/10: המסכה דו-רכיבית, «2 ב-1»; את הטקסטים s5.double ו-kit.double לא משנים. את המסכה מסירים אנשי מקצוע בקליניקה, והמטופל/ת יכול/ה להשתמש בה לאחר הטיפול.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>בקטלוג אין זמן חשיפה למסכה, ולכן השלב «ספיגה» במסך 6 מופיע בלי זמן. אם בדף הטכני של VM יש זמן – להוסיף?</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>פרוטוקולי המזמין/ה: להשאיר את המסכה עד 30 דקות, ולאחר מכן להסיר אותה ולהחדיר את שארית הסרום לעור בטפיחות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>כפתור ה-WhatsApp הראשי מוביל למספר 054-762-1889, ובמסך 7 מופיע הטלפון 054-326-2182 (שניהם מתוך site/proto/exocell-he-ui.json). כך זה מתוכנן?</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>כמו ב-mitoderm.com (המזמין/ה 11/10): כפתור WhatsApp +972-54-762-1889, טלפון 054-326-2182, דוא״ל info@mitoderm.com (Mitoderm@gmail.com — לאירועים בלבד). את זמן החזרה הטלפונית לא מציינים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>נדרשים צילומים של הקופסה: החזית בלי האמפולות (מה מודפס בפינה הימנית התחתונה), הדפנות, הצד האחורי, העומק, וכן הקופסה פתוחה עם המגש הפנימי. עד אז בעלילה לא פותחים את הקופסה, מסובבים אותה לא יותר מ-8°, והפינה הימנית התחתונה תמיד מוסתרת על ידי האמפולות או נמצאת בצל.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>נדרש צילום סטודיו של אמפולה אחת מלפנים ומאחור ברזולוציה גבוהה. בפקשוט האמפולה ברוחב של כ-70 px. ליד הכיתוב הגדול 'EXOSIGNAL' נראות שורות קטנות ('EXOSIGNAL HAIR', 'Siero nutriente per il cuoio capelluto' ואחרות), ודרך הזכוכית נשקף בתמונת ראי ההדפס שבצד האחורי. בלי צילום כזה התקריבים במסכים 2–5 ייראו גסים, וסיבוב האמפולה מוגבל ל-±30°.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>האם האמפולה נפתחת בשבירת הצוואר לאורך הטבעת הלבנה? על זה בנוי המעבר 2→3. אם היא נפתחת אחרת, נבנה את המעבר מחדש.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>בתמונה הנוזל באמפולה חסר צבע. נא לאשר: מזה נגזר שאין בדף טיפה צבעונית.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>נא לשלוח פקשוט סטודיו של בקבוק EXOSIGNAL SPRAY על רקע שקוף. כרגע יש רק תמונה ביד. בתמונה 400×300 לא משתמשים: מופיע בה בקבוק לבן אטום, ולא האמיתי.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>את תג הסדרה כותבים באותיות לטיניות, «HAIR», כמו V-TECH FACE אצל MASK? ואיך נקראת הסדרה בעברית (אצל MASK זה «התחדשות הפנים», שנלקח מ-products.ts של האתר ב-Make)? לא ממציאים בעצמנו: ניקח מ-products.ts או מהתשובה שלכם.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>מסך 4 בנוי בלי אנשים: במקום תמונה – ארבע קווצות זהב. האם נדרש, כמו אצל MASK, מסגרת-תמונה עם אדם – למשל, מריחת המוצר על השביל בשיער בקליניקה? אם כן, נדרש פריים מאושר.</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>אין פקשוט סטודיו של EXOSIGNAL SPRAY. site/img/exosignal-spray.png (400×300) – רנדר או מוקאפ ישן: הבקבוק בו לבן ואטום וללא בלוק הכיתובים של בקבוק המט האמיתי, ובצילום ביד אין קופסה. בגיליון Photo slots ב-Excel מסומן הצילום האמיתי שלכם (קופסה + בקבוק מט). שלחו אותו בצ׳אט או העלו אותו ל-Drive /products. אם אפשר, הוסיפו את הדופן והחלק העליון של הקופסה ואת הצד האחורי של הבקבוק.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>איך נראה המרסס שמתחת למכסה? נדרש צילום של הבקבוק ללא המכסה, מהצד ומלפנים; צילום בטלפון על רקע ניטרלי יספיק. כל עוד אין צילום כזה, את המכסה לא מסירים, הערפל נכנס לפריים מעבר לקצה, ואת הפיה לא מציגים.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>למסך 4 «Feel it» נדרש פריים מלמעלה על שביל השיער, שבו הטיפות נספגות. האם יש לכם צילום כזה? אם לא, ניצור אותו לפי הפרומפט המוכן מתוך site/prompts/exosignal-spray.md: קודם דוגמה אחת, ואת המחיר והיתרה נציג לפני ההפעלה.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>את הצילום של הבקבוק ביד (עם אדם: נשמר באופן פרטי, לא במאגר הקוד) (הבקבוק ליד הלחי, הפנים נראות) לא מציבים בעמוד, ומשתמשים בו רק כמקור לתווית. אבל זהו צילום עם אדם, והוא כבר נמצא במאגר הקוד הציבורי, אף שלפי כללי הפרויקט אין לתמונות כאלה מקום שם. להסיר אותו מהמאגר ולשמור עותק רק באופן מקומי?</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>הכפתור הראשי «איפה לקנות»: במקורות אין רשימה של קליניקות שותפות. בינתיים הוא מוביל ל-WhatsApp עם הטקסט «שלום, אשמח לקבל פרטים על EXOSIGNAL SPRAY», ו-«התייעצו עם מומחה» פותח טופס בקשה לשיחה חוזרת, כמו ב-MASK. האם זה מתאים? האם תהיה רשימת קליניקות שאליה אפשר יהיה להעביר את הכפתור בהמשך?</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>את טבלת אנשי המקצוע המזמין/ה ישלח/תשלח בהמשך (11/10). עד אז הכפתור מוביל לטופס הפנייה, וללא JS — ל-WhatsApp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>כמה לחיצות נדרשות ליישום אחד, ולכמה זמן מספיקים 15 מ״ל? בקטלוג אין את המידע הזה, ולכן בעמוד כותבים רק «15 מ״ל, מדי יום, ללא שטיפה», ובסצנת הפרוטוקול העננים מופיעים ללא ספירה.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>mitoderm.com: פעם ביום על קרקפת נקייה ויבשה, לנער, לרסס בשורשי השיער, לעסות קלות; עדיף בערב, משך הטיפול חודשיים. מספר הלחיצות לא מצוין שם.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>האם יש הרכב של הספריי (INCI או רכיבים פעילים)? בקטלוג יש רק «מה הספריי עושה», ולכן בכרטיס כותרת המשנה היא «מה הספריי עושה», ולא «רכיבים פעילים».</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>מופיע ב-mitoderm.com: אקסוזומים סינתטיים, PDRN במשקל מולקולרי נמוך, פנתנול, ביוטין, 8 סוגי פפטידים ביומימטיים; בקבוקון 15 מ״ל (גיליון mitoderm.com).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>איך נקראת סדרת HAIR בעברית, עבור התג? ב-MASK מופיע הצמד «V-TECH FACE · התחדשות הפנים», ולספריי נדרש צמד דומה «HAIR · …».</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>האם אתם מסכימים להציג את הפקשוט של EXOSIGNAL HAIR במסכים 2 ו-5 כסימן הסדרה וכקישור לעמוד שלו? או להשאיר בעמוד רק את האריזה של הספריי?</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>בקובץ הפרומפטים הישן העמוד של הספריי היה «כסף על שחור» (#d9d4cc). לפי כלל הסדרות, HAIR – שחור עם זהב, והכסף שייך למכשירים. האם אתם מאשרים את הזהב?</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>EXOTECH GEL</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>איך נפתח הכדור? המכסה – חצי הכדור העליון עם הכיתוב כולו 'EXOTECH / GEL', התפר – קו המשווה מתחת ל-'GEL'. הוא נפתח בהברגה או פשוט מורם? נדרשים צילומים של הצנצנת הפתוחה מלמעלה ובזווית שלושה רבעים, וצילום של המכסה מלמטה. בינתיים המכסה מתרומם ישר למעלה בכמה מילימטרים, הסדק מכוסה בזוהר, והפנים אינם נראים. תשובת המזמין/ה (18/10): נפתח בהברגה – הכדור הזהוב מתחלק לשני חצאים.</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>EXOTECH GEL</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>באיזה צבע הג׳ל ועד כמה הוא שקוף? נדרש צילום של הג׳ל בצנצנת פתוחה או על האצבע. בינתיים הטיפות והשכבה הדקה שקופות בגוון ניטרלי, עם ברקים חמים. תשובת המזמין/ה (18/10): לבן כמו קרם.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>EXOTECH GEL</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>האם יש צילומי מקור של הקובייה והכדור ברזולוציה גבוהה (מ-2000 px בצלע הארוכה)? בפקשוט הכדור רק כ-390 px, והכיתובים שורטטו לווקטור לפיו. ומה מודפס על הגב, הדופן הימנית והתחתית של הקובייה ועל הצד האחורי של הכדור? הנפח 30 ml אינו נראה בצדדים הנראים, וכרגע הוא נלקח מהקטלוג. עד לצילומים האלה הכדור בפריים אינו גדול מ-~420 CSS px, והסיבוב מוגבל ל-±8°.</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>EXOTECH GEL</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>לאן מוביל «איפה לקנות»? רשימה או דף של קליניקות שותפות אין במקורות, ולכן כרגע כל כפתורי «איפה לקנות» פותחים את ה-WhatsApp של MITODERM עם טקסט מוכן (שורה חדשה להגהה). משאירים «איפה לקנות», כמו בטקסט המאושר של האתר (בקטלוג מופיע «היכן לרכוש»)? והאם לקליניקות נדרש מתחת לפרטי הקשר קישור טקסט «לקבלת פרטים על מחירים», כמו ב-MASK?</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>את טבלת אנשי המקצוע המזמין/ה ישלח/תשלח בהמשך (11/10). עד אז הכפתור מוביל לטופס הפנייה, וללא JS — ל-WhatsApp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>EXOTECH GEL</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>במסך 4 אין אנשים: שכבת הג׳ל עפה אל הצופה ומתמוססת. האם נדרש פריים עם אדם, כמו ב-MASK, למשל קצה אצבע עם ג׳ל ליד הלחי? זו ג׳נרציה בתשלום: קודם מחיר ויתרה, דוגמה אחת, אחר כך «מאשר/ת», ורק אחרי התשובה לשאלה 2 על צבע הג׳ל.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>EXOTECH GEL</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH FACE ו-«סדרת האקסוזומים הסינתטיים» – סדרה אחת או רמות שונות (סדרה וטכנולוגיה)? כרגע במסכים 1 ו-7 הם מופיעים כרכיב אחד: «V-TECH FACE», ומתחתיו כיתוב קטן «סדרת האקסוזומים הסינתטיים». איזה שם הוא העיקרי עבור המבקרים באתר?</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10%</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>שלחו בבקשה צילומים של המזרק של MICRO BOOST 10%: מלפנים ומהצד על רקע ניטרלי, עם המכסה ובלעדיו, וגם טיפת סרום אחת על הקצה. האם יש על המזרק מחט או פיה? אנחנו מציגים אותו ללא מחט: לפי הקטלוג, את הסרום מעסים לתוך העור. האם יש על המזרק הדפס או סקאלה? מה האורך עם המכסה ומה קוטר הגוף במ״מ? מה הצבע של הסרום ועד כמה הוא שקוף? בינתיים המזרק שקוף, ללא כיתובים, וקנה המידה משוער.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10%</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>נדרשים צילומים של הקופסה מכל הצדדים (הדפנות, הגב, החלק העליון, התחתית) והמידות שלה רוחב×גובה×עומק. כל עוד אין אותם, הקופסה מסתובבת רק בגבולות זווית הפקשוט ואינה מסתובבת לשלושה רבעים, כדי שפאה ריקה לא תיכנס לפריים.</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10%</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>המסך «הרגישו»: האם פריים כזה מאושר? המטופלת מביטה במצלמה כמו במראה, ידיים של קוסמטיקאי/ת בכפפות מעסות את הסרום על הלחי, אחרי האצבעות ניצוצות זהב, בלי «לפני ואחרי». זהו פריים מג׳ונרט אחד: את המחיר ואת היתרה נציג לפני הג׳נרציה, וההפעלה רק אחרי «מאשר/ת». פריים עם אדם לא ייכנס למאגר.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10%</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>להציג במסך הפרוטוקול קופסה קטנה של DERMA RECOVERY CREAM ליד התווית «+ DERMA RECOVERY בבית»? את V-TECH, את Longevity Serum (הבקבוקון בטורקיז מתוך הערכה EXO-NAD) ואת EXOCELL MASK לא מציגים ב-3D: אלה סדרות אחרות, ו-design-rules אוסרים לערבב בעמוד אחד צבעים של שתי סדרות. מסכימים?</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10%</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>ב-b5.line כתוב «3 ml ℮ 0.10 fl. oz.» עם רווח, ועל הקופסה «fl.oz.». להתאים את השורה להדפס (באמצעות עורך/ת העברית)?</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5%</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>שלחו בבקשה תמונות של בקבוק CELL RENEW 1.5% מלפנים, מהצד ומלמעלה. האם זה אותו בקבוק airless לבן עם משאבה כמו של CELLULAR AGE DEFENSE 2.5%, או בקבוק אחר? אם הסרום אינו שקוף, שלחו גם תמונה של המרקם שלו. בלי תמונה לא מציבים את הבקבוק ב-3D, ואת הטיפה מציירים חסרת צבע.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5%</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>לקופסת CELL RENEW 1.5% נדרשים: צילום של החזית ברזולוציה גבוהה (מ-2000 px לגובה) או קובץ ההדפס, וגם צילומים של הדפנות, החלק העליון והגב. כל עוד אין אותם, לא מתקרבים להדפס בתקריב, הדפנות חלקות, הקופסה סגורה, והבקבוק, אחרי שתגיע תמונה, יעמוד לידה. אם הקופסה צריכה להיפתח, שלחו צילום של החלק העליון שלה או של הקופסה הפתוחה.</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5%</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>מה המידות של שלוש הקופסאות (ג×ר×ע, מ״מ): CELL RENEW 1.5%, DERMA RECOVERY CREAM, CELLULAR AGE DEFENSE 2.5%? מתאימה גם תמונה אחת של שלוש הקופסאות זו לצד זו. נדרשים גם צילומים של הדפנות של DERMA ושל CAD 2.5%. כל עוד אין מידות, DERMA עומדת חצי צעד עמוק יותר, כדי שהגבהים לא יושוו.</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5%</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>מסכים 2 ו-4 (המראה): משאירים מראה עגולה מופשטת ללא אנשים, או מציבים תמונה מאושרת של עור או של פנים ליד המראה, כמו הפריים עם המסכה ב-EXOCELL?</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5%</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>שלב 3 «הגנה»: האם ל-MITODERM יש קרם הגנה מהשמש משלה שאפשר להציג? אם לא, את השלב מציגים כפס של אור יום, ללא אריזה.</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5%</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>הכפתור «איפה לקנות» פועל בינתיים כמו בדגימה של MASK: פותח טופס פנייה, ובלי JS מוביל ל-WhatsApp. האם יש רשימה של קליניקות שותפות שאליה אפשר להעביר אותו כשתהיה מוכנה (למשל, בלוק אנשי המקצוע אחרי מסך הרכישה)?</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>את טבלת אנשי המקצוע המזמין/ה ישלח/תשלח בהמשך (11/10). עד אז הכפתור מוביל לטופס הפנייה, וללא JS — ל-WhatsApp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>CELLULAR AGE DEFENSE 2.5%</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>הבקבוק: ב-Figma יש תמונה מס׳ 9 (בקבוק airless לבן, הצומת 93:8095), במאגר הקובץ אינו קיים. מודפס עליו 'CELL CELLULAR / AGE DEFENSE / 2.5%'. זו טעות דפוס בעיצוב, או שכך זה על הבקבוק האמיתי? שלחו בבקשה פקשוט של הבקבוק האמיתי על רקע שקוף. עד לתשובה העמוד נבנה עם הקופסה בלבד. אחר כך נוסיף את הבקבוק למסכים 4 (בתקריב רק ראש המשאבה) ו-7.</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>CELLULAR AGE DEFENSE 2.5%</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>בקופסה יש רק בקבוק אחד של 30 מ״ל, בלי עלונים ובלי אביזרים? בזה תלויה השורה «מה בפנים» במסך הרכישה.</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>CELLULAR AGE DEFENSE 2.5%</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>הדפנות והפאות העליונות של הקופסאות CELLULAR AGE DEFENSE 2.5%, CELL RENEW 1.5% ו-DERMA RECOVERY CREAM: נדרשות תמונות (מהן רואים גם את העומק האמיתי) או אישור שאין עליהן הדפס. עד אז שלוש הקופסאות מסתובבות לא יותר מ-±20°.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>CELLULAR AGE DEFENSE 2.5%</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM: במאגר יש שתי גרסאות של הקופסה – עם פס ירוק כהה (protocols/print/img) ועם פס מרווה (protocols/assets/img). איזו מהן נמכרת כעת? בינתיים מציבים את גרסת המרווה, כמו ב-packaging-text.json וב-design-rules.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>CELLULAR AGE DEFENSE 2.5%</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>מסך 4 «Feel it» – בחרו אפשרות. (א) פריים עם אדם: אצבעות ליד קו הלסת, תנועה מעגלית עדינה אחת, כמו הפריים המאושר עם פנים של MASK. זו ג׳נרציה בתשלום, את המחיר ואת היתרה אציין לפני ה«מאשר/ת» שלכם. (ב) משטח עור חם ומופשט בלי אדם, בלי ג׳נרציה. אם (א) – האם יש תמונת רפרנס?</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>CELLULAR AGE DEFENSE 2.5%</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>את שלב 3 «הגנה» מציגים רק במעבר של האור לאור יום, בלי שפופרת של מוצר הגנה מהשמש (אין כזה בקטלוג MITODERM). זה מתאים?</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>CELLULAR AGE DEFENSE 2.5%</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>האם אתם מאשרים את מערך הכפתורים? «איפה לקנות» פותח את המסך «Ask your clinic» (החלטה 17). «לקליניקות: לקבלת הצעת מחיר» פותח את WhatsApp עם טקסט מוכן והקוד #CAD-HE-6. הפאנל הנעוץ בטלפון מופעל רק יחד עם המערך הזה.</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>את טבלת אנשי המקצוע המזמין/ה ישלח/תשלח בהמשך (11/10). עד אז הכפתור מוביל לטופס הפנייה, וללא JS — ל-WhatsApp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>CELLULAR AGE DEFENSE 2.5%</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>קופסת CELL RENEW 1.5% עומדת מדרגה אחת נמוך יותר במסך 2, ובמסך 5 יש כרטיס שלה עם קישור. אפשר להציג בעמוד הזה מוצר סמוך?</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>הצנצנת. החזית של הצנצנת נמצאת אצלכם ב-Figma: תמונה 1 (צומת 93:8080), הצנצנת הפתוחה – תמונה 73 (צומת 113:8211). לפיהן בונים את הצנצנת ומסובבים אותה לא יותר מ-±20°. אם צריך לסובב את הצנצנת בחופשיות רבה יותר, שלחו בבקשה צילומים מאחור, מהצדדים ומלמעלה על המכסה. ועוד שאלה: האם הצנצנת מזכוכית או מפלסטיק?</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>הקופסה. נדרשים צילומים של הדפנות, הדופן האחורית והחלק העליון (עם דש סגור ופתוח) או המידות רוחב×גובה×עומק במ״מ. בפקשוט הישן (הפס הכהה) הדפנות נקיות ולמעלה דש-לשונית. האם כך גם בקופסה החדשה?</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>מסך 4 לפי הסטוריבורד – סצנה ליד המראה, אישה מורחת קרם. בקולאז׳ אין תמונה כזאת. האם יש לכם תמונה מאושרת משלכם, או ליצור דוגמה אחת ב-AI? את המחיר נציג לפני ההפעלה. כל עוד אין «אוקיי», מציבים גרסת 3D ללא אנשים.</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>מסך 5: CELL RENEW 1.5% ו-CELLULAR AGE DEFENSE 2.5% מוצגים כ«או» (מתחלפים זה בזה), MICRO BOOST 10% – כענף קליני נפרד עם התג «מקצועי». V-TECH ו-EXO-NAD – רק כטקסט, כדי לא לערבב את צבעי הסדרות. מסכימים?</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>הכפתור הראשי «איפה לקנות» מוביל לבלוק של אנשי המקצוע והקליניקות (מסך 8). הכפתור «לקליניקות: בקשת הצעת מחיר» פותח את טופס הפנייה, שבו השדה «מקצוע» מפריד את הקליניקות. האם זה נכון?</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>את טבלת אנשי המקצוע המזמין/ה ישלח/תשלח בהמשך (11/10). עד אז הכפתור מוביל לטופס הפנייה, וללא JS — ל-WhatsApp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>תג הייעוד לכל האתר: «טיפוח ביתי» (design-rules, הדגם של MASK, ה-eyebrow של סרומי BIOSPICULE) או «טיפול ביתי» (מילון המונחים, home.sl-3)? בינתיים מציבים «טיפוח ביתי».</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>להגהה: ב-b5.line הנפח כתוב «1.69 fl. oz.» (EN) ו-«1.69 fl. oz» (HE), ואילו על האריזה וב-cat.kit – «50 ml ℮ 1.69 fl.oz.». להתאים את b5.line להדפס?</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>MITOPEN</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>האם ל-MITOPEN יש קופסה או נרתיק, ומה יש בהם מלבד העט: מחסניות, מטען או כבל, מעמד? בקטלוג ובפקשוט מופיע רק «1× MITOPEN», ולכן במסך הרכישה מציגים בינתיים עט אחד. אם יש קופסה, נדרשות תמונות שלה מכל הצדדים.</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>MITOPEN</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>במה נקבע עומק המחט ב-MITOPEN: בטבעת בזהב ורוד, בחרטום או במחסנית? במה מחליפים את 5 המהירויות – בכפתור? מה פירוש הנקודה שמעל הכפתור? בסטוריבורד יש הרמז «סובבו את הטבעת» ו«הגלילה מסובבת את הטבעת», אבל על האריזה הטבעת מתוארת כטבעת אחיזה. כל עוד אין תשובה, על הטבעת רק עובר ברק אור, הסקאלות זזות בעקבות הגלילה, והרמז – «גללו».</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>MITOPEN</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>אם תמונות MITOPEN מס׳ 56 ו-57 ב-Figma יתבררו כקטנות מ-2500 px בגובה או ללא תקריב של המחסנית: האם תוכלו לשלוח פקשוט ברזולוציה גבוהה ותמונת מאקרו של המחסנית עם המחטים בעומק המינימלי ובעומק המקסימלי? בלי זה אין מאקרו במסך 3, ואת המחטים לא מציגים.</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>MITOPEN</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>תמונה למסך 4 (מטפלת בכפפות מעבירה את MITOPEN על לחי המטופלת): יש צילום משלכם, או שניצור תמונה ב-AI לפי הפקשוט? העט בתמונה צריך להיות באותה זווית כמו בפקשוט. יצירת התמונה ב-AI כרוכה בתשלום: קודם דוגמה אחת, מחיר ו«מאשר/ת».</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>MITOPEN</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>בקטלוג הטווח כתוב עם מקף («0.25-2.5»), ובסטוריבורד עם קו מפריד («0.25–2.5»). את סדר המספרים באתר אנחנו מיישרים בבידוד LTR, אבל הסימן עצמו נשאר שונה. להאחיד את הקטלוג לקו המפריד, כמו בסטוריבורד?</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>MITOSCAN</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>זה חוסם את מסכים 3–5. האם יש צילומים אמיתיים מהמסך של MITOSCAN – אותו אזור בקרקפת בהגדלה ×50 וב-×200 – וצמד «לפני / אחרי» של האזור הזה לאורך סדרת הטיפולים, בהסכמת המטופל/ת להצגה באתר? אסור לייצר בג׳נרציה «צילום של המכשיר». כל עוד אין תשובה, את מסכים 3–5 ב-Figma לא בונים על ממלאי מקום. אם לא יהיו צילומים, מציבים את אפשרות הגיבוי: טיפוגרפיה גדולה ×50 → ×200 לפני המסך עם הלוגו, «מראה» עם הלוגו ושלושה שלבים בלי «לפני / אחרי».</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>MITOSCAN</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>נדרשים צילומים של הסורק (הקצה עם העדשה, הצד, הצד האחורי) וצילום של הטאבלט בלי הסורק (המחזיק הריק, המעמד בשלמותו). בלעדיהם כל העלילה מתנהלת בתנועת מצלמה על פני פקשוט שלם אחד: הסורק אינו יוצא מהמחזיק, והמערכת אינה מתפרקת לחלקים.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>MITOSCAN</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>מהו הגליל הכסוף עם הרשת בקצה? בקטלוג התמונות הוא נקרא מעמד-גליל, ובתיאור האריזה – בסיס. האם הוא מחובר בכבל לסורק? עד שתאשרו, באתר הוא נשאר בלי שם, בלי תפקיד ובלי קווי הפניה.</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>MITOSCAN</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>בקטלוג כתוב «1× MITOSCAN». האם כל שלושת הפריטים מהפקשוט כלולים בערכה: הטאבלט על המעמד, הסורק עם הכבל הספירלי והגליל? אם כן, נוסיף כיתובים לחלקים במסכים 6–7, ולשם כך נדרשות שלוש שורות חדשות קצרות.</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>MITOSCAN</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>פריים הצילום למסך 4 (המטפל/ת עם הסורק ליד שביל השיער של המטופל/ת): מצלמים בקליניקה או מייצרים בג׳נרציה, אחרי שנציג את המחיר ונקבל את ה«מאשר/ת» שלכם? בג׳נרציה מסך המכשיר בפריים מופנה הרחק מהמצלמה או מציג רק את הלוגו. אם לא זה ולא זה, מציבים את האפשרות «מראה» בלי אנשים.</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>MITOSCAN</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>הבלוק «מי מבצע/ת את הטיפול» אחרי מסך הרכישה: מציגים את כל אנשי המקצוע עם התווית קרקפת או רק את אלה שכבר יש להם MITOSCAN?</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Home — MITODERM</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>סימון המפתחות: «slug:מפתח» – מפתח של דף אחר ב-storyboard.he.json; «slug:cat.שדה» – אותו דף ב-product-pages.he.json (האינדקס זהה לזה שב-product-pages.json); «catalog.chips[i]» – הפריט ה-i בשורה «Chips HE» בגיליון Catalog (0 הכל … 2 פילינג, 4 שיער, 5 ביו-ספיקולות, 6 טיפוח ביתי, 7 מכשור); «#n» – המקטע ה-n בשורה המחולקת ב-« · »; «A + « – » + B» – חיבור של שורות מאומתות לשורה אחת (שורת הטקסט של מסך 5, המקרא של מסך 7); «new:» – שורה מתוך new_strings. האם כלי הבנייה יקבל שיטת הפניה כזו?</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Home — MITODERM</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>סדר הסדרות: ההצעה היא V-TECH FACE → PEELING → BIOSPICULE → DEVICES → HAIR. כך צבע הסביבה מתחלף בכל שלב, והמכשירים באים מיד לפני HAIR, שבה הם שלבים 1–2 של הפרוטוקול. להשאיר כך, או לקחת את הסדר מטבלת הפלטה (V-TECH FACE, HAIR, PEELING, BIOSPICULE, DEVICES)?</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Home — MITODERM</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>הכיתובים של הסדרות ב-dock ובתגים: כרגע אלה השמות בעברית של המסננים בקטלוג (פילינג, ביו-ספיקולות, מכשור, שיער), ועוד שם המותג הלטיני V-TECH FACE. או שבכל מקום ישמשו שמות המותג הלטיניים של הסדרות (V-TECH FACE · PEELING · BIOSPICULE · DEVICES · HAIR), כמו התג בדף MASK?</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Home — MITODERM</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>תג הטיפוח הביתי: בכללי הפלטה, במסנני הקטלוג וב-eyebrow של המוצרים – «טיפוח ביתי», ואילו ב-home.sl-3 המאומת, לפי מילון המונחים, כתוב «טיפול ביתי». איזו מילה להשאיר בדף הבית?</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Home — MITODERM</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>MITOTECH CELL BOOSTER: לאיזו סדרה הוא שייך? ב-Figma של דף הבית הוא בשורת המכשירים, ואילו בגיליון Catalog (Card 13) – PRO, מסנן [Exosomes], סדרה «לברר». האם יש צילום של האריזה (שני בקבוקונים) ומה הנפח שלהם? בינתיים הוא מוצג רק ככרטיס «חדש · בקרוב» ללא 3D.</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>בפרוטוקולים של המזמין/ה: שני בקבוקונים — בוסטר ותרכיז אבקה, לערבב עד לקבלת תמיסה שקופה, עד 2 מ״ל לפנים, לצוואר ולדקולטה. הסדרה לא מצוינת שם.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Home — MITODERM</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>נדרשים צילומים: פקשוט סטודיו של EXOSIGNAL SPRAY – הבקבוק והקופסה, בלי יד. עד שיהיה פקשוט כזה, בדף הבית אין בקבוק ואין ערפל, רק קופסה קטנה בעומק. לתקריב – אמפולה אחת של EXOSIGNAL HAIR על רקע שקוף. אופציונלי: צילום גדול יותר של Biphasic Peel וצילומים של הפאות הצדדיות של הקופסאות V-TECH SYSTEM, EXOSIGNAL HAIR, EXO-NAD ו-BIOSPICULE – בלעדיהן הדפנות יהיו בצבע אחיד ללא הדפס.</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Home — MITODERM</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>פרטי הקשר במסך 7 (מספר WhatsApp, טלפון, דוא״ל): לוקחים את אותם פרטים כמו בדוגמה המאושרת של EXOCELL MASK?</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>כמו ב-mitoderm.com (המזמין/ה 11/10): כפתור WhatsApp +972-54-762-1889, טלפון 054-326-2182, דוא״ל info@mitoderm.com (Mitoderm@gmail.com — לאירועים בלבד). את זמן החזרה הטלפונית לא מציינים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Home — MITODERM</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>מסך ה-hero: (א) להציג את כל 12 האריזות בבת אחת, או גם בדסקטופ אריזה עיקרית אחת לכל סדרה, ואת האחרות – בריחוף? (ב) הכפתור home.b2 «מוצרים מקצועיים» מוביל לקטלוג, אבל מסנן «מקצועי» אין בקטלוג: לפתוח על «הכל» או להוסיף מסנן כזה? (ג) המספר «4 עקרונות ליבה» הוסר משורת האמון, כי העקרונות עצמם מפורטים רק בדף About. מסכימים?</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>חמש סדרות בארבעה מסכים: V-TECH FACE ו-HAIR מוצגות באותו מסך, כי לשתיהן שחור עם זהב ושתיהן אקסוזומים סינתטיים של VM. להשאיר כך, או לתת ל-HAIR מסך משלה ולאחד את ה-hero עם מדף הקטגוריות?</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>MITOTECH CELL BOOSTER: הסדרה לא אושרה, ואין פקשוט ואין טקסט אריזה. כרגע הוא מוצג במסך המכשירים ככרטיס «בקרוב» בלי 3D, כמו בדף הבית, ונראה רק כשנבחר הצ׳יפ «All»; בגיליון Catalog הוא מסומן במסנן Exosomes. לאיזו סדרה ולאילו צ׳יפים לשייך אותו? ל-3D נדרש פקשוט של שני הבקבוקונים.</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>בפרוטוקולים של המזמין/ה: שני בקבוקונים — בוסטר ותרכיז אבקה, לערבב עד לקבלת תמיסה שקופה, עד 2 מ״ל לפנים, לצוואר ולדקולטה. הסדרה לא מצוינת שם.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>טיפול ביתי: בגיליון Catalog וב-design-rules מופיע «טיפוח ביתי», ובדף הבית (home.sl-3) ובמילון המונחים – «טיפול ביתי». בקטלוג התג והצ׳יפ נלקחים מאותו מפתח catalog.chips[6], כך שתשובה אחת תשנה את שניהם. באיזו מילה משתמשים בכל האתר?</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>הכפתור הראשי של הקטלוג – «לקבלת פרטים על מחירים», כמו בעמודי המוצרים; כשנבחר הצ׳יפ Home care, במקומו מופיע «איפה לקנות». בגיליון Catalog ובדף הבית מופיע «Contact us / צרו קשר». לתקן את הגיליון לפי כפתור המחיר או להשאיר «צרו קשר»?</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>את טבלת אנשי המקצוע המזמין/ה ישלח/תשלח בהמשך (11/10). עד אז הכפתור מוביל לטופס הפנייה, וללא JS — ל-WhatsApp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>תגי הסדרות עוצבו כמו בדף הבית: V-TECH FACE באותיות לטיניות, והשאר – במילים של הצ׳יפים (פילינג, שיער, ביו-ספיקולות, מכשור). זה מתאים, או לכתוב את PEELING, HAIR ו-BIOSPICULE™ באותיות לטיניות, כמו בגיליון Catalog?</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>הצ׳יפ «Masks»: בקטלוג העשן נשאר בשחור עם הזהב של V-TECH FACE, והטורקיז של EXOCELL מופיע רק כטיפה מתחת לקופסה; הסביבה בטורקיז-כחול של MASK נשארת בעמוד המוצר שלה. מסכימים?</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>ההדפס על הדפנות ידוע רק אצל EXOCELL MASK ו-EXOTECH GEL, ולכן רק הן מוצבות במבט 3/4. שאר הקופסאות עומדות כמעט בחזית מלאה (עד 12°) ומסתובבות רק אל החזית. תוכלו לשלוח צילומים של הדפנות, כדי להציב גם אותן במבט 3/4?</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>פרטי הקשר במסך 7 (WhatsApp, טלפון, e-mail) – אותם פרטים כמו בדגם של EXOCELL MASK?</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>כמו ב-mitoderm.com (המזמין/ה 11/10): כפתור WhatsApp +972-54-762-1889, טלפון 054-326-2182, דוא״ל info@mitoderm.com (Mitoderm@gmail.com — לאירועים בלבד). את זמן החזרה הטלפונית לא מציינים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>טכני, עבור כלי הבנייה של ה-Excel: site/tools/story3d_xlsx.py כבר מבין cat[slug].…, sb[slug].…, b6.cta[i] (ספירה מאפס) ו-home:מפתח. אבל את האינדקס בתוך מחרוזת חדשה הוא אינו מזהה: catalog.chips[i] יוצא כ-«⚠ חסר מפתח» (וכך גם בדף הבית). יש להשלים: לתמוך ב-[i] עבור מחרוזות חדשות ולחפש catalog.* מכל עמוד.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15459,6 +16879,2688 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D121"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>עמוד</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>בלוק</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>כותרת-על</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>המדע · BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>SCIENCE · BIOSPICULE™</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>שם</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>BIOSPICULE™</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>כותרת משנה</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>BIOMICRONEEDLING · הדור הרביעי</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>4TH GENERATION BIO-MICRONEEDLING</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>סלוגן</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>הדור הרביעי של טכנולוגיית הספיקולות</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Fourth-generation spicule technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>פסקת פתיחה</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ספונגילה (Spongilla) היא ספוג מים מתוקים שבשלדו מיליוני מחטים מינרליות זעירות העשויות מסיליקה – ספיקולות. בתהליך עיבוד קוריאני מתקדם הן מטוהרות וממוינות לפי גודלן, וכך חומר גלם טבעי הופך לטכנולוגיה קוסמטית מדויקת: חידוש פני העור והולכה – BIOMICRONEEDLING.</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Spongilla is a freshwater sponge whose skeleton holds millions of silica micro-needles. Purified and sorted by size with an advanced Korean process, they become a precise cosmetic technology: resurfacing plus delivery — BIOMICRONEEDLING.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>נתון 1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>80-300 · עומק חדירה במיקרון</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>80–300 · µm penetration depth</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>נתון 2</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>72 שעות · נשארות בעור</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>72 h · Continued stimulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>נתון 3</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4 · סוגי ספונגילה</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>4 · Spicule types</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>נתון 4</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>דור 4 · טכנולוגיית ספיקולות</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>4th · Generation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · כותרת-על</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>מנגנוני פעולה</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>MECHANISMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · כותרת</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>שני מסלולי פעולה מקבילים</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Two parallel mechanisms of action</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 1 · כותרת</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>חידוש פני העור</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Resurfacing</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 1 · טקסט</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>גירוי מכני קוסמטי מבוקר התומך בהסרה הדרגתית של תאים אפידרמליים ומשפר את מרקם העור.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Controlled mechanical stimulation supports the removal of dead cells and refines texture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 2 · כותרת</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>מערכת הולכה</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 2 · טקסט</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>מסלולים מיקרוסקופיים זמניים התומכים במעבר יעיל יותר של הרכיבים הפעילים הנמרחים במהלך הטיפול.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Temporary micro-pathways support the delivery of actives applied during the treatment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 3 · כותרת</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>טיהור</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Purification</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 3 · טקסט</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>שאריות בלתי רצויות מוסרות, והספיקולות מטוהרות וממוינות בהתאם למאפייניהן ולגודלן.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Residues are removed; spicules are sorted by characteristics and size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 4 · כותרת</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>ארכיטקטורה</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 4 · טקסט</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>השילוב בין ספיקולות קצרות וארוכות קובע את פיזור הגירוי בשכבות השונות של האפידרמיס.</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Length balance decides how stimulation spreads across epidermal layers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · כותרת-על</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>איך זה עובד</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>HOW IT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · כותרת</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Delivery ← Resurfacing ← Spicule</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Spicule → Resurfacing → Delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 1 · כותרת</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>חדירה</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Penetrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 1 · טקסט</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>מיליוני מיקרו-מחטים חודרות במהירות ומגיעות לעומק של 80-300 מיקרון באפידרמיס.</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Millions of micro-needles reach 80–300 µm into the epidermis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 2 · כותרת</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>גירוי</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Stimulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 2 · טקסט</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>החדירה מפעילה מיקרוסירקולציה, מאיצה חילוף חומרים ותומכת בייצור קולגן; הספיקולות נשארות בעור עד 72 שעות.</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Microcirculation, metabolism and collagen production are activated; spicules stay up to 72 h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 3 · כותרת</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>הולכה</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Deliver</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 3 · טקסט</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>המבנה החלול של הספיקולות והמסלולים המיקרוסקופיים הופכים את שלב החידוש לשער קוסמטי מדויק.</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Hollow spicules and micro-channels turn renewal into a delivery pathway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · כותרת-על</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>מוצרים</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>PRODUCTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · כותרת</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>סדרת BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>The BIOSPICULE™ range</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10% – טיפול מקצועי לקליניקה</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>MICRO BOOST 10% — professional in-clinic</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 2</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5% – סרום ביתי לחידוש והבהרה</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>CELL RENEW 1.5% — home serum</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 3</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>CELLULAR AGE DEFENSE 2.5% – סרום ביתי למיצוק ואנטי-אייג׳ינג</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>CELLULAR AGE DEFENSE 2.5% — home serum</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 4</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM – קרם משקם, ללא ספיקולות</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>DERMA RECOVERY CREAM — recovery, no spicules</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 5 · כותרת-על</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>אינדיקציות</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>INDICATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 5 · כותרת</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>למי מתאים הטיפול?</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>What it addresses</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 5 · תגיות</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>אנטי-אייג׳ינג · קמטים וקמטוטים · נקבוביות פעורות · מיצוק · הבהרה · שיפור גוון העור · פיגמנטציה פוסט דלקתית PIH · צלקות ופוסט אקנה · אקנה קל עד בינוני · עור דק וחסר ברק</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Anti-ageing · Wrinkles &amp; fine lines · Enlarged pores · Firming · Brightening · Uneven tone · PIH · Scars &amp; post-acne · Mild to moderate acne · Dull, thin skin</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>קריאה לפעולה · כותרת</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>גלו את פרוטוקולי BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Discover the BIOSPICULE™ protocols</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>קריאה לפעולה · טקסט</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>המומחים שלנו ישמחו לייעץ על MICRO BOOST 10% בקליניקה ועל שגרת הטיפוח הביתית.</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Our specialist will advise on MICRO BOOST 10% in the clinic and the home-care routine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>המדע: BIOSPICULE™‎</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>קריאה לפעולה · כפתור</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>צרו קשר</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Contact us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>כותרת-על</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>המדע</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>SCIENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>שם</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>Synthetic exosomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>כותרת משנה</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>מערכות נשא מתקדמות</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>ENGINEERED DELIVERY</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>סלוגן</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>מערכת נשא מתוכננת – לא ממקור חי</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>Engineered delivery, not biological material</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>פסקת פתיחה</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>MITODERM היא היבואנית והמפיצה הבלעדית בישראל של VM Corporation. האקסוזומים הסינתטיים פותחו בהשראת מנגנון ביולוגי – מערכות נשא מתקדמות המשלבות בתוכן רכיבים פעילים, מגנות עליהם ומשפרות את חדירותם אל העור.</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>MITODERM is the exclusive importer of VM Corporation in Israel. Synthetic exosomes are engineered delivery systems inspired by natural vesicles: they encapsulate selected actives, protect them and enhance their penetration into the skin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>נתון 1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>VM · תאגיד איטלקי</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>VM · Corporation, Italy</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>נתון 2</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>מעל 100 · מדינות בעולם</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>100+ · Countries</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>נתון 3</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>ננו · מבנה הנשא</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>Nano · Scale delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>נתון 4</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>0 · חומר ממקור חי</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>0 · Biological source material</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · כותרת-על</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>יתרונות</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>ADVANTAGES</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · כותרת</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>למה דווקא הגרסה הסינתטית</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Why synthetic</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 1 · כותרת</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>ללא מקור חי</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>No biological source</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 1 · טקסט</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>בניגוד לאקסוזומים המופקים מתאים אנושיים, מבעלי חיים או מצמחים – הסינתטיים אינם מופקים ממקור חי.</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Not obtained from human, animal or plant living material.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 2 · כותרת</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>מולקולות גדולות</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Larger molecules</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 2 · טקסט</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>המבנה הייחודי מאפשר לשלב רכיבים פעילים ומולקולות גדולות שלא היו חודרות לולא המבנה.</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>The engineered structure carries actives whose delivery is otherwise limited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 3 · כותרת</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>הגנה</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>Protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 3 · טקסט</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>המבנה הננומטרי נועד להגן על הרכיבים שהוא נושא ולתמוך בהעברתם.</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>The nanoscale structure protects the encapsulated ingredients.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 4 · כותרת</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>הובלה ממוקדת</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Targeted delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 4 · טקסט</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>האקסוזומים מובילים את הרכיבים הפעילים באופן ממוקד ויעיל פנימה אל התאים.</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Supports efficient, targeted delivery into the skin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · כותרת-על</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>איך זה עובד</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>HOW IT WORKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · כותרת</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>מהבועית אל העור</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>From vesicle to skin</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 1 · כותרת</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>שילוב</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>Encapsulate</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 1 · טקסט</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>בתוך הבועיות יש רכיבים פעילים כגון PDRN, פפטידים ורכיבים נוספים שנבחרו בקפידה בהתאם למטרת הפורמולה.</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Selected actives — PDRN, peptides and more — are encapsulated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 2 · כותרת</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>הגנה</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 2 · טקסט</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>המבנה מגן על הרכיבים שהוא נושא בדרכם פנימה אל העור.</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>The structure shields the ingredients on their way into the skin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 3 · כותרת</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>הובלה</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Deliver</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 3 · טקסט</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>חדירה ושחרור ממוקד במקום שבו הפורמולה נועדה לפעול – שם מופעלת שרשרת של תהליכי התחדשות ושיקום.</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Penetration and targeted release where the formulation is designed to act.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · כותרת-על</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>מוצרים</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>PRODUCTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · כותרת</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>המוצרים המבוססים על הטכנולוגיה</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Built on synthetic exosomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 1</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM – ערכה מקצועית</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>V-TECH SYSTEM — professional kit</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 2</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>EXO-NAD – מערכת פילינג מקצועית</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>EXO-NAD — longevity peel</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 3</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK – מסכת ביו-צלולוז</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>EXOCELL MASK — bio-cellulose mask</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 4</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR – מערכת מקצועית לקרקפת</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL HAIR — scalp system</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 5</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>EXOTECH GEL – טיפול ביתי משלים</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>EXOTECH GEL — home care</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 6</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY – ספריי ביתי לקרקפת</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>EXOSIGNAL SPRAY — home scalp care</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 5 · כותרת-על</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>רכיבים</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVES</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 5 · כותרת</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>הרכיבים שהמערכת נושאת</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Carried by the system</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 5 · תגיות</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>PDRN · פפטידים ביומימטיים · NAD⁺ · חומצה היאלורונית · תאי גזע צמחיים · ויטמינים ונוגדי חמצון</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>PDRN · Biomimetic peptides · NAD+ · Hyaluronic acid · Plant stem cells · Vitamins &amp; antioxidants</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>קריאה לפעולה · כותרת</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>הכירו את פרוטוקולי האקסוזומים</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Discover the exosome protocols</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>קריאה לפעולה · טקסט</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>המומחים שלנו ילוו אתכם בהטמעת V-TECH, EXO-NAD ו-EXOSIGNAL בקליניקה שלכם.</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Our specialist will walk you through V-TECH, EXO-NAD and EXOSIGNAL in your clinic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>המדע: אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>קריאה לפעולה · כפתור</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>צרו קשר</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Contact us</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>כותרת-על</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>אודות</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>ABOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>שם</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>MITODERM</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>MITODERM</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>כותרת משנה</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>WHERE SCIENCE MEETS BEAUTY</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>WHERE SCIENCE MEETS BEAUTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>סלוגן</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>המקום שבו מדע פוגש יופי</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Where science meets beauty</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>פסקת פתיחה</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>חברה ישראלית המתמחה בפיתוח, בייבוא ובהנגשה של טכנולוגיות מתקדמות לעולמות הקוסמטיקה והאסתטיקה המקצועית בתחום העור והקרקפת – בשיתוף פעולה עם מעבדות, יצרנים ותאגידים מובילים באיטליה ובדרום קוריאה.</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>An Israeli company specialising in the development, import and distribution of advanced technologies for professional aesthetics, skin and scalp care — in partnership with leading laboratories in Italy and South Korea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>נתון 1</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>IL · חברה ישראלית</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>IL · Founded in Israel</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>נתון 2</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>IT · KR · מעבדות שותפות</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>IT · KR · Laboratory partners</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>נתון 3</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>מעל 100 · מדינות שבהן משווקת VM</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>100+ · Countries where VM is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>נתון 4</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>4 · עקרונות ליבה</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>4 · Core principles</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · כותרת-על</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>עקרונות</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>PRINCIPLES</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · כותרת</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>הסטנדרט שלנו</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>Our standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 1 · כותרת</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>חדשנות</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 1 · טקסט</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>כל מוצר וכל טכנולוגיה הנכנסים למערך המקצועי של MITODERM נבחנים לפי עקרון החדשנות.</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>Every technology in the portfolio is evaluated for genuine innovation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 2 · כותרת</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>איכות</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 2 · טקסט</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>עבודה ישירה עם השותפים המקצועיים בחו״ל – מבחירת חומרי הגלם ועד פיתוח הפורמולות.</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Direct work with partners from raw material to formulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 3 · כותרת</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>בטיחות</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 3 · טקסט</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>תהליכי טיהור ובקרה קפדניים – כמו בספיקולות BIOSPICULE™‎ המבוססות על ספונגילות.</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Rigorous purification and quality control, e.g. BIOSPICULE™ spicules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 4 · כותרת</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>נוחות יישום</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Ease of use</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 1 · פריט 4 · טקסט</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>פרוטוקול טיפול שלם, הדרכות מקצועיות וידע מדעי – מעטפת מלאה עבור הקליניקה.</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Complete protocols, training and scientific education for clinics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · כותרת-על</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>הגישה שלנו</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>APPROACH</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · כותרת</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>החיבור בין מדע לקליניקה</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Bridging science and clinical practice</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 1 · כותרת</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>ידע</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Knowledge</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 1 · טקסט</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>MITODERM נוסדה מתוך היכרות עמוקה עם העור מבפנים ומתוך הבנה אמיתית של הצרכים בשטח.</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Founded on in-depth knowledge of skin biology and real clinical needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 2 · כותרת</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>פרוטוקולים</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Protocols</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 2 · טקסט</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>טיפול מקצועי ברמה גבוהה הוא לא רק הטיפול עצמו – אלא גם הידע, הבנת מנגנון הפעולה ופרוטוקול מדויק.</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Precise treatment protocols and a clear understanding of mechanisms of action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 3 · כותרת</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>הדרכה</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 2 · שלב 3 · טקסט</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>לצד פיתוח ושיווק המוצרים – הדרכות מקצועיות, ידע מדעי ופרוטוקול טיפול שלם ומותאם אישית.</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Professional training and scientific education alongside distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · כותרת-על</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>הפורטפוליו</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>PORTFOLIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · כותרת</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>בליבת הפעילות שלנו</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>What we work with</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 1</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>אקסוזומים סינתטיים</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Synthetic exosomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 2</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>פפטידים ו-PDRN</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Peptides and PDRN</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 3</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>NAD⁺ ורכיבים ביומימטיים</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>NAD+ and biomimetic ingredients</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 4</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>BIOSPICULE™‎ – ספיקולות מטוהרות המבוססות על ספונגילות</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>BIOSPICULE™ purified Spongilla spicules</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 3 · פריט 5</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>מכשור מקצועי: MITOPEN, MITOSCAN</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Professional devices: MITOPEN, MITOSCAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 5 · כותרת-על</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>השם</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>THE NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 5 · כותרת</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>חיבור בין שני עולמות</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>MITO + DERM</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>מקטע 5 · תגיות</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>MITO – מיטוכונדריה, אנרגיית התא · DERM – הדרמיס, העור · תפקוד · התחדשות · חיוניות · מדע ואסתטיקה נפגשים</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>MITO — cellular energy · DERM — the skin · Function · renewal · vitality · Science meets aesthetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>קריאה לפעולה · כותרת</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>שיתוף פעולה עם MITODERM</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Work with MITODERM</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>קריאה לפעולה · טקסט</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>קליניקות, הדרכות ושיתופי פעולה – המומחים שלנו יחזרו אליכם.</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Clinics, training and partnerships — our specialist will get back to you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>אודות MITODERM</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>קריאה לפעולה · כפתור</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>צרו קשר</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>Contact us</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -19956,7 +24058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20814,7 +24916,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21696,7 +25798,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23958,1423 +28060,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C100"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>עמוד</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>שאלה למזמין/ה</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>תשובה / החלטה (מקור)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>V-TECH SYSTEM</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>איך נפתחת הקופסה של V-TECH SYSTEM? בצילום מס׳ 44 יש בפנים מגש פנימי שחור (השקיות מונחות שטוחות, 5 בקבוקונים בשקעים), ובפקשוט נראים פסים שחורים מעל הזהב ומתחתיו. חלק הזהב הוא שרוול שנשלף, או מכסה? נדרשים המקור של צילום 44 וצילום של פתיחת הקופסה, וכן החלק העליון, התחתית והצד האחורי של הקופסה. כל עוד אין תשובה, חלק הזהב פשוט מתרומם ונסוג לאחור.</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>V-TECH SYSTEM</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>בקבוקון או אמפולה? בפקשוט – בקבוקונים, בתרשים הערכה (צילומים 78 ו-83) – VIALS ו-POUCHES, ובקטלוג ובטקסטים של האתר – אמפולות. ב-3D מציגים כמו בצילום. את המילה בטקסט משאירים או משנים?</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>בטקסט — «אמפולות», כמו ב-mitoderm.com («5 אמפולות V-Tech Serum בנפח 5 מ׳׳ל כל אחת»); ב-3D — בקבוקון, כמו בתמונה. המזמין/ה 11/10: «5 מסכות ו-5 אמפולות».</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>V-TECH SYSTEM</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>מכסה הבקבוקון: בפקשוט – flip-off לבן, בצילומים 45, 46, 48 ו-79 – כסוף. איזה להציג? ואיך לוקחים את הסרום מהבקבוקון: במזרק, בטפטפת, מסירים את הפקק? כל עוד אין תשובה, המכסה סגור, והטיפה מופיעה באוויר מעל הבקבוקון.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>כסוף, כמו בתמונה 79. את הסרום שואבים למזרק 3 מ״ל במחט שאיבה (פרוטוקולי המזמין/ה, V-TECH + MITOPEN, שלב 1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>V-TECH SYSTEM</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>מה הצבע והמראה של הסרום ושל הג׳ל – שקופים, זהובים? בינתיים הטיפה והג׳ל שקופים, ללא חלקיקים.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>V-TECH SYSTEM</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>חומצה היאלורונית ואלוורה (הפריט האחרון ברשימת הרכיבים) – בסרום או במסכת הג׳ל? בינתיים, ברשימת הרכיבים הפתוחה זו שורה נפרדת אחרי שתי הקבוצות.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>במסכת הג׳ל: mitoderm.com, הרכב V-Tech Gel Mask 5ml — «חומצה היאלורונית במשקל מולקולרי נמוך, אלוורה».</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>V-TECH SYSTEM</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>כמה בקבוקונים ושקיות נדרשים לטיפול אחד, והאם קופסה אחת מספיקה לסדרת טיפולים? בערכה 5 + 5, סדרת הטיפולים – לפחות ארבעה טיפולים, סרום לטיפול – 1–1.5 מ״ל מבקבוקון של 5 מ״ל. בינתיים את הערכה ואת סדרת הטיפולים מציגים כעובדות נפרדות.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>פרוטוקולי המזמין/ה: לכל אזור (פנים, צוואר או דקולטה) עד 2 מ״ל סרום ועד 2 מ״ל מסכת ג׳ל; פעם ב-14 יום, סדרה של 4–6 טיפולים, ולאחר מכן תחזוקה פעם ב-2–3 חודשים. כמה טיפולים יש באריזה אחת — לא מופיע בפרוטוקולים.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>V-TECH SYSTEM</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>שלב 1 בפרוטוקול: להשאיר את השדה המופשט של המיקרו-תעלות (אחת מארבע השיטות שבקטלוג – מיקרונידלינג, מיקרונידלינג RF, BIOSPICULE™ 10%, לייזר CO₂) או להציג שם את MITOPEN כמכירה צולבת?</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>הפרוטוקול של המזמין/ה נקרא «V-TECH + MITOPEN»: את הסרום מחדירים באמצעות MITOPEN, מזופן או ציוד מתאים אחר. את MITOPEN מציגים כמכירה צולבת.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>V-TECH SYSTEM</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>הסיום: בקטלוג – «EXOCELL MASK או DERMA RECOVERY ומקדם הגנה», ובתווית הפרוטוקול באתר רק EXOCELL MASK + SPF. בדף מציגים שני צ׳יפים-קישורים. לבקש מעורך/ת העברית להוסיף את DERMA RECOVERY לתווית הזו?</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>פרוטוקול המזמין/ה: מומלצת EXOCELL MASK, בסיום DERMA RECOVERY CREAM, הגנה מהשמש היא חובה. מציגים את שני הצ׳יפים.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>V-TECH SYSTEM</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>צילומים 79 (הבקבוקון בתקריב), 80 (דופן הקופסה) ו-82 (השקית) מופיעים ב-Figma כתמונות ממוזערות בקולאז׳. אפשר לקבל את המקורות שלהם בגודל מלא, כדי לפענח את הכיתובים? הצד האחורי של השקית לא מופיע בצילומים – האם יש צילום כזה? שורות קטנות בלתי קריאות משרטטים כקווים אפורים דקים.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>EXO-NAD</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>הפקשוט exo-nad.webp הוא, כנראה, רנדר. בתמונות שלכם בקבוק הפילינג עם תווית אחרת: ב-28, 31 ו-35 – מונוגרמה VM, «EXO-NAD PEELING» ושורות קטנות בכמה שפות, ועל התושבת (תמונה 29) הוא גם מסומן «EXO-NAD PEELING». בפקשוט – «EXO-NAD / SKIN LONGEVITY PEELING». על מכסה הקופסה (תמונה 32) מתחת ל-«SKIN LONGEVITY PEELING» יש גוש של טקסט קטן שאינו מופיע בפקשוט. לפי איזו גרסה לבנות? את תמונה 64 עם הכיתוב «SKIN LONGEVITY PILING» לא לוקחים.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>EXO-NAD</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>לתקריבים נדרשים צילומי סטודיו: בקבוק הפילינג, pH Normalizer ו-Longevity Serum – מלפנים וב-3/4, לפחות 1500 px בגובה; הקופסה – דפנות, חלק עליון, גב ועומק. כל עוד אין אותם, הכלים על המסך אינם גדולים מהמקור (בקבוק ≈210 px, בקבוקונים ≈140 px), והקופסה מסתובבת לא יותר מ-10°.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>EXO-NAD</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>לכמה טיפולים מיועדת קופסה אחת (15 מ״ל פילינג, 5 + 5 בקבוקונים של 5 מ״ל)? בקטלוג אין את המידע הזה, ולכן במסך הרכישה לא כותבים מספר.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>פרוטוקולי המזמין/ה: הערכה מספיקה לעד 15 טיפולים, בהתאם לכמות השימוש.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>EXO-NAD</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>מסך 4: להשאיר את מעטה השמפניה המופשט (ללא פנים) או להציב פריים של פנים, כמו ב-MASK? לפנים נדרש צילום מאושר; תמונה 30 – עם אדם, רק בהסכמתכם.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>EXO-NAD</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>סיום הפרוטוקול: בסטוריבורד «EXOCELL MASK + SPF», בקטלוג «EXOCELL MASK או DERMA RECOVERY CREAM ומקדם הגנה». איזו גרסה נכונה? אם זו של הקטלוג – נוסיף קישור שני, ל-DERMA RECOVERY CREAM. את שקית ה-MASK לא מציגים כאובייקט (טורקיז של סדרה אחרת) – מסכימים?</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>EXO-NAD</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>פרטי קשר למסך הרכישה: מספר WhatsApp, טלפון ודוא״ל. תג הסדרה: «PEELING» באותיות לטיניות, כמו BIOSPICULE, או בעברית, כמו «מכשור» בדף הבית?</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>כמו ב-mitoderm.com (המזמין/ה 11/10): כפתור WhatsApp +972-54-762-1889, טלפון 054-326-2182, דוא״ל info@mitoderm.com (Mitoderm@gmail.com — לאירועים בלבד). את זמן החזרה הטלפונית לא מציינים.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>EXOCELL MASK</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>בפריימים המאושרים (03-mirror, הערכה) – הקופסה הכהה «Your Second Skin», ואותה משאירים. אם במכירה כבר נמצאת הבהירה (sources/exocell-box-v2-front.png, אין תמונה של הדופן שלה), אמרו לנו: טקסטורת החזית תוחלף ותתווסף השורה «Total 125 ml». שורת ה-Net זהה בשתי הקופסאות.</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>EXOCELL MASK</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>שלחו בבקשה צילום של גב השקית: ההדפס שלו אינו ידוע. בינתיים הגב טורקיז חלק, ללא כיתובים.</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>EXOCELL MASK</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>לקופסה נדרשים צילומים של הדופן הימנית, החלק העליון, הגב ושל הקופסה הפתוחה (איך היא נפתחת, הדש מבפנים, התושבת). כל עוד אין אותם, הפאות האלה טורקיז חלק ללא הדפס, הקופסה מסובבת כך שרואים רק את החזית ואת הדופן השמאלית, והפתיחה במסך 2 משוערת. זה מתאים?</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>EXOCELL MASK</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>במסך 7 אין את השורות המאומתות b6.label1–2 («הדרכה ופרוטוקולים», «היבואנית…»). משאירים את מסך הרכישה בלעדיהן (מה בפנים, כפתור אחד, פרטי קשר) או מחזירים אותן כשורה קטנה מתחת לפרטי הקשר?</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>כמו ב-mitoderm.com (המזמין/ה 11/10): כפתור WhatsApp +972-54-762-1889, טלפון 054-326-2182, דוא״ל info@mitoderm.com (Mitoderm@gmail.com — לאירועים בלבד). את זמן החזרה הטלפונית לא מציינים.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>EXOCELL MASK</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>את שכבות המסכה מניחים בזו אחר זו (כך בטקסטים של הדוגמה s5.double ו-kit.double) או יחד, «2 ב-1»? אם בזו אחר זו – איזו שכבה מונחת על העור ראשונה, הלבנה או התכלת, והאם לכתוב זאת בשלב 01 של הפרוטוקול? בלי אישורכם את הטקסטים לא משנים.</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>המזמין/ה 11/10: המסכה דו-רכיבית, «2 ב-1»; את הטקסטים s5.double ו-kit.double לא משנים. את המסכה מסירים אנשי מקצוע בקליניקה, והמטופל/ת יכול/ה להשתמש בה לאחר הטיפול.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>EXOCELL MASK</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>בקטלוג אין זמן חשיפה למסכה, ולכן השלב «ספיגה» במסך 6 מופיע בלי זמן. אם בדף הטכני של VM יש זמן – להוסיף?</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>פרוטוקולי המזמין/ה: להשאיר את המסכה עד 30 דקות, ולאחר מכן להסיר אותה ולהחדיר את שארית הסרום לעור בטפיחות.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>EXOCELL MASK</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>כפתור ה-WhatsApp הראשי מוביל למספר 054-762-1889, ובמסך 7 מופיע הטלפון 054-326-2182 (שניהם מתוך site/proto/exocell-he-ui.json). כך זה מתוכנן?</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>כמו ב-mitoderm.com (המזמין/ה 11/10): כפתור WhatsApp +972-54-762-1889, טלפון 054-326-2182, דוא״ל info@mitoderm.com (Mitoderm@gmail.com — לאירועים בלבד). את זמן החזרה הטלפונית לא מציינים.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL HAIR</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>נדרשים צילומים של הקופסה: החזית בלי האמפולות (מה מודפס בפינה הימנית התחתונה), הדפנות, הצד האחורי, העומק, וכן הקופסה פתוחה עם המגש הפנימי. עד אז בעלילה לא פותחים את הקופסה, מסובבים אותה לא יותר מ-8°, והפינה הימנית התחתונה תמיד מוסתרת על ידי האמפולות או נמצאת בצל.</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL HAIR</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>נדרש צילום סטודיו של אמפולה אחת מלפנים ומאחור ברזולוציה גבוהה. בפקשוט האמפולה ברוחב של כ-70 px. ליד הכיתוב הגדול 'EXOSIGNAL' נראות שורות קטנות ('EXOSIGNAL HAIR', 'Siero nutriente per il cuoio capelluto' ואחרות), ודרך הזכוכית נשקף בתמונת ראי ההדפס שבצד האחורי. בלי צילום כזה התקריבים במסכים 2–5 ייראו גסים, וסיבוב האמפולה מוגבל ל-±30°.</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL HAIR</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>האם האמפולה נפתחת בשבירת הצוואר לאורך הטבעת הלבנה? על זה בנוי המעבר 2→3. אם היא נפתחת אחרת, נבנה את המעבר מחדש.</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL HAIR</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>בתמונה הנוזל באמפולה חסר צבע. נא לאשר: מזה נגזר שאין בדף טיפה צבעונית.</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL HAIR</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>נא לשלוח פקשוט סטודיו של בקבוק EXOSIGNAL SPRAY על רקע שקוף. כרגע יש רק תמונה ביד. בתמונה 400×300 לא משתמשים: מופיע בה בקבוק לבן אטום, ולא האמיתי.</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL HAIR</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>את תג הסדרה כותבים באותיות לטיניות, «HAIR», כמו V-TECH FACE אצל MASK? ואיך נקראת הסדרה בעברית (אצל MASK זה «התחדשות הפנים», שנלקח מ-products.ts של האתר ב-Make)? לא ממציאים בעצמנו: ניקח מ-products.ts או מהתשובה שלכם.</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL HAIR</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>מסך 4 בנוי בלי אנשים: במקום תמונה – ארבע קווצות זהב. האם נדרש, כמו אצל MASK, מסגרת-תמונה עם אדם – למשל, מריחת המוצר על השביל בשיער בקליניקה? אם כן, נדרש פריים מאושר.</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL SPRAY</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>אין פקשוט סטודיו של EXOSIGNAL SPRAY. site/img/exosignal-spray.png (400×300) – רנדר או מוקאפ ישן: הבקבוק בו לבן ואטום וללא בלוק הכיתובים של בקבוק המט האמיתי, ובצילום ביד אין קופסה. בגיליון Photo slots ב-Excel מסומן הצילום האמיתי שלכם (קופסה + בקבוק מט). שלחו אותו בצ׳אט או העלו אותו ל-Drive /products. אם אפשר, הוסיפו את הדופן והחלק העליון של הקופסה ואת הצד האחורי של הבקבוק.</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL SPRAY</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>איך נראה המרסס שמתחת למכסה? נדרש צילום של הבקבוק ללא המכסה, מהצד ומלפנים; צילום בטלפון על רקע ניטרלי יספיק. כל עוד אין צילום כזה, את המכסה לא מסירים, הערפל נכנס לפריים מעבר לקצה, ואת הפיה לא מציגים.</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL SPRAY</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>למסך 4 «Feel it» נדרש פריים מלמעלה על שביל השיער, שבו הטיפות נספגות. האם יש לכם צילום כזה? אם לא, ניצור אותו לפי הפרומפט המוכן מתוך site/prompts/exosignal-spray.md: קודם דוגמה אחת, ואת המחיר והיתרה נציג לפני ההפעלה.</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL SPRAY</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>את הצילום של הבקבוק ביד (עם אדם: נשמר באופן פרטי, לא במאגר הקוד) (הבקבוק ליד הלחי, הפנים נראות) לא מציבים בעמוד, ומשתמשים בו רק כמקור לתווית. אבל זהו צילום עם אדם, והוא כבר נמצא במאגר הקוד הציבורי, אף שלפי כללי הפרויקט אין לתמונות כאלה מקום שם. להסיר אותו מהמאגר ולשמור עותק רק באופן מקומי?</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL SPRAY</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>הכפתור הראשי «איפה לקנות»: במקורות אין רשימה של קליניקות שותפות. בינתיים הוא מוביל ל-WhatsApp עם הטקסט «שלום, אשמח לקבל פרטים על EXOSIGNAL SPRAY», ו-«התייעצו עם מומחה» פותח טופס בקשה לשיחה חוזרת, כמו ב-MASK. האם זה מתאים? האם תהיה רשימת קליניקות שאליה אפשר יהיה להעביר את הכפתור בהמשך?</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>את טבלת אנשי המקצוע המזמין/ה ישלח/תשלח בהמשך (11/10). עד אז הכפתור מוביל לטופס הפנייה, וללא JS — ל-WhatsApp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL SPRAY</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>כמה לחיצות נדרשות ליישום אחד, ולכמה זמן מספיקים 15 מ״ל? בקטלוג אין את המידע הזה, ולכן בעמוד כותבים רק «15 מ״ל, מדי יום, ללא שטיפה», ובסצנת הפרוטוקול העננים מופיעים ללא ספירה.</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>mitoderm.com: פעם ביום על קרקפת נקייה ויבשה, לנער, לרסס בשורשי השיער, לעסות קלות; עדיף בערב, משך הטיפול חודשיים. מספר הלחיצות לא מצוין שם.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL SPRAY</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>האם יש הרכב של הספריי (INCI או רכיבים פעילים)? בקטלוג יש רק «מה הספריי עושה», ולכן בכרטיס כותרת המשנה היא «מה הספריי עושה», ולא «רכיבים פעילים».</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>מופיע ב-mitoderm.com: אקסוזומים סינתטיים, PDRN במשקל מולקולרי נמוך, פנתנול, ביוטין, 8 סוגי פפטידים ביומימטיים; בקבוקון 15 מ״ל (גיליון mitoderm.com).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL SPRAY</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>איך נקראת סדרת HAIR בעברית, עבור התג? ב-MASK מופיע הצמד «V-TECH FACE · התחדשות הפנים», ולספריי נדרש צמד דומה «HAIR · …».</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL SPRAY</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>האם אתם מסכימים להציג את הפקשוט של EXOSIGNAL HAIR במסכים 2 ו-5 כסימן הסדרה וכקישור לעמוד שלו? או להשאיר בעמוד רק את האריזה של הספריי?</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>EXOSIGNAL SPRAY</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>בקובץ הפרומפטים הישן העמוד של הספריי היה «כסף על שחור» (#d9d4cc). לפי כלל הסדרות, HAIR – שחור עם זהב, והכסף שייך למכשירים. האם אתם מאשרים את הזהב?</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>EXOTECH GEL</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>איך נפתח הכדור? המכסה – חצי הכדור העליון עם הכיתוב כולו 'EXOTECH / GEL', התפר – קו המשווה מתחת ל-'GEL'. הוא נפתח בהברגה או פשוט מורם? נדרשים צילומים של הצנצנת הפתוחה מלמעלה ובזווית שלושה רבעים, וצילום של המכסה מלמטה. בינתיים המכסה מתרומם ישר למעלה בכמה מילימטרים, הסדק מכוסה בזוהר, והפנים אינם נראים. תשובת המזמין/ה (18/10): נפתח בהברגה – הכדור הזהוב מתחלק לשני חצאים.</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>EXOTECH GEL</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>באיזה צבע הג׳ל ועד כמה הוא שקוף? נדרש צילום של הג׳ל בצנצנת פתוחה או על האצבע. בינתיים הטיפות והשכבה הדקה שקופות בגוון ניטרלי, עם ברקים חמים. תשובת המזמין/ה (18/10): לבן כמו קרם.</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>EXOTECH GEL</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>האם יש צילומי מקור של הקובייה והכדור ברזולוציה גבוהה (מ-2000 px בצלע הארוכה)? בפקשוט הכדור רק כ-390 px, והכיתובים שורטטו לווקטור לפיו. ומה מודפס על הגב, הדופן הימנית והתחתית של הקובייה ועל הצד האחורי של הכדור? הנפח 30 ml אינו נראה בצדדים הנראים, וכרגע הוא נלקח מהקטלוג. עד לצילומים האלה הכדור בפריים אינו גדול מ-~420 CSS px, והסיבוב מוגבל ל-±8°.</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>EXOTECH GEL</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>לאן מוביל «איפה לקנות»? רשימה או דף של קליניקות שותפות אין במקורות, ולכן כרגע כל כפתורי «איפה לקנות» פותחים את ה-WhatsApp של MITODERM עם טקסט מוכן (שורה חדשה להגהה). משאירים «איפה לקנות», כמו בטקסט המאושר של האתר (בקטלוג מופיע «היכן לרכוש»)? והאם לקליניקות נדרש מתחת לפרטי הקשר קישור טקסט «לקבלת פרטים על מחירים», כמו ב-MASK?</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>את טבלת אנשי המקצוע המזמין/ה ישלח/תשלח בהמשך (11/10). עד אז הכפתור מוביל לטופס הפנייה, וללא JS — ל-WhatsApp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>EXOTECH GEL</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>במסך 4 אין אנשים: שכבת הג׳ל עפה אל הצופה ומתמוססת. האם נדרש פריים עם אדם, כמו ב-MASK, למשל קצה אצבע עם ג׳ל ליד הלחי? זו ג׳נרציה בתשלום: קודם מחיר ויתרה, דוגמה אחת, אחר כך «מאשר/ת», ורק אחרי התשובה לשאלה 2 על צבע הג׳ל.</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>EXOTECH GEL</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>V-TECH FACE ו-«סדרת האקסוזומים הסינתטיים» – סדרה אחת או רמות שונות (סדרה וטכנולוגיה)? כרגע במסכים 1 ו-7 הם מופיעים כרכיב אחד: «V-TECH FACE», ומתחתיו כיתוב קטן «סדרת האקסוזומים הסינתטיים». איזה שם הוא העיקרי עבור המבקרים באתר?</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>MICRO BOOST 10%</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>שלחו בבקשה צילומים של המזרק של MICRO BOOST 10%: מלפנים ומהצד על רקע ניטרלי, עם המכסה ובלעדיו, וגם טיפת סרום אחת על הקצה. האם יש על המזרק מחט או פיה? אנחנו מציגים אותו ללא מחט: לפי הקטלוג, את הסרום מעסים לתוך העור. האם יש על המזרק הדפס או סקאלה? מה האורך עם המכסה ומה קוטר הגוף במ״מ? מה הצבע של הסרום ועד כמה הוא שקוף? בינתיים המזרק שקוף, ללא כיתובים, וקנה המידה משוער.</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>MICRO BOOST 10%</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>נדרשים צילומים של הקופסה מכל הצדדים (הדפנות, הגב, החלק העליון, התחתית) והמידות שלה רוחב×גובה×עומק. כל עוד אין אותם, הקופסה מסתובבת רק בגבולות זווית הפקשוט ואינה מסתובבת לשלושה רבעים, כדי שפאה ריקה לא תיכנס לפריים.</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>MICRO BOOST 10%</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>המסך «הרגישו»: האם פריים כזה מאושר? המטופלת מביטה במצלמה כמו במראה, ידיים של קוסמטיקאי/ת בכפפות מעסות את הסרום על הלחי, אחרי האצבעות ניצוצות זהב, בלי «לפני ואחרי». זהו פריים מג׳ונרט אחד: את המחיר ואת היתרה נציג לפני הג׳נרציה, וההפעלה רק אחרי «מאשר/ת». פריים עם אדם לא ייכנס למאגר.</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>MICRO BOOST 10%</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>להציג במסך הפרוטוקול קופסה קטנה של DERMA RECOVERY CREAM ליד התווית «+ DERMA RECOVERY בבית»? את V-TECH, את Longevity Serum (הבקבוקון בטורקיז מתוך הערכה EXO-NAD) ואת EXOCELL MASK לא מציגים ב-3D: אלה סדרות אחרות, ו-design-rules אוסרים לערבב בעמוד אחד צבעים של שתי סדרות. מסכימים?</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>MICRO BOOST 10%</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>ב-b5.line כתוב «3 ml ℮ 0.10 fl. oz.» עם רווח, ועל הקופסה «fl.oz.». להתאים את השורה להדפס (באמצעות עורך/ת העברית)?</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CELL RENEW 1.5%</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>שלחו בבקשה תמונות של בקבוק CELL RENEW 1.5% מלפנים, מהצד ומלמעלה. האם זה אותו בקבוק airless לבן עם משאבה כמו של CELLULAR AGE DEFENSE 2.5%, או בקבוק אחר? אם הסרום אינו שקוף, שלחו גם תמונה של המרקם שלו. בלי תמונה לא מציבים את הבקבוק ב-3D, ואת הטיפה מציירים חסרת צבע.</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CELL RENEW 1.5%</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>לקופסת CELL RENEW 1.5% נדרשים: צילום של החזית ברזולוציה גבוהה (מ-2000 px לגובה) או קובץ ההדפס, וגם צילומים של הדפנות, החלק העליון והגב. כל עוד אין אותם, לא מתקרבים להדפס בתקריב, הדפנות חלקות, הקופסה סגורה, והבקבוק, אחרי שתגיע תמונה, יעמוד לידה. אם הקופסה צריכה להיפתח, שלחו צילום של החלק העליון שלה או של הקופסה הפתוחה.</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CELL RENEW 1.5%</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>מה המידות של שלוש הקופסאות (ג×ר×ע, מ״מ): CELL RENEW 1.5%, DERMA RECOVERY CREAM, CELLULAR AGE DEFENSE 2.5%? מתאימה גם תמונה אחת של שלוש הקופסאות זו לצד זו. נדרשים גם צילומים של הדפנות של DERMA ושל CAD 2.5%. כל עוד אין מידות, DERMA עומדת חצי צעד עמוק יותר, כדי שהגבהים לא יושוו.</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CELL RENEW 1.5%</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>מסכים 2 ו-4 (המראה): משאירים מראה עגולה מופשטת ללא אנשים, או מציבים תמונה מאושרת של עור או של פנים ליד המראה, כמו הפריים עם המסכה ב-EXOCELL?</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CELL RENEW 1.5%</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>שלב 3 «הגנה»: האם ל-MITODERM יש קרם הגנה מהשמש משלה שאפשר להציג? אם לא, את השלב מציגים כפס של אור יום, ללא אריזה.</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CELL RENEW 1.5%</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>הכפתור «איפה לקנות» פועל בינתיים כמו בדגימה של MASK: פותח טופס פנייה, ובלי JS מוביל ל-WhatsApp. האם יש רשימה של קליניקות שותפות שאליה אפשר להעביר אותו כשתהיה מוכנה (למשל, בלוק אנשי המקצוע אחרי מסך הרכישה)?</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>את טבלת אנשי המקצוע המזמין/ה ישלח/תשלח בהמשך (11/10). עד אז הכפתור מוביל לטופס הפנייה, וללא JS — ל-WhatsApp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CELLULAR AGE DEFENSE 2.5%</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>הבקבוק: ב-Figma יש תמונה מס׳ 9 (בקבוק airless לבן, הצומת 93:8095), במאגר הקובץ אינו קיים. מודפס עליו 'CELL CELLULAR / AGE DEFENSE / 2.5%'. זו טעות דפוס בעיצוב, או שכך זה על הבקבוק האמיתי? שלחו בבקשה פקשוט של הבקבוק האמיתי על רקע שקוף. עד לתשובה העמוד נבנה עם הקופסה בלבד. אחר כך נוסיף את הבקבוק למסכים 4 (בתקריב רק ראש המשאבה) ו-7.</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CELLULAR AGE DEFENSE 2.5%</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>בקופסה יש רק בקבוק אחד של 30 מ״ל, בלי עלונים ובלי אביזרים? בזה תלויה השורה «מה בפנים» במסך הרכישה.</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CELLULAR AGE DEFENSE 2.5%</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>הדפנות והפאות העליונות של הקופסאות CELLULAR AGE DEFENSE 2.5%, CELL RENEW 1.5% ו-DERMA RECOVERY CREAM: נדרשות תמונות (מהן רואים גם את העומק האמיתי) או אישור שאין עליהן הדפס. עד אז שלוש הקופסאות מסתובבות לא יותר מ-±20°.</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CELLULAR AGE DEFENSE 2.5%</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>DERMA RECOVERY CREAM: במאגר יש שתי גרסאות של הקופסה – עם פס ירוק כהה (protocols/print/img) ועם פס מרווה (protocols/assets/img). איזו מהן נמכרת כעת? בינתיים מציבים את גרסת המרווה, כמו ב-packaging-text.json וב-design-rules.</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CELLULAR AGE DEFENSE 2.5%</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>מסך 4 «Feel it» – בחרו אפשרות. (א) פריים עם אדם: אצבעות ליד קו הלסת, תנועה מעגלית עדינה אחת, כמו הפריים המאושר עם פנים של MASK. זו ג׳נרציה בתשלום, את המחיר ואת היתרה אציין לפני ה«מאשר/ת» שלכם. (ב) משטח עור חם ומופשט בלי אדם, בלי ג׳נרציה. אם (א) – האם יש תמונת רפרנס?</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CELLULAR AGE DEFENSE 2.5%</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>את שלב 3 «הגנה» מציגים רק במעבר של האור לאור יום, בלי שפופרת של מוצר הגנה מהשמש (אין כזה בקטלוג MITODERM). זה מתאים?</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>CELLULAR AGE DEFENSE 2.5%</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>האם אתם מאשרים את מערך הכפתורים? «איפה לקנות» פותח את המסך «Ask your clinic» (החלטה 17). «לקליניקות: לקבלת הצעת מחיר» פותח את WhatsApp עם טקסט מוכן והקוד #CAD-HE-6. הפאנל הנעוץ בטלפון מופעל רק יחד עם המערך הזה.</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>את טבלת אנשי המקצוע המזמין/ה ישלח/תשלח בהמשך (11/10). עד אז הכפתור מוביל לטופס הפנייה, וללא JS — ל-WhatsApp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>CELLULAR AGE DEFENSE 2.5%</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>קופסת CELL RENEW 1.5% עומדת מדרגה אחת נמוך יותר במסך 2, ובמסך 5 יש כרטיס שלה עם קישור. אפשר להציג בעמוד הזה מוצר סמוך?</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>DERMA RECOVERY CREAM</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>הצנצנת. החזית של הצנצנת נמצאת אצלכם ב-Figma: תמונה 1 (צומת 93:8080), הצנצנת הפתוחה – תמונה 73 (צומת 113:8211). לפיהן בונים את הצנצנת ומסובבים אותה לא יותר מ-±20°. אם צריך לסובב את הצנצנת בחופשיות רבה יותר, שלחו בבקשה צילומים מאחור, מהצדדים ומלמעלה על המכסה. ועוד שאלה: האם הצנצנת מזכוכית או מפלסטיק?</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>DERMA RECOVERY CREAM</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>הקופסה. נדרשים צילומים של הדפנות, הדופן האחורית והחלק העליון (עם דש סגור ופתוח) או המידות רוחב×גובה×עומק במ״מ. בפקשוט הישן (הפס הכהה) הדפנות נקיות ולמעלה דש-לשונית. האם כך גם בקופסה החדשה?</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>DERMA RECOVERY CREAM</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>מסך 4 לפי הסטוריבורד – סצנה ליד המראה, אישה מורחת קרם. בקולאז׳ אין תמונה כזאת. האם יש לכם תמונה מאושרת משלכם, או ליצור דוגמה אחת ב-AI? את המחיר נציג לפני ההפעלה. כל עוד אין «אוקיי», מציבים גרסת 3D ללא אנשים.</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>DERMA RECOVERY CREAM</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>מסך 5: CELL RENEW 1.5% ו-CELLULAR AGE DEFENSE 2.5% מוצגים כ«או» (מתחלפים זה בזה), MICRO BOOST 10% – כענף קליני נפרד עם התג «מקצועי». V-TECH ו-EXO-NAD – רק כטקסט, כדי לא לערבב את צבעי הסדרות. מסכימים?</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>DERMA RECOVERY CREAM</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>הכפתור הראשי «איפה לקנות» מוביל לבלוק של אנשי המקצוע והקליניקות (מסך 8). הכפתור «לקליניקות: בקשת הצעת מחיר» פותח את טופס הפנייה, שבו השדה «מקצוע» מפריד את הקליניקות. האם זה נכון?</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>את טבלת אנשי המקצוע המזמין/ה ישלח/תשלח בהמשך (11/10). עד אז הכפתור מוביל לטופס הפנייה, וללא JS — ל-WhatsApp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>DERMA RECOVERY CREAM</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>תג הייעוד לכל האתר: «טיפוח ביתי» (design-rules, הדגם של MASK, ה-eyebrow של סרומי BIOSPICULE) או «טיפול ביתי» (מילון המונחים, home.sl-3)? בינתיים מציבים «טיפוח ביתי».</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>DERMA RECOVERY CREAM</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>להגהה: ב-b5.line הנפח כתוב «1.69 fl. oz.» (EN) ו-«1.69 fl. oz» (HE), ואילו על האריזה וב-cat.kit – «50 ml ℮ 1.69 fl.oz.». להתאים את b5.line להדפס?</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>MITOPEN</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>האם ל-MITOPEN יש קופסה או נרתיק, ומה יש בהם מלבד העט: מחסניות, מטען או כבל, מעמד? בקטלוג ובפקשוט מופיע רק «1× MITOPEN», ולכן במסך הרכישה מציגים בינתיים עט אחד. אם יש קופסה, נדרשות תמונות שלה מכל הצדדים.</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>MITOPEN</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>במה נקבע עומק המחט ב-MITOPEN: בטבעת בזהב ורוד, בחרטום או במחסנית? במה מחליפים את 5 המהירויות – בכפתור? מה פירוש הנקודה שמעל הכפתור? בסטוריבורד יש הרמז «סובבו את הטבעת» ו«הגלילה מסובבת את הטבעת», אבל על האריזה הטבעת מתוארת כטבעת אחיזה. כל עוד אין תשובה, על הטבעת רק עובר ברק אור, הסקאלות זזות בעקבות הגלילה, והרמז – «גללו».</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>MITOPEN</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>אם תמונות MITOPEN מס׳ 56 ו-57 ב-Figma יתבררו כקטנות מ-2500 px בגובה או ללא תקריב של המחסנית: האם תוכלו לשלוח פקשוט ברזולוציה גבוהה ותמונת מאקרו של המחסנית עם המחטים בעומק המינימלי ובעומק המקסימלי? בלי זה אין מאקרו במסך 3, ואת המחטים לא מציגים.</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>MITOPEN</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>תמונה למסך 4 (מטפלת בכפפות מעבירה את MITOPEN על לחי המטופלת): יש צילום משלכם, או שניצור תמונה ב-AI לפי הפקשוט? העט בתמונה צריך להיות באותה זווית כמו בפקשוט. יצירת התמונה ב-AI כרוכה בתשלום: קודם דוגמה אחת, מחיר ו«מאשר/ת».</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>MITOPEN</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>בקטלוג הטווח כתוב עם מקף («0.25-2.5»), ובסטוריבורד עם קו מפריד («0.25–2.5»). את סדר המספרים באתר אנחנו מיישרים בבידוד LTR, אבל הסימן עצמו נשאר שונה. להאחיד את הקטלוג לקו המפריד, כמו בסטוריבורד?</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>MITOSCAN</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>זה חוסם את מסכים 3–5. האם יש צילומים אמיתיים מהמסך של MITOSCAN – אותו אזור בקרקפת בהגדלה ×50 וב-×200 – וצמד «לפני / אחרי» של האזור הזה לאורך סדרת הטיפולים, בהסכמת המטופל/ת להצגה באתר? אסור לייצר בג׳נרציה «צילום של המכשיר». כל עוד אין תשובה, את מסכים 3–5 ב-Figma לא בונים על ממלאי מקום. אם לא יהיו צילומים, מציבים את אפשרות הגיבוי: טיפוגרפיה גדולה ×50 → ×200 לפני המסך עם הלוגו, «מראה» עם הלוגו ושלושה שלבים בלי «לפני / אחרי».</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>MITOSCAN</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>נדרשים צילומים של הסורק (הקצה עם העדשה, הצד, הצד האחורי) וצילום של הטאבלט בלי הסורק (המחזיק הריק, המעמד בשלמותו). בלעדיהם כל העלילה מתנהלת בתנועת מצלמה על פני פקשוט שלם אחד: הסורק אינו יוצא מהמחזיק, והמערכת אינה מתפרקת לחלקים.</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>MITOSCAN</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>מהו הגליל הכסוף עם הרשת בקצה? בקטלוג התמונות הוא נקרא מעמד-גליל, ובתיאור האריזה – בסיס. האם הוא מחובר בכבל לסורק? עד שתאשרו, באתר הוא נשאר בלי שם, בלי תפקיד ובלי קווי הפניה.</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>MITOSCAN</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>בקטלוג כתוב «1× MITOSCAN». האם כל שלושת הפריטים מהפקשוט כלולים בערכה: הטאבלט על המעמד, הסורק עם הכבל הספירלי והגליל? אם כן, נוסיף כיתובים לחלקים במסכים 6–7, ולשם כך נדרשות שלוש שורות חדשות קצרות.</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>MITOSCAN</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>פריים הצילום למסך 4 (המטפל/ת עם הסורק ליד שביל השיער של המטופל/ת): מצלמים בקליניקה או מייצרים בג׳נרציה, אחרי שנציג את המחיר ונקבל את ה«מאשר/ת» שלכם? בג׳נרציה מסך המכשיר בפריים מופנה הרחק מהמצלמה או מציג רק את הלוגו. אם לא זה ולא זה, מציבים את האפשרות «מראה» בלי אנשים.</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>MITOSCAN</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>הבלוק «מי מבצע/ת את הטיפול» אחרי מסך הרכישה: מציגים את כל אנשי המקצוע עם התווית קרקפת או רק את אלה שכבר יש להם MITOSCAN?</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Home — MITODERM</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>סימון המפתחות: «slug:מפתח» – מפתח של דף אחר ב-storyboard.he.json; «slug:cat.שדה» – אותו דף ב-product-pages.he.json (האינדקס זהה לזה שב-product-pages.json); «catalog.chips[i]» – הפריט ה-i בשורה «Chips HE» בגיליון Catalog (0 הכל … 2 פילינג, 4 שיער, 5 ביו-ספיקולות, 6 טיפוח ביתי, 7 מכשור); «#n» – המקטע ה-n בשורה המחולקת ב-« · »; «A + « – » + B» – חיבור של שורות מאומתות לשורה אחת (שורת הטקסט של מסך 5, המקרא של מסך 7); «new:» – שורה מתוך new_strings. האם כלי הבנייה יקבל שיטת הפניה כזו?</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Home — MITODERM</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>סדר הסדרות: ההצעה היא V-TECH FACE → PEELING → BIOSPICULE → DEVICES → HAIR. כך צבע הסביבה מתחלף בכל שלב, והמכשירים באים מיד לפני HAIR, שבה הם שלבים 1–2 של הפרוטוקול. להשאיר כך, או לקחת את הסדר מטבלת הפלטה (V-TECH FACE, HAIR, PEELING, BIOSPICULE, DEVICES)?</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Home — MITODERM</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>הכיתובים של הסדרות ב-dock ובתגים: כרגע אלה השמות בעברית של המסננים בקטלוג (פילינג, ביו-ספיקולות, מכשור, שיער), ועוד שם המותג הלטיני V-TECH FACE. או שבכל מקום ישמשו שמות המותג הלטיניים של הסדרות (V-TECH FACE · PEELING · BIOSPICULE · DEVICES · HAIR), כמו התג בדף MASK?</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Home — MITODERM</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>תג הטיפוח הביתי: בכללי הפלטה, במסנני הקטלוג וב-eyebrow של המוצרים – «טיפוח ביתי», ואילו ב-home.sl-3 המאומת, לפי מילון המונחים, כתוב «טיפול ביתי». איזו מילה להשאיר בדף הבית?</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Home — MITODERM</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>MITOTECH CELL BOOSTER: לאיזו סדרה הוא שייך? ב-Figma של דף הבית הוא בשורת המכשירים, ואילו בגיליון Catalog (Card 13) – PRO, מסנן [Exosomes], סדרה «לברר». האם יש צילום של האריזה (שני בקבוקונים) ומה הנפח שלהם? בינתיים הוא מוצג רק ככרטיס «חדש · בקרוב» ללא 3D.</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>בפרוטוקולים של המזמין/ה: שני בקבוקונים — בוסטר ותרכיז אבקה, לערבב עד לקבלת תמיסה שקופה, עד 2 מ״ל לפנים, לצוואר ולדקולטה. הסדרה לא מצוינת שם.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Home — MITODERM</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>נדרשים צילומים: פקשוט סטודיו של EXOSIGNAL SPRAY – הבקבוק והקופסה, בלי יד. עד שיהיה פקשוט כזה, בדף הבית אין בקבוק ואין ערפל, רק קופסה קטנה בעומק. לתקריב – אמפולה אחת של EXOSIGNAL HAIR על רקע שקוף. אופציונלי: צילום גדול יותר של Biphasic Peel וצילומים של הפאות הצדדיות של הקופסאות V-TECH SYSTEM, EXOSIGNAL HAIR, EXO-NAD ו-BIOSPICULE – בלעדיהן הדפנות יהיו בצבע אחיד ללא הדפס.</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Home — MITODERM</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>פרטי הקשר במסך 7 (מספר WhatsApp, טלפון, דוא״ל): לוקחים את אותם פרטים כמו בדוגמה המאושרת של EXOCELL MASK?</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>כמו ב-mitoderm.com (המזמין/ה 11/10): כפתור WhatsApp +972-54-762-1889, טלפון 054-326-2182, דוא״ל info@mitoderm.com (Mitoderm@gmail.com — לאירועים בלבד). את זמן החזרה הטלפונית לא מציינים.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Home — MITODERM</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>מסך ה-hero: (א) להציג את כל 12 האריזות בבת אחת, או גם בדסקטופ אריזה עיקרית אחת לכל סדרה, ואת האחרות – בריחוף? (ב) הכפתור home.b2 «מוצרים מקצועיים» מוביל לקטלוג, אבל מסנן «מקצועי» אין בקטלוג: לפתוח על «הכל» או להוסיף מסנן כזה? (ג) המספר «4 עקרונות ליבה» הוסר משורת האמון, כי העקרונות עצמם מפורטים רק בדף About. מסכימים?</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>חמש סדרות בארבעה מסכים: V-TECH FACE ו-HAIR מוצגות באותו מסך, כי לשתיהן שחור עם זהב ושתיהן אקסוזומים סינתטיים של VM. להשאיר כך, או לתת ל-HAIR מסך משלה ולאחד את ה-hero עם מדף הקטגוריות?</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>MITOTECH CELL BOOSTER: הסדרה לא אושרה, ואין פקשוט ואין טקסט אריזה. כרגע הוא מוצג במסך המכשירים ככרטיס «בקרוב» בלי 3D, כמו בדף הבית, ונראה רק כשנבחר הצ׳יפ «All»; בגיליון Catalog הוא מסומן במסנן Exosomes. לאיזו סדרה ולאילו צ׳יפים לשייך אותו? ל-3D נדרש פקשוט של שני הבקבוקונים.</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>בפרוטוקולים של המזמין/ה: שני בקבוקונים — בוסטר ותרכיז אבקה, לערבב עד לקבלת תמיסה שקופה, עד 2 מ״ל לפנים, לצוואר ולדקולטה. הסדרה לא מצוינת שם.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>טיפול ביתי: בגיליון Catalog וב-design-rules מופיע «טיפוח ביתי», ובדף הבית (home.sl-3) ובמילון המונחים – «טיפול ביתי». בקטלוג התג והצ׳יפ נלקחים מאותו מפתח catalog.chips[6], כך שתשובה אחת תשנה את שניהם. באיזו מילה משתמשים בכל האתר?</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>הכפתור הראשי של הקטלוג – «לקבלת פרטים על מחירים», כמו בעמודי המוצרים; כשנבחר הצ׳יפ Home care, במקומו מופיע «איפה לקנות». בגיליון Catalog ובדף הבית מופיע «Contact us / צרו קשר». לתקן את הגיליון לפי כפתור המחיר או להשאיר «צרו קשר»?</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>את טבלת אנשי המקצוע המזמין/ה ישלח/תשלח בהמשך (11/10). עד אז הכפתור מוביל לטופס הפנייה, וללא JS — ל-WhatsApp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>תגי הסדרות עוצבו כמו בדף הבית: V-TECH FACE באותיות לטיניות, והשאר – במילים של הצ׳יפים (פילינג, שיער, ביו-ספיקולות, מכשור). זה מתאים, או לכתוב את PEELING, HAIR ו-BIOSPICULE™ באותיות לטיניות, כמו בגיליון Catalog?</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>הצ׳יפ «Masks»: בקטלוג העשן נשאר בשחור עם הזהב של V-TECH FACE, והטורקיז של EXOCELL מופיע רק כטיפה מתחת לקופסה; הסביבה בטורקיז-כחול של MASK נשארת בעמוד המוצר שלה. מסכימים?</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>ההדפס על הדפנות ידוע רק אצל EXOCELL MASK ו-EXOTECH GEL, ולכן רק הן מוצבות במבט 3/4. שאר הקופסאות עומדות כמעט בחזית מלאה (עד 12°) ומסתובבות רק אל החזית. תוכלו לשלוח צילומים של הדפנות, כדי להציב גם אותן במבט 3/4?</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>פרטי הקשר במסך 7 (WhatsApp, טלפון, e-mail) – אותם פרטים כמו בדגם של EXOCELL MASK?</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>כמו ב-mitoderm.com (המזמין/ה 11/10): כפתור WhatsApp +972-54-762-1889, טלפון 054-326-2182, דוא״ל info@mitoderm.com (Mitoderm@gmail.com — לאירועים בלבד). את זמן החזרה הטלפונית לא מציינים.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>טכני, עבור כלי הבנייה של ה-Excel: site/tools/story3d_xlsx.py כבר מבין cat[slug].…, sb[slug].…, b6.cta[i] (ספירה מאפס) ו-home:מפתח. אבל את האינדקס בתוך מחרוזת חדשה הוא אינו מזהה: catalog.chips[i] יוצא כ-«⚠ חסר מפתח» (וכך גם בדף הבית). יש להשלים: לתמוך ב-[i] עבור מחרוזות חדשות ולחפש catalog.* מכל עמוד.</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/mitoderm-catalog/site/MITODERM-3D-story.xlsx
+++ b/mitoderm-catalog/site/MITODERM-3D-story.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -477,7 +477,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>סטטוס נכון ל-18/10, ערב</t>
+          <t>סטטוס נכון ל-23/10</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>מוכן, עודכן ב-17/10</t>
+          <t>הושלם; מפת הדרכים עודכנה ב-23/10</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>נבנה מחדש ב-17/10, ממתין ל«אוקיי»</t>
+          <t>19–21/10: בטלפון התנועה חלקה והחדות מלאה, כל התמונות ב-HD; העמוד פורסם ונמצא ב-site/public; ממתין ל«אוקיי»</t>
         </is>
       </c>
     </row>
@@ -543,22 +543,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>V-TECH ב-HD ‏(Blender Cycles): הקופסה נפתחת כמו בצילומים – העטיפה המוזהבת עולה, הקופסה השחורה נפתחת, 5 אמפולות ו-5 שקיות; רדיד סאטן בלי צללים כבדים; תאי אקסוזום, מולקולות PDRN וסליל DNA; תנועה גם בטלפון</t>
+          <t>‏V-TECH ב-HD ‏(‏Blender Cycles‏)‏: הקופסה נפתחת כמו בצילומים – העטיפה המוזהבת עולה, הקופסה השחורה נפתחת, 5 אמפולות ו-5 שקיות; רדיד סאטן בלי צללים כבדים; תאי אקסוזום, מולקולות PDRN וסליל DNA; תנועה גם בטלפון</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>הדוגמה מוכנה; רינדור סופי על ה-Mac כ-3–4 שעות</t>
+          <t>הפריימים ברוחב 2400 מוכנים; רמת 3840 — רינדור על ה-Mac</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>תיקונים לדוגמה, «אוקיי», הרצת הרינדור על ה-Mac</t>
+          <t>תיקונים לעמוד; לא חובה: הרצת render_mac.sh על ה-Mac לרמת 3840</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>הדוגמה פורסמה ב-17/10; ב-18/10 נוספו מולקולות PDRN וסליל DNA; ממתינה לתיקונים</t>
+          <t>21/10: ‏200 פריימים ברוחב 2400 פיקסלים עברו רינדור בענן, והעמוד ב-HD פורסם (עבר את כל 55 הבדיקות); פריים ניסיון ברוחב 3840 נראה חד יותר באופן ניכר במסך ה-MacBook</t>
         </is>
       </c>
     </row>
@@ -570,22 +570,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Figma למתכנת: כל העמודים לפי ההחלטות האחרונות (טקסט מימין, 3D משמאל, Rubik, בלוק «מה באריזה» אחד), עם מפרט: מנוע הפריימים, הנכסים, נקודות השבירה והתנועה בטלפון</t>
+          <t>‏Figma למתכנת: כל העמודים לפי ההחלטות האחרונות (טקסט מימין, 3D משמאל, Rubik, בלוק «מה באריזה» אחד), עם מפרט: מנוע הפריימים, הנכסים, נקודות השבירה והתנועה בטלפון</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>יום אחד</t>
+          <t>1 יום</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>«אוקיי» על V-TECH ועל MASK</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18/10: ב-Figma יש עמוד התחלה למתכנת, ועמודי V-TECH ו-MASK עודכנו; שאר העמודים — לפי התבנית; המתכנת בונה ב-React</t>
+          <t>18/10: ב-Figma יש עמוד התחלה למתכנת ועמודי V-TECH ו-MASK; מ-22/10 העמודים החיים (הקישורים ב-HANDOFF, התיקייה site/public‏)‏ והטקסטים ב-Excel הם מקור האמת לבנייה; המתכנת בונה ב-React</t>
         </is>
       </c>
     </row>
@@ -597,22 +597,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>פיילוט של השיטה המהירה על EXOTECH GEL: פריימים מרכזיים מ-Firefly (של המזמין/ה) ומעברים ב-Kling, שהופכים לפריימים לאתר באותו מנוע; השוואה ל-Blender באיכות, בזמן ובמחיר</t>
+          <t>בחירת השיטה לעמודי המוצרים: פיילוט על EXOTECH GEL — סצנה חיה ב-three.js מול פריימים מ-Firefly ומ-Kling ומול רינדור ב-Blender</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>יום אחד</t>
+          <t>1 יום</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>שישה פריימים מ-Firefly ‏(2400×1500, המוצר בחצי השמאלי ולפחות 10% מהשוליים, רקע שחור נקי, קו אור דק לאורך הקצוות של הפאות השחורות של הקופסה); אישור להוצאה לפני כל יצירה</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18/10: הכלי שהופך סרטוני Kling לפריימים לאתר מוכן ונבדק; טיוטת עמוד EXOTECH GEL על התבנית (תמונות זמניות מתמונת המוצר) ממתינה לבדיקה; ממתינים לשישה פריימים מ-Firefly</t>
+          <t>הושלם ב-19–21/10: עמוד EXOTECH GEL ב-three.js אושר כדוגמה; לא היה צורך ב-Firefly או ב-Kling, ולא היו הוצאות</t>
         </is>
       </c>
     </row>
@@ -624,61 +624,61 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>שאר עמודי המוצרים בשיטה הטובה מבין השתיים – קודם גרסה קלה לטלפון, אחר כך 3D: MICRO BOOST 10% → DERMA RECOVERY CREAM → MITOPEN → EXO-NAD → EXOSIGNAL HAIR → EXOSIGNAL SPRAY → CELL RENEW 1.5% → CELLULAR AGE DEFENSE 2.5% → MITOSCAN</t>
+          <t>שאר עמודי המוצרים ב-three.js לפי הדוגמה של EXOTECH GEL, אחד אחרי השני: EXOSIGNAL HAIR ‏← EXOSIGNAL SPRAY ‏← EXO-NAD ‏← MICRO BOOST 10% ‏← CELLULAR AGE DEFENSE 2.5% ‏← CELL RENEW 1.5% ‏← MITOPEN ‏← MITOSCAN ‏← DERMA RECOVERY CREAM. ב-3D רק מה שקיים באמת: המוצרים והאריזות האמיתיים, חלקיקים של הרכיבים האמיתיים וזוהר רך בצבע הסדרה</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>יום עבודה לכל עמוד</t>
+          <t>2–4 שעות לכל עמוד (בנייה, שתי בדיקות, תיקונים)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>צילומי HD של האריזות (גם פתוחות), מידות במ״מ, צילומי לפני/אחרי באישור הלקוחות</t>
+          <t>‏BIOSPICULE: ההדפסה שעל צידי הקופסאות, כקבצים (פריסת הקופסה או צילום חזיתי של כל צד), ומידות במ״מ; EXO-NAD: הצילומים כקבצים בגודל מלא; EXOSIGNAL SPRAY: פקשוט סטודיו; תשובות לשאלות: האם ב-HAIR יש PDRN בריכוז 2%; האם להשאיר את סליל ה-DNA ומולקולות ה-PDRN ב-V-TECH, ב-GEL וב-HAIR; האם הזהב נמצא ב-pH Normalizer או בפילינג של EXO-NAD</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>אחרי הפיילוט; בונה העמודים כבר מתאים לכל מוצר, והדוגמה היא טיוטת EXOTECH GEL</t>
+          <t>23/10: פורסמו 11 מתוך 12 העמודים, והם נמצאים ב-site/public ‏(‏הקישורים ב-HANDOFF‏)‏; בעמוד DERMA RECOVERY CREAM נעשים התיקונים האחרונים אחרי הבדיקה; כשיגיעו הקבצים של BIOSPICULE, ההדפסה על צידי ארבע הקופסאות תתווסף לעמודים, באותם קישורים</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4א</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>דף הבית – דף בית אמיתי: מסך פתיחה כמו ב-Make → כל המוצרים ב-3D מתכנסים ומתפזרים לפי סדרות → בחירת תחום למעלה → כל סדרה פעם אחת; לחיצה על סדרה פותחת את חלון הסדרה; «אודות» למטה; עמוד כל המוצרים</t>
+          <t>כתובת משותפת לאתר: אחסון התיקייה site/public ‏(‏כל העמודים ודף הפתיחה‏)‏ ב-Vercel או ב-GitHub Pages — קישורים ישירים, בלי הצ׳אט, זמינים מיד למתכנת ולצוות</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1 יום</t>
+          <t>30 דקות</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>דוגמה למסך הפתיחה מ-Make</t>
+          <t>פעולה אחת: לתת לאפליקציה של Vercel גישה למאגר GregoryDich או להפעיל את GitHub Pages</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>אחרי שלב 4</t>
+          <t>האתר בנוי ומתעדכן עם כל עמוד חדש; ממתין לגישה — שירותי האחסון החיצוניים חסומים מסביבת העבודה בענן</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>חשבון ותוכנית נאמנות: בחירת תחום → הדגשים אישיים; הרשמה (שם, email, טלפון, תפקיד); אימות סטטוס מקצועי עבור המוצרים המקצועיים; קוד קופון, 5% על הבאת חבר/ה, מדרגות עד 15%; הפרוטוקולים של המוצרים שנרכשו – בחשבון ובדוא״ל</t>
+          <t>דף הבית – דף בית אמיתי: מסך פתיחה כמו ב-Make ← כל המוצרים ב-3D מתכנסים ומתפזרים לפי סדרות ← בחירת תחום למעלה ← כל סדרה פעם אחת; לחיצה על סדרה פותחת את חלון הסדרה; «אודות» למטה; עמוד כל המוצרים</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -688,91 +688,118 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>כללי התוכנית (מדרגות, מועדים), מי מאמת/ת את הסטטוס</t>
+          <t>דוגמה למסך הפתיחה מ-Make</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>אחרי שלב 5</t>
+          <t>השלב הבא — אחרי העמוד של DERMA RECOVERY CREAM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>אירועי האקדמיה בדף הבית וטופס להזמנת מקומות</t>
+          <t>חשבון ותוכנית נאמנות: בחירת תחום ← הדגשים אישיים; הרשמה (שם, email, טלפון, תפקיד); אימות סטטוס מקצועי עבור המוצרים המקצועיים; קוד קופון, 5% על הבאת חבר/ה, מדרגות עד 15%; הפרוטוקולים של המוצרים שנרכשו – בחשבון ובדוא״ל</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3 שעות</t>
+          <t>1 יום</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>תאריכים, מחירים</t>
+          <t>כללי התוכנית (מדרגות, מועדים), מי מאמת/ת את הסטטוס</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>אחרי שלב 6</t>
+          <t>אחרי שלב 5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>עמודי שירות: נגישות, פרטיות, תנאי שימוש, פאנל ניהול</t>
+          <t>אירועי האקדמיה בדף הבית וטופס להזמנת מקומות</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2 שעות</t>
+          <t>3 שעות</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>טקסטים משפטיים</t>
+          <t>תאריכים, מחירים</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>בסוף</t>
+          <t>אחרי שלב 6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>עמודי שירות: נגישות, פרטיות, תנאי שימוש, פאנל ניהול</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2 שעות</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>טקסטים משפטיים</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>בסוף</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>התוצר הסופי – קישור אחד: מפת האתר עם כל העמודים ומסלולי המשתמש</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>2 שעות</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>בסוף, טיוטה – מוקדם יותר</t>
         </is>

--- a/mitoderm-catalog/site/MITODERM-3D-story.xlsx
+++ b/mitoderm-catalog/site/MITODERM-3D-story.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23/10: פורסמו 11 מתוך 12 העמודים, והם נמצאים ב-site/public ‏(‏הקישורים ב-HANDOFF‏)‏; בעמוד DERMA RECOVERY CREAM נעשים התיקונים האחרונים אחרי הבדיקה; כשיגיעו הקבצים של BIOSPICULE, ההדפסה על צידי ארבע הקופסאות תתווסף לעמודים, באותם קישורים</t>
+          <t>23/10: כל 12 העמודים פורסמו, והם נמצאים ב-site/public ‏(‏הקישורים ב-HANDOFF‏)‏; כשיגיעו הקבצים של BIOSPICULE, ההדפסה על צידי ארבע הקופסאות תתווסף לעמודים, באותם קישורים</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>השלב הבא — אחרי העמוד של DERMA RECOVERY CREAM</t>
+          <t>השלב הבא</t>
         </is>
       </c>
     </row>

--- a/mitoderm-catalog/site/MITODERM-3D-story.xlsx
+++ b/mitoderm-catalog/site/MITODERM-3D-story.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -526,12 +526,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>«אוקיי» על העמוד</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>19–21/10: בטלפון התנועה חלקה והחדות מלאה, כל התמונות ב-HD; העמוד פורסם ונמצא ב-site/public; ממתין ל«אוקיי»</t>
+          <t>23/10: התקבל ‏«‏אוקיי‏»‏ — הדוגמה אושרה; העמוד פורסם ונמצא ב-site/public</t>
         </is>
       </c>
     </row>
@@ -802,6 +802,33 @@
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>בסוף, טיוטה – מוקדם יותר</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>גרסת React ל-Vercel: כל העיצוב של האתר — כל העמודים, מנוע הפריימים וסצנות ה-three.js — כאפליקציית React עם פריסה ב-Vercel, כדי שהמתכנת והצוות ימשיכו מקוד מוכן</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2–3 ימים</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>גישה של Vercel למאגר GregoryDich ‏(‏אותה פעולה כמו בשלב 4א‏)‏</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>אחרי העיצוב של כל העמודים; הבסיס כבר קיים: המנוע ב-React ‏(‏proto/react: ה-hook‏ useFrameStory, ‏StoryPage ודמו‏)‏</t>
         </is>
       </c>
     </row>

--- a/mitoderm-catalog/site/MITODERM-3D-story.xlsx
+++ b/mitoderm-catalog/site/MITODERM-3D-story.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>גרסת React ל-Vercel: כל העיצוב של האתר — כל העמודים, מנוע הפריימים וסצנות ה-three.js — כאפליקציית React עם פריסה ב-Vercel, כדי שהמתכנת והצוות ימשיכו מקוד מוכן</t>
+          <t>גרסת React ל-Vercel: כל העיצוב של האתר — כל העמודים, מנוע הפריימים וסצנות ה-three.js — כאפליקציית React עם פריסה ב-Vercel, כדי שהמתכנת והצוות ימשיכו לעבוד על בסיס קוד מוכן</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
